--- a/Data Analysis/1_Data/ecological_multifunctionality.xlsx
+++ b/Data Analysis/1_Data/ecological_multifunctionality.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P79"/>
+  <dimension ref="A1:W79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -435,6 +435,41 @@
           <t>sowndiv</t>
         </is>
       </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>meanHerb</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>herbivory_standardized</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>mean_diversity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>mean_div_standardized</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>mean_flower_cover</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>mean_flower_cover_standardized</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>multifunctionality</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -449,16 +484,16 @@
         <v>0.610565427738763</v>
       </c>
       <c r="D2">
-        <v>838.5122853789989</v>
+        <v>828.3773512579434</v>
       </c>
       <c r="E2">
-        <v>2.97084605893075</v>
+        <v>2.866126361212376</v>
       </c>
       <c r="F2">
-        <v>0.7165116871340331</v>
+        <v>0.714235008308102</v>
       </c>
       <c r="G2">
-        <v>0.7231906046276005</v>
+        <v>0.7252486892235276</v>
       </c>
       <c r="H2">
         <v>152.379692735</v>
@@ -489,6 +524,21 @@
       <c r="P2">
         <v>16</v>
       </c>
+      <c r="Q2">
+        <v>9.570568743000001</v>
+      </c>
+      <c r="R2">
+        <v>0.3347127449144382</v>
+      </c>
+      <c r="S2">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="T2">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="W2">
+        <v>0.4932434099009808</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -503,16 +553,16 @@
         <v>0.4620636362039917</v>
       </c>
       <c r="D3">
-        <v>660.0670013747729</v>
+        <v>655.9329685983965</v>
       </c>
       <c r="E3">
-        <v>2.565993862540551</v>
+        <v>2.472243181288298</v>
       </c>
       <c r="F3">
-        <v>0.5640295664395354</v>
+        <v>0.5655517845399826</v>
       </c>
       <c r="G3">
-        <v>0.6246377685383359</v>
+        <v>0.6255799293903792</v>
       </c>
       <c r="H3">
         <v>275.3171712859375</v>
@@ -543,6 +593,21 @@
       <c r="P3">
         <v>8</v>
       </c>
+      <c r="Q3">
+        <v>7.007383158000001</v>
+      </c>
+      <c r="R3">
+        <v>0.2450701222115849</v>
+      </c>
+      <c r="S3">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="T3">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="W3">
+        <v>0.4788904729574147</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -557,16 +622,16 @@
         <v>0.4317317976282808</v>
       </c>
       <c r="D4">
-        <v>791.4414147973444</v>
+        <v>776.4263094419364</v>
       </c>
       <c r="E4">
-        <v>2.70031376700534</v>
+        <v>2.584558235505043</v>
       </c>
       <c r="F4">
-        <v>0.6762894632222095</v>
+        <v>0.6694423148252061</v>
       </c>
       <c r="G4">
-        <v>0.6573351520434152</v>
+        <v>0.6540002903881085</v>
       </c>
       <c r="H4">
         <v>111.1061707528571</v>
@@ -597,6 +662,21 @@
       <c r="P4">
         <v>8</v>
       </c>
+      <c r="Q4">
+        <v>4.280052659</v>
+      </c>
+      <c r="R4">
+        <v>0.1496868380910004</v>
+      </c>
+      <c r="S4">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="T4">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="W4">
+        <v>0.4703560638209432</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -611,16 +691,16 @@
         <v>0.5960137607947789</v>
       </c>
       <c r="D5">
-        <v>703.4578914819959</v>
+        <v>701.0418942996629</v>
       </c>
       <c r="E5">
-        <v>2.339456723734069</v>
+        <v>2.261728394637732</v>
       </c>
       <c r="F5">
-        <v>0.6011072341363437</v>
+        <v>0.6044451389684781</v>
       </c>
       <c r="G5">
-        <v>0.5694920197737462</v>
+        <v>0.5723109684866764</v>
       </c>
       <c r="H5">
         <v>95.08300676656251</v>
@@ -651,6 +731,21 @@
       <c r="P5">
         <v>4</v>
       </c>
+      <c r="Q5">
+        <v>4.303033941000001</v>
+      </c>
+      <c r="R5">
+        <v>0.1504905654541729</v>
+      </c>
+      <c r="S5">
+        <v>4.333333333333333</v>
+      </c>
+      <c r="T5">
+        <v>0.5416666666666666</v>
+      </c>
+      <c r="W5">
+        <v>0.4958839889788147</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -665,16 +760,16 @@
         <v>0.5739943813713894</v>
       </c>
       <c r="D6">
-        <v>480.9244606295291</v>
+        <v>480.0111760454392</v>
       </c>
       <c r="E6">
-        <v>1.933272949921366</v>
+        <v>1.84865571757305</v>
       </c>
       <c r="F6">
-        <v>0.4109516374157101</v>
+        <v>0.4138703041436016</v>
       </c>
       <c r="G6">
-        <v>0.4706150388913192</v>
+        <v>0.467786471015291</v>
       </c>
       <c r="H6">
         <v>104.9201081617857</v>
@@ -705,6 +800,21 @@
       <c r="P6">
         <v>2</v>
       </c>
+      <c r="Q6">
+        <v>12.810452095</v>
+      </c>
+      <c r="R6">
+        <v>0.4480216065997663</v>
+      </c>
+      <c r="S6">
+        <v>4</v>
+      </c>
+      <c r="T6">
+        <v>0.5</v>
+      </c>
+      <c r="W6">
+        <v>0.4739831500377737</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -719,16 +829,16 @@
         <v>0.4001670962665013</v>
       </c>
       <c r="D7">
-        <v>833.420160436881</v>
+        <v>834.7057465626099</v>
       </c>
       <c r="E7">
-        <v>3.16693315731714</v>
+        <v>3.054211065243965</v>
       </c>
       <c r="F7">
-        <v>0.7121604485213215</v>
+        <v>0.7196914122840697</v>
       </c>
       <c r="G7">
-        <v>0.7709239251796469</v>
+        <v>0.7728419101323939</v>
       </c>
       <c r="H7">
         <v>190.1838700915625</v>
@@ -759,6 +869,21 @@
       <c r="P7">
         <v>16</v>
       </c>
+      <c r="Q7">
+        <v>8.956316193999999</v>
+      </c>
+      <c r="R7">
+        <v>0.3132304106595532</v>
+      </c>
+      <c r="S7">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="T7">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="W7">
+        <v>0.4734804399188681</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -773,16 +898,16 @@
         <v>0.2741130279694455</v>
       </c>
       <c r="D8">
-        <v>705.0635147786796</v>
+        <v>692.6924213740515</v>
       </c>
       <c r="E8">
-        <v>2.363540556440479</v>
+        <v>2.262530900179275</v>
       </c>
       <c r="F8">
-        <v>0.602479244871629</v>
+        <v>0.5972461422125475</v>
       </c>
       <c r="G8">
-        <v>0.5753547272958477</v>
+        <v>0.5725140356298335</v>
       </c>
       <c r="H8">
         <v>116.0377657446875</v>
@@ -813,6 +938,21 @@
       <c r="P8">
         <v>2</v>
       </c>
+      <c r="Q8">
+        <v>1.0562739425</v>
+      </c>
+      <c r="R8">
+        <v>0.0369412059167705</v>
+      </c>
+      <c r="S8">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="T8">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="W8">
+        <v>0.3907675091892621</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -827,16 +967,16 @@
         <v>0.4657660919363158</v>
       </c>
       <c r="D9">
-        <v>608.6143162907655</v>
+        <v>604.6068150246119</v>
       </c>
       <c r="E9">
-        <v>2.1328302823301</v>
+        <v>2.077015005533984</v>
       </c>
       <c r="F9">
-        <v>0.5200630666756649</v>
+        <v>0.521297875776632</v>
       </c>
       <c r="G9">
-        <v>0.5191931156478395</v>
+        <v>0.525570829900162</v>
       </c>
       <c r="H9">
         <v>98.8683452184375</v>
@@ -867,6 +1007,21 @@
       <c r="P9">
         <v>1</v>
       </c>
+      <c r="Q9">
+        <v>3.7317630585</v>
+      </c>
+      <c r="R9">
+        <v>0.1305114346098203</v>
+      </c>
+      <c r="S9">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="T9">
+        <v>0.2083333333333333</v>
+      </c>
+      <c r="W9">
+        <v>0.4490356151852044</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -887,10 +1042,10 @@
         <v>3.16392122</v>
       </c>
       <c r="F10">
-        <v>0.578143948656714</v>
+        <v>0.5833578585929273</v>
       </c>
       <c r="G10">
-        <v>0.7701907317639413</v>
+        <v>0.8006031236671898</v>
       </c>
       <c r="H10">
         <v>214.3728571428572</v>
@@ -921,6 +1076,9 @@
       <c r="P10">
         <v>1</v>
       </c>
+      <c r="W10">
+        <v>0.5289702298300806</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -935,16 +1093,16 @@
         <v>0.4168513922003523</v>
       </c>
       <c r="D11">
-        <v>904.9628227093937</v>
+        <v>912.9959398422051</v>
       </c>
       <c r="E11">
-        <v>2.823966321413124</v>
+        <v>2.774944281334617</v>
       </c>
       <c r="F11">
-        <v>0.7732939042151387</v>
+        <v>0.7871939783097828</v>
       </c>
       <c r="G11">
-        <v>0.6874357913266561</v>
+        <v>0.7021758460973625</v>
       </c>
       <c r="H11">
         <v>119.3581357134375</v>
@@ -975,6 +1133,27 @@
       <c r="P11">
         <v>16</v>
       </c>
+      <c r="Q11">
+        <v>8.72065508</v>
+      </c>
+      <c r="R11">
+        <v>0.3049886038814318</v>
+      </c>
+      <c r="S11">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="T11">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="U11">
+        <v>13.57215189873418</v>
+      </c>
+      <c r="V11">
+        <v>0.8925979653646036</v>
+      </c>
+      <c r="W11">
+        <v>0.5223220037545615</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -989,16 +1168,16 @@
         <v>0.636337515390192</v>
       </c>
       <c r="D12">
-        <v>715.411547835948</v>
+        <v>705.031891045062</v>
       </c>
       <c r="E12">
-        <v>2.50219542563568</v>
+        <v>2.407601046433697</v>
       </c>
       <c r="F12">
-        <v>0.6113216753925256</v>
+        <v>0.607885352965483</v>
       </c>
       <c r="G12">
-        <v>0.6091073676881028</v>
+        <v>0.6092227916848111</v>
       </c>
       <c r="H12">
         <v>120.089965424375</v>
@@ -1029,6 +1208,27 @@
       <c r="P12">
         <v>8</v>
       </c>
+      <c r="Q12">
+        <v>3.2370576185</v>
+      </c>
+      <c r="R12">
+        <v>0.1132100369402601</v>
+      </c>
+      <c r="S12">
+        <v>3.666666666666667</v>
+      </c>
+      <c r="T12">
+        <v>0.4583333333333333</v>
+      </c>
+      <c r="U12">
+        <v>15.20522388059701</v>
+      </c>
+      <c r="V12">
+        <v>1</v>
+      </c>
+      <c r="W12">
+        <v>0.5548534139593566</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1043,16 +1243,16 @@
         <v>0.6203428154920557</v>
       </c>
       <c r="D13">
-        <v>640.3380100317063</v>
+        <v>633.0952679188338</v>
       </c>
       <c r="E13">
-        <v>2.132626445225951</v>
+        <v>2.054620898268954</v>
       </c>
       <c r="F13">
-        <v>0.5471710741798972</v>
+        <v>0.5458608969151152</v>
       </c>
       <c r="G13">
-        <v>0.5191434957497799</v>
+        <v>0.5199041931600346</v>
       </c>
       <c r="H13">
         <v>99.45453668906251</v>
@@ -1083,6 +1283,27 @@
       <c r="P13">
         <v>4</v>
       </c>
+      <c r="Q13">
+        <v>3.0434590775</v>
+      </c>
+      <c r="R13">
+        <v>0.1064392899962046</v>
+      </c>
+      <c r="S13">
+        <v>3.666666666666667</v>
+      </c>
+      <c r="T13">
+        <v>0.4583333333333333</v>
+      </c>
+      <c r="U13">
+        <v>7.139013452914798</v>
+      </c>
+      <c r="V13">
+        <v>0.4695105780076481</v>
+      </c>
+      <c r="W13">
+        <v>0.4617924123004704</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1097,16 +1318,16 @@
         <v>0.3178037465134191</v>
       </c>
       <c r="D14">
-        <v>824.649209229755</v>
+        <v>814.3056057503242</v>
       </c>
       <c r="E14">
-        <v>3.017254140396925</v>
+        <v>2.903930960374873</v>
       </c>
       <c r="F14">
-        <v>0.7046656399695927</v>
+        <v>0.7021022124822849</v>
       </c>
       <c r="G14">
-        <v>0.7344876856036539</v>
+        <v>0.7348148187425432</v>
       </c>
       <c r="H14">
         <v>192.928677510625</v>
@@ -1137,6 +1358,21 @@
       <c r="P14">
         <v>8</v>
       </c>
+      <c r="Q14">
+        <v>8.9541739505</v>
+      </c>
+      <c r="R14">
+        <v>0.3131554896991156</v>
+      </c>
+      <c r="S14">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="T14">
+        <v>0.2083333333333333</v>
+      </c>
+      <c r="W14">
+        <v>0.4420971429333643</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1151,16 +1387,16 @@
         <v>0.1082411417357679</v>
       </c>
       <c r="D15">
-        <v>676.0137929068999</v>
+        <v>662.3028872476706</v>
       </c>
       <c r="E15">
-        <v>2.229868411556935</v>
+        <v>2.123226916759468</v>
       </c>
       <c r="F15">
-        <v>0.5776561557027977</v>
+        <v>0.5710439903474895</v>
       </c>
       <c r="G15">
-        <v>0.5428150273711092</v>
+        <v>0.5372643576163021</v>
       </c>
       <c r="H15">
         <v>67.78081792354838</v>
@@ -1191,6 +1427,21 @@
       <c r="P15">
         <v>1</v>
       </c>
+      <c r="Q15">
+        <v>1.54509958</v>
+      </c>
+      <c r="R15">
+        <v>0.05403696848906753</v>
+      </c>
+      <c r="S15">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="T15">
+        <v>0.2083333333333333</v>
+      </c>
+      <c r="W15">
+        <v>0.3347002785531547</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1205,16 +1456,16 @@
         <v>0.2179889820497641</v>
       </c>
       <c r="D16">
-        <v>755.0739306573498</v>
+        <v>745.9491221775057</v>
       </c>
       <c r="E16">
-        <v>2.540195833020724</v>
+        <v>2.427065160490093</v>
       </c>
       <c r="F16">
-        <v>0.6452133205438827</v>
+        <v>0.6431645875720862</v>
       </c>
       <c r="G16">
-        <v>0.618357775500474</v>
+        <v>0.6141480187778436</v>
       </c>
       <c r="H16">
         <v>126.9768313448387</v>
@@ -1245,6 +1496,21 @@
       <c r="P16">
         <v>2</v>
       </c>
+      <c r="Q16">
+        <v>0.535635516</v>
+      </c>
+      <c r="R16">
+        <v>0.01873285053880956</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0.3262262325049453</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1259,16 +1525,16 @@
         <v>0.2605178292431412</v>
       </c>
       <c r="D17">
-        <v>725.290061394231</v>
+        <v>714.1590786180997</v>
       </c>
       <c r="E17">
-        <v>2.740560684207819</v>
+        <v>2.624414273372065</v>
       </c>
       <c r="F17">
-        <v>0.6197628998557099</v>
+        <v>0.6157549028537781</v>
       </c>
       <c r="G17">
-        <v>0.6671324258868582</v>
+        <v>0.6640855188734547</v>
       </c>
       <c r="H17">
         <v>184.2882473682143</v>
@@ -1299,6 +1565,21 @@
       <c r="P17">
         <v>2</v>
       </c>
+      <c r="Q17">
+        <v>0.952643172</v>
+      </c>
+      <c r="R17">
+        <v>0.03331691350708239</v>
+      </c>
+      <c r="S17">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="T17">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="W17">
+        <v>0.4167213545534574</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1313,16 +1594,16 @@
         <v>0.07919459164904936</v>
       </c>
       <c r="D18">
-        <v>43.07590075083588</v>
+        <v>63.60968471467833</v>
       </c>
       <c r="E18">
-        <v>2.099670939616793</v>
+        <v>2.011711592971416</v>
       </c>
       <c r="F18">
-        <v>0.03680850818762804</v>
+        <v>0.05484488877161147</v>
       </c>
       <c r="G18">
-        <v>0.5111211642137349</v>
+        <v>0.509046361543229</v>
       </c>
       <c r="H18">
         <v>85.71637923125</v>
@@ -1353,6 +1634,21 @@
       <c r="P18">
         <v>1</v>
       </c>
+      <c r="Q18">
+        <v>2.007709605</v>
+      </c>
+      <c r="R18">
+        <v>0.07021588903712161</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <v>0.2278784972800412</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1367,16 +1663,16 @@
         <v>0.3340402332393468</v>
       </c>
       <c r="D19">
-        <v>806.7681763377711</v>
+        <v>799.4162616745616</v>
       </c>
       <c r="E19">
-        <v>2.899925692042487</v>
+        <v>2.781380475817904</v>
       </c>
       <c r="F19">
-        <v>0.689386234684143</v>
+        <v>0.6892644752197857</v>
       </c>
       <c r="G19">
-        <v>0.7059265182384208</v>
+        <v>0.7038044698997749</v>
       </c>
       <c r="H19">
         <v>196.8196160846875</v>
@@ -1407,6 +1703,21 @@
       <c r="P19">
         <v>4</v>
       </c>
+      <c r="Q19">
+        <v>6.889186623000001</v>
+      </c>
+      <c r="R19">
+        <v>0.2409364194263496</v>
+      </c>
+      <c r="S19">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="T19">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="W19">
+        <v>0.4474402982820094</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1421,16 +1732,16 @@
         <v>0.8152682271065561</v>
       </c>
       <c r="D20">
-        <v>927.9524351192214</v>
+        <v>917.5395358708413</v>
       </c>
       <c r="E20">
-        <v>2.818653791119292</v>
+        <v>2.73056528632354</v>
       </c>
       <c r="F20">
-        <v>0.792938608605937</v>
+        <v>0.7911115109926038</v>
       </c>
       <c r="G20">
-        <v>0.6861425664610495</v>
+        <v>0.6909461221059798</v>
       </c>
       <c r="H20">
         <v>123.234310468125</v>
@@ -1461,6 +1772,27 @@
       <c r="P20">
         <v>16</v>
       </c>
+      <c r="Q20">
+        <v>4.3663490965</v>
+      </c>
+      <c r="R20">
+        <v>0.1527048946190503</v>
+      </c>
+      <c r="S20">
+        <v>7.333333333333333</v>
+      </c>
+      <c r="T20">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="U20">
+        <v>9.609856262833675</v>
+      </c>
+      <c r="V20">
+        <v>0.6320101787581411</v>
+      </c>
+      <c r="W20">
+        <v>0.5959205787772528</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1475,16 +1807,16 @@
         <v>0.1805002814128076</v>
       </c>
       <c r="D21">
-        <v>816.27801928422</v>
+        <v>813.5264000739855</v>
       </c>
       <c r="E21">
-        <v>2.578405044145887</v>
+        <v>2.500077708360005</v>
       </c>
       <c r="F21">
-        <v>0.697512428817196</v>
+        <v>0.7014303737702917</v>
       </c>
       <c r="G21">
-        <v>0.6276590122350008</v>
+        <v>0.632623217693053</v>
       </c>
       <c r="H21">
         <v>140.165478528125</v>
@@ -1515,6 +1847,21 @@
       <c r="P21">
         <v>4</v>
       </c>
+      <c r="Q21">
+        <v>1.290140285</v>
+      </c>
+      <c r="R21">
+        <v>0.04512024391788496</v>
+      </c>
+      <c r="S21">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="T21">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="W21">
+        <v>0.3811919274477344</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1529,16 +1876,16 @@
         <v>0.6202905884155975</v>
       </c>
       <c r="D22">
-        <v>793.6436460464511</v>
+        <v>790.0249197554833</v>
       </c>
       <c r="E22">
-        <v>2.429227737617762</v>
+        <v>2.375324300110834</v>
       </c>
       <c r="F22">
-        <v>0.678171277544159</v>
+        <v>0.6811671688854066</v>
       </c>
       <c r="G22">
-        <v>0.5913449036057501</v>
+        <v>0.6010554379073053</v>
       </c>
       <c r="H22">
         <v>112.8774740863333</v>
@@ -1569,6 +1916,21 @@
       <c r="P22">
         <v>4</v>
       </c>
+      <c r="Q22">
+        <v>4.387179358499999</v>
+      </c>
+      <c r="R22">
+        <v>0.1534333940801097</v>
+      </c>
+      <c r="S22">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="T22">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="W22">
+        <v>0.4737394269870207</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1583,16 +1945,16 @@
         <v>0.2693628410006011</v>
       </c>
       <c r="D23">
-        <v>881.2327876255912</v>
+        <v>873.7027658075027</v>
       </c>
       <c r="E23">
-        <v>3.318511036216795</v>
+        <v>3.219755117538084</v>
       </c>
       <c r="F23">
-        <v>0.7530165060539895</v>
+        <v>0.7533150215269718</v>
       </c>
       <c r="G23">
-        <v>0.8078224031603823</v>
+        <v>0.8147314124794834</v>
       </c>
       <c r="H23">
         <v>195.54534427125</v>
@@ -1623,6 +1985,15 @@
       <c r="P23">
         <v>2</v>
       </c>
+      <c r="Q23">
+        <v>12.19512195</v>
+      </c>
+      <c r="R23">
+        <v>0.4265015854398755</v>
+      </c>
+      <c r="W23">
+        <v>0.4998207561341838</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1637,16 +2008,16 @@
         <v>0.199693206235296</v>
       </c>
       <c r="D24">
-        <v>553.9846610817077</v>
+        <v>548.7226506533721</v>
       </c>
       <c r="E24">
-        <v>1.994075948565801</v>
+        <v>1.92094178688546</v>
       </c>
       <c r="F24">
-        <v>0.4733818348035518</v>
+        <v>0.4731140057765997</v>
       </c>
       <c r="G24">
-        <v>0.4854162626776055</v>
+        <v>0.4860778407634728</v>
       </c>
       <c r="H24">
         <v>119.3736232370968</v>
@@ -1677,6 +2048,21 @@
       <c r="P24">
         <v>1</v>
       </c>
+      <c r="Q24">
+        <v>21.34269891</v>
+      </c>
+      <c r="R24">
+        <v>0.7464209837344761</v>
+      </c>
+      <c r="S24">
+        <v>2</v>
+      </c>
+      <c r="T24">
+        <v>0.25</v>
+      </c>
+      <c r="W24">
+        <v>0.4432293818749224</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1691,16 +2077,16 @@
         <v>0.2152649369175783</v>
       </c>
       <c r="D25">
-        <v>652.1949513278475</v>
+        <v>648.7983906320918</v>
       </c>
       <c r="E25">
-        <v>2.115440590062089</v>
+        <v>2.035724943587848</v>
       </c>
       <c r="F25">
-        <v>0.5573028720801598</v>
+        <v>0.5594002820329425</v>
       </c>
       <c r="G25">
-        <v>0.5149599572087525</v>
+        <v>0.5151227339230796</v>
       </c>
       <c r="H25">
         <v>80.2080049490625</v>
@@ -1731,6 +2117,15 @@
       <c r="P25">
         <v>1</v>
       </c>
+      <c r="Q25">
+        <v>13.7963962</v>
+      </c>
+      <c r="R25">
+        <v>0.4825031579660976</v>
+      </c>
+      <c r="W25">
+        <v>0.4067309299760255</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1745,16 +2140,16 @@
         <v>0.4507372541192763</v>
       </c>
       <c r="D26">
-        <v>959.8176835622598</v>
+        <v>953.7906142421343</v>
       </c>
       <c r="E26">
-        <v>2.682356307495869</v>
+        <v>2.598086318190543</v>
       </c>
       <c r="F26">
-        <v>0.8201675750993103</v>
+        <v>0.8223675433097354</v>
       </c>
       <c r="G26">
-        <v>0.6529637824932527</v>
+        <v>0.6574234556637719</v>
       </c>
       <c r="H26">
         <v>123.441344703125</v>
@@ -1785,6 +2180,27 @@
       <c r="P26">
         <v>4</v>
       </c>
+      <c r="Q26">
+        <v>3.726573942</v>
+      </c>
+      <c r="R26">
+        <v>0.130329954963831</v>
+      </c>
+      <c r="S26">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="T26">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="U26">
+        <v>3.663265306122449</v>
+      </c>
+      <c r="V26">
+        <v>0.2409214974333292</v>
+      </c>
+      <c r="W26">
+        <v>0.420141677762516</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1799,16 +2215,16 @@
         <v>0.2110303258330461</v>
       </c>
       <c r="D27">
-        <v>869.9157391431398</v>
+        <v>857.7172489851876</v>
       </c>
       <c r="E27">
-        <v>2.428058173350535</v>
+        <v>2.350635469275505</v>
       </c>
       <c r="F27">
-        <v>0.7433460484555373</v>
+        <v>0.7395321534620042</v>
       </c>
       <c r="G27">
-        <v>0.5910601975412861</v>
+        <v>0.5948081410525323</v>
       </c>
       <c r="H27">
         <v>177.1940864143333</v>
@@ -1839,6 +2255,15 @@
       <c r="P27">
         <v>2</v>
       </c>
+      <c r="S27">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="T27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="W27">
+        <v>0.4783956940990148</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1853,16 +2278,16 @@
         <v>0.2586670395235937</v>
       </c>
       <c r="D28">
-        <v>1022.824380327325</v>
+        <v>1010.778519775807</v>
       </c>
       <c r="E28">
-        <v>2.625903684408127</v>
+        <v>2.521925385274342</v>
       </c>
       <c r="F28">
-        <v>0.8740070183454807</v>
+        <v>0.8715030696740116</v>
       </c>
       <c r="G28">
-        <v>0.6392215670388673</v>
+        <v>0.6381515849203792</v>
       </c>
       <c r="H28">
         <v>168.7766671846875</v>
@@ -1893,6 +2318,21 @@
       <c r="P28">
         <v>4</v>
       </c>
+      <c r="Q28">
+        <v>8.2729372335</v>
+      </c>
+      <c r="R28">
+        <v>0.2893305094281839</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>0</v>
+      </c>
+      <c r="W28">
+        <v>0.4276020592026076</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1907,16 +2347,16 @@
         <v>0.4825822758431113</v>
       </c>
       <c r="D29">
-        <v>1116.137185166221</v>
+        <v>1107.679249668098</v>
       </c>
       <c r="E29">
-        <v>3.763369925755268</v>
+        <v>3.62140707432442</v>
       </c>
       <c r="F29">
-        <v>0.9537431371742064</v>
+        <v>0.9550518213565412</v>
       </c>
       <c r="G29">
-        <v>0.9161140355498039</v>
+        <v>0.9163659946547561</v>
       </c>
       <c r="H29">
         <v>232.0746173662963</v>
@@ -1947,6 +2387,21 @@
       <c r="P29">
         <v>16</v>
       </c>
+      <c r="Q29">
+        <v>18.2184374865</v>
+      </c>
+      <c r="R29">
+        <v>0.6371557827865354</v>
+      </c>
+      <c r="S29">
+        <v>3</v>
+      </c>
+      <c r="T29">
+        <v>0.375</v>
+      </c>
+      <c r="W29">
+        <v>0.620783011502694</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1961,16 +2416,16 @@
         <v>0.4772544363776005</v>
       </c>
       <c r="D30">
-        <v>846.744701410228</v>
+        <v>845.6928104684499</v>
       </c>
       <c r="E30">
-        <v>2.818128962349951</v>
+        <v>2.759213488094072</v>
       </c>
       <c r="F30">
-        <v>0.7235463154902047</v>
+        <v>0.7291645656339926</v>
       </c>
       <c r="G30">
-        <v>0.6860148078268097</v>
+        <v>0.6981953038112486</v>
       </c>
       <c r="H30">
         <v>164.713646173125</v>
@@ -2001,6 +2456,27 @@
       <c r="P30">
         <v>8</v>
       </c>
+      <c r="Q30">
+        <v>3.4872954225</v>
+      </c>
+      <c r="R30">
+        <v>0.1219616361928607</v>
+      </c>
+      <c r="S30">
+        <v>3</v>
+      </c>
+      <c r="T30">
+        <v>0.375</v>
+      </c>
+      <c r="U30">
+        <v>7.326145552560646</v>
+      </c>
+      <c r="V30">
+        <v>0.4818176706960131</v>
+      </c>
+      <c r="W30">
+        <v>0.4558834320945868</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2015,16 +2491,16 @@
         <v>0.1341662185010995</v>
       </c>
       <c r="D31">
-        <v>813.2676254031625</v>
+        <v>797.0526848735647</v>
       </c>
       <c r="E31">
-        <v>2.603925704623097</v>
+        <v>2.48792606317468</v>
       </c>
       <c r="F31">
-        <v>0.694940036693353</v>
+        <v>0.6872265763159427</v>
       </c>
       <c r="G31">
-        <v>0.6338714855556991</v>
+        <v>0.6295483481193197</v>
       </c>
       <c r="H31">
         <v>93.236065658125</v>
@@ -2055,6 +2531,21 @@
       <c r="P31">
         <v>1</v>
       </c>
+      <c r="Q31">
+        <v>4.2902386335</v>
+      </c>
+      <c r="R31">
+        <v>0.150043073501463</v>
+      </c>
+      <c r="S31">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="T31">
+        <v>0.2083333333333333</v>
+      </c>
+      <c r="W31">
+        <v>0.3930519448680388</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2069,16 +2560,16 @@
         <v>0.4633724794549839</v>
       </c>
       <c r="D32">
-        <v>1014.441793336792</v>
+        <v>1004.951093615742</v>
       </c>
       <c r="E32">
-        <v>3.273989335155462</v>
+        <v>3.163390120458246</v>
       </c>
       <c r="F32">
-        <v>0.8668440683781825</v>
+        <v>0.8664786061664954</v>
       </c>
       <c r="G32">
-        <v>0.7969845222096664</v>
+        <v>0.8004687334840782</v>
       </c>
       <c r="H32">
         <v>144.923307941875</v>
@@ -2109,6 +2600,21 @@
       <c r="P32">
         <v>8</v>
       </c>
+      <c r="Q32">
+        <v>3.3371393965</v>
+      </c>
+      <c r="R32">
+        <v>0.1167102099738428</v>
+      </c>
+      <c r="S32">
+        <v>5.666666666666667</v>
+      </c>
+      <c r="T32">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="W32">
+        <v>0.5197390191561372</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2123,16 +2629,16 @@
         <v>0.6307577357793411</v>
       </c>
       <c r="D33">
-        <v>746.5567119805829</v>
+        <v>736.0154404505465</v>
       </c>
       <c r="E33">
-        <v>2.433372691311163</v>
+        <v>2.332496835604216</v>
       </c>
       <c r="F33">
-        <v>0.6379353273287668</v>
+        <v>0.6345996705810426</v>
       </c>
       <c r="G33">
-        <v>0.5923539062629808</v>
+        <v>0.5902183154005872</v>
       </c>
       <c r="H33">
         <v>67.318532718125</v>
@@ -2163,6 +2669,21 @@
       <c r="P33">
         <v>1</v>
       </c>
+      <c r="Q33">
+        <v>15.4121761</v>
+      </c>
+      <c r="R33">
+        <v>0.5390120384756428</v>
+      </c>
+      <c r="S33">
+        <v>4.333333333333333</v>
+      </c>
+      <c r="T33">
+        <v>0.5416666666666666</v>
+      </c>
+      <c r="W33">
+        <v>0.5245231236588833</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2177,16 +2698,16 @@
         <v>0.6709576642995183</v>
       </c>
       <c r="D34">
-        <v>886.8744559537673</v>
+        <v>877.0060330270752</v>
       </c>
       <c r="E34">
-        <v>2.661909060432544</v>
+        <v>2.576887445112982</v>
       </c>
       <c r="F34">
-        <v>0.7578373314164289</v>
+        <v>0.7561631306482949</v>
       </c>
       <c r="G34">
-        <v>0.6479863260133912</v>
+        <v>0.6520592626817104</v>
       </c>
       <c r="H34">
         <v>173.841501374375</v>
@@ -2217,6 +2738,27 @@
       <c r="P34">
         <v>4</v>
       </c>
+      <c r="Q34">
+        <v>5.991139977</v>
+      </c>
+      <c r="R34">
+        <v>0.2095289173211359</v>
+      </c>
+      <c r="S34">
+        <v>5.666666666666667</v>
+      </c>
+      <c r="T34">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="U34">
+        <v>10.38050314465409</v>
+      </c>
+      <c r="V34">
+        <v>0.6826932129490296</v>
+      </c>
+      <c r="W34">
+        <v>0.5640751533954733</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2231,16 +2773,16 @@
         <v>0.4630105586674286</v>
       </c>
       <c r="D35">
-        <v>996.8868634902527</v>
+        <v>985.8426334202379</v>
       </c>
       <c r="E35">
-        <v>3.031392411166201</v>
+        <v>2.923565604627012</v>
       </c>
       <c r="F35">
-        <v>0.8518433192881699</v>
+        <v>0.8500031059542238</v>
       </c>
       <c r="G35">
-        <v>0.7379293531903284</v>
+        <v>0.7397831970387502</v>
       </c>
       <c r="H35">
         <v>124.1271808390625</v>
@@ -2271,6 +2813,21 @@
       <c r="P35">
         <v>8</v>
       </c>
+      <c r="Q35">
+        <v>4.1281363245</v>
+      </c>
+      <c r="R35">
+        <v>0.144373848373955</v>
+      </c>
+      <c r="S35">
+        <v>2</v>
+      </c>
+      <c r="T35">
+        <v>0.25</v>
+      </c>
+      <c r="W35">
+        <v>0.4727393644924107</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2285,16 +2842,16 @@
         <v>0.5201561521819427</v>
       </c>
       <c r="D36">
-        <v>1109.042837095878</v>
+        <v>1091.19812954318</v>
       </c>
       <c r="E36">
-        <v>3.159648312820989</v>
+        <v>3.047672135596225</v>
       </c>
       <c r="F36">
-        <v>0.9476809918799372</v>
+        <v>0.9408416393042771</v>
       </c>
       <c r="G36">
-        <v>0.769150581495294</v>
+        <v>0.7711872900779094</v>
       </c>
       <c r="H36">
         <v>175.416226305</v>
@@ -2325,6 +2882,21 @@
       <c r="P36">
         <v>16</v>
       </c>
+      <c r="Q36">
+        <v>5.496096239</v>
+      </c>
+      <c r="R36">
+        <v>0.1922156883116398</v>
+      </c>
+      <c r="S36">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="T36">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="W36">
+        <v>0.4962518629488541</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2339,16 +2911,16 @@
         <v>0.2381006711132589</v>
       </c>
       <c r="D37">
-        <v>974.8858844858954</v>
+        <v>971.6103559477901</v>
       </c>
       <c r="E37">
-        <v>2.921347919249836</v>
+        <v>2.805361940402622</v>
       </c>
       <c r="F37">
-        <v>0.8330434056078505</v>
+        <v>0.8377318979071418</v>
       </c>
       <c r="G37">
-        <v>0.711141313330203</v>
+        <v>0.709872773792828</v>
       </c>
       <c r="H37">
         <v>161.3252078546875</v>
@@ -2379,6 +2951,21 @@
       <c r="P37">
         <v>2</v>
       </c>
+      <c r="Q37">
+        <v>2.3825254305</v>
+      </c>
+      <c r="R37">
+        <v>0.08332437163197633</v>
+      </c>
+      <c r="S37">
+        <v>2</v>
+      </c>
+      <c r="T37">
+        <v>0.25</v>
+      </c>
+      <c r="W37">
+        <v>0.4304837966716102</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2393,16 +2980,16 @@
         <v>0.2185991742350068</v>
       </c>
       <c r="D38">
-        <v>969.444026261466</v>
+        <v>962.3463114578503</v>
       </c>
       <c r="E38">
-        <v>2.705460061016351</v>
+        <v>2.61686311036833</v>
       </c>
       <c r="F38">
-        <v>0.8283933186794666</v>
+        <v>0.8297443486541463</v>
       </c>
       <c r="G38">
-        <v>0.6585879101478703</v>
+        <v>0.6621747618514734</v>
       </c>
       <c r="H38">
         <v>125.714529449375</v>
@@ -2433,6 +3020,21 @@
       <c r="P38">
         <v>2</v>
       </c>
+      <c r="Q38">
+        <v>11.5596577745</v>
+      </c>
+      <c r="R38">
+        <v>0.4042774142136917</v>
+      </c>
+      <c r="S38">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="T38">
+        <v>0.04166666666666666</v>
+      </c>
+      <c r="W38">
+        <v>0.4416730167146239</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2447,16 +3049,16 @@
         <v>0.7815000922619931</v>
       </c>
       <c r="D39">
-        <v>1158.769982529947</v>
+        <v>1151.611594239395</v>
       </c>
       <c r="E39">
-        <v>3.180854621013021</v>
+        <v>3.091423669845631</v>
       </c>
       <c r="F39">
-        <v>0.9901730119643173</v>
+        <v>0.9929307160924066</v>
       </c>
       <c r="G39">
-        <v>0.7743128155993507</v>
+        <v>0.7822582405060957</v>
       </c>
       <c r="H39">
         <v>151.1668673634375</v>
@@ -2487,6 +3089,27 @@
       <c r="P39">
         <v>8</v>
       </c>
+      <c r="Q39">
+        <v>6.628213125</v>
+      </c>
+      <c r="R39">
+        <v>0.231809359351744</v>
+      </c>
+      <c r="S39">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="T39">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="U39">
+        <v>5.419354838709677</v>
+      </c>
+      <c r="V39">
+        <v>0.3564140114783297</v>
+      </c>
+      <c r="W39">
+        <v>0.5653336670300094</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2501,16 +3124,16 @@
         <v>0.7880786007919891</v>
       </c>
       <c r="D40">
-        <v>1170.270213920661</v>
+        <v>1159.810624825328</v>
       </c>
       <c r="E40">
-        <v>3.549197143705678</v>
+        <v>3.445955299958285</v>
       </c>
       <c r="F40">
         <v>1</v>
       </c>
       <c r="G40">
-        <v>0.8639781319476615</v>
+        <v>0.8719694282287189</v>
       </c>
       <c r="H40">
         <v>181.2209807528125</v>
@@ -2541,6 +3164,21 @@
       <c r="P40">
         <v>16</v>
       </c>
+      <c r="Q40">
+        <v>25.94770115</v>
+      </c>
+      <c r="R40">
+        <v>0.9074723257683438</v>
+      </c>
+      <c r="S40">
+        <v>4.333333333333333</v>
+      </c>
+      <c r="T40">
+        <v>0.5416666666666666</v>
+      </c>
+      <c r="W40">
+        <v>0.7235380718650894</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2555,16 +3193,16 @@
         <v>0.3292744248832039</v>
       </c>
       <c r="D41">
-        <v>774.518655621975</v>
+        <v>769.90286227345</v>
       </c>
       <c r="E41">
-        <v>2.421090658334184</v>
+        <v>2.366237997369227</v>
       </c>
       <c r="F41">
-        <v>0.66182890618669</v>
+        <v>0.6638177352353538</v>
       </c>
       <c r="G41">
-        <v>0.5893641011103454</v>
+        <v>0.598756226943539</v>
       </c>
       <c r="H41">
         <v>133.0338306171875</v>
@@ -2595,6 +3233,21 @@
       <c r="P41">
         <v>1</v>
       </c>
+      <c r="Q41">
+        <v>4.1289946215</v>
+      </c>
+      <c r="R41">
+        <v>0.1444038657065228</v>
+      </c>
+      <c r="S41">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="T41">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="W41">
+        <v>0.37646345915159</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2609,16 +3262,16 @@
         <v>0.2029109549727941</v>
       </c>
       <c r="D42">
-        <v>709.0261628268142</v>
+        <v>696.5614238650267</v>
       </c>
       <c r="E42">
-        <v>2.042518790220467</v>
+        <v>1.964231324205769</v>
       </c>
       <c r="F42">
-        <v>0.6058653415192219</v>
+        <v>0.6005820337867067</v>
       </c>
       <c r="G42">
-        <v>0.4972086636472894</v>
+        <v>0.4970318868318977</v>
       </c>
       <c r="H42">
         <v>108.986184225625</v>
@@ -2649,6 +3302,21 @@
       <c r="P42">
         <v>2</v>
       </c>
+      <c r="Q42">
+        <v>19.2733721</v>
+      </c>
+      <c r="R42">
+        <v>0.6740501481760632</v>
+      </c>
+      <c r="S42">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="T42">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="W42">
+        <v>0.4099046792214609</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2663,16 +3331,16 @@
         <v>0.393646808658651</v>
       </c>
       <c r="D43">
-        <v>910.2836568886207</v>
+        <v>890.8958090422312</v>
       </c>
       <c r="E43">
-        <v>2.668170109526379</v>
+        <v>2.573170232495415</v>
       </c>
       <c r="F43">
-        <v>0.7778405756726656</v>
+        <v>0.7681390306080387</v>
       </c>
       <c r="G43">
-        <v>0.6495104480277789</v>
+        <v>0.6511186539161865</v>
       </c>
       <c r="H43">
         <v>119.8886665934375</v>
@@ -2703,6 +3371,21 @@
       <c r="P43">
         <v>4</v>
       </c>
+      <c r="Q43">
+        <v>4.188993805</v>
+      </c>
+      <c r="R43">
+        <v>0.1465022249515362</v>
+      </c>
+      <c r="S43">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="T43">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="W43">
+        <v>0.4214333394030312</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2717,16 +3400,16 @@
         <v>0.509696657779067</v>
       </c>
       <c r="D44">
-        <v>786.1018984701632</v>
+        <v>772.0165795662651</v>
       </c>
       <c r="E44">
-        <v>2.759771868657469</v>
+        <v>2.672861675954276</v>
       </c>
       <c r="F44">
-        <v>0.6717268278037684</v>
+        <v>0.6656402028413334</v>
       </c>
       <c r="G44">
-        <v>0.6718089886646532</v>
+        <v>0.676344718500707</v>
       </c>
       <c r="H44">
         <v>155.2948253259375</v>
@@ -2757,6 +3440,15 @@
       <c r="P44">
         <v>8</v>
       </c>
+      <c r="Q44">
+        <v>10.51540466</v>
+      </c>
+      <c r="R44">
+        <v>0.3677566142773877</v>
+      </c>
+      <c r="W44">
+        <v>0.483212964426785</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2771,16 +3463,16 @@
         <v>0.7850121586853936</v>
       </c>
       <c r="D45">
-        <v>989.2747870089976</v>
+        <v>972.281952784939</v>
       </c>
       <c r="E45">
-        <v>3.053720102565585</v>
+        <v>2.964106549473492</v>
       </c>
       <c r="F45">
-        <v>0.8453387732519574</v>
+        <v>0.8383109552314787</v>
       </c>
       <c r="G45">
-        <v>0.7433645646832021</v>
+        <v>0.7500417353599131</v>
       </c>
       <c r="H45">
         <v>112.6675989174194</v>
@@ -2811,6 +3503,21 @@
       <c r="P45">
         <v>8</v>
       </c>
+      <c r="Q45">
+        <v>13.8868205085</v>
+      </c>
+      <c r="R45">
+        <v>0.4856655790632932</v>
+      </c>
+      <c r="S45">
+        <v>3.666666666666667</v>
+      </c>
+      <c r="T45">
+        <v>0.4583333333333333</v>
+      </c>
+      <c r="W45">
+        <v>0.5624289102487416</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2825,16 +3532,16 @@
         <v>0.3657024017760291</v>
       </c>
       <c r="D46">
-        <v>885.9869034265213</v>
+        <v>884.1512260972701</v>
       </c>
       <c r="E46">
-        <v>2.884637727701012</v>
+        <v>2.829127670606511</v>
       </c>
       <c r="F46">
-        <v>0.7570789146707163</v>
+        <v>0.762323785601142</v>
       </c>
       <c r="G46">
-        <v>0.7022049816941761</v>
+        <v>0.7158864879514457</v>
       </c>
       <c r="H46">
         <v>202.9518392865625</v>
@@ -2865,6 +3572,15 @@
       <c r="P46">
         <v>1</v>
       </c>
+      <c r="Q46">
+        <v>4.674182018</v>
+      </c>
+      <c r="R46">
+        <v>0.1634707754038947</v>
+      </c>
+      <c r="W46">
+        <v>0.4872242467485989</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2879,16 +3595,16 @@
         <v>0.8060187768140616</v>
       </c>
       <c r="D47">
-        <v>973.8520814727282</v>
+        <v>963.5470426919795</v>
       </c>
       <c r="E47">
-        <v>2.772787198332522</v>
+        <v>2.690502686665903</v>
       </c>
       <c r="F47">
-        <v>0.8321600173092594</v>
+        <v>0.8307796308014451</v>
       </c>
       <c r="G47">
-        <v>0.6749772996273952</v>
+        <v>0.6808086249314667</v>
       </c>
       <c r="H47">
         <v>107.9302736590323</v>
@@ -2919,6 +3635,21 @@
       <c r="P47">
         <v>8</v>
       </c>
+      <c r="Q47">
+        <v>2.032820474</v>
+      </c>
+      <c r="R47">
+        <v>0.07109409472331182</v>
+      </c>
+      <c r="S47">
+        <v>6</v>
+      </c>
+      <c r="T47">
+        <v>0.75</v>
+      </c>
+      <c r="W47">
+        <v>0.5342697677556737</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2933,16 +3664,16 @@
         <v>0.3376223447015321</v>
       </c>
       <c r="D48">
-        <v>808.2592789153852</v>
+        <v>800.328067796833</v>
       </c>
       <c r="E48">
-        <v>2.378107430316842</v>
+        <v>2.308053410886439</v>
       </c>
       <c r="F48">
-        <v>0.6906603870635482</v>
+        <v>0.6900506433258149</v>
       </c>
       <c r="G48">
-        <v>0.5789007293832032</v>
+        <v>0.5840331164586947</v>
       </c>
       <c r="H48">
         <v>115.11182788125</v>
@@ -2973,6 +3704,15 @@
       <c r="P48">
         <v>2</v>
       </c>
+      <c r="Q48">
+        <v>4.697584461000001</v>
+      </c>
+      <c r="R48">
+        <v>0.1642892320854752</v>
+      </c>
+      <c r="W48">
+        <v>0.4179917693622398</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2987,16 +3727,16 @@
         <v>0.6074170814250149</v>
       </c>
       <c r="D49">
-        <v>939.6187433940207</v>
+        <v>922.4330881276862</v>
       </c>
       <c r="E49">
-        <v>3.168864542971522</v>
+        <v>3.070241885028659</v>
       </c>
       <c r="F49">
-        <v>0.8029075099212278</v>
+        <v>0.795330779338746</v>
       </c>
       <c r="G49">
-        <v>0.7713940807957423</v>
+        <v>0.7768983715617881</v>
       </c>
       <c r="H49">
         <v>254.4268867953125</v>
@@ -3027,6 +3767,15 @@
       <c r="P49">
         <v>16</v>
       </c>
+      <c r="Q49">
+        <v>12.379006285</v>
+      </c>
+      <c r="R49">
+        <v>0.4329325961945533</v>
+      </c>
+      <c r="W49">
+        <v>0.606320754357994</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3041,16 +3790,16 @@
         <v>0.4424933210974757</v>
       </c>
       <c r="D50">
-        <v>883.5898757239555</v>
+        <v>874.7313058615135</v>
       </c>
       <c r="E50">
-        <v>2.773832746173914</v>
+        <v>2.721435365830919</v>
       </c>
       <c r="F50">
-        <v>0.7550306460964568</v>
+        <v>0.7542018387641959</v>
       </c>
       <c r="G50">
-        <v>0.6752318164756548</v>
+        <v>0.6886358740444857</v>
       </c>
       <c r="H50">
         <v>231.912202086875</v>
@@ -3081,6 +3830,21 @@
       <c r="P50">
         <v>4</v>
       </c>
+      <c r="Q50">
+        <v>3.746202177</v>
+      </c>
+      <c r="R50">
+        <v>0.1310164157783443</v>
+      </c>
+      <c r="S50">
+        <v>0</v>
+      </c>
+      <c r="T50">
+        <v>0</v>
+      </c>
+      <c r="W50">
+        <v>0.4492060625342239</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3095,16 +3859,16 @@
         <v>0.1924011613385643</v>
       </c>
       <c r="D51">
-        <v>788.1642834068953</v>
+        <v>771.2549657006074</v>
       </c>
       <c r="E51">
-        <v>2.209945455981751</v>
+        <v>2.128997105629884</v>
       </c>
       <c r="F51">
-        <v>0.6734891429615836</v>
+        <v>0.6649835319595915</v>
       </c>
       <c r="G51">
-        <v>0.5379651987355684</v>
+        <v>0.5387244544115707</v>
       </c>
       <c r="H51">
         <v>115.4052684690625</v>
@@ -3135,6 +3899,21 @@
       <c r="P51">
         <v>1</v>
       </c>
+      <c r="Q51">
+        <v>12.95935475</v>
+      </c>
+      <c r="R51">
+        <v>0.453229198511851</v>
+      </c>
+      <c r="S51">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="T51">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="W51">
+        <v>0.4825433598131469</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3149,16 +3928,16 @@
         <v>0.5046578548722646</v>
       </c>
       <c r="D52">
-        <v>891.4107010741079</v>
+        <v>870.8383767477686</v>
       </c>
       <c r="E52">
-        <v>3.06189055738368</v>
+        <v>2.965250120862364</v>
       </c>
       <c r="F52">
-        <v>0.7617135687728794</v>
+        <v>0.7508453174231958</v>
       </c>
       <c r="G52">
-        <v>0.7453534917574333</v>
+        <v>0.7503311062899729</v>
       </c>
       <c r="H52">
         <v>268.7253422890625</v>
@@ -3189,6 +3968,15 @@
       <c r="P52">
         <v>4</v>
       </c>
+      <c r="Q52">
+        <v>6.039216124</v>
+      </c>
+      <c r="R52">
+        <v>0.2112102906605259</v>
+      </c>
+      <c r="W52">
+        <v>0.5510318786865512</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3203,16 +3991,16 @@
         <v>0.7690660755356117</v>
       </c>
       <c r="D53">
-        <v>947.5171811851311</v>
+        <v>941.7955308036528</v>
       </c>
       <c r="E53">
-        <v>2.824249943250409</v>
+        <v>2.753839423059208</v>
       </c>
       <c r="F53">
-        <v>0.8096567527005077</v>
+        <v>0.8120252657156772</v>
       </c>
       <c r="G53">
-        <v>0.6875048331564659</v>
+        <v>0.6968354427544988</v>
       </c>
       <c r="H53">
         <v>102.683986036875</v>
@@ -3243,6 +4031,27 @@
       <c r="P53">
         <v>16</v>
       </c>
+      <c r="Q53">
+        <v>1.8869790155</v>
+      </c>
+      <c r="R53">
+        <v>0.06599356243440643</v>
+      </c>
+      <c r="S53">
+        <v>3.666666666666667</v>
+      </c>
+      <c r="T53">
+        <v>0.4583333333333333</v>
+      </c>
+      <c r="U53">
+        <v>3.789203084832905</v>
+      </c>
+      <c r="V53">
+        <v>0.2492040311006671</v>
+      </c>
+      <c r="W53">
+        <v>0.4601312466705123</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3257,16 +4066,16 @@
         <v>0.09192467864779168</v>
       </c>
       <c r="D54">
-        <v>817.4078139342062</v>
+        <v>803.6205597323058</v>
       </c>
       <c r="E54">
-        <v>2.088873974044982</v>
+        <v>2.029796058820261</v>
       </c>
       <c r="F54">
-        <v>0.698477842305933</v>
+        <v>0.6928894618923964</v>
       </c>
       <c r="G54">
-        <v>0.5084928677940841</v>
+        <v>0.513622480492372</v>
       </c>
       <c r="H54">
         <v>89.29260579419355</v>
@@ -3297,6 +4106,15 @@
       <c r="P54">
         <v>1</v>
       </c>
+      <c r="S54">
+        <v>1</v>
+      </c>
+      <c r="T54">
+        <v>0.125</v>
+      </c>
+      <c r="W54">
+        <v>0.3800142014784028</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3311,16 +4129,16 @@
         <v>0.2024155572005722</v>
       </c>
       <c r="D55">
-        <v>849.6132644649703</v>
+        <v>838.7181694002497</v>
       </c>
       <c r="E55">
-        <v>2.43235040648148</v>
+        <v>2.367598667232508</v>
       </c>
       <c r="F55">
-        <v>0.7259975126757947</v>
+        <v>0.7231509622759007</v>
       </c>
       <c r="G55">
-        <v>0.5921050523104652</v>
+        <v>0.5991005327802131</v>
       </c>
       <c r="H55">
         <v>118.3972807875</v>
@@ -3351,6 +4169,21 @@
       <c r="P55">
         <v>2</v>
       </c>
+      <c r="Q55">
+        <v>1.4268861685</v>
+      </c>
+      <c r="R55">
+        <v>0.04990267547980357</v>
+      </c>
+      <c r="S55">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="T55">
+        <v>0.04166666666666666</v>
+      </c>
+      <c r="W55">
+        <v>0.3538823364394203</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3365,16 +4198,16 @@
         <v>0.6800972507888947</v>
       </c>
       <c r="D56">
-        <v>925.6561715906782</v>
+        <v>917.4690102689739</v>
       </c>
       <c r="E56">
-        <v>2.726848370543213</v>
+        <v>2.654039794401924</v>
       </c>
       <c r="F56">
-        <v>0.7909764433715932</v>
+        <v>0.7910507031328051</v>
       </c>
       <c r="G56">
-        <v>0.6637944486866801</v>
+        <v>0.671582002833562</v>
       </c>
       <c r="H56">
         <v>151.9766271153571</v>
@@ -3405,6 +4238,27 @@
       <c r="P56">
         <v>8</v>
       </c>
+      <c r="Q56">
+        <v>4.5886640015</v>
+      </c>
+      <c r="R56">
+        <v>0.1604799426946799</v>
+      </c>
+      <c r="S56">
+        <v>8</v>
+      </c>
+      <c r="T56">
+        <v>1</v>
+      </c>
+      <c r="U56">
+        <v>9.417177914110429</v>
+      </c>
+      <c r="V56">
+        <v>0.6193383266212503</v>
+      </c>
+      <c r="W56">
+        <v>0.6003992957894583</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3419,16 +4273,16 @@
         <v>0.3359062704610818</v>
       </c>
       <c r="D57">
-        <v>875.9664235181975</v>
+        <v>863.5299298005199</v>
       </c>
       <c r="E57">
-        <v>2.771670046757356</v>
+        <v>2.677901633048614</v>
       </c>
       <c r="F57">
-        <v>0.7485163794637807</v>
+        <v>0.7445439033898924</v>
       </c>
       <c r="G57">
-        <v>0.6747053523413092</v>
+        <v>0.6776200364091838</v>
       </c>
       <c r="H57">
         <v>143.5188982909375</v>
@@ -3459,6 +4313,21 @@
       <c r="P57">
         <v>2</v>
       </c>
+      <c r="Q57">
+        <v>7.5261303</v>
+      </c>
+      <c r="R57">
+        <v>0.2632123334508423</v>
+      </c>
+      <c r="S57">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="T57">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="W57">
+        <v>0.5416239726013282</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3473,16 +4342,16 @@
         <v>0.7855024272212476</v>
       </c>
       <c r="D58">
-        <v>1131.347600839915</v>
+        <v>1111.033140487697</v>
       </c>
       <c r="E58">
-        <v>3.395709812390539</v>
+        <v>3.307029389479954</v>
       </c>
       <c r="F58">
-        <v>0.9667404906851838</v>
+        <v>0.9579435786381274</v>
       </c>
       <c r="G58">
-        <v>0.8266148375410768</v>
+        <v>0.8368154183298063</v>
       </c>
       <c r="H58">
         <v>183.8040500878125</v>
@@ -3513,6 +4382,27 @@
       <c r="P58">
         <v>16</v>
       </c>
+      <c r="Q58">
+        <v>12.729408163</v>
+      </c>
+      <c r="R58">
+        <v>0.4451872466294438</v>
+      </c>
+      <c r="S58">
+        <v>5.333333333333333</v>
+      </c>
+      <c r="T58">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="U58">
+        <v>10.79144385026738</v>
+      </c>
+      <c r="V58">
+        <v>0.7097194973918178</v>
+      </c>
+      <c r="W58">
+        <v>0.6538995365993346</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3527,16 +4417,16 @@
         <v>0.4983457979034836</v>
       </c>
       <c r="D59">
-        <v>1058.37561877344</v>
+        <v>1050.074936152694</v>
       </c>
       <c r="E59">
-        <v>3.267601274666365</v>
+        <v>3.156049903851567</v>
       </c>
       <c r="F59">
-        <v>0.9043856762171621</v>
+        <v>0.9053848220357861</v>
       </c>
       <c r="G59">
-        <v>0.7954294819161378</v>
+        <v>0.7986113546383113</v>
       </c>
       <c r="H59">
         <v>117.7899405009375</v>
@@ -3567,6 +4457,21 @@
       <c r="P59">
         <v>4</v>
       </c>
+      <c r="Q59">
+        <v>23.116575517</v>
+      </c>
+      <c r="R59">
+        <v>0.8084590009320168</v>
+      </c>
+      <c r="S59">
+        <v>4.333333333333333</v>
+      </c>
+      <c r="T59">
+        <v>0.5416666666666666</v>
+      </c>
+      <c r="W59">
+        <v>0.601205727795501</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3581,16 +4486,16 @@
         <v>0.79717972385056</v>
       </c>
       <c r="D60">
-        <v>971.3052201220196</v>
+        <v>961.8098517393934</v>
       </c>
       <c r="E60">
-        <v>2.890628663185856</v>
+        <v>2.79305649673674</v>
       </c>
       <c r="F60">
-        <v>0.8299837153574426</v>
+        <v>0.8292818078677676</v>
       </c>
       <c r="G60">
-        <v>0.703663350175621</v>
+        <v>0.7067589868329188</v>
       </c>
       <c r="H60">
         <v>134.8362436684375</v>
@@ -3621,6 +4526,21 @@
       <c r="P60">
         <v>16</v>
       </c>
+      <c r="Q60">
+        <v>28.59338011</v>
+      </c>
+      <c r="R60">
+        <v>1</v>
+      </c>
+      <c r="S60">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="T60">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="W60">
+        <v>0.640209489531952</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3635,16 +4555,16 @@
         <v>0.440061038146458</v>
       </c>
       <c r="D61">
-        <v>940.8397822591651</v>
+        <v>940.1657715297354</v>
       </c>
       <c r="E61">
-        <v>3.132964085275568</v>
+        <v>3.062506222892643</v>
       </c>
       <c r="F61">
-        <v>0.8039508919116602</v>
+        <v>0.8106200714201319</v>
       </c>
       <c r="G61">
-        <v>0.7626548620033392</v>
+        <v>0.7749409286170713</v>
       </c>
       <c r="H61">
         <v>200.0871802265625</v>
@@ -3675,6 +4595,21 @@
       <c r="P61">
         <v>16</v>
       </c>
+      <c r="Q61">
+        <v>3.8597674015</v>
+      </c>
+      <c r="R61">
+        <v>0.1349881471393485</v>
+      </c>
+      <c r="S61">
+        <v>5.333333333333333</v>
+      </c>
+      <c r="T61">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="W61">
+        <v>0.5264661644781429</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3695,10 +4630,10 @@
         <v>2.543287669</v>
       </c>
       <c r="F62">
-        <v>0.5693268113762056</v>
+        <v>0.5744612051992042</v>
       </c>
       <c r="G62">
-        <v>0.6191104185815722</v>
+        <v>0.6435571275651567</v>
       </c>
       <c r="J62">
         <v>1.292398706065661</v>
@@ -3723,6 +4658,15 @@
       <c r="P62">
         <v>1</v>
       </c>
+      <c r="S62">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="T62">
+        <v>0.04166666666666666</v>
+      </c>
+      <c r="W62">
+        <v>0.3366837056205102</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3737,13 +4681,13 @@
         <v>0.4088897541213501</v>
       </c>
       <c r="D63">
-        <v>946.743245287853</v>
+        <v>931.0850222829723</v>
       </c>
       <c r="E63">
-        <v>4.107971038230725</v>
+        <v>3.951922152773463</v>
       </c>
       <c r="F63">
-        <v>0.8089954217633687</v>
+        <v>0.8027905611083682</v>
       </c>
       <c r="G63">
         <v>1</v>
@@ -3777,6 +4721,21 @@
       <c r="P63">
         <v>4</v>
       </c>
+      <c r="Q63">
+        <v>23.557545837</v>
+      </c>
+      <c r="R63">
+        <v>0.8238811132637373</v>
+      </c>
+      <c r="S63">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="T63">
+        <v>0.04166666666666666</v>
+      </c>
+      <c r="W63">
+        <v>0.5615865930568087</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3791,16 +4750,16 @@
         <v>0.2145907753266065</v>
       </c>
       <c r="D64">
-        <v>941.3028236748822</v>
+        <v>935.1347230762776</v>
       </c>
       <c r="E64">
-        <v>2.547215535780022</v>
+        <v>2.488230333792243</v>
       </c>
       <c r="F64">
-        <v>0.8043465624245121</v>
+        <v>0.8062822525161057</v>
       </c>
       <c r="G64">
-        <v>0.6200665759506158</v>
+        <v>0.6296253411889707</v>
       </c>
       <c r="H64">
         <v>190.33094006125</v>
@@ -3831,6 +4790,27 @@
       <c r="P64">
         <v>8</v>
       </c>
+      <c r="Q64">
+        <v>6.554619498</v>
+      </c>
+      <c r="R64">
+        <v>0.2292355598667974</v>
+      </c>
+      <c r="S64">
+        <v>2</v>
+      </c>
+      <c r="T64">
+        <v>0.25</v>
+      </c>
+      <c r="U64">
+        <v>3.131147540983607</v>
+      </c>
+      <c r="V64">
+        <v>0.2059257769284924</v>
+      </c>
+      <c r="W64">
+        <v>0.4119623682497291</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3845,16 +4825,16 @@
         <v>0.2582232262127954</v>
       </c>
       <c r="D65">
-        <v>914.7236170301899</v>
+        <v>899.7614602872376</v>
       </c>
       <c r="E65">
-        <v>2.214601743634963</v>
+        <v>2.162868994009377</v>
       </c>
       <c r="F65">
-        <v>0.7816345371772435</v>
+        <v>0.775783081330838</v>
       </c>
       <c r="G65">
-        <v>0.5390986749966906</v>
+        <v>0.5472954452029056</v>
       </c>
       <c r="H65">
         <v>68.9591740921875</v>
@@ -3885,6 +4865,27 @@
       <c r="P65">
         <v>4</v>
       </c>
+      <c r="Q65">
+        <v>3.2345367155</v>
+      </c>
+      <c r="R65">
+        <v>0.1131218730718997</v>
+      </c>
+      <c r="S65">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="T65">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="U65">
+        <v>6.712264150943396</v>
+      </c>
+      <c r="V65">
+        <v>0.4414446116448663</v>
+      </c>
+      <c r="W65">
+        <v>0.4392484941683347</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3899,16 +4900,16 @@
         <v>0.2334962175503798</v>
       </c>
       <c r="D66">
-        <v>836.3124456098574</v>
+        <v>825.6953914759764</v>
       </c>
       <c r="E66">
-        <v>2.905045313943119</v>
+        <v>2.814837724279613</v>
       </c>
       <c r="F66">
-        <v>0.7146319163400969</v>
+        <v>0.7119225965017602</v>
       </c>
       <c r="G66">
-        <v>0.7071727835730561</v>
+        <v>0.7122705396168183</v>
       </c>
       <c r="H66">
         <v>154.55160473125</v>
@@ -3939,6 +4940,21 @@
       <c r="P66">
         <v>8</v>
       </c>
+      <c r="Q66">
+        <v>14.8992245665</v>
+      </c>
+      <c r="R66">
+        <v>0.5210725178059405</v>
+      </c>
+      <c r="S66">
+        <v>0</v>
+      </c>
+      <c r="T66">
+        <v>0</v>
+      </c>
+      <c r="W66">
+        <v>0.4147416520014882</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3953,16 +4969,16 @@
         <v>0.1586442430473347</v>
       </c>
       <c r="D67">
-        <v>865.5534137679292</v>
+        <v>844.2071193141553</v>
       </c>
       <c r="E67">
-        <v>2.725973175927769</v>
+        <v>2.641342805042894</v>
       </c>
       <c r="F67">
-        <v>0.7396184261309496</v>
+        <v>0.7278835882722631</v>
       </c>
       <c r="G67">
-        <v>0.6635814007836403</v>
+        <v>0.6683691385947966</v>
       </c>
       <c r="H67">
         <v>73.60762752531249</v>
@@ -3993,6 +5009,21 @@
       <c r="P67">
         <v>1</v>
       </c>
+      <c r="Q67">
+        <v>11.85427911</v>
+      </c>
+      <c r="R67">
+        <v>0.4145812444837254</v>
+      </c>
+      <c r="S67">
+        <v>4.333333333333333</v>
+      </c>
+      <c r="T67">
+        <v>0.5416666666666666</v>
+      </c>
+      <c r="W67">
+        <v>0.4813979856424639</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4007,16 +5038,16 @@
         <v>0.4352799673327231</v>
       </c>
       <c r="D68">
-        <v>966.4187520481003</v>
+        <v>954.6694808040943</v>
       </c>
       <c r="E68">
-        <v>3.404996584776273</v>
+        <v>3.324423197436492</v>
       </c>
       <c r="F68">
-        <v>0.8258082112595057</v>
+        <v>0.8231253106065234</v>
       </c>
       <c r="G68">
-        <v>0.8288755088796297</v>
+        <v>0.8412167722239693</v>
       </c>
       <c r="H68">
         <v>330.164247171875</v>
@@ -4047,6 +5078,21 @@
       <c r="P68">
         <v>8</v>
       </c>
+      <c r="Q68">
+        <v>8.946038475</v>
+      </c>
+      <c r="R68">
+        <v>0.3128709666567644</v>
+      </c>
+      <c r="S68">
+        <v>3</v>
+      </c>
+      <c r="T68">
+        <v>0.375</v>
+      </c>
+      <c r="W68">
+        <v>0.5569571556953912</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4061,16 +5107,16 @@
         <v>0.5757805590701729</v>
       </c>
       <c r="D69">
-        <v>829.8724452236273</v>
+        <v>817.2379250340023</v>
       </c>
       <c r="E69">
-        <v>2.459239294630201</v>
+        <v>2.393989412593131</v>
       </c>
       <c r="F69">
-        <v>0.7091289134356185</v>
+        <v>0.7046304866857737</v>
       </c>
       <c r="G69">
-        <v>0.5986505921641986</v>
+        <v>0.6057784845060843</v>
       </c>
       <c r="H69">
         <v>76.5980043496875</v>
@@ -4101,6 +5147,27 @@
       <c r="P69">
         <v>4</v>
       </c>
+      <c r="Q69">
+        <v>3.395191248</v>
+      </c>
+      <c r="R69">
+        <v>0.1187404649236484</v>
+      </c>
+      <c r="S69">
+        <v>3</v>
+      </c>
+      <c r="T69">
+        <v>0.375</v>
+      </c>
+      <c r="U69">
+        <v>9.261224489795918</v>
+      </c>
+      <c r="V69">
+        <v>0.6090817578565169</v>
+      </c>
+      <c r="W69">
+        <v>0.46604203790316</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4115,16 +5182,16 @@
         <v>0.07697441512363405</v>
       </c>
       <c r="D70">
-        <v>874.6690429542745</v>
+        <v>857.5264607957037</v>
       </c>
       <c r="E70">
-        <v>2.620847362135744</v>
+        <v>2.553084119794869</v>
       </c>
       <c r="F70">
-        <v>0.7474077632241376</v>
+        <v>0.7393676540295967</v>
       </c>
       <c r="G70">
-        <v>0.6379907106805028</v>
+        <v>0.6460360354019402</v>
       </c>
       <c r="H70">
         <v>162.0354838759375</v>
@@ -4155,6 +5222,15 @@
       <c r="P70">
         <v>1</v>
       </c>
+      <c r="Q70">
+        <v>11.22132051</v>
+      </c>
+      <c r="R70">
+        <v>0.3924447010752518</v>
+      </c>
+      <c r="W70">
+        <v>0.4297091807310861</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4169,16 +5245,16 @@
         <v>0.1716522902583685</v>
       </c>
       <c r="D71">
-        <v>758.1492555458289</v>
+        <v>740.1297030877272</v>
       </c>
       <c r="E71">
-        <v>2.129566047493106</v>
+        <v>2.080240700410156</v>
       </c>
       <c r="F71">
-        <v>0.6478411964411731</v>
+        <v>0.63814702783844</v>
       </c>
       <c r="G71">
-        <v>0.518398505655068</v>
+        <v>0.5263870643176107</v>
       </c>
       <c r="H71">
         <v>88.9824012521875</v>
@@ -4209,6 +5285,21 @@
       <c r="P71">
         <v>1</v>
       </c>
+      <c r="Q71">
+        <v>1.424821897</v>
+      </c>
+      <c r="R71">
+        <v>0.04983048144425902</v>
+      </c>
+      <c r="S71">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="T71">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="W71">
+        <v>0.3378503059471598</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4223,16 +5314,16 @@
         <v>0.1356227346870708</v>
       </c>
       <c r="D72">
-        <v>919.7545057479</v>
+        <v>899.4694821174611</v>
       </c>
       <c r="E72">
-        <v>2.868243500880981</v>
+        <v>2.765656411943148</v>
       </c>
       <c r="F72">
-        <v>0.7859334492215445</v>
+        <v>0.7755313349133395</v>
       </c>
       <c r="G72">
-        <v>0.6982141485876476</v>
+        <v>0.6998256304219475</v>
       </c>
       <c r="H72">
         <v>102.4966450978125</v>
@@ -4263,6 +5354,21 @@
       <c r="P72">
         <v>2</v>
       </c>
+      <c r="Q72">
+        <v>2.512306821</v>
+      </c>
+      <c r="R72">
+        <v>0.08786323307475523</v>
+      </c>
+      <c r="S72">
+        <v>1</v>
+      </c>
+      <c r="T72">
+        <v>0.125</v>
+      </c>
+      <c r="W72">
+        <v>0.3515146467284684</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4277,16 +5383,16 @@
         <v>0.1134270450659731</v>
       </c>
       <c r="D73">
-        <v>908.6323312218375</v>
+        <v>892.7724353911411</v>
       </c>
       <c r="E73">
-        <v>2.735317546069518</v>
+        <v>2.631552202183076</v>
       </c>
       <c r="F73">
-        <v>0.7764295121019276</v>
+        <v>0.7697570760964498</v>
       </c>
       <c r="G73">
-        <v>0.665856093096411</v>
+        <v>0.6658917105278124</v>
       </c>
       <c r="H73">
         <v>60.3461720246875</v>
@@ -4317,6 +5423,21 @@
       <c r="P73">
         <v>2</v>
       </c>
+      <c r="Q73">
+        <v>1.71014179</v>
+      </c>
+      <c r="R73">
+        <v>0.0598090111564638</v>
+      </c>
+      <c r="S73">
+        <v>3</v>
+      </c>
+      <c r="T73">
+        <v>0.375</v>
+      </c>
+      <c r="W73">
+        <v>0.3657983878556848</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4331,16 +5452,16 @@
         <v>0.3652372069104391</v>
       </c>
       <c r="D74">
-        <v>1013.287169674876</v>
+        <v>984.282715387383</v>
       </c>
       <c r="E74">
-        <v>2.943490963080781</v>
+        <v>2.832724909576293</v>
       </c>
       <c r="F74">
-        <v>0.8658574384117171</v>
+        <v>0.8486581294559357</v>
       </c>
       <c r="G74">
-        <v>0.7165315762178601</v>
+        <v>0.7167967384145673</v>
       </c>
       <c r="H74">
         <v>135.46246887375</v>
@@ -4371,6 +5492,21 @@
       <c r="P74">
         <v>8</v>
       </c>
+      <c r="Q74">
+        <v>1.0787394635</v>
+      </c>
+      <c r="R74">
+        <v>0.03772689550343616</v>
+      </c>
+      <c r="S74">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="T74">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="W74">
+        <v>0.4221310198387213</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4385,16 +5521,16 @@
         <v>0.1806081823190923</v>
       </c>
       <c r="D75">
-        <v>723.1858394200564</v>
+        <v>706.9460658690535</v>
       </c>
       <c r="E75">
-        <v>2.285149276274667</v>
+        <v>2.220446207460934</v>
       </c>
       <c r="F75">
-        <v>0.6179648348027466</v>
+        <v>0.6095357731142722</v>
       </c>
       <c r="G75">
-        <v>0.5562720026524006</v>
+        <v>0.5618648651524227</v>
       </c>
       <c r="H75">
         <v>104.8937559309375</v>
@@ -4425,6 +5561,21 @@
       <c r="P75">
         <v>2</v>
       </c>
+      <c r="Q75">
+        <v>1.2469799705</v>
+      </c>
+      <c r="R75">
+        <v>0.04361079262762265</v>
+      </c>
+      <c r="S75">
+        <v>5</v>
+      </c>
+      <c r="T75">
+        <v>0.625</v>
+      </c>
+      <c r="W75">
+        <v>0.3847584218386811</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4439,16 +5590,16 @@
         <v>0.972937272628926</v>
       </c>
       <c r="D76">
-        <v>992.2671905734962</v>
+        <v>976.9563461971909</v>
       </c>
       <c r="E76">
-        <v>3.218582084816833</v>
+        <v>3.142902868993676</v>
       </c>
       <c r="F76">
-        <v>0.8478957925872385</v>
+        <v>0.8423412626904708</v>
       </c>
       <c r="G76">
-        <v>0.7834967809809715</v>
+        <v>0.795284610246683</v>
       </c>
       <c r="H76">
         <v>151.39790363125</v>
@@ -4479,6 +5630,21 @@
       <c r="P76">
         <v>16</v>
       </c>
+      <c r="Q76">
+        <v>4.6450910745</v>
+      </c>
+      <c r="R76">
+        <v>0.1624533740547682</v>
+      </c>
+      <c r="S76">
+        <v>5</v>
+      </c>
+      <c r="T76">
+        <v>0.625</v>
+      </c>
+      <c r="W76">
+        <v>0.5921918868649685</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4493,16 +5659,16 @@
         <v>0.8202332694912822</v>
       </c>
       <c r="D77">
-        <v>1002.040387198462</v>
+        <v>990.9597563929921</v>
       </c>
       <c r="E77">
-        <v>3.038933143547049</v>
+        <v>2.953631968905547</v>
       </c>
       <c r="F77">
-        <v>0.8562470233617309</v>
+        <v>0.8544151391458708</v>
       </c>
       <c r="G77">
-        <v>0.7397649874512984</v>
+        <v>0.7473912326012507</v>
       </c>
       <c r="H77">
         <v>152.0578600525</v>
@@ -4533,6 +5699,27 @@
       <c r="P77">
         <v>16</v>
       </c>
+      <c r="Q77">
+        <v>5.3957587795</v>
+      </c>
+      <c r="R77">
+        <v>0.1887065732957166</v>
+      </c>
+      <c r="S77">
+        <v>4</v>
+      </c>
+      <c r="T77">
+        <v>0.5</v>
+      </c>
+      <c r="U77">
+        <v>4.831024930747922</v>
+      </c>
+      <c r="V77">
+        <v>0.3177213942185137</v>
+      </c>
+      <c r="W77">
+        <v>0.5215506168239931</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4547,16 +5734,16 @@
         <v>0.7556177201866963</v>
       </c>
       <c r="D78">
-        <v>760.0407695596156</v>
+        <v>748.9641781174147</v>
       </c>
       <c r="E78">
-        <v>2.384652531651748</v>
+        <v>2.339591991004429</v>
       </c>
       <c r="F78">
-        <v>0.6494575017963695</v>
+        <v>0.6457641981251995</v>
       </c>
       <c r="G78">
-        <v>0.5804939980002394</v>
+        <v>0.5920136836102656</v>
       </c>
       <c r="H78">
         <v>61.79041457875</v>
@@ -4587,6 +5774,21 @@
       <c r="P78">
         <v>2</v>
       </c>
+      <c r="Q78">
+        <v>6.434649477000001</v>
+      </c>
+      <c r="R78">
+        <v>0.225039832725114</v>
+      </c>
+      <c r="S78">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="T78">
+        <v>0.2083333333333333</v>
+      </c>
+      <c r="W78">
+        <v>0.419695242054367</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4601,16 +5803,16 @@
         <v>0.5807343615337464</v>
       </c>
       <c r="D79">
-        <v>733.1019988490638</v>
+        <v>729.3911372457928</v>
       </c>
       <c r="E79">
-        <v>2.475522518662487</v>
+        <v>2.420880084084988</v>
       </c>
       <c r="F79">
-        <v>0.6264382277944268</v>
+        <v>0.6288881319358856</v>
       </c>
       <c r="G79">
-        <v>0.6026144039537039</v>
+        <v>0.61258293825095</v>
       </c>
       <c r="H79">
         <v>114.1203750196875</v>
@@ -4640,6 +5842,21 @@
       </c>
       <c r="P79">
         <v>4</v>
+      </c>
+      <c r="Q79">
+        <v>2.6573583345</v>
+      </c>
+      <c r="R79">
+        <v>0.0929361385144752</v>
+      </c>
+      <c r="S79">
+        <v>6</v>
+      </c>
+      <c r="T79">
+        <v>0.75</v>
+      </c>
+      <c r="W79">
+        <v>0.4564067199321807</v>
       </c>
     </row>
   </sheetData>

--- a/Data Analysis/1_Data/ecological_multifunctionality.xlsx
+++ b/Data Analysis/1_Data/ecological_multifunctionality.xlsx
@@ -362,52 +362,52 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>TNleaching_av</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>leaching_standardized</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>mean_micbiomass</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>mean_micrespiration</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>micbiomass_standardized</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>micrespiration_standardized</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>mean_root_biomass</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>root_biomass_standardized</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>mean_biomass</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>biomass_standardized</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>mean_micbiomass</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>mean_micrespiration</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>micbiomass_standardized</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>micrespiration_standardized</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>mean_root_biomass</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>root_biomass_standardized</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>TNleaching_av</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>leaching_standardized</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>435.4745416666667</v>
+        <v>2.095065631874623</v>
       </c>
       <c r="C2">
-        <v>0.610565427738763</v>
+        <v>0.8076929038682368</v>
       </c>
       <c r="D2">
         <v>828.3773512579434</v>
@@ -502,10 +502,10 @@
         <v>0.4615269340646537</v>
       </c>
       <c r="J2">
-        <v>2.095065631874623</v>
+        <v>435.4745416666667</v>
       </c>
       <c r="K2">
-        <v>0.1923070961317632</v>
+        <v>0.610565427738763</v>
       </c>
       <c r="L2">
         <v>16.37541437</v>
@@ -528,7 +528,7 @@
         <v>9.570568743000001</v>
       </c>
       <c r="R2">
-        <v>0.3347127449144382</v>
+        <v>0.6652872550855617</v>
       </c>
       <c r="S2">
         <v>2.666666666666667</v>
@@ -537,7 +537,7 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="W2">
-        <v>0.4932434099009808</v>
+        <v>0.6114884496394305</v>
       </c>
     </row>
     <row r="3">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>329.558375</v>
+        <v>2.614593071827771</v>
       </c>
       <c r="C3">
-        <v>0.4620636362039917</v>
+        <v>0.7600052267768216</v>
       </c>
       <c r="D3">
         <v>655.9329685983965</v>
@@ -571,10 +571,10 @@
         <v>0.8338794210586178</v>
       </c>
       <c r="J3">
-        <v>2.614593071827771</v>
+        <v>329.558375</v>
       </c>
       <c r="K3">
-        <v>0.2399947732231784</v>
+        <v>0.4620636362039917</v>
       </c>
       <c r="L3">
         <v>16.184261805</v>
@@ -597,7 +597,7 @@
         <v>7.007383158000001</v>
       </c>
       <c r="R3">
-        <v>0.2450701222115849</v>
+        <v>0.7549298777884151</v>
       </c>
       <c r="S3">
         <v>2.333333333333333</v>
@@ -606,7 +606,7 @@
         <v>0.2916666666666667</v>
       </c>
       <c r="W3">
-        <v>0.4788904729574147</v>
+        <v>0.6076242490987238</v>
       </c>
     </row>
     <row r="4">
@@ -616,10 +616,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>307.92475</v>
+        <v>7.874606776195011</v>
       </c>
       <c r="C4">
-        <v>0.4317317976282808</v>
+        <v>0.2771860034978646</v>
       </c>
       <c r="D4">
         <v>776.4263094419364</v>
@@ -640,10 +640,10 @@
         <v>0.3365178746777452</v>
       </c>
       <c r="J4">
-        <v>7.874606776195011</v>
+        <v>307.92475</v>
       </c>
       <c r="K4">
-        <v>0.7228139965021354</v>
+        <v>0.4317317976282808</v>
       </c>
       <c r="L4">
         <v>14.46322224386111</v>
@@ -666,7 +666,7 @@
         <v>4.280052659</v>
       </c>
       <c r="R4">
-        <v>0.1496868380910004</v>
+        <v>0.8503131619089996</v>
       </c>
       <c r="S4">
         <v>2.333333333333333</v>
@@ -675,7 +675,7 @@
         <v>0.2916666666666667</v>
       </c>
       <c r="W4">
-        <v>0.4703560638209432</v>
+        <v>0.5022308551726592</v>
       </c>
     </row>
     <row r="5">
@@ -685,10 +685,10 @@
         </is>
       </c>
       <c r="B5">
-        <v>425.0958333333334</v>
+        <v>6.762593017775271</v>
       </c>
       <c r="C5">
-        <v>0.5960137607947789</v>
+        <v>0.3792582887221329</v>
       </c>
       <c r="D5">
         <v>701.0418942996629</v>
@@ -709,10 +709,10 @@
         <v>0.287986987025475</v>
       </c>
       <c r="J5">
-        <v>6.762593017775271</v>
+        <v>425.0958333333334</v>
       </c>
       <c r="K5">
-        <v>0.6207417112778671</v>
+        <v>0.5960137607947789</v>
       </c>
       <c r="L5">
         <v>16.92879661722222</v>
@@ -735,7 +735,7 @@
         <v>4.303033941000001</v>
       </c>
       <c r="R5">
-        <v>0.1504905654541729</v>
+        <v>0.8495094345458271</v>
       </c>
       <c r="S5">
         <v>4.333333333333333</v>
@@ -744,7 +744,7 @@
         <v>0.5416666666666666</v>
       </c>
       <c r="W5">
-        <v>0.4958839889788147</v>
+        <v>0.5530759197958047</v>
       </c>
     </row>
     <row r="6">
@@ -754,10 +754,10 @@
         </is>
       </c>
       <c r="B6">
-        <v>409.3909166666667</v>
+        <v>5.452538173207431</v>
       </c>
       <c r="C6">
-        <v>0.5739943813713894</v>
+        <v>0.49950886183032</v>
       </c>
       <c r="D6">
         <v>480.0111760454392</v>
@@ -778,10 +778,10 @@
         <v>0.3177815558786625</v>
       </c>
       <c r="J6">
-        <v>5.452538173207431</v>
+        <v>409.3909166666667</v>
       </c>
       <c r="K6">
-        <v>0.50049113816968</v>
+        <v>0.5739943813713894</v>
       </c>
       <c r="L6">
         <v>16.25849923111111</v>
@@ -804,7 +804,7 @@
         <v>12.810452095</v>
       </c>
       <c r="R6">
-        <v>0.4480216065997663</v>
+        <v>0.5519783934002338</v>
       </c>
       <c r="S6">
         <v>4</v>
@@ -813,7 +813,7 @@
         <v>0.5</v>
       </c>
       <c r="W6">
-        <v>0.4739831500377737</v>
+        <v>0.4868549638454121</v>
       </c>
     </row>
     <row r="7">
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>285.4118083333333</v>
+        <v>1.266329559472203</v>
       </c>
       <c r="C7">
-        <v>0.4001670962665013</v>
+        <v>0.8837629921359487</v>
       </c>
       <c r="D7">
         <v>834.7057465626099</v>
@@ -847,10 +847,10 @@
         <v>0.576028057915543</v>
       </c>
       <c r="J7">
-        <v>1.266329559472203</v>
+        <v>285.4118083333333</v>
       </c>
       <c r="K7">
-        <v>0.1162370078640514</v>
+        <v>0.4001670962665013</v>
       </c>
       <c r="L7">
         <v>15.87036697694444</v>
@@ -873,7 +873,7 @@
         <v>8.956316193999999</v>
       </c>
       <c r="R7">
-        <v>0.3132304106595532</v>
+        <v>0.6867695893404469</v>
       </c>
       <c r="S7">
         <v>2.666666666666667</v>
@@ -882,7 +882,7 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="W7">
-        <v>0.4734804399188681</v>
+        <v>0.616113585287967</v>
       </c>
     </row>
     <row r="8">
@@ -892,10 +892,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>195.5060666666667</v>
+        <v>5.834182375549821</v>
       </c>
       <c r="C8">
-        <v>0.2741130279694455</v>
+        <v>0.4644775543660676</v>
       </c>
       <c r="D8">
         <v>692.6924213740515</v>
@@ -916,10 +916,10 @@
         <v>0.3514546676045188</v>
       </c>
       <c r="J8">
-        <v>5.834182375549821</v>
+        <v>195.5060666666667</v>
       </c>
       <c r="K8">
-        <v>0.5355224456339324</v>
+        <v>0.2741130279694455</v>
       </c>
       <c r="L8">
         <v>16.87932298833333</v>
@@ -942,7 +942,7 @@
         <v>1.0562739425</v>
       </c>
       <c r="R8">
-        <v>0.0369412059167705</v>
+        <v>0.9630587940832295</v>
       </c>
       <c r="S8">
         <v>1.333333333333333</v>
@@ -951,7 +951,7 @@
         <v>0.1666666666666667</v>
       </c>
       <c r="W8">
-        <v>0.3907675091892621</v>
+        <v>0.4976515963015863</v>
       </c>
     </row>
     <row r="9">
@@ -961,10 +961,10 @@
         </is>
       </c>
       <c r="B9">
-        <v>332.1990833333333</v>
+        <v>9.555711420707254</v>
       </c>
       <c r="C9">
-        <v>0.4657660919363158</v>
+        <v>0.1228765882885198</v>
       </c>
       <c r="D9">
         <v>604.6068150246119</v>
@@ -985,10 +985,10 @@
         <v>0.2994520032539114</v>
       </c>
       <c r="J9">
-        <v>9.555711420707254</v>
+        <v>332.1990833333333</v>
       </c>
       <c r="K9">
-        <v>0.8771234117114802</v>
+        <v>0.4657660919363158</v>
       </c>
       <c r="L9">
         <v>16.09618226416667</v>
@@ -1011,7 +1011,7 @@
         <v>3.7317630585</v>
       </c>
       <c r="R9">
-        <v>0.1305114346098203</v>
+        <v>0.8694885653901797</v>
       </c>
       <c r="S9">
         <v>1.666666666666667</v>
@@ -1020,7 +1020,7 @@
         <v>0.2083333333333333</v>
       </c>
       <c r="W9">
-        <v>0.4490356151852044</v>
+        <v>0.4471269036048793</v>
       </c>
     </row>
     <row r="10">
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="B10">
-        <v>95.10555555555555</v>
+        <v>4.444804068467144</v>
       </c>
       <c r="C10">
-        <v>0.1333445670230676</v>
+        <v>0.5920092667852441</v>
       </c>
       <c r="D10">
         <v>676.5846424714285</v>
@@ -1054,10 +1054,10 @@
         <v>0.649291554064787</v>
       </c>
       <c r="J10">
-        <v>4.444804068467144</v>
+        <v>95.10555555555555</v>
       </c>
       <c r="K10">
-        <v>0.4079907332147559</v>
+        <v>0.1333445670230676</v>
       </c>
       <c r="L10">
         <v>17.09475449166667</v>
@@ -1077,7 +1077,7 @@
         <v>1</v>
       </c>
       <c r="W10">
-        <v>0.5289702298300806</v>
+        <v>0.5596399854251619</v>
       </c>
     </row>
     <row r="11">
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="B11">
-        <v>297.311575</v>
+        <v>2.325544502250153</v>
       </c>
       <c r="C11">
-        <v>0.4168513922003523</v>
+        <v>0.7865371359498885</v>
       </c>
       <c r="D11">
         <v>912.9959398422051</v>
@@ -1111,10 +1111,10 @@
         <v>0.361511389364042</v>
       </c>
       <c r="J11">
-        <v>2.325544502250153</v>
+        <v>297.311575</v>
       </c>
       <c r="K11">
-        <v>0.2134628640501115</v>
+        <v>0.4168513922003523</v>
       </c>
       <c r="L11">
         <v>19.64938485194444</v>
@@ -1137,7 +1137,7 @@
         <v>8.72065508</v>
       </c>
       <c r="R11">
-        <v>0.3049886038814318</v>
+        <v>0.6950113961185682</v>
       </c>
       <c r="S11">
         <v>2.666666666666667</v>
@@ -1152,7 +1152,7 @@
         <v>0.8925979653646036</v>
       </c>
       <c r="W11">
-        <v>0.5223220037545615</v>
+        <v>0.629332788658663</v>
       </c>
     </row>
     <row r="12">
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="B12">
-        <v>453.8560083333334</v>
+        <v>6.7695929031412</v>
       </c>
       <c r="C12">
-        <v>0.636337515390192</v>
+        <v>0.3786157658304883</v>
       </c>
       <c r="D12">
         <v>705.031891045062</v>
@@ -1186,10 +1186,10 @@
         <v>0.363727951930117</v>
       </c>
       <c r="J12">
-        <v>6.7695929031412</v>
+        <v>453.8560083333334</v>
       </c>
       <c r="K12">
-        <v>0.6213842341695117</v>
+        <v>0.636337515390192</v>
       </c>
       <c r="L12">
         <v>16.648180935</v>
@@ -1212,7 +1212,7 @@
         <v>3.2370576185</v>
       </c>
       <c r="R12">
-        <v>0.1132100369402601</v>
+        <v>0.8867899630597399</v>
       </c>
       <c r="S12">
         <v>3.666666666666667</v>
@@ -1227,7 +1227,7 @@
         <v>1</v>
       </c>
       <c r="W12">
-        <v>0.5548534139593566</v>
+        <v>0.6138324648238518</v>
       </c>
     </row>
     <row r="13">
@@ -1237,10 +1237,10 @@
         </is>
       </c>
       <c r="B13">
-        <v>442.4480833333333</v>
+        <v>6.202177180698082</v>
       </c>
       <c r="C13">
-        <v>0.6203428154920557</v>
+        <v>0.4306991317271958</v>
       </c>
       <c r="D13">
         <v>633.0952679188338</v>
@@ -1261,10 +1261,10 @@
         <v>0.3012274573669663</v>
       </c>
       <c r="J13">
-        <v>6.202177180698082</v>
+        <v>442.4480833333333</v>
       </c>
       <c r="K13">
-        <v>0.5693008682728042</v>
+        <v>0.6203428154920557</v>
       </c>
       <c r="L13">
         <v>16.12420608472222</v>
@@ -1287,7 +1287,7 @@
         <v>3.0434590775</v>
       </c>
       <c r="R13">
-        <v>0.1064392899962046</v>
+        <v>0.8935607100037953</v>
       </c>
       <c r="S13">
         <v>3.666666666666667</v>
@@ -1302,7 +1302,7 @@
         <v>0.4695105780076481</v>
       </c>
       <c r="W13">
-        <v>0.4617924123004704</v>
+        <v>0.5338501549073573</v>
       </c>
     </row>
     <row r="14">
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="B14">
-        <v>226.6676666666667</v>
+        <v>1.699209011408265</v>
       </c>
       <c r="C14">
-        <v>0.3178037465134191</v>
+        <v>0.8440287761236099</v>
       </c>
       <c r="D14">
         <v>814.3056057503242</v>
@@ -1336,10 +1336,10 @@
         <v>0.5843415183903644</v>
       </c>
       <c r="J14">
-        <v>1.699209011408265</v>
+        <v>226.6676666666667</v>
       </c>
       <c r="K14">
-        <v>0.1559712238763901</v>
+        <v>0.3178037465134191</v>
       </c>
       <c r="L14">
         <v>14.841672665</v>
@@ -1362,7 +1362,7 @@
         <v>8.9541739505</v>
       </c>
       <c r="R14">
-        <v>0.3131554896991156</v>
+        <v>0.6868445103008844</v>
       </c>
       <c r="S14">
         <v>1.666666666666667</v>
@@ -1371,7 +1371,7 @@
         <v>0.2083333333333333</v>
       </c>
       <c r="W14">
-        <v>0.4420971429333643</v>
+        <v>0.574815464539488</v>
       </c>
     </row>
     <row r="15">
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="B15">
-        <v>77.20100000000001</v>
+        <v>3.853968818605062</v>
       </c>
       <c r="C15">
-        <v>0.1082411417357679</v>
+        <v>0.6462423225256484</v>
       </c>
       <c r="D15">
         <v>662.3028872476706</v>
@@ -1405,10 +1405,10 @@
         <v>0.2052942391677662</v>
       </c>
       <c r="J15">
-        <v>3.853968818605062</v>
+        <v>77.20100000000001</v>
       </c>
       <c r="K15">
-        <v>0.3537576774743516</v>
+        <v>0.1082411417357679</v>
       </c>
       <c r="L15">
         <v>18.24718734055556</v>
@@ -1431,7 +1431,7 @@
         <v>1.54509958</v>
       </c>
       <c r="R15">
-        <v>0.05403696848906753</v>
+        <v>0.9459630315109324</v>
       </c>
       <c r="S15">
         <v>1.666666666666667</v>
@@ -1440,7 +1440,7 @@
         <v>0.2083333333333333</v>
       </c>
       <c r="W15">
-        <v>0.3347002785531547</v>
+        <v>0.4827516170622999</v>
       </c>
     </row>
     <row r="16">
@@ -1450,10 +1450,10 @@
         </is>
       </c>
       <c r="B16">
-        <v>155.476625</v>
+        <v>1.136531189147966</v>
       </c>
       <c r="C16">
-        <v>0.2179889820497641</v>
+        <v>0.8956772478518207</v>
       </c>
       <c r="D16">
         <v>745.9491221775057</v>
@@ -1474,10 +1474,10 @@
         <v>0.3845868607291626</v>
       </c>
       <c r="J16">
-        <v>1.136531189147966</v>
+        <v>155.476625</v>
       </c>
       <c r="K16">
-        <v>0.1043227521481793</v>
+        <v>0.2179889820497641</v>
       </c>
       <c r="L16">
         <v>17.88303947</v>
@@ -1500,7 +1500,7 @@
         <v>0.535635516</v>
       </c>
       <c r="R16">
-        <v>0.01873285053880956</v>
+        <v>0.9812671494611904</v>
       </c>
       <c r="S16">
         <v>0</v>
@@ -1509,7 +1509,7 @@
         <v>0</v>
       </c>
       <c r="W16">
-        <v>0.3262262325049453</v>
+        <v>0.5454623318331981</v>
       </c>
     </row>
     <row r="17">
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="B17">
-        <v>185.8095416666667</v>
+        <v>2.892220428878251</v>
       </c>
       <c r="C17">
-        <v>0.2605178292431412</v>
+        <v>0.7345216762718467</v>
       </c>
       <c r="D17">
         <v>714.1590786180997</v>
@@ -1543,10 +1543,10 @@
         <v>0.5581714220930729</v>
       </c>
       <c r="J17">
-        <v>2.892220428878251</v>
+        <v>185.8095416666667</v>
       </c>
       <c r="K17">
-        <v>0.2654783237281533</v>
+        <v>0.2605178292431412</v>
       </c>
       <c r="L17">
         <v>18.39406902583333</v>
@@ -1569,7 +1569,7 @@
         <v>0.952643172</v>
       </c>
       <c r="R17">
-        <v>0.03331691350708239</v>
+        <v>0.9666830864929176</v>
       </c>
       <c r="S17">
         <v>2.333333333333333</v>
@@ -1578,7 +1578,7 @@
         <v>0.2916666666666667</v>
       </c>
       <c r="W17">
-        <v>0.4167213545534574</v>
+        <v>0.5920225452446485</v>
       </c>
     </row>
     <row r="18">
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="B18">
-        <v>56.48408333333333</v>
+        <v>2.173775254829633</v>
       </c>
       <c r="C18">
-        <v>0.07919459164904936</v>
+        <v>0.8004681091898189</v>
       </c>
       <c r="D18">
         <v>63.60968471467833</v>
@@ -1612,10 +1612,10 @@
         <v>0.259617387301867</v>
       </c>
       <c r="J18">
-        <v>2.173775254829633</v>
+        <v>56.48408333333333</v>
       </c>
       <c r="K18">
-        <v>0.1995318908101811</v>
+        <v>0.07919459164904936</v>
       </c>
       <c r="L18">
         <v>18.55946434555555</v>
@@ -1638,7 +1638,7 @@
         <v>2.007709605</v>
       </c>
       <c r="R18">
-        <v>0.07021588903712161</v>
+        <v>0.9297841109628784</v>
       </c>
       <c r="S18">
         <v>0</v>
@@ -1647,7 +1647,7 @@
         <v>0</v>
       </c>
       <c r="W18">
-        <v>0.2278784972800412</v>
+        <v>0.4104415523182156</v>
       </c>
     </row>
     <row r="19">
@@ -1657,10 +1657,10 @@
         </is>
       </c>
       <c r="B19">
-        <v>238.2480416666667</v>
+        <v>2.185989068317086</v>
       </c>
       <c r="C19">
-        <v>0.3340402332393468</v>
+        <v>0.7993469972930211</v>
       </c>
       <c r="D19">
         <v>799.4162616745616</v>
@@ -1681,10 +1681,10 @@
         <v>0.596126375798129</v>
       </c>
       <c r="J19">
-        <v>2.185989068317086</v>
+        <v>238.2480416666667</v>
       </c>
       <c r="K19">
-        <v>0.2006530027069789</v>
+        <v>0.3340402332393468</v>
       </c>
       <c r="L19">
         <v>18.48682638</v>
@@ -1707,7 +1707,7 @@
         <v>6.889186623000001</v>
       </c>
       <c r="R19">
-        <v>0.2409364194263496</v>
+        <v>0.7590635805736504</v>
       </c>
       <c r="S19">
         <v>1.333333333333333</v>
@@ -1716,7 +1716,7 @@
         <v>0.1666666666666667</v>
       </c>
       <c r="W19">
-        <v>0.4474402982820094</v>
+        <v>0.5870429427486773</v>
       </c>
     </row>
     <row r="20">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="B20">
-        <v>581.4750416666667</v>
+        <v>3.356827381619648</v>
       </c>
       <c r="C20">
-        <v>0.8152682271065561</v>
+        <v>0.6918751774868042</v>
       </c>
       <c r="D20">
         <v>917.5395358708413</v>
@@ -1750,10 +1750,10 @@
         <v>0.373251530181499</v>
       </c>
       <c r="J20">
-        <v>3.356827381619648</v>
+        <v>581.4750416666667</v>
       </c>
       <c r="K20">
-        <v>0.3081248225131958</v>
+        <v>0.8152682271065561</v>
       </c>
       <c r="L20">
         <v>19.49016020277778</v>
@@ -1776,7 +1776,7 @@
         <v>4.3663490965</v>
       </c>
       <c r="R20">
-        <v>0.1527048946190503</v>
+        <v>0.8472951053809497</v>
       </c>
       <c r="S20">
         <v>7.333333333333333</v>
@@ -1791,7 +1791,7 @@
         <v>0.6320101787581411</v>
       </c>
       <c r="W20">
-        <v>0.5959205787772528</v>
+        <v>0.7157361971923092</v>
       </c>
     </row>
     <row r="21">
@@ -1801,10 +1801,10 @@
         </is>
       </c>
       <c r="B21">
-        <v>128.7385</v>
+        <v>0.9990682892502492</v>
       </c>
       <c r="C21">
-        <v>0.1805002814128076</v>
+        <v>0.9082950344753011</v>
       </c>
       <c r="D21">
         <v>813.5264000739855</v>
@@ -1825,10 +1825,10 @@
         <v>0.4245325765244304</v>
       </c>
       <c r="J21">
-        <v>0.9990682892502492</v>
+        <v>128.7385</v>
       </c>
       <c r="K21">
-        <v>0.09170496552469892</v>
+        <v>0.1805002814128076</v>
       </c>
       <c r="L21">
         <v>18.26601297333333</v>
@@ -1851,7 +1851,7 @@
         <v>1.290140285</v>
       </c>
       <c r="R21">
-        <v>0.04512024391788496</v>
+        <v>0.9548797560821151</v>
       </c>
       <c r="S21">
         <v>2.666666666666667</v>
@@ -1860,7 +1860,7 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="W21">
-        <v>0.3811919274477344</v>
+        <v>0.5969856250870885</v>
       </c>
     </row>
     <row r="22">
@@ -1870,10 +1870,10 @@
         </is>
       </c>
       <c r="B22">
-        <v>442.4108333333334</v>
+        <v>1.87831184917383</v>
       </c>
       <c r="C22">
-        <v>0.6202905884155975</v>
+        <v>0.8275888392950747</v>
       </c>
       <c r="D22">
         <v>790.0249197554833</v>
@@ -1894,10 +1894,10 @@
         <v>0.3418827903179118</v>
       </c>
       <c r="J22">
-        <v>1.87831184917383</v>
+        <v>442.4108333333334</v>
       </c>
       <c r="K22">
-        <v>0.1724111607049253</v>
+        <v>0.6202905884155975</v>
       </c>
       <c r="L22">
         <v>18.15336036388889</v>
@@ -1920,7 +1920,7 @@
         <v>4.387179358499999</v>
       </c>
       <c r="R22">
-        <v>0.1534333940801097</v>
+        <v>0.8465666059198903</v>
       </c>
       <c r="S22">
         <v>4.666666666666667</v>
@@ -1929,7 +1929,7 @@
         <v>0.5833333333333334</v>
       </c>
       <c r="W22">
-        <v>0.4737394269870207</v>
+        <v>0.6422782882907619</v>
       </c>
     </row>
     <row r="23">
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="B23">
-        <v>192.1180833333333</v>
+        <v>0.7408975943918668</v>
       </c>
       <c r="C23">
-        <v>0.2693628410006011</v>
+        <v>0.9319926484684775</v>
       </c>
       <c r="D23">
         <v>873.7027658075027</v>
@@ -1963,10 +1963,10 @@
         <v>0.5922668670101464</v>
       </c>
       <c r="J23">
-        <v>0.7408975943918668</v>
+        <v>192.1180833333333</v>
       </c>
       <c r="K23">
-        <v>0.06800735153152251</v>
+        <v>0.2693628410006011</v>
       </c>
       <c r="L23">
         <v>16.39088118888889</v>
@@ -1989,10 +1989,10 @@
         <v>12.19512195</v>
       </c>
       <c r="R23">
-        <v>0.4265015854398755</v>
+        <v>0.5734984145601245</v>
       </c>
       <c r="W23">
-        <v>0.4998207561341838</v>
+        <v>0.6442467741423558</v>
       </c>
     </row>
     <row r="24">
@@ -2002,10 +2002,10 @@
         </is>
       </c>
       <c r="B24">
-        <v>142.4275</v>
+        <v>5.03432563844431</v>
       </c>
       <c r="C24">
-        <v>0.199693206235296</v>
+        <v>0.5378967943621695</v>
       </c>
       <c r="D24">
         <v>548.7226506533721</v>
@@ -2026,10 +2026,10 @@
         <v>0.3615582979066596</v>
       </c>
       <c r="J24">
-        <v>5.03432563844431</v>
+        <v>142.4275</v>
       </c>
       <c r="K24">
-        <v>0.4621032056378304</v>
+        <v>0.199693206235296</v>
       </c>
       <c r="L24">
         <v>16.1714261825</v>
@@ -2052,7 +2052,7 @@
         <v>21.34269891</v>
       </c>
       <c r="R24">
-        <v>0.7464209837344761</v>
+        <v>0.2535790162655239</v>
       </c>
       <c r="S24">
         <v>2</v>
@@ -2061,7 +2061,7 @@
         <v>0.25</v>
       </c>
       <c r="W24">
-        <v>0.4432293818749224</v>
+        <v>0.3910983345318457</v>
       </c>
     </row>
     <row r="25">
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="B25">
-        <v>153.53375</v>
+        <v>1.903937605799871</v>
       </c>
       <c r="C25">
-        <v>0.2152649369175783</v>
+        <v>0.8252366385964628</v>
       </c>
       <c r="D25">
         <v>648.7983906320918</v>
@@ -2095,10 +2095,10 @@
         <v>0.2429336478316754</v>
       </c>
       <c r="J25">
-        <v>1.903937605799871</v>
+        <v>153.53375</v>
       </c>
       <c r="K25">
-        <v>0.1747633614035372</v>
+        <v>0.2152649369175783</v>
       </c>
       <c r="L25">
         <v>18.74636130527778</v>
@@ -2121,10 +2121,10 @@
         <v>13.7963962</v>
       </c>
       <c r="R25">
-        <v>0.4825031579660976</v>
+        <v>0.5174968420339024</v>
       </c>
       <c r="W25">
-        <v>0.4067309299760255</v>
+        <v>0.5046547815847013</v>
       </c>
     </row>
     <row r="26">
@@ -2134,10 +2134,10 @@
         </is>
       </c>
       <c r="B26">
-        <v>321.4800416666667</v>
+        <v>2.494660573312057</v>
       </c>
       <c r="C26">
-        <v>0.4507372541192763</v>
+        <v>0.7710138893077165</v>
       </c>
       <c r="D26">
         <v>953.7906142421343</v>
@@ -2158,10 +2158,10 @@
         <v>0.3738785945495323</v>
       </c>
       <c r="J26">
-        <v>2.494660573312057</v>
+        <v>321.4800416666667</v>
       </c>
       <c r="K26">
-        <v>0.2289861106922835</v>
+        <v>0.4507372541192763</v>
       </c>
       <c r="L26">
         <v>20.25364036361111</v>
@@ -2184,7 +2184,7 @@
         <v>3.726573942</v>
       </c>
       <c r="R26">
-        <v>0.130329954963831</v>
+        <v>0.8696700450361691</v>
       </c>
       <c r="S26">
         <v>1.333333333333333</v>
@@ -2199,7 +2199,7 @@
         <v>0.2409214974333292</v>
       </c>
       <c r="W26">
-        <v>0.420141677762516</v>
+        <v>0.5625158853944906</v>
       </c>
     </row>
     <row r="27">
@@ -2209,10 +2209,10 @@
         </is>
       </c>
       <c r="B27">
-        <v>150.5134916666667</v>
+        <v>2.013311318365398</v>
       </c>
       <c r="C27">
-        <v>0.2110303258330461</v>
+        <v>0.8151971721775485</v>
       </c>
       <c r="D27">
         <v>857.7172489851876</v>
@@ -2233,10 +2233,10 @@
         <v>0.5366846590209104</v>
       </c>
       <c r="J27">
-        <v>2.013311318365398</v>
+        <v>150.5134916666667</v>
       </c>
       <c r="K27">
-        <v>0.1848028278224515</v>
+        <v>0.2110303258330461</v>
       </c>
       <c r="L27">
         <v>21.35522024472222</v>
@@ -2262,7 +2262,7 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="W27">
-        <v>0.4783956940990148</v>
+        <v>0.5684520290068859</v>
       </c>
     </row>
     <row r="28">
@@ -2272,10 +2272,10 @@
         </is>
       </c>
       <c r="B28">
-        <v>184.4895</v>
+        <v>0.9993273242222674</v>
       </c>
       <c r="C28">
-        <v>0.2586670395235937</v>
+        <v>0.9082712575288858</v>
       </c>
       <c r="D28">
         <v>1010.778519775807</v>
@@ -2296,10 +2296,10 @@
         <v>0.5111900171820443</v>
       </c>
       <c r="J28">
-        <v>0.9993273242222674</v>
+        <v>184.4895</v>
       </c>
       <c r="K28">
-        <v>0.09172874247111412</v>
+        <v>0.2586670395235937</v>
       </c>
       <c r="L28">
         <v>21.68805554777778</v>
@@ -2322,7 +2322,7 @@
         <v>8.2729372335</v>
       </c>
       <c r="R28">
-        <v>0.2893305094281839</v>
+        <v>0.7106694905718161</v>
       </c>
       <c r="S28">
         <v>0</v>
@@ -2331,7 +2331,7 @@
         <v>0</v>
       </c>
       <c r="W28">
-        <v>0.4276020592026076</v>
+        <v>0.582337246227783</v>
       </c>
     </row>
     <row r="29">
@@ -2341,10 +2341,10 @@
         </is>
       </c>
       <c r="B29">
-        <v>344.1929166666667</v>
+        <v>1.08660229088038</v>
       </c>
       <c r="C29">
-        <v>0.4825822758431113</v>
+        <v>0.9002602457745665</v>
       </c>
       <c r="D29">
         <v>1107.679249668098</v>
@@ -2365,10 +2365,10 @@
         <v>0.7029065665171318</v>
       </c>
       <c r="J29">
-        <v>1.08660229088038</v>
+        <v>344.1929166666667</v>
       </c>
       <c r="K29">
-        <v>0.09973975422543346</v>
+        <v>0.4825822758431113</v>
       </c>
       <c r="L29">
         <v>22.74975343416667</v>
@@ -2391,7 +2391,7 @@
         <v>18.2184374865</v>
       </c>
       <c r="R29">
-        <v>0.6371557827865354</v>
+        <v>0.3628442172134646</v>
       </c>
       <c r="S29">
         <v>3</v>
@@ -2400,7 +2400,7 @@
         <v>0.375</v>
       </c>
       <c r="W29">
-        <v>0.620783011502694</v>
+        <v>0.6865591272497017</v>
       </c>
     </row>
     <row r="30">
@@ -2410,10 +2410,10 @@
         </is>
       </c>
       <c r="B30">
-        <v>340.3929333333333</v>
+        <v>0.9556834864386684</v>
       </c>
       <c r="C30">
-        <v>0.4772544363776005</v>
+        <v>0.9122773466845272</v>
       </c>
       <c r="D30">
         <v>845.6928104684499</v>
@@ -2434,10 +2434,10 @@
         <v>0.4988839572547034</v>
       </c>
       <c r="J30">
-        <v>0.9556834864386684</v>
+        <v>340.3929333333333</v>
       </c>
       <c r="K30">
-        <v>0.08772265331547284</v>
+        <v>0.4772544363776005</v>
       </c>
       <c r="L30">
         <v>18.0566264525</v>
@@ -2460,7 +2460,7 @@
         <v>3.4872954225</v>
       </c>
       <c r="R30">
-        <v>0.1219616361928607</v>
+        <v>0.8780383638071393</v>
       </c>
       <c r="S30">
         <v>3</v>
@@ -2475,7 +2475,7 @@
         <v>0.4818176706960131</v>
       </c>
       <c r="W30">
-        <v>0.4558834320945868</v>
+        <v>0.6315091455371794</v>
       </c>
     </row>
     <row r="31">
@@ -2485,10 +2485,10 @@
         </is>
       </c>
       <c r="B31">
-        <v>95.69158333333333</v>
+        <v>5.517142053953108</v>
       </c>
       <c r="C31">
-        <v>0.1341662185010995</v>
+        <v>0.4935788401087917</v>
       </c>
       <c r="D31">
         <v>797.0526848735647</v>
@@ -2509,10 +2509,10 @@
         <v>0.2823929800296902</v>
       </c>
       <c r="J31">
-        <v>5.517142053953108</v>
+        <v>95.69158333333333</v>
       </c>
       <c r="K31">
-        <v>0.5064211598912083</v>
+        <v>0.1341662185010995</v>
       </c>
       <c r="L31">
         <v>15.58422212138889</v>
@@ -2535,7 +2535,7 @@
         <v>4.2902386335</v>
       </c>
       <c r="R31">
-        <v>0.150043073501463</v>
+        <v>0.8499569264985369</v>
       </c>
       <c r="S31">
         <v>1.666666666666667</v>
@@ -2544,7 +2544,7 @@
         <v>0.2083333333333333</v>
       </c>
       <c r="W31">
-        <v>0.3930519448680388</v>
+        <v>0.478935886519871</v>
       </c>
     </row>
     <row r="32">
@@ -2554,10 +2554,10 @@
         </is>
       </c>
       <c r="B32">
-        <v>330.4918833333333</v>
+        <v>1.365713000697533</v>
       </c>
       <c r="C32">
-        <v>0.4633724794549839</v>
+        <v>0.8746405375956945</v>
       </c>
       <c r="D32">
         <v>1004.951093615742</v>
@@ -2578,10 +2578,10 @@
         <v>0.4389430690429412</v>
       </c>
       <c r="J32">
-        <v>1.365713000697533</v>
+        <v>330.4918833333333</v>
       </c>
       <c r="K32">
-        <v>0.1253594624043055</v>
+        <v>0.4633724794549839</v>
       </c>
       <c r="L32">
         <v>18.20769756222222</v>
@@ -2604,7 +2604,7 @@
         <v>3.3371393965</v>
       </c>
       <c r="R32">
-        <v>0.1167102099738428</v>
+        <v>0.8832897900261572</v>
       </c>
       <c r="S32">
         <v>5.666666666666667</v>
@@ -2613,7 +2613,7 @@
         <v>0.7083333333333334</v>
       </c>
       <c r="W32">
-        <v>0.5197390191561372</v>
+        <v>0.7092216010616001</v>
       </c>
     </row>
     <row r="33">
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="B33">
-        <v>449.8763333333333</v>
+        <v>4.138422420662683</v>
       </c>
       <c r="C33">
-        <v>0.6307577357793411</v>
+        <v>0.6201321876622482</v>
       </c>
       <c r="D33">
         <v>736.0154404505465</v>
@@ -2647,10 +2647,10 @@
         <v>0.2038940717983941</v>
       </c>
       <c r="J33">
-        <v>4.138422420662683</v>
+        <v>449.8763333333333</v>
       </c>
       <c r="K33">
-        <v>0.3798678123377518</v>
+        <v>0.6307577357793411</v>
       </c>
       <c r="L33">
         <v>19.28953693527778</v>
@@ -2673,7 +2673,7 @@
         <v>15.4121761</v>
       </c>
       <c r="R33">
-        <v>0.5390120384756428</v>
+        <v>0.4609879615243572</v>
       </c>
       <c r="S33">
         <v>4.333333333333333</v>
@@ -2682,7 +2682,7 @@
         <v>0.5416666666666666</v>
       </c>
       <c r="W33">
-        <v>0.5245231236588833</v>
+        <v>0.5448031609555346</v>
       </c>
     </row>
     <row r="34">
@@ -2692,10 +2692,10 @@
         </is>
       </c>
       <c r="B34">
-        <v>478.5481916666667</v>
+        <v>1.406406261621896</v>
       </c>
       <c r="C34">
-        <v>0.6709576642995183</v>
+        <v>0.870905283328985</v>
       </c>
       <c r="D34">
         <v>877.0060330270752</v>
@@ -2716,10 +2716,10 @@
         <v>0.5265303643973225</v>
       </c>
       <c r="J34">
-        <v>1.406406261621896</v>
+        <v>478.5481916666667</v>
       </c>
       <c r="K34">
-        <v>0.1290947166710151</v>
+        <v>0.6709576642995183</v>
       </c>
       <c r="L34">
         <v>21.148033835</v>
@@ -2742,7 +2742,7 @@
         <v>5.991139977</v>
       </c>
       <c r="R34">
-        <v>0.2095289173211359</v>
+        <v>0.7904710826788641</v>
       </c>
       <c r="S34">
         <v>5.666666666666667</v>
@@ -2757,7 +2757,7 @@
         <v>0.6826932129490296</v>
       </c>
       <c r="W34">
-        <v>0.5640751533954733</v>
+        <v>0.7110476791749953</v>
       </c>
     </row>
     <row r="35">
@@ -2767,10 +2767,10 @@
         </is>
       </c>
       <c r="B35">
-        <v>330.23375</v>
+        <v>2.906916865566272</v>
       </c>
       <c r="C35">
-        <v>0.4630105586674286</v>
+        <v>0.7331726831806715</v>
       </c>
       <c r="D35">
         <v>985.8426334202379</v>
@@ -2791,10 +2791,10 @@
         <v>0.3759558519806813</v>
       </c>
       <c r="J35">
-        <v>2.906916865566272</v>
+        <v>330.23375</v>
       </c>
       <c r="K35">
-        <v>0.2668273168193285</v>
+        <v>0.4630105586674286</v>
       </c>
       <c r="L35">
         <v>19.74005660527778</v>
@@ -2817,7 +2817,7 @@
         <v>4.1281363245</v>
       </c>
       <c r="R35">
-        <v>0.144373848373955</v>
+        <v>0.8556261516260451</v>
       </c>
       <c r="S35">
         <v>2</v>
@@ -2826,7 +2826,7 @@
         <v>0.25</v>
       </c>
       <c r="W35">
-        <v>0.4727393644924107</v>
+        <v>0.6199390731940898</v>
       </c>
     </row>
     <row r="36">
@@ -2836,10 +2836,10 @@
         </is>
       </c>
       <c r="B36">
-        <v>370.9917916666666</v>
+        <v>1.13456411529597</v>
       </c>
       <c r="C36">
-        <v>0.5201561521819427</v>
+        <v>0.8958578065200546</v>
       </c>
       <c r="D36">
         <v>1091.19812954318</v>
@@ -2860,10 +2860,10 @@
         <v>0.5312998842472573</v>
       </c>
       <c r="J36">
-        <v>1.13456411529597</v>
+        <v>370.9917916666666</v>
       </c>
       <c r="K36">
-        <v>0.1041421934799454</v>
+        <v>0.5201561521819427</v>
       </c>
       <c r="L36">
         <v>21.21049840166667</v>
@@ -2886,7 +2886,7 @@
         <v>5.496096239</v>
       </c>
       <c r="R36">
-        <v>0.1922156883116398</v>
+        <v>0.8077843116883603</v>
       </c>
       <c r="S36">
         <v>1.333333333333333</v>
@@ -2895,7 +2895,7 @@
         <v>0.1666666666666667</v>
       </c>
       <c r="W36">
-        <v>0.4962518629488541</v>
+        <v>0.6721623925009578</v>
       </c>
     </row>
     <row r="37">
@@ -2905,10 +2905,10 @@
         </is>
       </c>
       <c r="B37">
-        <v>169.8209166666667</v>
+        <v>0.7742258026830298</v>
       </c>
       <c r="C37">
-        <v>0.2381006711132589</v>
+        <v>0.9289334359749705</v>
       </c>
       <c r="D37">
         <v>971.6103559477901</v>
@@ -2929,10 +2929,10 @@
         <v>0.4886210703810875</v>
       </c>
       <c r="J37">
-        <v>0.7742258026830298</v>
+        <v>169.8209166666667</v>
       </c>
       <c r="K37">
-        <v>0.07106656402502957</v>
+        <v>0.2381006711132589</v>
       </c>
       <c r="L37">
         <v>21.82805563583333</v>
@@ -2955,7 +2955,7 @@
         <v>2.3825254305</v>
       </c>
       <c r="R37">
-        <v>0.08332437163197633</v>
+        <v>0.9166756283680236</v>
       </c>
       <c r="S37">
         <v>2</v>
@@ -2964,7 +2964,7 @@
         <v>0.25</v>
       </c>
       <c r="W37">
-        <v>0.4304837966716102</v>
+        <v>0.6418860627573587</v>
       </c>
     </row>
     <row r="38">
@@ -2974,10 +2974,10 @@
         </is>
       </c>
       <c r="B38">
-        <v>155.9118333333333</v>
+        <v>2.404323882427713</v>
       </c>
       <c r="C38">
-        <v>0.2185991742350068</v>
+        <v>0.7793059382219916</v>
       </c>
       <c r="D38">
         <v>962.3463114578503</v>
@@ -2998,10 +2998,10 @@
         <v>0.3807636063753785</v>
       </c>
       <c r="J38">
-        <v>2.404323882427713</v>
+        <v>155.9118333333333</v>
       </c>
       <c r="K38">
-        <v>0.2206940617780084</v>
+        <v>0.2185991742350068</v>
       </c>
       <c r="L38">
         <v>22.12220689805556</v>
@@ -3024,7 +3024,7 @@
         <v>11.5596577745</v>
       </c>
       <c r="R38">
-        <v>0.4042774142136917</v>
+        <v>0.5957225857863083</v>
       </c>
       <c r="S38">
         <v>0.3333333333333333</v>
@@ -3033,7 +3033,7 @@
         <v>0.04166666666666666</v>
       </c>
       <c r="W38">
-        <v>0.4416730167146239</v>
+        <v>0.5354301477166988</v>
       </c>
     </row>
     <row r="39">
@@ -3043,10 +3043,10 @@
         </is>
       </c>
       <c r="B39">
-        <v>557.3905416666666</v>
+        <v>1.57617971818797</v>
       </c>
       <c r="C39">
-        <v>0.7815000922619931</v>
+        <v>0.8553216949507725</v>
       </c>
       <c r="D39">
         <v>1151.611594239395</v>
@@ -3067,10 +3067,10 @@
         <v>0.457853533985901</v>
       </c>
       <c r="J39">
-        <v>1.57617971818797</v>
+        <v>557.3905416666666</v>
       </c>
       <c r="K39">
-        <v>0.1446783050492275</v>
+        <v>0.7815000922619931</v>
       </c>
       <c r="L39">
         <v>21.60189906472222</v>
@@ -3093,7 +3093,7 @@
         <v>6.628213125</v>
       </c>
       <c r="R39">
-        <v>0.231809359351744</v>
+        <v>0.7681906406482559</v>
       </c>
       <c r="S39">
         <v>4.666666666666667</v>
@@ -3108,7 +3108,7 @@
         <v>0.3564140114783297</v>
       </c>
       <c r="W39">
-        <v>0.5653336670300094</v>
+        <v>0.7038919638297936</v>
       </c>
     </row>
     <row r="40">
@@ -3118,10 +3118,10 @@
         </is>
       </c>
       <c r="B40">
-        <v>562.0825416666667</v>
+        <v>3.67911496942543</v>
       </c>
       <c r="C40">
-        <v>0.7880786007919891</v>
+        <v>0.6622922426196116</v>
       </c>
       <c r="D40">
         <v>1159.810624825328</v>
@@ -3142,10 +3142,10 @@
         <v>0.5488812986418652</v>
       </c>
       <c r="J40">
-        <v>3.67911496942543</v>
+        <v>562.0825416666667</v>
       </c>
       <c r="K40">
-        <v>0.3377077573803883</v>
+        <v>0.7880786007919891</v>
       </c>
       <c r="L40">
         <v>22.60901490388889</v>
@@ -3168,7 +3168,7 @@
         <v>25.94770115</v>
       </c>
       <c r="R40">
-        <v>0.9074723257683438</v>
+        <v>0.0925276742316562</v>
       </c>
       <c r="S40">
         <v>4.333333333333333</v>
@@ -3177,7 +3177,7 @@
         <v>0.5416666666666666</v>
       </c>
       <c r="W40">
-        <v>0.7235380718650894</v>
+        <v>0.6622430510779064</v>
       </c>
     </row>
     <row r="41">
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="B41">
-        <v>234.8489166666667</v>
+        <v>1.333235766632308</v>
       </c>
       <c r="C41">
-        <v>0.3292744248832039</v>
+        <v>0.8776216387499751</v>
       </c>
       <c r="D41">
         <v>769.90286227345</v>
@@ -3211,10 +3211,10 @@
         <v>0.4029322731238477</v>
       </c>
       <c r="J41">
-        <v>1.333235766632308</v>
+        <v>234.8489166666667</v>
       </c>
       <c r="K41">
-        <v>0.1223783612500249</v>
+        <v>0.3292744248832039</v>
       </c>
       <c r="L41">
         <v>19.02259681722222</v>
@@ -3237,7 +3237,7 @@
         <v>4.1289946215</v>
       </c>
       <c r="R41">
-        <v>0.1444038657065228</v>
+        <v>0.8555961342934773</v>
       </c>
       <c r="S41">
         <v>0.6666666666666666</v>
@@ -3246,7 +3246,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="W41">
-        <v>0.37646345915159</v>
+        <v>0.559767902412453</v>
       </c>
     </row>
     <row r="42">
@@ -3256,10 +3256,10 @@
         </is>
       </c>
       <c r="B42">
-        <v>144.7225</v>
+        <v>2.775396414933245</v>
       </c>
       <c r="C42">
-        <v>0.2029109549727941</v>
+        <v>0.745245009487961</v>
       </c>
       <c r="D42">
         <v>696.5614238650267</v>
@@ -3280,10 +3280,10 @@
         <v>0.3300968689347202</v>
       </c>
       <c r="J42">
-        <v>2.775396414933245</v>
+        <v>144.7225</v>
       </c>
       <c r="K42">
-        <v>0.2547549905120389</v>
+        <v>0.2029109549727941</v>
       </c>
       <c r="L42">
         <v>18.15723085875</v>
@@ -3306,7 +3306,7 @@
         <v>19.2733721</v>
       </c>
       <c r="R42">
-        <v>0.6740501481760632</v>
+        <v>0.3259498518239368</v>
       </c>
       <c r="S42">
         <v>0.6666666666666666</v>
@@ -3315,7 +3315,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="W42">
-        <v>0.4099046792214609</v>
+        <v>0.4277033945494354</v>
       </c>
     </row>
     <row r="43">
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="B43">
-        <v>280.7613333333333</v>
+        <v>1.815511680039976</v>
       </c>
       <c r="C43">
-        <v>0.393646808658651</v>
+        <v>0.8333532974480676</v>
       </c>
       <c r="D43">
         <v>890.8958090422312</v>
@@ -3349,10 +3349,10 @@
         <v>0.3631182589283404</v>
       </c>
       <c r="J43">
-        <v>1.815511680039976</v>
+        <v>280.7613333333333</v>
       </c>
       <c r="K43">
-        <v>0.1666467025519324</v>
+        <v>0.393646808658651</v>
       </c>
       <c r="L43">
         <v>16.84926868772222</v>
@@ -3375,7 +3375,7 @@
         <v>4.188993805</v>
       </c>
       <c r="R43">
-        <v>0.1465022249515362</v>
+        <v>0.8534977750484638</v>
       </c>
       <c r="S43">
         <v>2.333333333333333</v>
@@ -3384,7 +3384,7 @@
         <v>0.2916666666666667</v>
       </c>
       <c r="W43">
-        <v>0.4214333394030312</v>
+        <v>0.593146107527164</v>
       </c>
     </row>
     <row r="44">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="B44">
-        <v>363.53175</v>
+        <v>0.983265948598725</v>
       </c>
       <c r="C44">
-        <v>0.509696657779067</v>
+        <v>0.9097455390306455</v>
       </c>
       <c r="D44">
         <v>772.0165795662651</v>
@@ -3418,10 +3418,10 @@
         <v>0.47035627466076</v>
       </c>
       <c r="J44">
-        <v>0.983265948598725</v>
+        <v>363.53175</v>
       </c>
       <c r="K44">
-        <v>0.09025446096935456</v>
+        <v>0.509696657779067</v>
       </c>
       <c r="L44">
         <v>17.18627932666667</v>
@@ -3444,10 +3444,10 @@
         <v>10.51540466</v>
       </c>
       <c r="R44">
-        <v>0.3677566142773877</v>
+        <v>0.6322433857226123</v>
       </c>
       <c r="W44">
-        <v>0.483212964426785</v>
+        <v>0.6380669429277158</v>
       </c>
     </row>
     <row r="45">
@@ -3457,10 +3457,10 @@
         </is>
       </c>
       <c r="B45">
-        <v>559.8954583333333</v>
+        <v>1.469352354643475</v>
       </c>
       <c r="C45">
-        <v>0.7850121586853936</v>
+        <v>0.8651274307511693</v>
       </c>
       <c r="D45">
         <v>972.281952784939</v>
@@ -3481,10 +3481,10 @@
         <v>0.3412471213419044</v>
       </c>
       <c r="J45">
-        <v>1.469352354643475</v>
+        <v>559.8954583333333</v>
       </c>
       <c r="K45">
-        <v>0.1348725692488307</v>
+        <v>0.7850121586853936</v>
       </c>
       <c r="L45">
         <v>20.13906762361111</v>
@@ -3507,7 +3507,7 @@
         <v>13.8868205085</v>
       </c>
       <c r="R45">
-        <v>0.4856655790632932</v>
+        <v>0.5143344209367068</v>
       </c>
       <c r="S45">
         <v>3.666666666666667</v>
@@ -3516,7 +3516,7 @@
         <v>0.4583333333333333</v>
       </c>
       <c r="W45">
-        <v>0.5624289102487416</v>
+        <v>0.6572943731707107</v>
       </c>
     </row>
     <row r="46">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="B46">
-        <v>260.8305</v>
+        <v>0.7231897938302607</v>
       </c>
       <c r="C46">
-        <v>0.3657024017760291</v>
+        <v>0.9336180561182779</v>
       </c>
       <c r="D46">
         <v>884.1512260972701</v>
@@ -3550,10 +3550,10 @@
         <v>0.6146996260952234</v>
       </c>
       <c r="J46">
-        <v>0.7231897938302607</v>
+        <v>260.8305</v>
       </c>
       <c r="K46">
-        <v>0.06638194388172214</v>
+        <v>0.3657024017760291</v>
       </c>
       <c r="L46">
         <v>20.59998615166667</v>
@@ -3576,10 +3576,10 @@
         <v>4.674182018</v>
       </c>
       <c r="R46">
-        <v>0.1634707754038947</v>
+        <v>0.8365292245961053</v>
       </c>
       <c r="W46">
-        <v>0.4872242467485989</v>
+        <v>0.7072663269527084</v>
       </c>
     </row>
     <row r="47">
@@ -3589,10 +3589,10 @@
         </is>
       </c>
       <c r="B47">
-        <v>574.8780416666667</v>
+        <v>1.235925826614334</v>
       </c>
       <c r="C47">
-        <v>0.8060187768140616</v>
+        <v>0.8865537656031411</v>
       </c>
       <c r="D47">
         <v>963.5470426919795</v>
@@ -3613,10 +3613,10 @@
         <v>0.3268987317177518</v>
       </c>
       <c r="J47">
-        <v>1.235925826614334</v>
+        <v>574.8780416666667</v>
       </c>
       <c r="K47">
-        <v>0.1134462343968588</v>
+        <v>0.8060187768140616</v>
       </c>
       <c r="L47">
         <v>19.82994771638889</v>
@@ -3639,7 +3639,7 @@
         <v>2.032820474</v>
       </c>
       <c r="R47">
-        <v>0.07109409472331182</v>
+        <v>0.9289059052766881</v>
       </c>
       <c r="S47">
         <v>6</v>
@@ -3648,7 +3648,7 @@
         <v>0.75</v>
       </c>
       <c r="W47">
-        <v>0.5342697677556737</v>
+        <v>0.7381346854756311</v>
       </c>
     </row>
     <row r="48">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="B48">
-        <v>240.8029166666667</v>
+        <v>1.079519997394771</v>
       </c>
       <c r="C48">
-        <v>0.3376223447015321</v>
+        <v>0.9009103329477076</v>
       </c>
       <c r="D48">
         <v>800.328067796833</v>
@@ -3682,10 +3682,10 @@
         <v>0.3486501911314636</v>
       </c>
       <c r="J48">
-        <v>1.079519997394771</v>
+        <v>240.8029166666667</v>
       </c>
       <c r="K48">
-        <v>0.09908966705229239</v>
+        <v>0.3376223447015321</v>
       </c>
       <c r="L48">
         <v>20.03235579944445</v>
@@ -3708,10 +3708,10 @@
         <v>4.697584461000001</v>
       </c>
       <c r="R48">
-        <v>0.1642892320854752</v>
+        <v>0.8357107679145248</v>
       </c>
       <c r="W48">
-        <v>0.4179917693622398</v>
+        <v>0.6284549410371633</v>
       </c>
     </row>
     <row r="49">
@@ -3721,10 +3721,10 @@
         </is>
       </c>
       <c r="B49">
-        <v>433.2290416666667</v>
+        <v>0.8097760221559134</v>
       </c>
       <c r="C49">
-        <v>0.6074170814250149</v>
+        <v>0.9256702639913987</v>
       </c>
       <c r="D49">
         <v>922.4330881276862</v>
@@ -3745,10 +3745,10 @@
         <v>0.7706070205198943</v>
       </c>
       <c r="J49">
-        <v>0.8097760221559134</v>
+        <v>433.2290416666667</v>
       </c>
       <c r="K49">
-        <v>0.07432973600860122</v>
+        <v>0.6074170814250149</v>
       </c>
       <c r="L49">
         <v>22.44358842277778</v>
@@ -3771,10 +3771,10 @@
         <v>12.379006285</v>
       </c>
       <c r="R49">
-        <v>0.4329325961945533</v>
+        <v>0.5670674038054467</v>
       </c>
       <c r="W49">
-        <v>0.606320754357994</v>
+        <v>0.7471029451570927</v>
       </c>
     </row>
     <row r="50">
@@ -3784,10 +3784,10 @@
         </is>
       </c>
       <c r="B50">
-        <v>315.6002083333333</v>
+        <v>1.167208942651994</v>
       </c>
       <c r="C50">
-        <v>0.4424933210974757</v>
+        <v>0.8928613218958749</v>
       </c>
       <c r="D50">
         <v>874.7313058615135</v>
@@ -3808,10 +3808,10 @@
         <v>0.7024146438428492</v>
       </c>
       <c r="J50">
-        <v>1.167208942651994</v>
+        <v>315.6002083333333</v>
       </c>
       <c r="K50">
-        <v>0.1071386781041251</v>
+        <v>0.4424933210974757</v>
       </c>
       <c r="L50">
         <v>21.90207657555555</v>
@@ -3834,7 +3834,7 @@
         <v>3.746202177</v>
       </c>
       <c r="R50">
-        <v>0.1310164157783443</v>
+        <v>0.8689835842216557</v>
       </c>
       <c r="S50">
         <v>0</v>
@@ -3843,7 +3843,7 @@
         <v>0</v>
       </c>
       <c r="W50">
-        <v>0.4492060625342239</v>
+        <v>0.6396672890636066</v>
       </c>
     </row>
     <row r="51">
@@ -3853,10 +3853,10 @@
         </is>
       </c>
       <c r="B51">
-        <v>137.2265833333333</v>
+        <v>8.03801840660449</v>
       </c>
       <c r="C51">
-        <v>0.1924011613385643</v>
+        <v>0.2621863702452848</v>
       </c>
       <c r="D51">
         <v>771.2549657006074</v>
@@ -3877,10 +3877,10 @@
         <v>0.3495389626757058</v>
       </c>
       <c r="J51">
-        <v>8.03801840660449</v>
+        <v>137.2265833333333</v>
       </c>
       <c r="K51">
-        <v>0.7378136297547152</v>
+        <v>0.1924011613385643</v>
       </c>
       <c r="L51">
         <v>23.97247089055556</v>
@@ -3903,7 +3903,7 @@
         <v>12.95935475</v>
       </c>
       <c r="R51">
-        <v>0.453229198511851</v>
+        <v>0.546770801488149</v>
       </c>
       <c r="S51">
         <v>0.6666666666666666</v>
@@ -3912,7 +3912,7 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="W51">
-        <v>0.4825433598131469</v>
+        <v>0.4347826527465053</v>
       </c>
     </row>
     <row r="52">
@@ -3922,10 +3922,10 @@
         </is>
       </c>
       <c r="B52">
-        <v>359.9379166666667</v>
+        <v>1.145410111775375</v>
       </c>
       <c r="C52">
-        <v>0.5046578548722646</v>
+        <v>0.8948622472135219</v>
       </c>
       <c r="D52">
         <v>870.8383767477686</v>
@@ -3946,10 +3946,10 @@
         <v>0.813914118778497</v>
       </c>
       <c r="J52">
-        <v>1.145410111775375</v>
+        <v>359.9379166666667</v>
       </c>
       <c r="K52">
-        <v>0.1051377527864781</v>
+        <v>0.5046578548722646</v>
       </c>
       <c r="L52">
         <v>20.57208616027778</v>
@@ -3972,10 +3972,10 @@
         <v>6.039216124</v>
       </c>
       <c r="R52">
-        <v>0.2112102906605259</v>
+        <v>0.7887897093394741</v>
       </c>
       <c r="W52">
-        <v>0.5510318786865512</v>
+        <v>0.7463610091302644</v>
       </c>
     </row>
     <row r="53">
@@ -3985,10 +3985,10 @@
         </is>
       </c>
       <c r="B53">
-        <v>548.5222083333333</v>
+        <v>1.626887657587317</v>
       </c>
       <c r="C53">
-        <v>0.7690660755356117</v>
+        <v>0.850667188462597</v>
       </c>
       <c r="D53">
         <v>941.7955308036528</v>
@@ -4009,10 +4009,10 @@
         <v>0.3110087991551077</v>
       </c>
       <c r="J53">
-        <v>1.626887657587317</v>
+        <v>548.5222083333333</v>
       </c>
       <c r="K53">
-        <v>0.149332811537403</v>
+        <v>0.7690660755356117</v>
       </c>
       <c r="L53">
         <v>17.95481773666667</v>
@@ -4035,7 +4035,7 @@
         <v>1.8869790155</v>
       </c>
       <c r="R53">
-        <v>0.06599356243440643</v>
+        <v>0.9340064375655935</v>
       </c>
       <c r="S53">
         <v>3.666666666666667</v>
@@ -4050,7 +4050,7 @@
         <v>0.2492040311006671</v>
       </c>
       <c r="W53">
-        <v>0.4601312466705123</v>
+        <v>0.6345031635656657</v>
       </c>
     </row>
     <row r="54">
@@ -4060,10 +4060,10 @@
         </is>
       </c>
       <c r="B54">
-        <v>65.56358333333333</v>
+        <v>3.404752088070881</v>
       </c>
       <c r="C54">
-        <v>0.09192467864779168</v>
+        <v>0.6874761453083433</v>
       </c>
       <c r="D54">
         <v>803.6205597323058</v>
@@ -4084,10 +4084,10 @@
         <v>0.2704490463733044</v>
       </c>
       <c r="J54">
-        <v>3.404752088070881</v>
+        <v>65.56358333333333</v>
       </c>
       <c r="K54">
-        <v>0.3125238546916566</v>
+        <v>0.09192467864779168</v>
       </c>
       <c r="L54">
         <v>18.64826876722222</v>
@@ -4113,7 +4113,7 @@
         <v>0.125</v>
       </c>
       <c r="W54">
-        <v>0.3800142014784028</v>
+        <v>0.4335788144236438</v>
       </c>
     </row>
     <row r="55">
@@ -4123,10 +4123,10 @@
         </is>
       </c>
       <c r="B55">
-        <v>144.3691666666667</v>
+        <v>1.702722532239643</v>
       </c>
       <c r="C55">
-        <v>0.2024155572005722</v>
+        <v>0.8437062683329226</v>
       </c>
       <c r="D55">
         <v>838.7181694002497</v>
@@ -4147,10 +4147,10 @@
         <v>0.358601156247743</v>
       </c>
       <c r="J55">
-        <v>1.702722532239643</v>
+        <v>144.3691666666667</v>
       </c>
       <c r="K55">
-        <v>0.1562937316670774</v>
+        <v>0.2024155572005722</v>
       </c>
       <c r="L55">
         <v>19.96731887527778</v>
@@ -4173,7 +4173,7 @@
         <v>1.4268861685</v>
       </c>
       <c r="R55">
-        <v>0.04990267547980357</v>
+        <v>0.9500973245201965</v>
       </c>
       <c r="S55">
         <v>0.3333333333333333</v>
@@ -4182,7 +4182,7 @@
         <v>0.04166666666666666</v>
       </c>
       <c r="W55">
-        <v>0.3538823364394203</v>
+        <v>0.5523332346527</v>
       </c>
     </row>
     <row r="56">
@@ -4192,10 +4192,10 @@
         </is>
       </c>
       <c r="B56">
-        <v>485.0668333333334</v>
+        <v>3.520144908087444</v>
       </c>
       <c r="C56">
-        <v>0.6800972507888947</v>
+        <v>0.6768841820809268</v>
       </c>
       <c r="D56">
         <v>917.4690102689739</v>
@@ -4216,10 +4216,10 @@
         <v>0.4603061307126995</v>
       </c>
       <c r="J56">
-        <v>3.520144908087444</v>
+        <v>485.0668333333334</v>
       </c>
       <c r="K56">
-        <v>0.3231158179190732</v>
+        <v>0.6800972507888947</v>
       </c>
       <c r="L56">
         <v>19.90159328638889</v>
@@ -4242,7 +4242,7 @@
         <v>4.5886640015</v>
       </c>
       <c r="R56">
-        <v>0.1604799426946799</v>
+        <v>0.8395200573053201</v>
       </c>
       <c r="S56">
         <v>8</v>
@@ -4257,7 +4257,7 @@
         <v>0.6193383266212503</v>
       </c>
       <c r="W56">
-        <v>0.6003992957894583</v>
+        <v>0.7151557934308465</v>
       </c>
     </row>
     <row r="57">
@@ -4267,10 +4267,10 @@
         </is>
       </c>
       <c r="B57">
-        <v>239.5789583333333</v>
+        <v>7.967395770673756</v>
       </c>
       <c r="C57">
-        <v>0.3359062704610818</v>
+        <v>0.2686688564406494</v>
       </c>
       <c r="D57">
         <v>863.5299298005199</v>
@@ -4291,10 +4291,10 @@
         <v>0.434689399352878</v>
       </c>
       <c r="J57">
-        <v>7.967395770673756</v>
+        <v>239.5789583333333</v>
       </c>
       <c r="K57">
-        <v>0.7313311435593506</v>
+        <v>0.3359062704610818</v>
       </c>
       <c r="L57">
         <v>20.79732140694444</v>
@@ -4317,7 +4317,7 @@
         <v>7.5261303</v>
       </c>
       <c r="R57">
-        <v>0.2632123334508423</v>
+        <v>0.7367876665491577</v>
       </c>
       <c r="S57">
         <v>3.333333333333333</v>
@@ -4326,7 +4326,7 @@
         <v>0.4166666666666667</v>
       </c>
       <c r="W57">
-        <v>0.5416239726013282</v>
+        <v>0.54298810334878</v>
       </c>
     </row>
     <row r="58">
@@ -4336,10 +4336,10 @@
         </is>
       </c>
       <c r="B58">
-        <v>560.2451333333333</v>
+        <v>1.70503530389312</v>
       </c>
       <c r="C58">
-        <v>0.7855024272212476</v>
+        <v>0.8434939778948908</v>
       </c>
       <c r="D58">
         <v>1111.033140487697</v>
@@ -4360,10 +4360,10 @@
         <v>0.5567048875286876</v>
       </c>
       <c r="J58">
-        <v>1.70503530389312</v>
+        <v>560.2451333333333</v>
       </c>
       <c r="K58">
-        <v>0.1565060221051092</v>
+        <v>0.7855024272212476</v>
       </c>
       <c r="L58">
         <v>21.96775750277778</v>
@@ -4386,7 +4386,7 @@
         <v>12.729408163</v>
       </c>
       <c r="R58">
-        <v>0.4451872466294438</v>
+        <v>0.5548127533705562</v>
       </c>
       <c r="S58">
         <v>5.333333333333333</v>
@@ -4401,7 +4401,7 @@
         <v>0.7097194973918178</v>
       </c>
       <c r="W58">
-        <v>0.6538995365993346</v>
+        <v>0.7424121435472117</v>
       </c>
     </row>
     <row r="59">
@@ -4411,10 +4411,10 @@
         </is>
       </c>
       <c r="B59">
-        <v>355.4359583333333</v>
+        <v>1.189745895568634</v>
       </c>
       <c r="C59">
-        <v>0.4983457979034836</v>
+        <v>0.8907926439961857</v>
       </c>
       <c r="D59">
         <v>1050.074936152694</v>
@@ -4435,10 +4435,10 @@
         <v>0.3567616466952556</v>
       </c>
       <c r="J59">
-        <v>1.189745895568634</v>
+        <v>355.4359583333333</v>
       </c>
       <c r="K59">
-        <v>0.1092073560038142</v>
+        <v>0.4983457979034836</v>
       </c>
       <c r="L59">
         <v>22.57137774055555</v>
@@ -4461,7 +4461,7 @@
         <v>23.116575517</v>
       </c>
       <c r="R59">
-        <v>0.8084590009320168</v>
+        <v>0.1915409990679832</v>
       </c>
       <c r="S59">
         <v>4.333333333333333</v>
@@ -4470,7 +4470,7 @@
         <v>0.5416666666666666</v>
       </c>
       <c r="W59">
-        <v>0.601205727795501</v>
+        <v>0.6217891385615432</v>
       </c>
     </row>
     <row r="60">
@@ -4480,10 +4480,10 @@
         </is>
       </c>
       <c r="B60">
-        <v>568.57375</v>
+        <v>1.938789752776512</v>
       </c>
       <c r="C60">
-        <v>0.79717972385056</v>
+        <v>0.8220375430277773</v>
       </c>
       <c r="D60">
         <v>961.8098517393934</v>
@@ -4504,10 +4504,10 @@
         <v>0.408391413738524</v>
       </c>
       <c r="J60">
-        <v>1.938789752776512</v>
+        <v>568.57375</v>
       </c>
       <c r="K60">
-        <v>0.1779624569722227</v>
+        <v>0.79717972385056</v>
       </c>
       <c r="L60">
         <v>25.97261220583333</v>
@@ -4530,7 +4530,7 @@
         <v>28.59338011</v>
       </c>
       <c r="R60">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S60">
         <v>2.333333333333333</v>
@@ -4539,7 +4539,7 @@
         <v>0.2916666666666667</v>
       </c>
       <c r="W60">
-        <v>0.640209489531952</v>
+        <v>0.5957188752888963</v>
       </c>
     </row>
     <row r="61">
@@ -4549,10 +4549,10 @@
         </is>
       </c>
       <c r="B61">
-        <v>313.8654273333333</v>
+        <v>0.7219950451524363</v>
       </c>
       <c r="C61">
-        <v>0.440061038146458</v>
+        <v>0.9337277226821048</v>
       </c>
       <c r="D61">
         <v>940.1657715297354</v>
@@ -4573,10 +4573,10 @@
         <v>0.6060231595046155</v>
       </c>
       <c r="J61">
-        <v>0.7219950451524363</v>
+        <v>313.8654273333333</v>
       </c>
       <c r="K61">
-        <v>0.06627227731789516</v>
+        <v>0.440061038146458</v>
       </c>
       <c r="L61">
         <v>20.31620173861111</v>
@@ -4599,7 +4599,7 @@
         <v>3.8597674015</v>
       </c>
       <c r="R61">
-        <v>0.1349881471393485</v>
+        <v>0.8650118528606515</v>
       </c>
       <c r="S61">
         <v>5.333333333333333</v>
@@ -4608,7 +4608,7 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="W61">
-        <v>0.5264661644781429</v>
+        <v>0.7261510583638319</v>
       </c>
     </row>
     <row r="62">
@@ -4618,10 +4618,10 @@
         </is>
       </c>
       <c r="B62">
-        <v>4.230416666666667</v>
+        <v>1.292398706065661</v>
       </c>
       <c r="C62">
-        <v>0.005931336770482527</v>
+        <v>0.8813700924559824</v>
       </c>
       <c r="D62">
         <v>666.26620934</v>
@@ -4636,10 +4636,10 @@
         <v>0.6435571275651567</v>
       </c>
       <c r="J62">
-        <v>1.292398706065661</v>
+        <v>4.230416666666667</v>
       </c>
       <c r="K62">
-        <v>0.1186299075440176</v>
+        <v>0.005931336770482527</v>
       </c>
       <c r="L62">
         <v>18.13950867447222</v>
@@ -4665,7 +4665,7 @@
         <v>0.04166666666666666</v>
       </c>
       <c r="W62">
-        <v>0.3366837056205102</v>
+        <v>0.4638070697725044</v>
       </c>
     </row>
     <row r="63">
@@ -4675,10 +4675,10 @@
         </is>
       </c>
       <c r="B63">
-        <v>291.6330833333333</v>
+        <v>4.543539835776487</v>
       </c>
       <c r="C63">
-        <v>0.4088897541213501</v>
+        <v>0.5829462625496148</v>
       </c>
       <c r="D63">
         <v>931.0850222829723</v>
@@ -4699,10 +4699,10 @@
         <v>0.4443697834198685</v>
       </c>
       <c r="J63">
-        <v>4.543539835776487</v>
+        <v>291.6330833333333</v>
       </c>
       <c r="K63">
-        <v>0.4170537374503852</v>
+        <v>0.4088897541213501</v>
       </c>
       <c r="L63">
         <v>15.80551888080556</v>
@@ -4725,7 +4725,7 @@
         <v>23.557545837</v>
       </c>
       <c r="R63">
-        <v>0.8238811132637373</v>
+        <v>0.1761188867362627</v>
       </c>
       <c r="S63">
         <v>0.3333333333333333</v>
@@ -4734,7 +4734,7 @@
         <v>0.04166666666666666</v>
       </c>
       <c r="W63">
-        <v>0.5615865930568087</v>
+        <v>0.5013528803782781</v>
       </c>
     </row>
     <row r="64">
@@ -4744,10 +4744,10 @@
         </is>
       </c>
       <c r="B64">
-        <v>153.0529166666667</v>
+        <v>1.719547623997414</v>
       </c>
       <c r="C64">
-        <v>0.2145907753266065</v>
+        <v>0.8421618849547311</v>
       </c>
       <c r="D64">
         <v>935.1347230762776</v>
@@ -4768,10 +4768,10 @@
         <v>0.5764735027841117</v>
       </c>
       <c r="J64">
-        <v>1.719547623997414</v>
+        <v>153.0529166666667</v>
       </c>
       <c r="K64">
-        <v>0.1578381150452689</v>
+        <v>0.2145907753266065</v>
       </c>
       <c r="L64">
         <v>18.19182849305556</v>
@@ -4794,7 +4794,7 @@
         <v>6.554619498</v>
       </c>
       <c r="R64">
-        <v>0.2292355598667974</v>
+        <v>0.7707644401332026</v>
       </c>
       <c r="S64">
         <v>2</v>
@@ -4809,7 +4809,7 @@
         <v>0.2059257769284924</v>
       </c>
       <c r="W64">
-        <v>0.4119623682497291</v>
+        <v>0.54816821826927</v>
       </c>
     </row>
     <row r="65">
@@ -4819,10 +4819,10 @@
         </is>
       </c>
       <c r="B65">
-        <v>184.1729583333333</v>
+        <v>6.244953306955439</v>
       </c>
       <c r="C65">
-        <v>0.2582232262127954</v>
+        <v>0.4267726902357388</v>
       </c>
       <c r="D65">
         <v>899.7614602872376</v>
@@ -4843,10 +4843,10 @@
         <v>0.2088632390783643</v>
       </c>
       <c r="J65">
-        <v>6.244953306955439</v>
+        <v>184.1729583333333</v>
       </c>
       <c r="K65">
-        <v>0.5732273097642612</v>
+        <v>0.2582232262127954</v>
       </c>
       <c r="L65">
         <v>17.647548625</v>
@@ -4869,7 +4869,7 @@
         <v>3.2345367155</v>
       </c>
       <c r="R65">
-        <v>0.1131218730718997</v>
+        <v>0.8868781269281003</v>
       </c>
       <c r="S65">
         <v>3.333333333333333</v>
@@ -4884,7 +4884,7 @@
         <v>0.4414446116448663</v>
       </c>
       <c r="W65">
-        <v>0.4392484941683347</v>
+        <v>0.508948675760299</v>
       </c>
     </row>
     <row r="66">
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="B66">
-        <v>166.536875</v>
+        <v>1.565465264178534</v>
       </c>
       <c r="C66">
-        <v>0.2334962175503798</v>
+        <v>0.8563051799098323</v>
       </c>
       <c r="D66">
         <v>825.6953914759764</v>
@@ -4918,10 +4918,10 @@
         <v>0.4681052114367623</v>
       </c>
       <c r="J66">
-        <v>1.565465264178534</v>
+        <v>166.536875</v>
       </c>
       <c r="K66">
-        <v>0.1436948200901677</v>
+        <v>0.2334962175503798</v>
       </c>
       <c r="L66">
         <v>15.04469039813889</v>
@@ -4944,7 +4944,7 @@
         <v>14.8992245665</v>
       </c>
       <c r="R66">
-        <v>0.5210725178059405</v>
+        <v>0.4789274821940595</v>
       </c>
       <c r="S66">
         <v>0</v>
@@ -4953,7 +4953,7 @@
         <v>0</v>
       </c>
       <c r="W66">
-        <v>0.4147416520014882</v>
+        <v>0.4985498175274612</v>
       </c>
     </row>
     <row r="67">
@@ -4963,10 +4963,10 @@
         </is>
       </c>
       <c r="B67">
-        <v>113.1500833333333</v>
+        <v>6.692488984265891</v>
       </c>
       <c r="C67">
-        <v>0.1586442430473347</v>
+        <v>0.3856931721483144</v>
       </c>
       <c r="D67">
         <v>844.2071193141553</v>
@@ -4987,10 +4987,10 @@
         <v>0.2229424541143435</v>
       </c>
       <c r="J67">
-        <v>6.692488984265891</v>
+        <v>113.1500833333333</v>
       </c>
       <c r="K67">
-        <v>0.6143068278516856</v>
+        <v>0.1586442430473347</v>
       </c>
       <c r="L67">
         <v>14.34343415708333</v>
@@ -5013,7 +5013,7 @@
         <v>11.85427911</v>
       </c>
       <c r="R67">
-        <v>0.4145812444837254</v>
+        <v>0.5854187555162746</v>
       </c>
       <c r="S67">
         <v>4.333333333333333</v>
@@ -5022,7 +5022,7 @@
         <v>0.5416666666666666</v>
       </c>
       <c r="W67">
-        <v>0.4813979856424639</v>
+        <v>0.4741759675586112</v>
       </c>
     </row>
     <row r="68">
@@ -5032,10 +5032,10 @@
         </is>
       </c>
       <c r="B68">
-        <v>310.4554166666667</v>
+        <v>0.9113912774758922</v>
       </c>
       <c r="C68">
-        <v>0.4352799673327231</v>
+        <v>0.9163429501469215</v>
       </c>
       <c r="D68">
         <v>954.6694808040943</v>
@@ -5056,10 +5056,10 @@
         <v>1</v>
       </c>
       <c r="J68">
-        <v>0.9113912774758922</v>
+        <v>310.4554166666667</v>
       </c>
       <c r="K68">
-        <v>0.08365704985307856</v>
+        <v>0.4352799673327231</v>
       </c>
       <c r="L68">
         <v>16.67464521666666</v>
@@ -5082,7 +5082,7 @@
         <v>8.946038475</v>
       </c>
       <c r="R68">
-        <v>0.3128709666567644</v>
+        <v>0.6871290333432356</v>
       </c>
       <c r="S68">
         <v>3</v>
@@ -5091,7 +5091,7 @@
         <v>0.375</v>
       </c>
       <c r="W68">
-        <v>0.5569571556953912</v>
+        <v>0.7078251515679305</v>
       </c>
     </row>
     <row r="69">
@@ -5101,10 +5101,10 @@
         </is>
       </c>
       <c r="B69">
-        <v>410.664875</v>
+        <v>4.410626045842244</v>
       </c>
       <c r="C69">
-        <v>0.5757805590701729</v>
+        <v>0.5951464841509069</v>
       </c>
       <c r="D69">
         <v>817.2379250340023</v>
@@ -5125,10 +5125,10 @@
         <v>0.2319996941092551</v>
       </c>
       <c r="J69">
-        <v>4.410626045842244</v>
+        <v>410.664875</v>
       </c>
       <c r="K69">
-        <v>0.4048535158490932</v>
+        <v>0.5757805590701729</v>
       </c>
       <c r="L69">
         <v>16.21837887297222</v>
@@ -5151,7 +5151,7 @@
         <v>3.395191248</v>
       </c>
       <c r="R69">
-        <v>0.1187404649236484</v>
+        <v>0.8812595350763516</v>
       </c>
       <c r="S69">
         <v>3</v>
@@ -5166,7 +5166,7 @@
         <v>0.6090817578565169</v>
       </c>
       <c r="W69">
-        <v>0.46604203790316</v>
+        <v>0.5719100421758841</v>
       </c>
     </row>
     <row r="70">
@@ -5176,10 +5176,10 @@
         </is>
       </c>
       <c r="B70">
-        <v>54.90058333333334</v>
+        <v>1.557799648651538</v>
       </c>
       <c r="C70">
-        <v>0.07697441512363405</v>
+        <v>0.8570088104976437</v>
       </c>
       <c r="D70">
         <v>857.5264607957037</v>
@@ -5200,10 +5200,10 @@
         <v>0.4907723512279208</v>
       </c>
       <c r="J70">
-        <v>1.557799648651538</v>
+        <v>54.90058333333334</v>
       </c>
       <c r="K70">
-        <v>0.1429911895023564</v>
+        <v>0.07697441512363405</v>
       </c>
       <c r="L70">
         <v>14.81665724805556</v>
@@ -5226,10 +5226,10 @@
         <v>11.22132051</v>
       </c>
       <c r="R70">
-        <v>0.3924447010752518</v>
+        <v>0.6075552989247481</v>
       </c>
       <c r="W70">
-        <v>0.4297091807310861</v>
+        <v>0.5624417834231981</v>
       </c>
     </row>
     <row r="71">
@@ -5239,10 +5239,10 @@
         </is>
       </c>
       <c r="B71">
-        <v>122.4278333333333</v>
+        <v>4.056336430908098</v>
       </c>
       <c r="C71">
-        <v>0.1716522902583685</v>
+        <v>0.6276669006958829</v>
       </c>
       <c r="D71">
         <v>740.1297030877272</v>
@@ -5263,10 +5263,10 @@
         <v>0.2695095002393326</v>
       </c>
       <c r="J71">
-        <v>4.056336430908098</v>
+        <v>122.4278333333333</v>
       </c>
       <c r="K71">
-        <v>0.3723330993041171</v>
+        <v>0.1716522902583685</v>
       </c>
       <c r="L71">
         <v>14.4999541025</v>
@@ -5289,7 +5289,7 @@
         <v>1.424821897</v>
       </c>
       <c r="R71">
-        <v>0.04983048144425902</v>
+        <v>0.9501695185557409</v>
       </c>
       <c r="S71">
         <v>1.333333333333333</v>
@@ -5298,7 +5298,7 @@
         <v>0.1666666666666667</v>
       </c>
       <c r="W71">
-        <v>0.3378503059471598</v>
+        <v>0.4823094107600657</v>
       </c>
     </row>
     <row r="72">
@@ -5308,10 +5308,10 @@
         </is>
       </c>
       <c r="B72">
-        <v>96.73041666666667</v>
+        <v>1.035234654258313</v>
       </c>
       <c r="C72">
-        <v>0.1356227346870708</v>
+        <v>0.9049753061925556</v>
       </c>
       <c r="D72">
         <v>899.4694821174611</v>
@@ -5332,10 +5332,10 @@
         <v>0.3104413817540195</v>
       </c>
       <c r="J72">
-        <v>1.035234654258313</v>
+        <v>96.73041666666667</v>
       </c>
       <c r="K72">
-        <v>0.09502469380744438</v>
+        <v>0.1356227346870708</v>
       </c>
       <c r="L72">
         <v>16.62617626361111</v>
@@ -5358,7 +5358,7 @@
         <v>2.512306821</v>
       </c>
       <c r="R72">
-        <v>0.08786323307475523</v>
+        <v>0.9121367669252448</v>
       </c>
       <c r="S72">
         <v>1</v>
@@ -5367,7 +5367,7 @@
         <v>0.125</v>
       </c>
       <c r="W72">
-        <v>0.3515146467284684</v>
+        <v>0.5557926650079186</v>
       </c>
     </row>
     <row r="73">
@@ -5377,10 +5377,10 @@
         </is>
       </c>
       <c r="B73">
-        <v>80.89975</v>
+        <v>1.647421926406839</v>
       </c>
       <c r="C73">
-        <v>0.1134270450659731</v>
+        <v>0.848782337912909</v>
       </c>
       <c r="D73">
         <v>892.7724353911411</v>
@@ -5401,10 +5401,10 @@
         <v>0.1827762168120912</v>
       </c>
       <c r="J73">
-        <v>1.647421926406839</v>
+        <v>80.89975</v>
       </c>
       <c r="K73">
-        <v>0.151217662087091</v>
+        <v>0.1134270450659731</v>
       </c>
       <c r="L73">
         <v>17.35934430347222</v>
@@ -5427,7 +5427,7 @@
         <v>1.71014179</v>
       </c>
       <c r="R73">
-        <v>0.0598090111564638</v>
+        <v>0.9401909888435362</v>
       </c>
       <c r="S73">
         <v>3</v>
@@ -5436,7 +5436,7 @@
         <v>0.375</v>
       </c>
       <c r="W73">
-        <v>0.3657983878556848</v>
+        <v>0.5630417195447961</v>
       </c>
     </row>
     <row r="74">
@@ -5446,10 +5446,10 @@
         </is>
       </c>
       <c r="B74">
-        <v>260.4987083333334</v>
+        <v>2.668287177350798</v>
       </c>
       <c r="C74">
-        <v>0.3652372069104391</v>
+        <v>0.755076618643774</v>
       </c>
       <c r="D74">
         <v>984.282715387383</v>
@@ -5470,10 +5470,10 @@
         <v>0.4102881218487347</v>
       </c>
       <c r="J74">
-        <v>2.668287177350798</v>
+        <v>260.4987083333334</v>
       </c>
       <c r="K74">
-        <v>0.244923381356226</v>
+        <v>0.3652372069104391</v>
       </c>
       <c r="L74">
         <v>16.73865680055556</v>
@@ -5496,7 +5496,7 @@
         <v>1.0787394635</v>
       </c>
       <c r="R74">
-        <v>0.03772689550343616</v>
+        <v>0.9622731044965638</v>
       </c>
       <c r="S74">
         <v>1.333333333333333</v>
@@ -5505,7 +5505,7 @@
         <v>0.1666666666666667</v>
       </c>
       <c r="W74">
-        <v>0.4221310198387213</v>
+        <v>0.6014684506238057</v>
       </c>
     </row>
     <row r="75">
@@ -5515,10 +5515,10 @@
         </is>
       </c>
       <c r="B75">
-        <v>128.8154583333333</v>
+        <v>3.095392060730346</v>
       </c>
       <c r="C75">
-        <v>0.1806081823190923</v>
+        <v>0.7158724530955456</v>
       </c>
       <c r="D75">
         <v>706.9460658690535</v>
@@ -5539,10 +5539,10 @@
         <v>0.3177017403593446</v>
       </c>
       <c r="J75">
-        <v>3.095392060730346</v>
+        <v>128.8154583333333</v>
       </c>
       <c r="K75">
-        <v>0.2841275469044544</v>
+        <v>0.1806081823190923</v>
       </c>
       <c r="L75">
         <v>12.99774696763889</v>
@@ -5565,7 +5565,7 @@
         <v>1.2469799705</v>
       </c>
       <c r="R75">
-        <v>0.04361079262762265</v>
+        <v>0.9563892073723773</v>
       </c>
       <c r="S75">
         <v>5</v>
@@ -5574,7 +5574,7 @@
         <v>0.625</v>
       </c>
       <c r="W75">
-        <v>0.3847584218386811</v>
+        <v>0.5528238369556618</v>
       </c>
     </row>
     <row r="76">
@@ -5584,10 +5584,10 @@
         </is>
       </c>
       <c r="B76">
-        <v>693.9295833333333</v>
+        <v>2.93340592717423</v>
       </c>
       <c r="C76">
-        <v>0.972937272628926</v>
+        <v>0.730741239296728</v>
       </c>
       <c r="D76">
         <v>976.9563461971909</v>
@@ -5608,10 +5608,10 @@
         <v>0.4585532956039184</v>
       </c>
       <c r="J76">
-        <v>2.93340592717423</v>
+        <v>693.9295833333333</v>
       </c>
       <c r="K76">
-        <v>0.269258760703272</v>
+        <v>0.972937272628926</v>
       </c>
       <c r="L76">
         <v>17.45057982055556</v>
@@ -5634,7 +5634,7 @@
         <v>4.6450910745</v>
       </c>
       <c r="R76">
-        <v>0.1624533740547682</v>
+        <v>0.8375466259452318</v>
       </c>
       <c r="S76">
         <v>5</v>
@@ -5643,7 +5643,7 @@
         <v>0.625</v>
       </c>
       <c r="W76">
-        <v>0.5921918868649685</v>
+        <v>0.7342638531754585</v>
       </c>
     </row>
     <row r="77">
@@ -5653,10 +5653,10 @@
         </is>
       </c>
       <c r="B77">
-        <v>585.0162666666666</v>
+        <v>3.144980069906421</v>
       </c>
       <c r="C77">
-        <v>0.8202332694912822</v>
+        <v>0.7113207455487642</v>
       </c>
       <c r="D77">
         <v>990.9597563929921</v>
@@ -5677,10 +5677,10 @@
         <v>0.4605521686705908</v>
       </c>
       <c r="J77">
-        <v>3.144980069906421</v>
+        <v>585.0162666666666</v>
       </c>
       <c r="K77">
-        <v>0.2886792544512358</v>
+        <v>0.8202332694912822</v>
       </c>
       <c r="L77">
         <v>14.72761090888889</v>
@@ -5703,7 +5703,7 @@
         <v>5.3957587795</v>
       </c>
       <c r="R77">
-        <v>0.1887065732957166</v>
+        <v>0.8112934267042834</v>
       </c>
       <c r="S77">
         <v>4</v>
@@ -5718,7 +5718,7 @@
         <v>0.3177213942185137</v>
       </c>
       <c r="W77">
-        <v>0.5215506168239931</v>
+        <v>0.6376870995468926</v>
       </c>
     </row>
     <row r="78">
@@ -5728,10 +5728,10 @@
         </is>
       </c>
       <c r="B78">
-        <v>538.9304166666667</v>
+        <v>2.98039018954707</v>
       </c>
       <c r="C78">
-        <v>0.7556177201866963</v>
+        <v>0.7264285309388857</v>
       </c>
       <c r="D78">
         <v>748.9641781174147</v>
@@ -5752,10 +5752,10 @@
         <v>0.1871505322215688</v>
       </c>
       <c r="J78">
-        <v>2.98039018954707</v>
+        <v>538.9304166666667</v>
       </c>
       <c r="K78">
-        <v>0.2735714690611143</v>
+        <v>0.7556177201866963</v>
       </c>
       <c r="L78">
         <v>13.41004905030556</v>
@@ -5778,7 +5778,7 @@
         <v>6.434649477000001</v>
       </c>
       <c r="R78">
-        <v>0.225039832725114</v>
+        <v>0.774960167274886</v>
       </c>
       <c r="S78">
         <v>1.666666666666667</v>
@@ -5787,7 +5787,7 @@
         <v>0.2083333333333333</v>
       </c>
       <c r="W78">
-        <v>0.419695242054367</v>
+        <v>0.5450424166078099</v>
       </c>
     </row>
     <row r="79">
@@ -5797,10 +5797,10 @@
         </is>
       </c>
       <c r="B79">
-        <v>414.1980833333333</v>
+        <v>0.9985906350334441</v>
       </c>
       <c r="C79">
-        <v>0.5807343615337464</v>
+        <v>0.9083388785888178</v>
       </c>
       <c r="D79">
         <v>729.3911372457928</v>
@@ -5821,10 +5821,10 @@
         <v>0.3456472831241457</v>
       </c>
       <c r="J79">
-        <v>0.9985906350334441</v>
+        <v>414.1980833333333</v>
       </c>
       <c r="K79">
-        <v>0.09166112141118221</v>
+        <v>0.5807343615337464</v>
       </c>
       <c r="L79">
         <v>15.65610951194444</v>
@@ -5847,7 +5847,7 @@
         <v>2.6573583345</v>
       </c>
       <c r="R79">
-        <v>0.0929361385144752</v>
+        <v>0.9070638614855248</v>
       </c>
       <c r="S79">
         <v>6</v>
@@ -5856,7 +5856,7 @@
         <v>0.75</v>
       </c>
       <c r="W79">
-        <v>0.4564067199321807</v>
+        <v>0.6602574049507663</v>
       </c>
     </row>
   </sheetData>

--- a/Data Analysis/1_Data/ecological_multifunctionality.xlsx
+++ b/Data Analysis/1_Data/ecological_multifunctionality.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W79"/>
+  <dimension ref="A1:W92"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -481,7 +481,7 @@
         <v>2.095065631874623</v>
       </c>
       <c r="C2">
-        <v>0.8076929038682368</v>
+        <v>0.8650197313925341</v>
       </c>
       <c r="D2">
         <v>828.3773512579434</v>
@@ -490,28 +490,28 @@
         <v>2.866126361212376</v>
       </c>
       <c r="F2">
-        <v>0.714235008308102</v>
+        <v>0.6976528103196753</v>
       </c>
       <c r="G2">
-        <v>0.7252486892235276</v>
+        <v>0.6159109451427114</v>
       </c>
       <c r="H2">
         <v>152.379692735</v>
       </c>
       <c r="I2">
-        <v>0.4615269340646537</v>
+        <v>0.341094719692547</v>
       </c>
       <c r="J2">
         <v>435.4745416666667</v>
       </c>
       <c r="K2">
-        <v>0.610565427738763</v>
+        <v>0.6082417777902314</v>
       </c>
       <c r="L2">
-        <v>16.37541437</v>
+        <v>16.549191498125</v>
       </c>
       <c r="M2">
-        <v>0.5740180454932655</v>
+        <v>0.1942864793541164</v>
       </c>
       <c r="N2">
         <v>11.83333333333333</v>
@@ -525,10 +525,10 @@
         <v>16</v>
       </c>
       <c r="Q2">
-        <v>9.570568743000001</v>
+        <v>4.569769934333333</v>
       </c>
       <c r="R2">
-        <v>0.6652872550855617</v>
+        <v>0.7947096508245413</v>
       </c>
       <c r="S2">
         <v>2.666666666666667</v>
@@ -537,7 +537,7 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="W2">
-        <v>0.6114884496394305</v>
+        <v>0.5562811809812113</v>
       </c>
     </row>
     <row r="3">
@@ -550,7 +550,7 @@
         <v>2.614593071827771</v>
       </c>
       <c r="C3">
-        <v>0.7600052267768216</v>
+        <v>0.8139473727884285</v>
       </c>
       <c r="D3">
         <v>655.9329685983965</v>
@@ -559,28 +559,28 @@
         <v>2.472243181288298</v>
       </c>
       <c r="F3">
-        <v>0.5655517845399826</v>
+        <v>0.5403418864281665</v>
       </c>
       <c r="G3">
-        <v>0.6255799293903792</v>
+        <v>0.4765788354798875</v>
       </c>
       <c r="H3">
         <v>275.3171712859375</v>
       </c>
       <c r="I3">
-        <v>0.8338794210586178</v>
+        <v>0.7967257165554308</v>
       </c>
       <c r="J3">
         <v>329.558375</v>
       </c>
       <c r="K3">
-        <v>0.4620636362039917</v>
+        <v>0.4588539165409685</v>
       </c>
       <c r="L3">
-        <v>16.184261805</v>
+        <v>16.26800568854167</v>
       </c>
       <c r="M3">
-        <v>0.5673174503649161</v>
+        <v>0.1799169693057225</v>
       </c>
       <c r="N3">
         <v>5.728813559322034</v>
@@ -594,10 +594,10 @@
         <v>8</v>
       </c>
       <c r="Q3">
-        <v>7.007383158000001</v>
+        <v>3.58199777625</v>
       </c>
       <c r="R3">
-        <v>0.7549298777884151</v>
+        <v>0.8415107830527547</v>
       </c>
       <c r="S3">
         <v>2.333333333333333</v>
@@ -606,7 +606,7 @@
         <v>0.2916666666666667</v>
       </c>
       <c r="W3">
-        <v>0.6076242490987238</v>
+        <v>0.5499427683522532</v>
       </c>
     </row>
     <row r="4">
@@ -619,7 +619,7 @@
         <v>7.874606776195011</v>
       </c>
       <c r="C4">
-        <v>0.2771860034978646</v>
+        <v>0.2968595627659594</v>
       </c>
       <c r="D4">
         <v>776.4263094419364</v>
@@ -628,28 +628,28 @@
         <v>2.584558235505043</v>
       </c>
       <c r="F4">
-        <v>0.6694423148252061</v>
+        <v>0.6502609135285969</v>
       </c>
       <c r="G4">
-        <v>0.6540002903881085</v>
+        <v>0.5163091267147911</v>
       </c>
       <c r="H4">
         <v>111.1061707528571</v>
       </c>
       <c r="I4">
-        <v>0.3365178746777452</v>
+        <v>0.1881267542972417</v>
       </c>
       <c r="J4">
         <v>307.92475</v>
       </c>
       <c r="K4">
-        <v>0.4317317976282808</v>
+        <v>0.4283410961517118</v>
       </c>
       <c r="L4">
-        <v>14.46322224386111</v>
+        <v>14.43893112102083</v>
       </c>
       <c r="M4">
-        <v>0.5069887317884022</v>
+        <v>0.08644530579539533</v>
       </c>
       <c r="N4">
         <v>6.186440677966102</v>
@@ -663,10 +663,10 @@
         <v>8</v>
       </c>
       <c r="Q4">
-        <v>4.280052659</v>
+        <v>2.2009045385</v>
       </c>
       <c r="R4">
-        <v>0.8503131619089996</v>
+        <v>0.9069476621047519</v>
       </c>
       <c r="S4">
         <v>2.333333333333333</v>
@@ -675,7 +675,7 @@
         <v>0.2916666666666667</v>
       </c>
       <c r="W4">
-        <v>0.5022308551726592</v>
+        <v>0.4206196360031393</v>
       </c>
     </row>
     <row r="5">
@@ -688,7 +688,7 @@
         <v>6.762593017775271</v>
       </c>
       <c r="C5">
-        <v>0.3792582887221329</v>
+        <v>0.4061765325256969</v>
       </c>
       <c r="D5">
         <v>701.0418942996629</v>
@@ -697,28 +697,28 @@
         <v>2.261728394637732</v>
       </c>
       <c r="F5">
-        <v>0.6044451389684781</v>
+        <v>0.5814921208885685</v>
       </c>
       <c r="G5">
-        <v>0.5723109684866764</v>
+        <v>0.4021114024077352</v>
       </c>
       <c r="H5">
         <v>95.08300676656251</v>
       </c>
       <c r="I5">
-        <v>0.287986987025475</v>
+        <v>0.1287416890915327</v>
       </c>
       <c r="J5">
         <v>425.0958333333334</v>
       </c>
       <c r="K5">
-        <v>0.5960137607947789</v>
+        <v>0.5936032850157896</v>
       </c>
       <c r="L5">
-        <v>16.92879661722222</v>
+        <v>16.83161025833333</v>
       </c>
       <c r="M5">
-        <v>0.5934161131564027</v>
+        <v>0.2087189971923463</v>
       </c>
       <c r="N5">
         <v>3.35</v>
@@ -732,10 +732,10 @@
         <v>4</v>
       </c>
       <c r="Q5">
-        <v>4.303033941000001</v>
+        <v>2.788366455</v>
       </c>
       <c r="R5">
-        <v>0.8495094345458271</v>
+        <v>0.8791134266404671</v>
       </c>
       <c r="S5">
         <v>4.333333333333333</v>
@@ -744,7 +744,7 @@
         <v>0.5416666666666666</v>
       </c>
       <c r="W5">
-        <v>0.5530759197958047</v>
+        <v>0.4677030150536003</v>
       </c>
     </row>
     <row r="6">
@@ -757,7 +757,7 @@
         <v>5.452538173207431</v>
       </c>
       <c r="C6">
-        <v>0.49950886183032</v>
+        <v>0.5349620126898404</v>
       </c>
       <c r="D6">
         <v>480.0111760454392</v>
@@ -766,28 +766,28 @@
         <v>1.84865571757305</v>
       </c>
       <c r="F6">
-        <v>0.4138703041436016</v>
+        <v>0.3798587248873637</v>
       </c>
       <c r="G6">
-        <v>0.467786471015291</v>
+        <v>0.2559912061846156</v>
       </c>
       <c r="H6">
         <v>104.9201081617857</v>
       </c>
       <c r="I6">
-        <v>0.3177815558786625</v>
+        <v>0.1651999633930487</v>
       </c>
       <c r="J6">
         <v>409.3909166666667</v>
       </c>
       <c r="K6">
-        <v>0.5739943813713894</v>
+        <v>0.5714525219569752</v>
       </c>
       <c r="L6">
-        <v>16.25849923111111</v>
+        <v>16.21302675770833</v>
       </c>
       <c r="M6">
-        <v>0.5699197431237987</v>
+        <v>0.1771073669995812</v>
       </c>
       <c r="N6">
         <v>1.864406779661017</v>
@@ -801,10 +801,10 @@
         <v>2</v>
       </c>
       <c r="Q6">
-        <v>12.810452095</v>
+        <v>7.410009961</v>
       </c>
       <c r="R6">
-        <v>0.5519783934002338</v>
+        <v>0.6601376769537439</v>
       </c>
       <c r="S6">
         <v>4</v>
@@ -813,7 +813,7 @@
         <v>0.5</v>
       </c>
       <c r="W6">
-        <v>0.4868549638454121</v>
+        <v>0.4055886841331461</v>
       </c>
     </row>
     <row r="7">
@@ -826,7 +826,7 @@
         <v>1.266329559472203</v>
       </c>
       <c r="C7">
-        <v>0.8837629921359487</v>
+        <v>0.9464889717501007</v>
       </c>
       <c r="D7">
         <v>834.7057465626099</v>
@@ -835,28 +835,28 @@
         <v>3.054211065243965</v>
       </c>
       <c r="F7">
-        <v>0.7196914122840697</v>
+        <v>0.7034258352032589</v>
       </c>
       <c r="G7">
-        <v>0.7728419101323939</v>
+        <v>0.6824439679874053</v>
       </c>
       <c r="H7">
         <v>190.1838700915625</v>
       </c>
       <c r="I7">
-        <v>0.576028057915543</v>
+        <v>0.4812045968234252</v>
       </c>
       <c r="J7">
         <v>285.4118083333333</v>
       </c>
       <c r="K7">
-        <v>0.4001670962665013</v>
+        <v>0.3965880568201705</v>
       </c>
       <c r="L7">
-        <v>15.87036697694444</v>
+        <v>15.98448257208333</v>
       </c>
       <c r="M7">
-        <v>0.556314290895499</v>
+        <v>0.1654280152687566</v>
       </c>
       <c r="N7">
         <v>12.89830508474576</v>
@@ -870,10 +870,10 @@
         <v>16</v>
       </c>
       <c r="Q7">
-        <v>8.956316193999999</v>
+        <v>4.619948390499999</v>
       </c>
       <c r="R7">
-        <v>0.6867695893404469</v>
+        <v>0.7923321708127331</v>
       </c>
       <c r="S7">
         <v>2.666666666666667</v>
@@ -882,7 +882,7 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="W7">
-        <v>0.616113585287967</v>
+        <v>0.562655618499898</v>
       </c>
     </row>
     <row r="8">
@@ -895,7 +895,7 @@
         <v>5.834182375549821</v>
       </c>
       <c r="C8">
-        <v>0.4644775543660676</v>
+        <v>0.4974443224539482</v>
       </c>
       <c r="D8">
         <v>692.6924213740515</v>
@@ -904,28 +904,28 @@
         <v>2.262530900179275</v>
       </c>
       <c r="F8">
-        <v>0.5972461422125475</v>
+        <v>0.5738753851058309</v>
       </c>
       <c r="G8">
-        <v>0.5725140356298335</v>
+        <v>0.4023952804604635</v>
       </c>
       <c r="H8">
         <v>116.0377657446875</v>
       </c>
       <c r="I8">
-        <v>0.3514546676045188</v>
+        <v>0.2064042362233141</v>
       </c>
       <c r="J8">
         <v>195.5060666666667</v>
       </c>
       <c r="K8">
-        <v>0.2741130279694455</v>
+        <v>0.269781858254839</v>
       </c>
       <c r="L8">
-        <v>16.87932298833333</v>
+        <v>16.644063020625</v>
       </c>
       <c r="M8">
-        <v>0.5916818818803816</v>
+        <v>0.1991347229333008</v>
       </c>
       <c r="N8">
         <v>2</v>
@@ -939,10 +939,10 @@
         <v>2</v>
       </c>
       <c r="Q8">
-        <v>1.0562739425</v>
+        <v>0.63398203825</v>
       </c>
       <c r="R8">
-        <v>0.9630587940832295</v>
+        <v>0.9811892233043098</v>
       </c>
       <c r="S8">
         <v>1.333333333333333</v>
@@ -951,7 +951,7 @@
         <v>0.1666666666666667</v>
       </c>
       <c r="W8">
-        <v>0.4976515963015863</v>
+        <v>0.4121114619253342</v>
       </c>
     </row>
     <row r="9">
@@ -964,7 +964,7 @@
         <v>9.555711420707254</v>
       </c>
       <c r="C9">
-        <v>0.1228765882885198</v>
+        <v>0.1315978794498683</v>
       </c>
       <c r="D9">
         <v>604.6068150246119</v>
@@ -973,28 +973,28 @@
         <v>2.077015005533984</v>
       </c>
       <c r="F9">
-        <v>0.521297875776632</v>
+        <v>0.4935200386302585</v>
       </c>
       <c r="G9">
-        <v>0.525570829900162</v>
+        <v>0.3367709474237064</v>
       </c>
       <c r="H9">
         <v>98.8683452184375</v>
       </c>
       <c r="I9">
-        <v>0.2994520032539114</v>
+        <v>0.1427709139676277</v>
       </c>
       <c r="J9">
         <v>332.1990833333333</v>
       </c>
       <c r="K9">
-        <v>0.4657660919363158</v>
+        <v>0.4625784638175073</v>
       </c>
       <c r="L9">
-        <v>16.09618226416667</v>
+        <v>15.94020312770833</v>
       </c>
       <c r="M9">
-        <v>0.5642299409599805</v>
+        <v>0.1631651915443776</v>
       </c>
       <c r="N9">
         <v>1</v>
@@ -1008,10 +1008,10 @@
         <v>1</v>
       </c>
       <c r="Q9">
-        <v>3.7317630585</v>
+        <v>2.164679347</v>
       </c>
       <c r="R9">
-        <v>0.8694885653901797</v>
+        <v>0.908664029551951</v>
       </c>
       <c r="S9">
         <v>1.666666666666667</v>
@@ -1020,7 +1020,7 @@
         <v>0.2083333333333333</v>
       </c>
       <c r="W9">
-        <v>0.4471269036048793</v>
+        <v>0.3559250997148288</v>
       </c>
     </row>
     <row r="10">
@@ -1033,7 +1033,7 @@
         <v>4.444804068467144</v>
       </c>
       <c r="C10">
-        <v>0.5920092667852441</v>
+        <v>0.6340277282168674</v>
       </c>
       <c r="D10">
         <v>676.5846424714285</v>
@@ -1042,28 +1042,28 @@
         <v>3.16392122</v>
       </c>
       <c r="F10">
-        <v>0.5833578585929273</v>
+        <v>0.5591812005697393</v>
       </c>
       <c r="G10">
-        <v>0.8006031236671898</v>
+        <v>0.7212528029230316</v>
       </c>
       <c r="H10">
         <v>214.3728571428572</v>
       </c>
       <c r="I10">
-        <v>0.649291554064787</v>
+        <v>0.5708538430353383</v>
       </c>
       <c r="J10">
         <v>95.10555555555555</v>
       </c>
       <c r="K10">
-        <v>0.1333445670230676</v>
+        <v>0.1281734702697966</v>
       </c>
       <c r="L10">
-        <v>17.09475449166667</v>
+        <v>17.21739746645833</v>
       </c>
       <c r="M10">
-        <v>0.5992335424177557</v>
+        <v>0.228433979153593</v>
       </c>
       <c r="N10">
         <v>0.9523809523809523</v>
@@ -1077,128 +1077,92 @@
         <v>1</v>
       </c>
       <c r="W10">
-        <v>0.5596399854251619</v>
+        <v>0.4736538373613944</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B1A11</t>
+          <t>B1A10</t>
         </is>
       </c>
       <c r="B11">
-        <v>2.325544502250153</v>
+        <v>7.113432774102546</v>
       </c>
       <c r="C11">
-        <v>0.7865371359498885</v>
+        <v>0.3716870860215055</v>
       </c>
       <c r="D11">
-        <v>912.9959398422051</v>
+        <v>466.45181375</v>
       </c>
       <c r="E11">
-        <v>2.774944281334617</v>
+        <v>2.6041568625</v>
       </c>
       <c r="F11">
-        <v>0.7871939783097828</v>
+        <v>0.3674893117630961</v>
       </c>
       <c r="G11">
-        <v>0.7021758460973625</v>
-      </c>
-      <c r="H11">
-        <v>119.3581357134375</v>
-      </c>
-      <c r="I11">
-        <v>0.361511389364042</v>
-      </c>
-      <c r="J11">
-        <v>297.311575</v>
-      </c>
-      <c r="K11">
-        <v>0.4168513922003523</v>
+        <v>0.5232419387384689</v>
       </c>
       <c r="L11">
-        <v>19.64938485194444</v>
+        <v>15.60870769744681</v>
       </c>
       <c r="M11">
-        <v>0.6887826611900342</v>
-      </c>
-      <c r="N11">
-        <v>11.03333333333333</v>
+        <v>0.1462246961360277</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="P11">
-        <v>16</v>
-      </c>
-      <c r="Q11">
-        <v>8.72065508</v>
-      </c>
-      <c r="R11">
-        <v>0.6950113961185682</v>
-      </c>
-      <c r="S11">
-        <v>2.666666666666667</v>
-      </c>
-      <c r="T11">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="U11">
-        <v>13.57215189873418</v>
-      </c>
-      <c r="V11">
-        <v>0.8925979653646036</v>
-      </c>
       <c r="W11">
-        <v>0.629332788658663</v>
+        <v>0.3521607581647745</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>B1A12</t>
+          <t>B1A11</t>
         </is>
       </c>
       <c r="B12">
-        <v>6.7695929031412</v>
+        <v>2.325544502250153</v>
       </c>
       <c r="C12">
-        <v>0.3786157658304883</v>
+        <v>0.8423624112718686</v>
       </c>
       <c r="D12">
-        <v>705.031891045062</v>
+        <v>912.9959398422051</v>
       </c>
       <c r="E12">
-        <v>2.407601046433697</v>
+        <v>2.774944281334617</v>
       </c>
       <c r="F12">
-        <v>0.607885352965483</v>
+        <v>0.7748453992766966</v>
       </c>
       <c r="G12">
-        <v>0.6092227916848111</v>
+        <v>0.5836562254685655</v>
       </c>
       <c r="H12">
-        <v>120.089965424375</v>
+        <v>119.3581357134375</v>
       </c>
       <c r="I12">
-        <v>0.363727951930117</v>
+        <v>0.2187101944766251</v>
       </c>
       <c r="J12">
-        <v>453.8560083333334</v>
+        <v>297.311575</v>
       </c>
       <c r="K12">
-        <v>0.636337515390192</v>
+        <v>0.4133719034003929</v>
       </c>
       <c r="L12">
-        <v>16.648180935</v>
+        <v>19.78529996729167</v>
       </c>
       <c r="M12">
-        <v>0.5835795092205013</v>
+        <v>0.3596621547279532</v>
       </c>
       <c r="N12">
-        <v>5.3</v>
+        <v>11.03333333333333</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1206,74 +1170,74 @@
         </is>
       </c>
       <c r="P12">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Q12">
-        <v>3.2370576185</v>
+        <v>4.68073917325</v>
       </c>
       <c r="R12">
-        <v>0.8867899630597399</v>
+        <v>0.7894518735311615</v>
       </c>
       <c r="S12">
-        <v>3.666666666666667</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="T12">
-        <v>0.4583333333333333</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="U12">
-        <v>15.20522388059701</v>
+        <v>13.57215189873418</v>
       </c>
       <c r="V12">
-        <v>1</v>
+        <v>0.8669983345808914</v>
       </c>
       <c r="W12">
-        <v>0.6138324648238518</v>
+        <v>0.5758213144519431</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>B1A13</t>
+          <t>B1A12</t>
         </is>
       </c>
       <c r="B13">
-        <v>6.202177180698082</v>
+        <v>6.7695929031412</v>
       </c>
       <c r="C13">
-        <v>0.4306991317271958</v>
+        <v>0.4054884059165834</v>
       </c>
       <c r="D13">
-        <v>633.0952679188338</v>
+        <v>705.031891045062</v>
       </c>
       <c r="E13">
-        <v>2.054620898268954</v>
+        <v>2.407601046433697</v>
       </c>
       <c r="F13">
-        <v>0.5458608969151152</v>
+        <v>0.58513196154132</v>
       </c>
       <c r="G13">
-        <v>0.5199041931600346</v>
+        <v>0.4537123474411335</v>
       </c>
       <c r="H13">
-        <v>99.45453668906251</v>
+        <v>120.089965424375</v>
       </c>
       <c r="I13">
-        <v>0.3012274573669663</v>
+        <v>0.2214225024290789</v>
       </c>
       <c r="J13">
-        <v>442.4480833333333</v>
+        <v>453.8560083333334</v>
       </c>
       <c r="K13">
-        <v>0.6203428154920557</v>
+        <v>0.6341676404642451</v>
       </c>
       <c r="L13">
-        <v>16.12420608472222</v>
+        <v>16.47564418041667</v>
       </c>
       <c r="M13">
-        <v>0.5652122781600712</v>
+        <v>0.1905279720439203</v>
       </c>
       <c r="N13">
-        <v>3.2</v>
+        <v>5.3</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -1281,13 +1245,13 @@
         </is>
       </c>
       <c r="P13">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q13">
-        <v>3.0434590775</v>
+        <v>3.779633855</v>
       </c>
       <c r="R13">
-        <v>0.8935607100037953</v>
+        <v>0.8321466881256491</v>
       </c>
       <c r="S13">
         <v>3.666666666666667</v>
@@ -1296,59 +1260,59 @@
         <v>0.4583333333333333</v>
       </c>
       <c r="U13">
-        <v>7.139013452914798</v>
+        <v>15.20522388059701</v>
       </c>
       <c r="V13">
-        <v>0.4695105780076481</v>
+        <v>1</v>
       </c>
       <c r="W13">
-        <v>0.5338501549073573</v>
+        <v>0.531214539032807</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>B1A14</t>
+          <t>B1A13</t>
         </is>
       </c>
       <c r="B14">
-        <v>1.699209011408265</v>
+        <v>6.202177180698082</v>
       </c>
       <c r="C14">
-        <v>0.8440287761236099</v>
+        <v>0.4612684418215895</v>
       </c>
       <c r="D14">
-        <v>814.3056057503242</v>
+        <v>633.0952679188338</v>
       </c>
       <c r="E14">
-        <v>2.903930960374873</v>
+        <v>2.054620898268954</v>
       </c>
       <c r="F14">
-        <v>0.7021022124822849</v>
+        <v>0.5195083878934385</v>
       </c>
       <c r="G14">
-        <v>0.7348148187425432</v>
+        <v>0.3288492631064082</v>
       </c>
       <c r="H14">
-        <v>192.928677510625</v>
+        <v>99.45453668906251</v>
       </c>
       <c r="I14">
-        <v>0.5843415183903644</v>
+        <v>0.1449434573389538</v>
       </c>
       <c r="J14">
-        <v>226.6676666666667</v>
+        <v>442.4480833333333</v>
       </c>
       <c r="K14">
-        <v>0.3178037465134191</v>
+        <v>0.6180775045513266</v>
       </c>
       <c r="L14">
-        <v>14.841672665</v>
+        <v>15.69750223</v>
       </c>
       <c r="M14">
-        <v>0.5202548004294639</v>
+        <v>0.1507623857500812</v>
       </c>
       <c r="N14">
-        <v>6.559322033898305</v>
+        <v>3.2</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -1356,68 +1320,74 @@
         </is>
       </c>
       <c r="P14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q14">
-        <v>8.9541739505</v>
+        <v>1.93711442825</v>
       </c>
       <c r="R14">
-        <v>0.6868445103008844</v>
+        <v>0.919446167685493</v>
       </c>
       <c r="S14">
-        <v>1.666666666666667</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="T14">
-        <v>0.2083333333333333</v>
+        <v>0.4583333333333333</v>
+      </c>
+      <c r="U14">
+        <v>7.139013452914798</v>
+      </c>
+      <c r="V14">
+        <v>0.343066666737522</v>
       </c>
       <c r="W14">
-        <v>0.574815464539488</v>
+        <v>0.4382506231353496</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B1A15</t>
+          <t>B1A14</t>
         </is>
       </c>
       <c r="B15">
-        <v>3.853968818605062</v>
+        <v>1.699209011408265</v>
       </c>
       <c r="C15">
-        <v>0.6462423225256484</v>
+        <v>0.9039345792359711</v>
       </c>
       <c r="D15">
-        <v>662.3028872476706</v>
+        <v>814.3056057503242</v>
       </c>
       <c r="E15">
-        <v>2.123226916759468</v>
+        <v>2.903930960374873</v>
       </c>
       <c r="F15">
-        <v>0.5710439903474895</v>
+        <v>0.6848159799606366</v>
       </c>
       <c r="G15">
-        <v>0.5372643576163021</v>
+        <v>0.6292839319183426</v>
       </c>
       <c r="H15">
-        <v>67.78081792354838</v>
+        <v>192.928677510625</v>
       </c>
       <c r="I15">
-        <v>0.2052942391677662</v>
+        <v>0.4913774046220325</v>
       </c>
       <c r="J15">
-        <v>77.20100000000001</v>
+        <v>226.6676666666667</v>
       </c>
       <c r="K15">
-        <v>0.1082411417357679</v>
+        <v>0.3137332674080375</v>
       </c>
       <c r="L15">
-        <v>18.24718734055556</v>
+        <v>15.27959484229167</v>
       </c>
       <c r="M15">
-        <v>0.6396305202611589</v>
+        <v>0.1294059580702085</v>
       </c>
       <c r="N15">
-        <v>0.95</v>
+        <v>6.559322033898305</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -1425,13 +1395,13 @@
         </is>
       </c>
       <c r="P15">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Q15">
-        <v>1.54509958</v>
+        <v>5.21802827</v>
       </c>
       <c r="R15">
-        <v>0.9459630315109324</v>
+        <v>0.7639948510224823</v>
       </c>
       <c r="S15">
         <v>1.666666666666667</v>
@@ -1440,53 +1410,53 @@
         <v>0.2083333333333333</v>
       </c>
       <c r="W15">
-        <v>0.4827516170622999</v>
+        <v>0.5156099131963806</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B1A16</t>
+          <t>B1A15</t>
         </is>
       </c>
       <c r="B16">
-        <v>1.136531189147966</v>
+        <v>3.853968818605062</v>
       </c>
       <c r="C16">
-        <v>0.8956772478518207</v>
+        <v>0.692110030394446</v>
       </c>
       <c r="D16">
-        <v>745.9491221775057</v>
+        <v>662.3028872476706</v>
       </c>
       <c r="E16">
-        <v>2.427065160490093</v>
+        <v>2.123226916759468</v>
       </c>
       <c r="F16">
-        <v>0.6431645875720862</v>
+        <v>0.5461527906303022</v>
       </c>
       <c r="G16">
-        <v>0.6141480187778436</v>
+        <v>0.3531179340704553</v>
       </c>
       <c r="H16">
-        <v>126.9768313448387</v>
+        <v>67.78081792354838</v>
       </c>
       <c r="I16">
-        <v>0.3845868607291626</v>
+        <v>0.02755429151588618</v>
       </c>
       <c r="J16">
-        <v>155.476625</v>
+        <v>77.20100000000001</v>
       </c>
       <c r="K16">
-        <v>0.2179889820497641</v>
+        <v>0.1029202596859885</v>
       </c>
       <c r="L16">
-        <v>17.88303947</v>
+        <v>17.93460484791667</v>
       </c>
       <c r="M16">
-        <v>0.6268658082237172</v>
+        <v>0.2650856106492196</v>
       </c>
       <c r="N16">
-        <v>1.983050847457627</v>
+        <v>0.95</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -1494,68 +1464,68 @@
         </is>
       </c>
       <c r="P16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q16">
-        <v>0.535635516</v>
+        <v>1.54509958</v>
       </c>
       <c r="R16">
-        <v>0.9812671494611904</v>
+        <v>0.9380200246202453</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>0.2083333333333333</v>
       </c>
       <c r="W16">
-        <v>0.5454623318331981</v>
+        <v>0.3916617843624846</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B1A17</t>
+          <t>B1A16</t>
         </is>
       </c>
       <c r="B17">
-        <v>2.892220428878251</v>
+        <v>1.136531189147966</v>
       </c>
       <c r="C17">
-        <v>0.7345216762718467</v>
+        <v>0.9592488539153734</v>
       </c>
       <c r="D17">
-        <v>714.1590786180997</v>
+        <v>745.9491221775057</v>
       </c>
       <c r="E17">
-        <v>2.624414273372065</v>
+        <v>2.427065160490093</v>
       </c>
       <c r="F17">
-        <v>0.6157549028537781</v>
+        <v>0.622458358222127</v>
       </c>
       <c r="G17">
-        <v>0.6640855188734547</v>
+        <v>0.4605975769010921</v>
       </c>
       <c r="H17">
-        <v>184.2882473682143</v>
+        <v>126.9768313448387</v>
       </c>
       <c r="I17">
-        <v>0.5581714220930729</v>
+        <v>0.2469466112817081</v>
       </c>
       <c r="J17">
-        <v>185.8095416666667</v>
+        <v>155.476625</v>
       </c>
       <c r="K17">
-        <v>0.2605178292431412</v>
+        <v>0.2133229354503053</v>
       </c>
       <c r="L17">
-        <v>18.39406902583333</v>
+        <v>17.775413358125</v>
       </c>
       <c r="M17">
-        <v>0.6447792594623096</v>
+        <v>0.2569504073984943</v>
       </c>
       <c r="N17">
-        <v>2</v>
+        <v>1.983050847457627</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -1566,65 +1536,65 @@
         <v>2</v>
       </c>
       <c r="Q17">
-        <v>0.952643172</v>
+        <v>1.852894555</v>
       </c>
       <c r="R17">
-        <v>0.9666830864929176</v>
+        <v>0.9234365468351391</v>
       </c>
       <c r="S17">
-        <v>2.333333333333333</v>
+        <v>0</v>
       </c>
       <c r="T17">
-        <v>0.2916666666666667</v>
+        <v>0</v>
       </c>
       <c r="W17">
-        <v>0.5920225452446485</v>
+        <v>0.4603701612505299</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B1A18</t>
+          <t>B1A17</t>
         </is>
       </c>
       <c r="B18">
-        <v>2.173775254829633</v>
+        <v>2.892220428878251</v>
       </c>
       <c r="C18">
-        <v>0.8004681091898189</v>
+        <v>0.7866551012986476</v>
       </c>
       <c r="D18">
-        <v>63.60968471467833</v>
+        <v>714.1590786180997</v>
       </c>
       <c r="E18">
-        <v>2.011711592971416</v>
+        <v>2.624414273372065</v>
       </c>
       <c r="F18">
-        <v>0.05484488877161147</v>
+        <v>0.5934581609077576</v>
       </c>
       <c r="G18">
-        <v>0.509046361543229</v>
+        <v>0.5304077887594206</v>
       </c>
       <c r="H18">
-        <v>85.71637923125</v>
+        <v>184.2882473682143</v>
       </c>
       <c r="I18">
-        <v>0.259617387301867</v>
+        <v>0.4593542344259761</v>
       </c>
       <c r="J18">
-        <v>56.48408333333333</v>
+        <v>185.8095416666667</v>
       </c>
       <c r="K18">
-        <v>0.07919459164904936</v>
+        <v>0.2561055406832375</v>
       </c>
       <c r="L18">
-        <v>18.55946434555555</v>
+        <v>18.00750354520833</v>
       </c>
       <c r="M18">
-        <v>0.6505769691272703</v>
+        <v>0.2688109713450515</v>
       </c>
       <c r="N18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -1632,68 +1602,68 @@
         </is>
       </c>
       <c r="P18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q18">
-        <v>2.007709605</v>
+        <v>0.55887011425</v>
       </c>
       <c r="R18">
-        <v>0.9297841109628784</v>
+        <v>0.9847480633245231</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>2.333333333333333</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="W18">
-        <v>0.4104415523182156</v>
+        <v>0.5214008159264101</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B1A19</t>
+          <t>B1A18</t>
         </is>
       </c>
       <c r="B19">
-        <v>2.185989068317086</v>
+        <v>2.173775254829633</v>
       </c>
       <c r="C19">
-        <v>0.7993469972930211</v>
+        <v>0.8572821495440859</v>
       </c>
       <c r="D19">
-        <v>799.4162616745616</v>
+        <v>63.60968471467833</v>
       </c>
       <c r="E19">
-        <v>2.781380475817904</v>
+        <v>2.011711592971416</v>
       </c>
       <c r="F19">
-        <v>0.6892644752197857</v>
+        <v>0</v>
       </c>
       <c r="G19">
-        <v>0.7038044698997749</v>
+        <v>0.313670539220751</v>
       </c>
       <c r="H19">
-        <v>196.8196160846875</v>
+        <v>85.71637923125</v>
       </c>
       <c r="I19">
-        <v>0.596126375798129</v>
+        <v>0.09402708544534275</v>
       </c>
       <c r="J19">
-        <v>238.2480416666667</v>
+        <v>56.48408333333333</v>
       </c>
       <c r="K19">
-        <v>0.3340402332393468</v>
+        <v>0.07370039675182005</v>
       </c>
       <c r="L19">
-        <v>18.48682638</v>
+        <v>18.12868266854167</v>
       </c>
       <c r="M19">
-        <v>0.6480307432990436</v>
+        <v>0.27500361895047</v>
       </c>
       <c r="N19">
-        <v>3.559322033898305</v>
+        <v>1</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -1701,68 +1671,68 @@
         </is>
       </c>
       <c r="P19">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q19">
-        <v>6.889186623000001</v>
+        <v>1.045497178</v>
       </c>
       <c r="R19">
-        <v>0.7590635805736504</v>
+        <v>0.9616914329366177</v>
       </c>
       <c r="S19">
-        <v>1.333333333333333</v>
+        <v>0</v>
       </c>
       <c r="T19">
-        <v>0.1666666666666667</v>
+        <v>0</v>
       </c>
       <c r="W19">
-        <v>0.5870429427486773</v>
+        <v>0.3219219028561359</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B1A20</t>
+          <t>B1A19</t>
         </is>
       </c>
       <c r="B20">
-        <v>3.356827381619648</v>
+        <v>2.185989068317086</v>
       </c>
       <c r="C20">
-        <v>0.6918751774868042</v>
+        <v>0.8560814655871208</v>
       </c>
       <c r="D20">
-        <v>917.5395358708413</v>
+        <v>799.4162616745616</v>
       </c>
       <c r="E20">
-        <v>2.73056528632354</v>
+        <v>2.781380475817904</v>
       </c>
       <c r="F20">
-        <v>0.7911115109926038</v>
+        <v>0.6712333022498698</v>
       </c>
       <c r="G20">
-        <v>0.6909461221059798</v>
+        <v>0.5859329628396042</v>
       </c>
       <c r="H20">
-        <v>123.234310468125</v>
+        <v>196.8196160846875</v>
       </c>
       <c r="I20">
-        <v>0.373251530181499</v>
+        <v>0.5057980047687795</v>
       </c>
       <c r="J20">
-        <v>581.4750416666667</v>
+        <v>238.2480416666667</v>
       </c>
       <c r="K20">
-        <v>0.8152682271065561</v>
+        <v>0.3300666328248477</v>
       </c>
       <c r="L20">
-        <v>19.49016020277778</v>
+        <v>18.22061450770833</v>
       </c>
       <c r="M20">
-        <v>0.683201256051582</v>
+        <v>0.2797016351434999</v>
       </c>
       <c r="N20">
-        <v>12.15254237288136</v>
+        <v>3.559322033898305</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -1770,74 +1740,68 @@
         </is>
       </c>
       <c r="P20">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="Q20">
-        <v>4.3663490965</v>
+        <v>3.5945891465</v>
       </c>
       <c r="R20">
-        <v>0.8472951053809497</v>
+        <v>0.8409141977175818</v>
       </c>
       <c r="S20">
-        <v>7.333333333333333</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="T20">
-        <v>0.9166666666666666</v>
-      </c>
-      <c r="U20">
-        <v>9.609856262833675</v>
-      </c>
-      <c r="V20">
-        <v>0.6320101787581411</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="W20">
-        <v>0.7157361971923092</v>
+        <v>0.5295493584747463</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B1A21</t>
+          <t>B1A20</t>
         </is>
       </c>
       <c r="B21">
-        <v>0.9990682892502492</v>
+        <v>3.356827381619648</v>
       </c>
       <c r="C21">
-        <v>0.9082950344753011</v>
+        <v>0.7409817237721223</v>
       </c>
       <c r="D21">
-        <v>813.5264000739855</v>
+        <v>917.5395358708413</v>
       </c>
       <c r="E21">
-        <v>2.500077708360005</v>
+        <v>2.73056528632354</v>
       </c>
       <c r="F21">
-        <v>0.7014303737702917</v>
+        <v>0.7789902561750838</v>
       </c>
       <c r="G21">
-        <v>0.632623217693053</v>
+        <v>0.5679576140152887</v>
       </c>
       <c r="H21">
-        <v>140.165478528125</v>
+        <v>123.234310468125</v>
       </c>
       <c r="I21">
-        <v>0.4245325765244304</v>
+        <v>0.233076076942331</v>
       </c>
       <c r="J21">
-        <v>128.7385</v>
+        <v>581.4750416666667</v>
       </c>
       <c r="K21">
-        <v>0.1805002814128076</v>
+        <v>0.8141659829681285</v>
       </c>
       <c r="L21">
-        <v>18.26601297333333</v>
+        <v>19.373500355</v>
       </c>
       <c r="M21">
-        <v>0.6402904274053757</v>
+        <v>0.3386178542509189</v>
       </c>
       <c r="N21">
-        <v>3.694915254237288</v>
+        <v>12.15254237288136</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -1845,200 +1809,218 @@
         </is>
       </c>
       <c r="P21">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="Q21">
-        <v>1.290140285</v>
+        <v>3.626466306</v>
       </c>
       <c r="R21">
-        <v>0.9548797560821151</v>
+        <v>0.839403842171912</v>
       </c>
       <c r="S21">
-        <v>2.666666666666667</v>
+        <v>7.333333333333333</v>
       </c>
       <c r="T21">
-        <v>0.3333333333333333</v>
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="U21">
+        <v>9.609856262833675</v>
+      </c>
+      <c r="V21">
+        <v>0.5442985856962799</v>
       </c>
       <c r="W21">
-        <v>0.5969856250870885</v>
+        <v>0.6415731780731924</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B2A01</t>
+          <t>B1A21</t>
         </is>
       </c>
       <c r="B22">
-        <v>1.87831184917383</v>
+        <v>0.9990682892502492</v>
       </c>
       <c r="C22">
-        <v>0.8275888392950747</v>
+        <v>0.9727622008118715</v>
       </c>
       <c r="D22">
-        <v>790.0249197554833</v>
+        <v>813.5264000739855</v>
       </c>
       <c r="E22">
-        <v>2.375324300110834</v>
+        <v>2.500077708360005</v>
       </c>
       <c r="F22">
-        <v>0.6811671688854066</v>
+        <v>0.6841051561984712</v>
       </c>
       <c r="G22">
-        <v>0.6010554379073053</v>
+        <v>0.4864250121536806</v>
       </c>
       <c r="H22">
-        <v>112.8774740863333</v>
+        <v>140.165478528125</v>
       </c>
       <c r="I22">
-        <v>0.3418827903179118</v>
+        <v>0.2958263876869464</v>
       </c>
       <c r="J22">
-        <v>442.4108333333334</v>
+        <v>128.7385</v>
       </c>
       <c r="K22">
-        <v>0.6202905884155975</v>
+        <v>0.1756105499545552</v>
       </c>
       <c r="L22">
-        <v>18.15336036388889</v>
+        <v>17.93935104833333</v>
       </c>
       <c r="M22">
-        <v>0.6363415422515757</v>
+        <v>0.2653281569380242</v>
       </c>
       <c r="N22">
-        <v>3.6</v>
+        <v>3.694915254237288</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="P22">
         <v>4</v>
       </c>
       <c r="Q22">
-        <v>4.387179358499999</v>
+        <v>0.6450701425000001</v>
       </c>
       <c r="R22">
-        <v>0.8465666059198903</v>
+        <v>0.9806638634539456</v>
       </c>
       <c r="S22">
-        <v>4.666666666666667</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="T22">
-        <v>0.5833333333333334</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="W22">
-        <v>0.6422782882907619</v>
+        <v>0.5242568325663535</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>B2A02</t>
+          <t>B1A22</t>
         </is>
       </c>
       <c r="B23">
-        <v>0.7408975943918668</v>
+        <v>1.370103848357541</v>
       </c>
       <c r="C23">
-        <v>0.9319926484684775</v>
+        <v>0.9362873976112719</v>
       </c>
       <c r="D23">
-        <v>873.7027658075027</v>
+        <v>961.0739699344375</v>
       </c>
       <c r="E23">
-        <v>3.219755117538084</v>
+        <v>3.028067005123522</v>
       </c>
       <c r="F23">
-        <v>0.7533150215269718</v>
+        <v>0.8187041740077048</v>
       </c>
       <c r="G23">
-        <v>0.8147314124794834</v>
+        <v>0.6731957765504538</v>
       </c>
       <c r="H23">
-        <v>195.54534427125</v>
+        <v>151.3133351287097</v>
       </c>
       <c r="I23">
-        <v>0.5922668670101464</v>
+        <v>0.3371425841445167</v>
       </c>
       <c r="J23">
-        <v>192.1180833333333</v>
+        <v>659.353575</v>
       </c>
       <c r="K23">
-        <v>0.2693628410006011</v>
+        <v>0.9240085867748759</v>
       </c>
       <c r="L23">
-        <v>16.39088118888889</v>
+        <v>20.34326158791667</v>
       </c>
       <c r="M23">
-        <v>0.5745602139506857</v>
+        <v>0.3881758095459888</v>
       </c>
       <c r="N23">
-        <v>1.983050847457627</v>
+        <v>33.2280701754386</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="P23">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="Q23">
-        <v>12.19512195</v>
+        <v>7.306620341</v>
       </c>
       <c r="R23">
-        <v>0.5734984145601245</v>
+        <v>0.6650363281629801</v>
+      </c>
+      <c r="S23">
+        <v>6.333333333333333</v>
+      </c>
+      <c r="T23">
+        <v>0.7916666666666666</v>
+      </c>
+      <c r="U23">
+        <v>3.057603686635945</v>
+      </c>
+      <c r="V23">
+        <v>0.01066595066272064</v>
       </c>
       <c r="W23">
-        <v>0.6442467741423558</v>
+        <v>0.6160981415696866</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>B2A04</t>
+          <t>B2A01</t>
         </is>
       </c>
       <c r="B24">
-        <v>5.03432563844431</v>
+        <v>1.87831184917383</v>
       </c>
       <c r="C24">
-        <v>0.5378967943621695</v>
+        <v>0.886327801125847</v>
       </c>
       <c r="D24">
-        <v>548.7226506533721</v>
+        <v>790.0249197554833</v>
       </c>
       <c r="E24">
-        <v>1.92094178688546</v>
+        <v>2.375324300110834</v>
       </c>
       <c r="F24">
-        <v>0.4731140057765997</v>
+        <v>0.6626661303241366</v>
       </c>
       <c r="G24">
-        <v>0.4860778407634728</v>
+        <v>0.4422947815550168</v>
       </c>
       <c r="H24">
-        <v>119.3736232370968</v>
+        <v>112.8774740863333</v>
       </c>
       <c r="I24">
-        <v>0.3615582979066596</v>
+        <v>0.1946915603522473</v>
       </c>
       <c r="J24">
-        <v>142.4275</v>
+        <v>442.4108333333334</v>
       </c>
       <c r="K24">
-        <v>0.199693206235296</v>
+        <v>0.6180249658501381</v>
       </c>
       <c r="L24">
-        <v>16.1714261825</v>
+        <v>17.9985813475</v>
       </c>
       <c r="M24">
-        <v>0.5668675149450444</v>
+        <v>0.2683550180029762</v>
       </c>
       <c r="N24">
-        <v>1</v>
+        <v>3.6</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -2046,68 +2028,68 @@
         </is>
       </c>
       <c r="P24">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q24">
-        <v>21.34269891</v>
+        <v>2.5428031785</v>
       </c>
       <c r="R24">
-        <v>0.2535790162655239</v>
+        <v>0.8907483358448023</v>
       </c>
       <c r="S24">
-        <v>2</v>
+        <v>4.666666666666667</v>
       </c>
       <c r="T24">
-        <v>0.25</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="W24">
-        <v>0.3910983345318457</v>
+        <v>0.5683052407985623</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>B2A05</t>
+          <t>B2A02</t>
         </is>
       </c>
       <c r="B25">
-        <v>1.903937605799871</v>
+        <v>0.7408975943918668</v>
       </c>
       <c r="C25">
-        <v>0.8252366385964628</v>
+        <v>0.9981417771246597</v>
       </c>
       <c r="D25">
-        <v>648.7983906320918</v>
+        <v>873.7027658075027</v>
       </c>
       <c r="E25">
-        <v>2.035724943587848</v>
+        <v>3.219755117538084</v>
       </c>
       <c r="F25">
-        <v>0.5594002820329425</v>
+        <v>0.7390005348937705</v>
       </c>
       <c r="G25">
-        <v>0.5151227339230796</v>
+        <v>0.7410034679201478</v>
       </c>
       <c r="H25">
-        <v>80.2080049490625</v>
+        <v>195.54534427125</v>
       </c>
       <c r="I25">
-        <v>0.2429336478316754</v>
+        <v>0.5010752973936624</v>
       </c>
       <c r="J25">
-        <v>153.53375</v>
+        <v>192.1180833333333</v>
       </c>
       <c r="K25">
-        <v>0.2152649369175783</v>
+        <v>0.2650033282150609</v>
       </c>
       <c r="L25">
-        <v>18.74636130527778</v>
+        <v>16.56638317395833</v>
       </c>
       <c r="M25">
-        <v>0.6571283897572682</v>
+        <v>0.1951650299431444</v>
       </c>
       <c r="N25">
-        <v>0.9833333333333333</v>
+        <v>1.983050847457627</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -2115,62 +2097,62 @@
         </is>
       </c>
       <c r="P25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q25">
-        <v>13.7963962</v>
+        <v>6.1132243405</v>
       </c>
       <c r="R25">
-        <v>0.5174968420339024</v>
+        <v>0.7215800195020812</v>
       </c>
       <c r="W25">
-        <v>0.5046547815847013</v>
+        <v>0.5944242078560753</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>B2A06</t>
+          <t>B2A03</t>
         </is>
       </c>
       <c r="B26">
-        <v>2.494660573312057</v>
+        <v>1.389876030177799</v>
       </c>
       <c r="C26">
-        <v>0.7710138893077165</v>
+        <v>0.9343436851474973</v>
       </c>
       <c r="D26">
-        <v>953.7906142421343</v>
+        <v>1016.709276471273</v>
       </c>
       <c r="E26">
-        <v>2.598086318190543</v>
+        <v>3.368916242312652</v>
       </c>
       <c r="F26">
-        <v>0.8223675433097354</v>
+        <v>0.8694570100080276</v>
       </c>
       <c r="G26">
-        <v>0.6574234556637719</v>
+        <v>0.7937676763296724</v>
       </c>
       <c r="H26">
-        <v>123.441344703125</v>
+        <v>221.300390919375</v>
       </c>
       <c r="I26">
-        <v>0.3738785945495323</v>
+        <v>0.5965286751337395</v>
       </c>
       <c r="J26">
-        <v>321.4800416666667</v>
+        <v>713.231575</v>
       </c>
       <c r="K26">
-        <v>0.4507372541192763</v>
+        <v>1</v>
       </c>
       <c r="L26">
-        <v>20.25364036361111</v>
+        <v>19.00962763604167</v>
       </c>
       <c r="M26">
-        <v>0.7099640224642182</v>
+        <v>0.3200227740114285</v>
       </c>
       <c r="N26">
-        <v>3.677966101694915</v>
+        <v>33.47457627118644</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -2178,74 +2160,74 @@
         </is>
       </c>
       <c r="P26">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="Q26">
-        <v>3.726573942</v>
+        <v>4.071412934</v>
       </c>
       <c r="R26">
-        <v>0.8696700450361691</v>
+        <v>0.8183220513954514</v>
       </c>
       <c r="S26">
-        <v>1.333333333333333</v>
+        <v>4.666666666666667</v>
       </c>
       <c r="T26">
-        <v>0.1666666666666667</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="U26">
-        <v>3.663265306122449</v>
+        <v>3.079295154185022</v>
       </c>
       <c r="V26">
-        <v>0.2409214974333292</v>
+        <v>0.01243256067223224</v>
       </c>
       <c r="W26">
-        <v>0.5625158853944906</v>
+        <v>0.6586897517812647</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>B2A08</t>
+          <t>B2A04</t>
         </is>
       </c>
       <c r="B27">
-        <v>2.013311318365398</v>
+        <v>5.03432563844431</v>
       </c>
       <c r="C27">
-        <v>0.8151971721775485</v>
+        <v>0.576074567880535</v>
       </c>
       <c r="D27">
-        <v>857.7172489851876</v>
+        <v>548.7226506533721</v>
       </c>
       <c r="E27">
-        <v>2.350635469275505</v>
+        <v>1.92094178688546</v>
       </c>
       <c r="F27">
-        <v>0.7395321534620042</v>
+        <v>0.4425401841835008</v>
       </c>
       <c r="G27">
-        <v>0.5948081410525323</v>
+        <v>0.2815616571454121</v>
       </c>
       <c r="H27">
-        <v>177.1940864143333</v>
+        <v>119.3736232370968</v>
       </c>
       <c r="I27">
-        <v>0.5366846590209104</v>
+        <v>0.2187675943511546</v>
       </c>
       <c r="J27">
-        <v>150.5134916666667</v>
+        <v>142.4275</v>
       </c>
       <c r="K27">
-        <v>0.2110303258330461</v>
+        <v>0.1949179937282425</v>
       </c>
       <c r="L27">
-        <v>21.35522024472222</v>
+        <v>16.046611876875</v>
       </c>
       <c r="M27">
-        <v>0.7485784181688261</v>
+        <v>0.168603024956573</v>
       </c>
       <c r="N27">
-        <v>1.627118644067797</v>
+        <v>1</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -2253,62 +2235,68 @@
         </is>
       </c>
       <c r="P27">
+        <v>1</v>
+      </c>
+      <c r="Q27">
+        <v>21.34269891</v>
+      </c>
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27">
         <v>2</v>
       </c>
-      <c r="S27">
-        <v>2.666666666666667</v>
-      </c>
       <c r="T27">
-        <v>0.3333333333333333</v>
+        <v>0.25</v>
       </c>
       <c r="W27">
-        <v>0.5684520290068859</v>
+        <v>0.2665581277806773</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>B2A09</t>
+          <t>B2A05</t>
         </is>
       </c>
       <c r="B28">
-        <v>0.9993273242222674</v>
+        <v>1.903937605799871</v>
       </c>
       <c r="C28">
-        <v>0.9082712575288858</v>
+        <v>0.8838086505839147</v>
       </c>
       <c r="D28">
-        <v>1010.778519775807</v>
+        <v>648.7983906320918</v>
       </c>
       <c r="E28">
-        <v>2.521925385274342</v>
+        <v>2.035724943587848</v>
       </c>
       <c r="F28">
-        <v>0.8715030696740116</v>
+        <v>0.533833428256634</v>
       </c>
       <c r="G28">
-        <v>0.6381515849203792</v>
+        <v>0.322165014161533</v>
       </c>
       <c r="H28">
-        <v>168.7766671846875</v>
+        <v>80.2080049490625</v>
       </c>
       <c r="I28">
-        <v>0.5111900171820443</v>
+        <v>0.07361194357916995</v>
       </c>
       <c r="J28">
-        <v>184.4895</v>
+        <v>153.53375</v>
       </c>
       <c r="K28">
-        <v>0.2586670395235937</v>
+        <v>0.2105826366832804</v>
       </c>
       <c r="L28">
-        <v>21.68805554777778</v>
+        <v>18.54128809604167</v>
       </c>
       <c r="M28">
-        <v>0.7602455104215341</v>
+        <v>0.2960890992073462</v>
       </c>
       <c r="N28">
-        <v>3.933333333333333</v>
+        <v>0.9833333333333333</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -2316,68 +2304,62 @@
         </is>
       </c>
       <c r="P28">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q28">
-        <v>8.2729372335</v>
+        <v>13.7963962</v>
       </c>
       <c r="R28">
-        <v>0.7106694905718161</v>
-      </c>
-      <c r="S28">
-        <v>0</v>
-      </c>
-      <c r="T28">
-        <v>0</v>
+        <v>0.3575475458329737</v>
       </c>
       <c r="W28">
-        <v>0.582337246227783</v>
+        <v>0.382519759757836</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>B2A10</t>
+          <t>B2A06</t>
         </is>
       </c>
       <c r="B29">
-        <v>1.08660229088038</v>
+        <v>2.494660573312057</v>
       </c>
       <c r="C29">
-        <v>0.9002602457745665</v>
+        <v>0.8257373863689109</v>
       </c>
       <c r="D29">
-        <v>1107.679249668098</v>
+        <v>953.7906142421343</v>
       </c>
       <c r="E29">
-        <v>3.62140707432442</v>
+        <v>2.598086318190543</v>
       </c>
       <c r="F29">
-        <v>0.9550518213565412</v>
+        <v>0.8120599946188712</v>
       </c>
       <c r="G29">
-        <v>0.9163659946547561</v>
+        <v>0.5210945463425779</v>
       </c>
       <c r="H29">
-        <v>232.0746173662963</v>
+        <v>123.441344703125</v>
       </c>
       <c r="I29">
-        <v>0.7029065665171318</v>
+        <v>0.2338433874158308</v>
       </c>
       <c r="J29">
-        <v>344.1929166666667</v>
+        <v>321.4800416666667</v>
       </c>
       <c r="K29">
-        <v>0.4825822758431113</v>
+        <v>0.4474599530214684</v>
       </c>
       <c r="L29">
-        <v>22.74975343416667</v>
+        <v>20.663866608125</v>
       </c>
       <c r="M29">
-        <v>0.7974618966380425</v>
+        <v>0.4045597695554779</v>
       </c>
       <c r="N29">
-        <v>12.86440677966102</v>
+        <v>3.677966101694915</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -2385,212 +2367,182 @@
         </is>
       </c>
       <c r="P29">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="Q29">
-        <v>18.2184374865</v>
+        <v>2.91523699475</v>
       </c>
       <c r="R29">
-        <v>0.3628442172134646</v>
+        <v>0.8731022378677181</v>
       </c>
       <c r="S29">
-        <v>3</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="T29">
-        <v>0.375</v>
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="U29">
+        <v>3.663265306122449</v>
+      </c>
+      <c r="V29">
+        <v>0.05999262148114465</v>
       </c>
       <c r="W29">
-        <v>0.6865591272497017</v>
+        <v>0.4827240625931852</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>B2A12</t>
+          <t>B2A07</t>
         </is>
       </c>
       <c r="B30">
-        <v>0.9556834864386684</v>
+        <v>5.358723557574902</v>
       </c>
       <c r="C30">
-        <v>0.9122773466845272</v>
+        <v>0.5441844970543293</v>
       </c>
       <c r="D30">
-        <v>845.6928104684499</v>
+        <v>765.69556865</v>
       </c>
       <c r="E30">
-        <v>2.759213488094072</v>
+        <v>3.559882353</v>
       </c>
       <c r="F30">
-        <v>0.7291645656339926</v>
+        <v>0.6404718863536584</v>
       </c>
       <c r="G30">
-        <v>0.6981953038112486</v>
-      </c>
-      <c r="H30">
-        <v>164.713646173125</v>
-      </c>
-      <c r="I30">
-        <v>0.4988839572547034</v>
-      </c>
-      <c r="J30">
-        <v>340.3929333333333</v>
-      </c>
-      <c r="K30">
-        <v>0.4772544363776005</v>
+        <v>0.8613199670400836</v>
       </c>
       <c r="L30">
-        <v>18.0566264525</v>
+        <v>19.07895547791667</v>
       </c>
       <c r="M30">
-        <v>0.6329506655693896</v>
-      </c>
-      <c r="N30">
-        <v>6.135593220338983</v>
+        <v>0.3235656523733645</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="P30">
-        <v>8</v>
-      </c>
-      <c r="Q30">
-        <v>3.4872954225</v>
-      </c>
-      <c r="R30">
-        <v>0.8780383638071393</v>
-      </c>
-      <c r="S30">
-        <v>3</v>
-      </c>
-      <c r="T30">
-        <v>0.375</v>
-      </c>
-      <c r="U30">
-        <v>7.326145552560646</v>
-      </c>
-      <c r="V30">
-        <v>0.4818176706960131</v>
-      </c>
       <c r="W30">
-        <v>0.6315091455371794</v>
+        <v>0.5923855007053589</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>B2A13</t>
+          <t>B2A08</t>
         </is>
       </c>
       <c r="B31">
-        <v>5.517142053953108</v>
+        <v>2.013311318365398</v>
       </c>
       <c r="C31">
-        <v>0.4935788401087917</v>
+        <v>0.8730566227978314</v>
       </c>
       <c r="D31">
-        <v>797.0526848735647</v>
+        <v>857.7172489851876</v>
       </c>
       <c r="E31">
-        <v>2.48792606317468</v>
+        <v>2.350635469275505</v>
       </c>
       <c r="F31">
-        <v>0.6872265763159427</v>
+        <v>0.7244178829023376</v>
       </c>
       <c r="G31">
-        <v>0.6295483481193197</v>
+        <v>0.4335613624583748</v>
       </c>
       <c r="H31">
-        <v>93.236065658125</v>
+        <v>177.1940864143333</v>
       </c>
       <c r="I31">
-        <v>0.2823929800296902</v>
+        <v>0.4330618485285115</v>
       </c>
       <c r="J31">
-        <v>95.69158333333333</v>
+        <v>150.5134916666667</v>
       </c>
       <c r="K31">
-        <v>0.1341662185010995</v>
+        <v>0.206322758828591</v>
       </c>
       <c r="L31">
-        <v>15.58422212138889</v>
+        <v>21.30009535354167</v>
       </c>
       <c r="M31">
-        <v>0.546283869252254</v>
+        <v>0.4370731291872781</v>
       </c>
       <c r="N31">
+        <v>1.627118644067797</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="P31">
+        <v>2</v>
+      </c>
+      <c r="Q31">
+        <v>0.236966825</v>
+      </c>
+      <c r="R31">
         <v>1</v>
       </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>B2</t>
-        </is>
-      </c>
-      <c r="P31">
-        <v>1</v>
-      </c>
-      <c r="Q31">
-        <v>4.2902386335</v>
-      </c>
-      <c r="R31">
-        <v>0.8499569264985369</v>
-      </c>
       <c r="S31">
-        <v>1.666666666666667</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="T31">
-        <v>0.2083333333333333</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="W31">
-        <v>0.478935886519871</v>
+        <v>0.5551033672545322</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>B2A14</t>
+          <t>B2A09</t>
         </is>
       </c>
       <c r="B32">
-        <v>1.365713000697533</v>
+        <v>0.9993273242222674</v>
       </c>
       <c r="C32">
-        <v>0.8746405375956945</v>
+        <v>0.9727367362724371</v>
       </c>
       <c r="D32">
-        <v>1004.951093615742</v>
+        <v>1010.778519775807</v>
       </c>
       <c r="E32">
-        <v>3.163390120458246</v>
+        <v>2.521925385274342</v>
       </c>
       <c r="F32">
-        <v>0.8664786061664954</v>
+        <v>0.8640467275694197</v>
       </c>
       <c r="G32">
-        <v>0.8004687334840782</v>
+        <v>0.4941534023740833</v>
       </c>
       <c r="H32">
-        <v>144.923307941875</v>
+        <v>168.7766671846875</v>
       </c>
       <c r="I32">
-        <v>0.4389430690429412</v>
+        <v>0.4018652015838838</v>
       </c>
       <c r="J32">
-        <v>330.4918833333333</v>
+        <v>184.4895</v>
       </c>
       <c r="K32">
-        <v>0.4633724794549839</v>
+        <v>0.2542437078058841</v>
       </c>
       <c r="L32">
-        <v>18.20769756222222</v>
+        <v>21.769751060625</v>
       </c>
       <c r="M32">
-        <v>0.6382462593891171</v>
+        <v>0.461074064413063</v>
       </c>
       <c r="N32">
-        <v>6</v>
+        <v>3.933333333333333</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -2598,68 +2550,68 @@
         </is>
       </c>
       <c r="P32">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q32">
-        <v>3.3371393965</v>
+        <v>6.5395552285</v>
       </c>
       <c r="R32">
-        <v>0.8832897900261572</v>
+        <v>0.7013802516720424</v>
       </c>
       <c r="S32">
-        <v>5.666666666666667</v>
+        <v>0</v>
       </c>
       <c r="T32">
-        <v>0.7083333333333334</v>
+        <v>0</v>
       </c>
       <c r="W32">
-        <v>0.7092216010616001</v>
+        <v>0.5186875114613516</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>B2A15</t>
+          <t>B2A10</t>
         </is>
       </c>
       <c r="B33">
-        <v>4.138422420662683</v>
+        <v>1.08660229088038</v>
       </c>
       <c r="C33">
-        <v>0.6201321876622482</v>
+        <v>0.9641571347893538</v>
       </c>
       <c r="D33">
-        <v>736.0154404505465</v>
+        <v>1107.679249668098</v>
       </c>
       <c r="E33">
-        <v>2.332496835604216</v>
+        <v>3.62140707432442</v>
       </c>
       <c r="F33">
-        <v>0.6345996705810426</v>
+        <v>0.9524435956495637</v>
       </c>
       <c r="G33">
-        <v>0.5902183154005872</v>
+        <v>0.8830837022171001</v>
       </c>
       <c r="H33">
-        <v>67.318532718125</v>
+        <v>232.0746173662963</v>
       </c>
       <c r="I33">
-        <v>0.2038940717983941</v>
+        <v>0.6364601231697685</v>
       </c>
       <c r="J33">
-        <v>449.8763333333333</v>
+        <v>344.1929166666667</v>
       </c>
       <c r="K33">
-        <v>0.6307577357793411</v>
+        <v>0.4794949853102615</v>
       </c>
       <c r="L33">
-        <v>19.28953693527778</v>
+        <v>23.14746620666667</v>
       </c>
       <c r="M33">
-        <v>0.67616867823164</v>
+        <v>0.531479792441109</v>
       </c>
       <c r="N33">
-        <v>0.7333333333333333</v>
+        <v>12.86440677966102</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -2667,143 +2619,95 @@
         </is>
       </c>
       <c r="P33">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="Q33">
-        <v>15.4121761</v>
+        <v>9.12461412</v>
       </c>
       <c r="R33">
-        <v>0.4609879615243572</v>
+        <v>0.5788988858947699</v>
       </c>
       <c r="S33">
-        <v>4.333333333333333</v>
+        <v>3</v>
       </c>
       <c r="T33">
-        <v>0.5416666666666666</v>
+        <v>0.375</v>
       </c>
       <c r="W33">
-        <v>0.5448031609555346</v>
+        <v>0.6751272774339908</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>B2A16</t>
+          <t>B2A11</t>
         </is>
       </c>
       <c r="B34">
-        <v>1.406406261621896</v>
+        <v>1.577238168341571</v>
       </c>
       <c r="C34">
-        <v>0.870905283328985</v>
-      </c>
-      <c r="D34">
-        <v>877.0060330270752</v>
-      </c>
-      <c r="E34">
-        <v>2.576887445112982</v>
-      </c>
-      <c r="F34">
-        <v>0.7561631306482949</v>
-      </c>
-      <c r="G34">
-        <v>0.6520592626817104</v>
-      </c>
-      <c r="H34">
-        <v>173.841501374375</v>
-      </c>
-      <c r="I34">
-        <v>0.5265303643973225</v>
-      </c>
-      <c r="J34">
-        <v>478.5481916666667</v>
-      </c>
-      <c r="K34">
-        <v>0.6709576642995183</v>
+        <v>0.9159249731156649</v>
       </c>
       <c r="L34">
-        <v>21.148033835</v>
+        <v>21.70601268541667</v>
       </c>
       <c r="M34">
-        <v>0.7413157782578998</v>
-      </c>
-      <c r="N34">
-        <v>3.610169491525424</v>
+        <v>0.4578168259898949</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="P34">
-        <v>4</v>
-      </c>
-      <c r="Q34">
-        <v>5.991139977</v>
-      </c>
-      <c r="R34">
-        <v>0.7904710826788641</v>
-      </c>
-      <c r="S34">
-        <v>5.666666666666667</v>
-      </c>
-      <c r="T34">
-        <v>0.7083333333333334</v>
-      </c>
-      <c r="U34">
-        <v>10.38050314465409</v>
-      </c>
-      <c r="V34">
-        <v>0.6826932129490296</v>
-      </c>
       <c r="W34">
-        <v>0.7110476791749953</v>
+        <v>0.6868708995527799</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>B2A17</t>
+          <t>B2A12</t>
         </is>
       </c>
       <c r="B35">
-        <v>2.906916865566272</v>
+        <v>0.9556834864386684</v>
       </c>
       <c r="C35">
-        <v>0.7331726831806715</v>
+        <v>0.9770271616912454</v>
       </c>
       <c r="D35">
-        <v>985.8426334202379</v>
+        <v>845.6928104684499</v>
       </c>
       <c r="E35">
-        <v>2.923565604627012</v>
+        <v>2.759213488094072</v>
       </c>
       <c r="F35">
-        <v>0.8500031059542238</v>
+        <v>0.7134486909624694</v>
       </c>
       <c r="G35">
-        <v>0.7397831970387502</v>
+        <v>0.5780916197159226</v>
       </c>
       <c r="H35">
-        <v>124.1271808390625</v>
+        <v>164.713646173125</v>
       </c>
       <c r="I35">
-        <v>0.3759558519806813</v>
+        <v>0.3868068293479019</v>
       </c>
       <c r="J35">
-        <v>330.23375</v>
+        <v>340.3929333333333</v>
       </c>
       <c r="K35">
-        <v>0.4630105586674286</v>
+        <v>0.4741353560788141</v>
       </c>
       <c r="L35">
-        <v>19.74005660527778</v>
+        <v>18.16133644729167</v>
       </c>
       <c r="M35">
-        <v>0.691961037104918</v>
+        <v>0.2766723333232239</v>
       </c>
       <c r="N35">
-        <v>6.220338983050848</v>
+        <v>6.135593220338983</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -2814,65 +2718,71 @@
         <v>8</v>
       </c>
       <c r="Q35">
-        <v>4.1281363245</v>
+        <v>2.07165073475</v>
       </c>
       <c r="R35">
-        <v>0.8556261516260451</v>
+        <v>0.9130717711017509</v>
       </c>
       <c r="S35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T35">
-        <v>0.25</v>
+        <v>0.375</v>
+      </c>
+      <c r="U35">
+        <v>7.326145552560646</v>
+      </c>
+      <c r="V35">
+        <v>0.3583071957421785</v>
       </c>
       <c r="W35">
-        <v>0.6199390731940898</v>
+        <v>0.5613956619959451</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>B2A18</t>
+          <t>B2A13</t>
         </is>
       </c>
       <c r="B36">
-        <v>1.13456411529597</v>
+        <v>5.517142053953108</v>
       </c>
       <c r="C36">
-        <v>0.8958578065200546</v>
+        <v>0.5286111016292858</v>
       </c>
       <c r="D36">
-        <v>1091.19812954318</v>
+        <v>797.0526848735647</v>
       </c>
       <c r="E36">
-        <v>3.047672135596225</v>
+        <v>2.48792606317468</v>
       </c>
       <c r="F36">
-        <v>0.9408416393042771</v>
+        <v>0.6690771493818031</v>
       </c>
       <c r="G36">
-        <v>0.7711872900779094</v>
+        <v>0.4821264930854841</v>
       </c>
       <c r="H36">
-        <v>175.416226305</v>
+        <v>93.236065658125</v>
       </c>
       <c r="I36">
-        <v>0.5312998842472573</v>
+        <v>0.1218965542449143</v>
       </c>
       <c r="J36">
-        <v>370.9917916666666</v>
+        <v>95.69158333333333</v>
       </c>
       <c r="K36">
-        <v>0.5201561521819427</v>
+        <v>0.1290000243182489</v>
       </c>
       <c r="L36">
-        <v>21.21049840166667</v>
+        <v>15.50459700958333</v>
       </c>
       <c r="M36">
-        <v>0.7435053893211944</v>
+        <v>0.140904301135952</v>
       </c>
       <c r="N36">
-        <v>11.2</v>
+        <v>1</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -2880,68 +2790,68 @@
         </is>
       </c>
       <c r="P36">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="Q36">
-        <v>5.496096239</v>
+        <v>3.345633474666667</v>
       </c>
       <c r="R36">
-        <v>0.8077843116883603</v>
+        <v>0.8527098402866575</v>
       </c>
       <c r="S36">
-        <v>1.333333333333333</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="T36">
-        <v>0.1666666666666667</v>
+        <v>0.2083333333333333</v>
       </c>
       <c r="W36">
-        <v>0.6721623925009578</v>
+        <v>0.3915823496769599</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>B2A19</t>
+          <t>B2A14</t>
         </is>
       </c>
       <c r="B37">
-        <v>0.7742258026830298</v>
+        <v>1.365713000697533</v>
       </c>
       <c r="C37">
-        <v>0.9289334359749705</v>
+        <v>0.9367190416959195</v>
       </c>
       <c r="D37">
-        <v>971.6103559477901</v>
+        <v>1004.951093615742</v>
       </c>
       <c r="E37">
-        <v>2.805361940402622</v>
+        <v>3.163390120458246</v>
       </c>
       <c r="F37">
-        <v>0.8377318979071418</v>
+        <v>0.8587307075343737</v>
       </c>
       <c r="G37">
-        <v>0.709872773792828</v>
+        <v>0.7210649319415701</v>
       </c>
       <c r="H37">
-        <v>161.3252078546875</v>
+        <v>144.923307941875</v>
       </c>
       <c r="I37">
-        <v>0.4886210703810875</v>
+        <v>0.313459859466606</v>
       </c>
       <c r="J37">
-        <v>169.8209166666667</v>
+        <v>330.4918833333333</v>
       </c>
       <c r="K37">
-        <v>0.2381006711132589</v>
+        <v>0.4601705693029016</v>
       </c>
       <c r="L37">
-        <v>21.82805563583333</v>
+        <v>18.41559329854167</v>
       </c>
       <c r="M37">
-        <v>0.7651530245215595</v>
+        <v>0.2896656859547942</v>
       </c>
       <c r="N37">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -2949,68 +2859,68 @@
         </is>
       </c>
       <c r="P37">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Q37">
-        <v>2.3825254305</v>
+        <v>1.730854418</v>
       </c>
       <c r="R37">
-        <v>0.9166756283680236</v>
+        <v>0.9292188687422164</v>
       </c>
       <c r="S37">
-        <v>2</v>
+        <v>5.666666666666667</v>
       </c>
       <c r="T37">
-        <v>0.25</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="W37">
-        <v>0.6418860627573587</v>
+        <v>0.6521703747464643</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>B2A20</t>
+          <t>B2A15</t>
         </is>
       </c>
       <c r="B38">
-        <v>2.404323882427713</v>
+        <v>4.138422420662683</v>
       </c>
       <c r="C38">
-        <v>0.7793059382219916</v>
+        <v>0.6641467020824199</v>
       </c>
       <c r="D38">
-        <v>962.3463114578503</v>
+        <v>736.0154404505465</v>
       </c>
       <c r="E38">
-        <v>2.61686311036833</v>
+        <v>2.332496835604216</v>
       </c>
       <c r="F38">
-        <v>0.8297443486541463</v>
+        <v>0.6133964414115498</v>
       </c>
       <c r="G38">
-        <v>0.6621747618514734</v>
+        <v>0.4271450080044754</v>
       </c>
       <c r="H38">
-        <v>125.714529449375</v>
+        <v>67.318532718125</v>
       </c>
       <c r="I38">
-        <v>0.3807636063753785</v>
+        <v>0.02584096965940489</v>
       </c>
       <c r="J38">
-        <v>155.9118333333333</v>
+        <v>449.8763333333333</v>
       </c>
       <c r="K38">
-        <v>0.2185991742350068</v>
+        <v>0.6285545678292791</v>
       </c>
       <c r="L38">
-        <v>22.12220689805556</v>
+        <v>18.939353515625</v>
       </c>
       <c r="M38">
-        <v>0.7754640999426193</v>
+        <v>0.3164315377361496</v>
       </c>
       <c r="N38">
-        <v>1.88135593220339</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -3018,68 +2928,68 @@
         </is>
       </c>
       <c r="P38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q38">
-        <v>11.5596577745</v>
+        <v>5.754061869666667</v>
       </c>
       <c r="R38">
-        <v>0.5957225857863083</v>
+        <v>0.7385973145850881</v>
       </c>
       <c r="S38">
-        <v>0.3333333333333333</v>
+        <v>4.333333333333333</v>
       </c>
       <c r="T38">
-        <v>0.04166666666666666</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="W38">
-        <v>0.5354301477166988</v>
+        <v>0.4944724009968792</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>B2A21</t>
+          <t>B2A16</t>
         </is>
       </c>
       <c r="B39">
-        <v>1.57617971818797</v>
+        <v>1.406406261621896</v>
       </c>
       <c r="C39">
-        <v>0.8553216949507725</v>
+        <v>0.9327186739484778</v>
       </c>
       <c r="D39">
-        <v>1151.611594239395</v>
+        <v>877.0060330270752</v>
       </c>
       <c r="E39">
-        <v>3.091423669845631</v>
+        <v>2.576887445112982</v>
       </c>
       <c r="F39">
-        <v>0.9929307160924066</v>
+        <v>0.7420139123674653</v>
       </c>
       <c r="G39">
-        <v>0.7822582405060957</v>
+        <v>0.5135956637831848</v>
       </c>
       <c r="H39">
-        <v>151.1668673634375</v>
+        <v>173.841501374375</v>
       </c>
       <c r="I39">
-        <v>0.457853533985901</v>
+        <v>0.4206364947484525</v>
       </c>
       <c r="J39">
-        <v>557.3905416666666</v>
+        <v>478.5481916666667</v>
       </c>
       <c r="K39">
-        <v>0.7815000922619931</v>
+        <v>0.6689943583660577</v>
       </c>
       <c r="L39">
-        <v>21.60189906472222</v>
+        <v>21.43688112</v>
       </c>
       <c r="M39">
-        <v>0.7572254112110538</v>
+        <v>0.4440633270515046</v>
       </c>
       <c r="N39">
-        <v>6.915254237288136</v>
+        <v>3.610169491525424</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -3087,74 +2997,74 @@
         </is>
       </c>
       <c r="P39">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q39">
-        <v>6.628213125</v>
+        <v>4.4228744065</v>
       </c>
       <c r="R39">
-        <v>0.7681906406482559</v>
+        <v>0.8016696334132396</v>
       </c>
       <c r="S39">
-        <v>4.666666666666667</v>
+        <v>5.666666666666667</v>
       </c>
       <c r="T39">
-        <v>0.5833333333333334</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="U39">
-        <v>5.419354838709677</v>
+        <v>10.38050314465409</v>
       </c>
       <c r="V39">
-        <v>0.3564140114783297</v>
+        <v>0.6070620890020189</v>
       </c>
       <c r="W39">
-        <v>0.7038919638297936</v>
+        <v>0.6487874984459705</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>B2A22</t>
+          <t>B2A17</t>
         </is>
       </c>
       <c r="B40">
-        <v>3.67911496942543</v>
+        <v>2.906916865566272</v>
       </c>
       <c r="C40">
-        <v>0.6622922426196116</v>
+        <v>0.7852103620471447</v>
       </c>
       <c r="D40">
-        <v>1159.810624825328</v>
+        <v>985.8426334202379</v>
       </c>
       <c r="E40">
-        <v>3.445955299958285</v>
+        <v>2.923565604627012</v>
       </c>
       <c r="F40">
-        <v>1</v>
+        <v>0.8412991769670165</v>
       </c>
       <c r="G40">
-        <v>0.8719694282287189</v>
+        <v>0.6362294846750176</v>
       </c>
       <c r="H40">
-        <v>181.2209807528125</v>
+        <v>124.1271808390625</v>
       </c>
       <c r="I40">
-        <v>0.5488812986418652</v>
+        <v>0.2363852339380231</v>
       </c>
       <c r="J40">
-        <v>562.0825416666667</v>
+        <v>330.23375</v>
       </c>
       <c r="K40">
-        <v>0.7880786007919891</v>
+        <v>0.4598064890326519</v>
       </c>
       <c r="L40">
-        <v>22.60901490388889</v>
+        <v>19.872664053125</v>
       </c>
       <c r="M40">
-        <v>0.7925284974427435</v>
+        <v>0.3641267438589305</v>
       </c>
       <c r="N40">
-        <v>11.22033898305085</v>
+        <v>6.220338983050848</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
@@ -3162,470 +3072,446 @@
         </is>
       </c>
       <c r="P40">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="Q40">
-        <v>25.94770115</v>
+        <v>3.12606545625</v>
       </c>
       <c r="R40">
-        <v>0.0925276742316562</v>
+        <v>0.863113081336643</v>
       </c>
       <c r="S40">
-        <v>4.333333333333333</v>
+        <v>2</v>
       </c>
       <c r="T40">
-        <v>0.5416666666666666</v>
+        <v>0.25</v>
       </c>
       <c r="W40">
-        <v>0.6622430510779064</v>
+        <v>0.5545213214819285</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>B3A01</t>
+          <t>B2A18</t>
         </is>
       </c>
       <c r="B41">
-        <v>1.333235766632308</v>
+        <v>1.13456411529597</v>
       </c>
       <c r="C41">
-        <v>0.8776216387499751</v>
+        <v>0.9594422279192161</v>
       </c>
       <c r="D41">
-        <v>769.90286227345</v>
+        <v>1091.19812954318</v>
       </c>
       <c r="E41">
-        <v>2.366237997369227</v>
+        <v>3.047672135596225</v>
       </c>
       <c r="F41">
-        <v>0.6638177352353538</v>
+        <v>0.9374088337533967</v>
       </c>
       <c r="G41">
-        <v>0.598756226943539</v>
+        <v>0.6801308891122624</v>
       </c>
       <c r="H41">
-        <v>133.0338306171875</v>
+        <v>175.416226305</v>
       </c>
       <c r="I41">
-        <v>0.4029322731238477</v>
+        <v>0.4264727417447518</v>
       </c>
       <c r="J41">
-        <v>234.8489166666667</v>
+        <v>370.9917916666666</v>
       </c>
       <c r="K41">
-        <v>0.3292744248832039</v>
+        <v>0.5172930547280841</v>
       </c>
       <c r="L41">
-        <v>19.02259681722222</v>
+        <v>21.186137615625</v>
       </c>
       <c r="M41">
-        <v>0.6668114527368942</v>
+        <v>0.4312495178801773</v>
       </c>
       <c r="N41">
-        <v>1</v>
+        <v>11.2</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>B3</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="P41">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="Q41">
-        <v>4.1289946215</v>
+        <v>3.69489422</v>
       </c>
       <c r="R41">
-        <v>0.8555961342934773</v>
+        <v>0.8361616938434666</v>
       </c>
       <c r="S41">
-        <v>0.6666666666666666</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="T41">
-        <v>0.08333333333333333</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="W41">
-        <v>0.559767902412453</v>
+        <v>0.6193532032060027</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>B3A02</t>
+          <t>B2A19</t>
         </is>
       </c>
       <c r="B42">
-        <v>2.775396414933245</v>
+        <v>0.7742258026830298</v>
       </c>
       <c r="C42">
-        <v>0.745245009487961</v>
+        <v>0.9948654339046902</v>
       </c>
       <c r="D42">
-        <v>696.5614238650267</v>
+        <v>971.6103559477901</v>
       </c>
       <c r="E42">
-        <v>1.964231324205769</v>
+        <v>2.805361940402622</v>
       </c>
       <c r="F42">
-        <v>0.6005820337867067</v>
+        <v>0.8283159026861067</v>
       </c>
       <c r="G42">
-        <v>0.4970318868318977</v>
+        <v>0.5944161584257603</v>
       </c>
       <c r="H42">
-        <v>108.986184225625</v>
+        <v>161.3252078546875</v>
       </c>
       <c r="I42">
-        <v>0.3300968689347202</v>
+        <v>0.3742485961139383</v>
       </c>
       <c r="J42">
-        <v>144.7225</v>
+        <v>169.8209166666667</v>
       </c>
       <c r="K42">
-        <v>0.2029109549727941</v>
+        <v>0.233554625480807</v>
       </c>
       <c r="L42">
-        <v>18.15723085875</v>
+        <v>21.99163470125</v>
       </c>
       <c r="M42">
-        <v>0.6364772172241332</v>
+        <v>0.4724130406162352</v>
       </c>
       <c r="N42">
-        <v>1.932203389830508</v>
+        <v>2</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>B3</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="P42">
         <v>2</v>
       </c>
       <c r="Q42">
-        <v>19.2733721</v>
+        <v>1.35963345075</v>
       </c>
       <c r="R42">
-        <v>0.3259498518239368</v>
+        <v>0.9468075013352468</v>
       </c>
       <c r="S42">
-        <v>0.6666666666666666</v>
+        <v>2</v>
       </c>
       <c r="T42">
-        <v>0.08333333333333333</v>
+        <v>0.25</v>
       </c>
       <c r="W42">
-        <v>0.4277033945494354</v>
+        <v>0.586827657320348</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>B3A03</t>
+          <t>B2A20</t>
         </is>
       </c>
       <c r="B43">
-        <v>1.815511680039976</v>
+        <v>2.404323882427713</v>
       </c>
       <c r="C43">
-        <v>0.8333532974480676</v>
+        <v>0.834617971910975</v>
       </c>
       <c r="D43">
-        <v>890.8958090422312</v>
+        <v>962.3463114578503</v>
       </c>
       <c r="E43">
-        <v>2.573170232495415</v>
+        <v>2.61686311036833</v>
       </c>
       <c r="F43">
-        <v>0.7681390306080387</v>
+        <v>0.8198648567592489</v>
       </c>
       <c r="G43">
-        <v>0.6511186539161865</v>
+        <v>0.5277366427817703</v>
       </c>
       <c r="H43">
-        <v>119.8886665934375</v>
+        <v>125.714529449375</v>
       </c>
       <c r="I43">
-        <v>0.3631182589283404</v>
+        <v>0.2422682668276714</v>
       </c>
       <c r="J43">
-        <v>280.7613333333333</v>
+        <v>155.9118333333333</v>
       </c>
       <c r="K43">
-        <v>0.393646808658651</v>
+        <v>0.2139367684860035</v>
       </c>
       <c r="L43">
-        <v>16.84926868772222</v>
+        <v>21.91894548875</v>
       </c>
       <c r="M43">
-        <v>0.5906283689428977</v>
+        <v>0.4686983852750701</v>
       </c>
       <c r="N43">
-        <v>3.491525423728814</v>
+        <v>1.88135593220339</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>B3</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="P43">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q43">
-        <v>4.188993805</v>
+        <v>6.598724384</v>
       </c>
       <c r="R43">
-        <v>0.8534977750484638</v>
+        <v>0.6985767878897056</v>
       </c>
       <c r="S43">
-        <v>2.333333333333333</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="T43">
-        <v>0.2916666666666667</v>
+        <v>0.04166666666666666</v>
       </c>
       <c r="W43">
-        <v>0.593146107527164</v>
+        <v>0.4809207933246389</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>B3A04</t>
+          <t>B2A21</t>
         </is>
       </c>
       <c r="B44">
-        <v>0.983265948598725</v>
+        <v>1.57617971818797</v>
       </c>
       <c r="C44">
-        <v>0.9097455390306455</v>
+        <v>0.9160290244932286</v>
       </c>
       <c r="D44">
-        <v>772.0165795662651</v>
+        <v>1151.611594239395</v>
       </c>
       <c r="E44">
-        <v>2.672861675954276</v>
+        <v>3.091423669845631</v>
       </c>
       <c r="F44">
-        <v>0.6656402028413334</v>
+        <v>0.9925205039642586</v>
       </c>
       <c r="G44">
-        <v>0.676344718500707</v>
+        <v>0.6956075427970684</v>
       </c>
       <c r="H44">
-        <v>155.2948253259375</v>
+        <v>151.1668673634375</v>
       </c>
       <c r="I44">
-        <v>0.47035627466076</v>
+        <v>0.3365997451772152</v>
       </c>
       <c r="J44">
-        <v>363.53175</v>
+        <v>557.3905416666666</v>
       </c>
       <c r="K44">
-        <v>0.509696657779067</v>
+        <v>0.780196362866779</v>
       </c>
       <c r="L44">
-        <v>17.18627932666667</v>
+        <v>21.42118804020833</v>
       </c>
       <c r="M44">
-        <v>0.6024418219588855</v>
+        <v>0.4432613595977034</v>
       </c>
       <c r="N44">
-        <v>6.35593220338983</v>
+        <v>6.915254237288136</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>B3</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="P44">
         <v>8</v>
       </c>
       <c r="Q44">
-        <v>10.51540466</v>
+        <v>3.78289459325</v>
       </c>
       <c r="R44">
-        <v>0.6322433857226123</v>
+        <v>0.831992192738478</v>
+      </c>
+      <c r="S44">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="T44">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="U44">
+        <v>5.419354838709677</v>
+      </c>
+      <c r="V44">
+        <v>0.2030131588813034</v>
       </c>
       <c r="W44">
-        <v>0.6380669429277158</v>
+        <v>0.6425059137610408</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>B3A05</t>
+          <t>B2A22</t>
         </is>
       </c>
       <c r="B45">
-        <v>1.469352354643475</v>
+        <v>3.67911496942543</v>
       </c>
       <c r="C45">
-        <v>0.8651274307511693</v>
+        <v>0.7092991099345289</v>
       </c>
       <c r="D45">
-        <v>972.281952784939</v>
+        <v>1159.810624825328</v>
       </c>
       <c r="E45">
-        <v>2.964106549473492</v>
+        <v>3.445955299958285</v>
       </c>
       <c r="F45">
-        <v>0.8383109552314787</v>
+        <v>1</v>
       </c>
       <c r="G45">
-        <v>0.7500417353599131</v>
+        <v>0.8210194478581516</v>
       </c>
       <c r="H45">
-        <v>112.6675989174194</v>
+        <v>181.2209807528125</v>
       </c>
       <c r="I45">
-        <v>0.3412471213419044</v>
+        <v>0.4479863280552536</v>
       </c>
       <c r="J45">
-        <v>559.8954583333333</v>
+        <v>562.0825416666667</v>
       </c>
       <c r="K45">
-        <v>0.7850121586853936</v>
+        <v>0.7868141235641375</v>
       </c>
       <c r="L45">
-        <v>20.13906762361111</v>
+        <v>22.94683949083333</v>
       </c>
       <c r="M45">
-        <v>0.7059478297257863</v>
+        <v>0.5212271142799483</v>
       </c>
       <c r="N45">
-        <v>5.491525423728813</v>
+        <v>11.22033898305085</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>B3</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="P45">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Q45">
-        <v>13.8868205085</v>
+        <v>13.236153298</v>
       </c>
       <c r="R45">
-        <v>0.5143344209367068</v>
+        <v>0.3840921309600713</v>
       </c>
       <c r="S45">
-        <v>3.666666666666667</v>
+        <v>4.333333333333333</v>
       </c>
       <c r="T45">
-        <v>0.4583333333333333</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="W45">
-        <v>0.6572943731707107</v>
+        <v>0.6515131151648448</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>B3A06</t>
+          <t>B2A23</t>
         </is>
       </c>
       <c r="B46">
-        <v>0.7231897938302607</v>
+        <v>5.981748578534632</v>
       </c>
       <c r="C46">
-        <v>0.9336180561182779</v>
-      </c>
-      <c r="D46">
-        <v>884.1512260972701</v>
-      </c>
-      <c r="E46">
-        <v>2.829127670606511</v>
-      </c>
-      <c r="F46">
-        <v>0.762323785601142</v>
-      </c>
-      <c r="G46">
-        <v>0.7158864879514457</v>
-      </c>
-      <c r="H46">
-        <v>202.9518392865625</v>
-      </c>
-      <c r="I46">
-        <v>0.6146996260952234</v>
-      </c>
-      <c r="J46">
-        <v>260.8305</v>
-      </c>
-      <c r="K46">
-        <v>0.3657024017760291</v>
+        <v>0.4829377661931928</v>
       </c>
       <c r="L46">
-        <v>20.59998615166667</v>
+        <v>16.410262208</v>
       </c>
       <c r="M46">
-        <v>0.7221047065307353</v>
-      </c>
-      <c r="N46">
-        <v>1</v>
+        <v>0.1871867404539718</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>B3</t>
-        </is>
-      </c>
-      <c r="P46">
-        <v>1</v>
-      </c>
-      <c r="Q46">
-        <v>4.674182018</v>
-      </c>
-      <c r="R46">
-        <v>0.8365292245961053</v>
+          <t>B2</t>
+        </is>
       </c>
       <c r="W46">
-        <v>0.7072663269527084</v>
+        <v>0.3350622533235823</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>B3A07</t>
+          <t>B3A01</t>
         </is>
       </c>
       <c r="B47">
-        <v>1.235925826614334</v>
+        <v>1.333235766632308</v>
       </c>
       <c r="C47">
-        <v>0.8865537656031411</v>
+        <v>0.9399117295447043</v>
       </c>
       <c r="D47">
-        <v>963.5470426919795</v>
+        <v>769.90286227345</v>
       </c>
       <c r="E47">
-        <v>2.690502686665903</v>
+        <v>2.366237997369227</v>
       </c>
       <c r="F47">
-        <v>0.8307796308014451</v>
+        <v>0.6443099542383888</v>
       </c>
       <c r="G47">
-        <v>0.6808086249314667</v>
+        <v>0.4390805957391429</v>
       </c>
       <c r="H47">
-        <v>107.9302736590323</v>
+        <v>133.0338306171875</v>
       </c>
       <c r="I47">
-        <v>0.3268987317177518</v>
+        <v>0.2693950675945206</v>
       </c>
       <c r="J47">
-        <v>574.8780416666667</v>
+        <v>234.8489166666667</v>
       </c>
       <c r="K47">
-        <v>0.8060187768140616</v>
+        <v>0.3252723881892107</v>
       </c>
       <c r="L47">
-        <v>19.82994771638889</v>
+        <v>18.75657013854167</v>
       </c>
       <c r="M47">
-        <v>0.695112048660494</v>
+        <v>0.3070907122600335</v>
       </c>
       <c r="N47">
-        <v>6.203389830508475</v>
+        <v>1</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -3633,68 +3519,68 @@
         </is>
       </c>
       <c r="P47">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Q47">
-        <v>2.032820474</v>
+        <v>2.06449731075</v>
       </c>
       <c r="R47">
-        <v>0.9289059052766881</v>
+        <v>0.9134107038604532</v>
       </c>
       <c r="S47">
-        <v>6</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="T47">
-        <v>0.75</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="W47">
-        <v>0.7381346854756311</v>
+        <v>0.4902255605949734</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>B3A08</t>
+          <t>B3A02</t>
         </is>
       </c>
       <c r="B48">
-        <v>1.079519997394771</v>
+        <v>2.775396414933245</v>
       </c>
       <c r="C48">
-        <v>0.9009103329477076</v>
+        <v>0.7981395340252586</v>
       </c>
       <c r="D48">
-        <v>800.328067796833</v>
+        <v>696.5614238650267</v>
       </c>
       <c r="E48">
-        <v>2.308053410886439</v>
+        <v>1.964231324205769</v>
       </c>
       <c r="F48">
-        <v>0.6900506433258149</v>
+        <v>0.5774048497773214</v>
       </c>
       <c r="G48">
-        <v>0.5840331164586947</v>
+        <v>0.2968748841847817</v>
       </c>
       <c r="H48">
-        <v>115.11182788125</v>
+        <v>108.986184225625</v>
       </c>
       <c r="I48">
-        <v>0.3486501911314636</v>
+        <v>0.1802696582666082</v>
       </c>
       <c r="J48">
-        <v>240.8029166666667</v>
+        <v>144.7225</v>
       </c>
       <c r="K48">
-        <v>0.3376223447015321</v>
+        <v>0.1981549418954287</v>
       </c>
       <c r="L48">
-        <v>20.03235579944445</v>
+        <v>17.8247310559375</v>
       </c>
       <c r="M48">
-        <v>0.7022071907804054</v>
+        <v>0.259470702271591</v>
       </c>
       <c r="N48">
-        <v>1.864406779661017</v>
+        <v>1.932203389830508</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -3705,59 +3591,65 @@
         <v>2</v>
       </c>
       <c r="Q48">
-        <v>4.697584461000001</v>
+        <v>9.63668605</v>
       </c>
       <c r="R48">
-        <v>0.8357107679145248</v>
+        <v>0.5546366651891479</v>
+      </c>
+      <c r="S48">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="T48">
+        <v>0.08333333333333333</v>
       </c>
       <c r="W48">
-        <v>0.6284549410371633</v>
+        <v>0.3685355711179338</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>B3A09</t>
+          <t>B3A03</t>
         </is>
       </c>
       <c r="B49">
-        <v>0.8097760221559134</v>
+        <v>1.815511680039976</v>
       </c>
       <c r="C49">
-        <v>0.9256702639913987</v>
+        <v>0.8925013975747504</v>
       </c>
       <c r="D49">
-        <v>922.4330881276862</v>
+        <v>890.8958090422312</v>
       </c>
       <c r="E49">
-        <v>3.070241885028659</v>
+        <v>2.573170232495415</v>
       </c>
       <c r="F49">
-        <v>0.795330779338746</v>
+        <v>0.7546847426020699</v>
       </c>
       <c r="G49">
-        <v>0.7768983715617881</v>
+        <v>0.5122807381847606</v>
       </c>
       <c r="H49">
-        <v>254.4268867953125</v>
+        <v>119.8886665934375</v>
       </c>
       <c r="I49">
-        <v>0.7706070205198943</v>
+        <v>0.2206764485154273</v>
       </c>
       <c r="J49">
-        <v>433.2290416666667</v>
+        <v>280.7613333333333</v>
       </c>
       <c r="K49">
-        <v>0.6074170814250149</v>
+        <v>0.3900288644333315</v>
       </c>
       <c r="L49">
-        <v>22.44358842277778</v>
+        <v>16.74420179975</v>
       </c>
       <c r="M49">
-        <v>0.7867296954573603</v>
+        <v>0.2042521404694234</v>
       </c>
       <c r="N49">
-        <v>11.5</v>
+        <v>3.491525423728814</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -3765,62 +3657,68 @@
         </is>
       </c>
       <c r="P49">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="Q49">
-        <v>12.379006285</v>
+        <v>2.79178667325</v>
       </c>
       <c r="R49">
-        <v>0.5670674038054467</v>
+        <v>0.8789513750122068</v>
+      </c>
+      <c r="S49">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="T49">
+        <v>0.2916666666666667</v>
       </c>
       <c r="W49">
-        <v>0.7471029451570927</v>
+        <v>0.5181302966823296</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>B3A11</t>
+          <t>B3A04</t>
         </is>
       </c>
       <c r="B50">
-        <v>1.167208942651994</v>
+        <v>0.983265948598725</v>
       </c>
       <c r="C50">
-        <v>0.8928613218958749</v>
+        <v>0.9743156564072326</v>
       </c>
       <c r="D50">
-        <v>874.7313058615135</v>
+        <v>772.0165795662651</v>
       </c>
       <c r="E50">
-        <v>2.721435365830919</v>
+        <v>2.672861675954276</v>
       </c>
       <c r="F50">
-        <v>0.7542018387641959</v>
+        <v>0.6462381748916222</v>
       </c>
       <c r="G50">
-        <v>0.6886358740444857</v>
+        <v>0.5475455574012923</v>
       </c>
       <c r="H50">
-        <v>231.912202086875</v>
+        <v>155.2948253259375</v>
       </c>
       <c r="I50">
-        <v>0.7024146438428492</v>
+        <v>0.3518987868009025</v>
       </c>
       <c r="J50">
-        <v>315.6002083333333</v>
+        <v>363.53175</v>
       </c>
       <c r="K50">
-        <v>0.4424933210974757</v>
+        <v>0.5067711513729426</v>
       </c>
       <c r="L50">
-        <v>21.90207657555555</v>
+        <v>17.139229081875</v>
       </c>
       <c r="M50">
-        <v>0.7677477286423154</v>
+        <v>0.2244393202858452</v>
       </c>
       <c r="N50">
-        <v>3.254237288135593</v>
+        <v>6.35593220338983</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -3828,68 +3726,62 @@
         </is>
       </c>
       <c r="P50">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q50">
-        <v>3.746202177</v>
+        <v>5.7939364345</v>
       </c>
       <c r="R50">
-        <v>0.8689835842216557</v>
-      </c>
-      <c r="S50">
-        <v>0</v>
-      </c>
-      <c r="T50">
-        <v>0</v>
+        <v>0.7367080380287125</v>
       </c>
       <c r="W50">
-        <v>0.6396672890636066</v>
+        <v>0.5697023835983642</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>B3A12</t>
+          <t>B3A05</t>
         </is>
       </c>
       <c r="B51">
-        <v>8.03801840660449</v>
+        <v>1.469352354643475</v>
       </c>
       <c r="C51">
-        <v>0.2621863702452848</v>
+        <v>0.9265307323917905</v>
       </c>
       <c r="D51">
-        <v>771.2549657006074</v>
+        <v>972.281952784939</v>
       </c>
       <c r="E51">
-        <v>2.128997105629884</v>
+        <v>2.964106549473492</v>
       </c>
       <c r="F51">
-        <v>0.6649835319595915</v>
+        <v>0.8289285611984056</v>
       </c>
       <c r="G51">
-        <v>0.5387244544115707</v>
+        <v>0.6505704254947626</v>
       </c>
       <c r="H51">
-        <v>115.4052684690625</v>
+        <v>112.6675989174194</v>
       </c>
       <c r="I51">
-        <v>0.3495389626757058</v>
+        <v>0.1939137208068444</v>
       </c>
       <c r="J51">
-        <v>137.2265833333333</v>
+        <v>559.8954583333333</v>
       </c>
       <c r="K51">
-        <v>0.1924011613385643</v>
+        <v>0.7837293848332805</v>
       </c>
       <c r="L51">
-        <v>23.97247089055556</v>
+        <v>20.12160857166667</v>
       </c>
       <c r="M51">
-        <v>0.8403226065198436</v>
+        <v>0.3768486189989947</v>
       </c>
       <c r="N51">
-        <v>1</v>
+        <v>5.491525423728813</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -3897,68 +3789,68 @@
         </is>
       </c>
       <c r="P51">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Q51">
-        <v>12.95935475</v>
+        <v>7.691581521</v>
       </c>
       <c r="R51">
-        <v>0.546770801488149</v>
+        <v>0.6467966775102746</v>
       </c>
       <c r="S51">
-        <v>0.6666666666666666</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="T51">
-        <v>0.08333333333333333</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="W51">
-        <v>0.4347826527465053</v>
+        <v>0.6082064318209608</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>B3A13</t>
+          <t>B3A06</t>
         </is>
       </c>
       <c r="B52">
-        <v>1.145410111775375</v>
+        <v>0.7231897938302607</v>
       </c>
       <c r="C52">
-        <v>0.8948622472135219</v>
+        <v>0.9998825497399692</v>
       </c>
       <c r="D52">
-        <v>870.8383767477686</v>
+        <v>884.1512260972701</v>
       </c>
       <c r="E52">
-        <v>2.965250120862364</v>
+        <v>2.829127670606511</v>
       </c>
       <c r="F52">
-        <v>0.7508453174231958</v>
+        <v>0.7485320540773909</v>
       </c>
       <c r="G52">
-        <v>0.7503311062899729</v>
+        <v>0.6028230402012745</v>
       </c>
       <c r="H52">
-        <v>268.7253422890625</v>
+        <v>202.9518392865625</v>
       </c>
       <c r="I52">
-        <v>0.813914118778497</v>
+        <v>0.5285252560788698</v>
       </c>
       <c r="J52">
-        <v>359.9379166666667</v>
+        <v>260.8305</v>
       </c>
       <c r="K52">
-        <v>0.5046578548722646</v>
+        <v>0.3619177208913587</v>
       </c>
       <c r="L52">
-        <v>20.57208616027778</v>
+        <v>20.597621738125</v>
       </c>
       <c r="M52">
-        <v>0.7211267099949243</v>
+        <v>0.4011744410905382</v>
       </c>
       <c r="N52">
-        <v>3.033898305084746</v>
+        <v>1</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -3966,62 +3858,62 @@
         </is>
       </c>
       <c r="P52">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q52">
-        <v>6.039216124</v>
+        <v>2.337091009</v>
       </c>
       <c r="R52">
-        <v>0.7887897093394741</v>
+        <v>0.9004950799364797</v>
       </c>
       <c r="W52">
-        <v>0.7463610091302644</v>
+        <v>0.649050020287983</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>B3A16</t>
+          <t>B3A07</t>
         </is>
       </c>
       <c r="B53">
-        <v>1.626887657587317</v>
+        <v>1.235925826614334</v>
       </c>
       <c r="C53">
-        <v>0.850667188462597</v>
+        <v>0.9494778232101132</v>
       </c>
       <c r="D53">
-        <v>941.7955308036528</v>
+        <v>963.5470426919795</v>
       </c>
       <c r="E53">
-        <v>2.753839423059208</v>
+        <v>2.690502686665903</v>
       </c>
       <c r="F53">
-        <v>0.8120252657156772</v>
+        <v>0.8209602136324221</v>
       </c>
       <c r="G53">
-        <v>0.6968354427544988</v>
+        <v>0.5537858828691359</v>
       </c>
       <c r="H53">
-        <v>102.683986036875</v>
+        <v>107.9302736590323</v>
       </c>
       <c r="I53">
-        <v>0.3110087991551077</v>
+        <v>0.1763562415467805</v>
       </c>
       <c r="J53">
-        <v>548.5222083333333</v>
+        <v>574.8780416666667</v>
       </c>
       <c r="K53">
-        <v>0.7690660755356117</v>
+        <v>0.8048613437267657</v>
       </c>
       <c r="L53">
-        <v>17.95481773666667</v>
+        <v>19.94108721166667</v>
       </c>
       <c r="M53">
-        <v>0.6293818984679053</v>
+        <v>0.36762338995805</v>
       </c>
       <c r="N53">
-        <v>10.33898305084746</v>
+        <v>6.203389830508475</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -4029,74 +3921,68 @@
         </is>
       </c>
       <c r="P53">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="Q53">
-        <v>1.8869790155</v>
+        <v>1.34282915525</v>
       </c>
       <c r="R53">
-        <v>0.9340064375655935</v>
+        <v>0.9476036971474709</v>
       </c>
       <c r="S53">
-        <v>3.666666666666667</v>
+        <v>6</v>
       </c>
       <c r="T53">
-        <v>0.4583333333333333</v>
-      </c>
-      <c r="U53">
-        <v>3.789203084832905</v>
-      </c>
-      <c r="V53">
-        <v>0.2492040311006671</v>
+        <v>0.75</v>
       </c>
       <c r="W53">
-        <v>0.6345031635656657</v>
+        <v>0.6713335740113423</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>B3A17</t>
+          <t>B3A08</t>
         </is>
       </c>
       <c r="B54">
-        <v>3.404752088070881</v>
+        <v>1.079519997394771</v>
       </c>
       <c r="C54">
-        <v>0.6874761453083433</v>
+        <v>0.964853362562557</v>
       </c>
       <c r="D54">
-        <v>803.6205597323058</v>
+        <v>800.328067796833</v>
       </c>
       <c r="E54">
-        <v>2.029796058820261</v>
+        <v>2.308053410886439</v>
       </c>
       <c r="F54">
-        <v>0.6928894618923964</v>
+        <v>0.6720650896429542</v>
       </c>
       <c r="G54">
-        <v>0.513622480492372</v>
+        <v>0.4184983987891018</v>
       </c>
       <c r="H54">
-        <v>89.29260579419355</v>
+        <v>115.11182788125</v>
       </c>
       <c r="I54">
-        <v>0.2704490463733044</v>
+        <v>0.2029725244562933</v>
       </c>
       <c r="J54">
-        <v>65.56358333333333</v>
+        <v>240.8029166666667</v>
       </c>
       <c r="K54">
-        <v>0.09192467864779168</v>
+        <v>0.3336701177697888</v>
       </c>
       <c r="L54">
-        <v>18.64826876722222</v>
+        <v>19.97367921229167</v>
       </c>
       <c r="M54">
-        <v>0.6536898882512985</v>
+        <v>0.3692889472675465</v>
       </c>
       <c r="N54">
-        <v>1</v>
+        <v>1.864406779661017</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -4104,62 +3990,62 @@
         </is>
       </c>
       <c r="P54">
-        <v>1</v>
-      </c>
-      <c r="S54">
-        <v>1</v>
-      </c>
-      <c r="T54">
-        <v>0.125</v>
+        <v>2</v>
+      </c>
+      <c r="Q54">
+        <v>2.3487922305</v>
+      </c>
+      <c r="R54">
+        <v>0.8999406702882915</v>
       </c>
       <c r="W54">
-        <v>0.4335788144236438</v>
+        <v>0.5516127301109333</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>B3A19</t>
+          <t>B3A09</t>
         </is>
       </c>
       <c r="B55">
-        <v>1.702722532239643</v>
+        <v>0.8097760221559134</v>
       </c>
       <c r="C55">
-        <v>0.8437062683329226</v>
+        <v>0.9913706549618542</v>
       </c>
       <c r="D55">
-        <v>838.7181694002497</v>
+        <v>922.4330881276862</v>
       </c>
       <c r="E55">
-        <v>2.367598667232508</v>
+        <v>3.070241885028659</v>
       </c>
       <c r="F55">
-        <v>0.7231509622759007</v>
+        <v>0.7834543576712484</v>
       </c>
       <c r="G55">
-        <v>0.5991005327802131</v>
+        <v>0.6881147050334921</v>
       </c>
       <c r="H55">
-        <v>118.3972807875</v>
+        <v>254.4268867953125</v>
       </c>
       <c r="I55">
-        <v>0.358601156247743</v>
+        <v>0.7193021248289343</v>
       </c>
       <c r="J55">
-        <v>144.3691666666667</v>
+        <v>433.2290416666667</v>
       </c>
       <c r="K55">
-        <v>0.2024155572005722</v>
+        <v>0.6050746461521413</v>
       </c>
       <c r="L55">
-        <v>19.96731887527778</v>
+        <v>22.50614931416667</v>
       </c>
       <c r="M55">
-        <v>0.6999274091973855</v>
+        <v>0.4987064119328997</v>
       </c>
       <c r="N55">
-        <v>1.983050847457627</v>
+        <v>11.5</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -4167,143 +4053,101 @@
         </is>
       </c>
       <c r="P55">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="Q55">
-        <v>1.4268861685</v>
+        <v>6.217877152250001</v>
       </c>
       <c r="R55">
-        <v>0.9500973245201965</v>
-      </c>
-      <c r="S55">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="T55">
-        <v>0.04166666666666666</v>
+        <v>0.7166215176444565</v>
       </c>
       <c r="W55">
-        <v>0.5523332346527</v>
+        <v>0.714663488317861</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>B3A20</t>
+          <t>B3A10</t>
         </is>
       </c>
       <c r="B56">
-        <v>3.520144908087444</v>
+        <v>6.435055089500657</v>
       </c>
       <c r="C56">
-        <v>0.6768841820809268</v>
+        <v>0.4383752832419159</v>
       </c>
       <c r="D56">
-        <v>917.4690102689739</v>
+        <v>750.8267404082933</v>
       </c>
       <c r="E56">
-        <v>2.654039794401924</v>
+        <v>2.78332076369537</v>
       </c>
       <c r="F56">
-        <v>0.7910507031328051</v>
+        <v>0.6269079240383133</v>
       </c>
       <c r="G56">
-        <v>0.671582002833562</v>
-      </c>
-      <c r="H56">
-        <v>151.9766271153571</v>
-      </c>
-      <c r="I56">
-        <v>0.4603061307126995</v>
-      </c>
-      <c r="J56">
-        <v>485.0668333333334</v>
-      </c>
-      <c r="K56">
-        <v>0.6800972507888947</v>
+        <v>0.586619319650709</v>
       </c>
       <c r="L56">
-        <v>19.90159328638889</v>
+        <v>19.45792183833333</v>
       </c>
       <c r="M56">
-        <v>0.69762348740216</v>
-      </c>
-      <c r="N56">
-        <v>5.186440677966102</v>
+        <v>0.3429320668168241</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="P56">
-        <v>8</v>
-      </c>
-      <c r="Q56">
-        <v>4.5886640015</v>
-      </c>
-      <c r="R56">
-        <v>0.8395200573053201</v>
-      </c>
-      <c r="S56">
-        <v>8</v>
-      </c>
-      <c r="T56">
-        <v>1</v>
-      </c>
-      <c r="U56">
-        <v>9.417177914110429</v>
-      </c>
-      <c r="V56">
-        <v>0.6193383266212503</v>
-      </c>
       <c r="W56">
-        <v>0.7151557934308465</v>
+        <v>0.4987086484369406</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>B3A21</t>
+          <t>B3A11</t>
         </is>
       </c>
       <c r="B57">
-        <v>7.967395770673756</v>
+        <v>1.167208942651994</v>
       </c>
       <c r="C57">
-        <v>0.2686688564406494</v>
+        <v>0.9562330647430684</v>
       </c>
       <c r="D57">
-        <v>863.5299298005199</v>
+        <v>874.7313058615135</v>
       </c>
       <c r="E57">
-        <v>2.677901633048614</v>
+        <v>2.721435365830919</v>
       </c>
       <c r="F57">
-        <v>0.7445439033898924</v>
+        <v>0.7399388118249205</v>
       </c>
       <c r="G57">
-        <v>0.6776200364091838</v>
+        <v>0.5647279988701689</v>
       </c>
       <c r="H57">
-        <v>143.5188982909375</v>
+        <v>231.912202086875</v>
       </c>
       <c r="I57">
-        <v>0.434689399352878</v>
+        <v>0.635858179510758</v>
       </c>
       <c r="J57">
-        <v>239.5789583333333</v>
+        <v>315.6002083333333</v>
       </c>
       <c r="K57">
-        <v>0.3359062704610818</v>
+        <v>0.4391668306982903</v>
       </c>
       <c r="L57">
-        <v>20.79732140694444</v>
+        <v>21.96201894354166</v>
       </c>
       <c r="M57">
-        <v>0.7290220275207302</v>
+        <v>0.4708995790065924</v>
       </c>
       <c r="N57">
-        <v>1.983050847457627</v>
+        <v>3.254237288135593</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -4311,68 +4155,68 @@
         </is>
       </c>
       <c r="P57">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q57">
-        <v>7.5261303</v>
+        <v>2.509934303333333</v>
       </c>
       <c r="R57">
-        <v>0.7367876665491577</v>
+        <v>0.8923056793680828</v>
       </c>
       <c r="S57">
-        <v>3.333333333333333</v>
+        <v>0</v>
       </c>
       <c r="T57">
-        <v>0.4166666666666667</v>
+        <v>0</v>
       </c>
       <c r="W57">
-        <v>0.54298810334878</v>
+        <v>0.5873912680027351</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>B3A22</t>
+          <t>B3A12</t>
         </is>
       </c>
       <c r="B58">
-        <v>1.70503530389312</v>
+        <v>8.03801840660449</v>
       </c>
       <c r="C58">
-        <v>0.8434939778948908</v>
+        <v>0.2807953152468926</v>
       </c>
       <c r="D58">
-        <v>1111.033140487697</v>
+        <v>771.2549657006074</v>
       </c>
       <c r="E58">
-        <v>3.307029389479954</v>
+        <v>2.128997105629884</v>
       </c>
       <c r="F58">
-        <v>0.9579435786381274</v>
+        <v>0.645543399109382</v>
       </c>
       <c r="G58">
-        <v>0.8368154183298063</v>
+        <v>0.3551590788297286</v>
       </c>
       <c r="H58">
-        <v>183.8040500878125</v>
+        <v>115.4052684690625</v>
       </c>
       <c r="I58">
-        <v>0.5567048875286876</v>
+        <v>0.2040600742346113</v>
       </c>
       <c r="J58">
-        <v>560.2451333333333</v>
+        <v>137.2265833333333</v>
       </c>
       <c r="K58">
-        <v>0.7855024272212476</v>
+        <v>0.1875824391871292</v>
       </c>
       <c r="L58">
-        <v>21.96775750277778</v>
+        <v>24.04860521375</v>
       </c>
       <c r="M58">
-        <v>0.7700500848831051</v>
+        <v>0.5775309286505486</v>
       </c>
       <c r="N58">
-        <v>12.3</v>
+        <v>1</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -4380,74 +4224,68 @@
         </is>
       </c>
       <c r="P58">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="Q58">
-        <v>12.729408163</v>
+        <v>5.195490260333333</v>
       </c>
       <c r="R58">
-        <v>0.5548127533705562</v>
+        <v>0.765062713041004</v>
       </c>
       <c r="S58">
-        <v>5.333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="T58">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="U58">
-        <v>10.79144385026738</v>
-      </c>
-      <c r="V58">
-        <v>0.7097194973918178</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="W58">
-        <v>0.7424121435472117</v>
+        <v>0.3873834102040787</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>B3A23</t>
+          <t>B3A13</t>
         </is>
       </c>
       <c r="B59">
-        <v>1.189745895568634</v>
+        <v>1.145410111775375</v>
       </c>
       <c r="C59">
-        <v>0.8907926439961857</v>
+        <v>0.9583760077756468</v>
       </c>
       <c r="D59">
-        <v>1050.074936152694</v>
+        <v>870.8383767477686</v>
       </c>
       <c r="E59">
-        <v>3.156049903851567</v>
+        <v>2.965250120862364</v>
       </c>
       <c r="F59">
-        <v>0.9053848220357861</v>
+        <v>0.7363875202949643</v>
       </c>
       <c r="G59">
-        <v>0.7986113546383113</v>
+        <v>0.6509749520708715</v>
       </c>
       <c r="H59">
-        <v>117.7899405009375</v>
+        <v>268.7253422890625</v>
       </c>
       <c r="I59">
-        <v>0.3567616466952556</v>
+        <v>0.7722950738222517</v>
       </c>
       <c r="J59">
-        <v>355.4359583333333</v>
+        <v>359.9379166666667</v>
       </c>
       <c r="K59">
-        <v>0.4983457979034836</v>
+        <v>0.5017022833025696</v>
       </c>
       <c r="L59">
-        <v>22.57137774055555</v>
+        <v>20.71277758875</v>
       </c>
       <c r="M59">
-        <v>0.7912091774886731</v>
+        <v>0.4070592798565461</v>
       </c>
       <c r="N59">
-        <v>3.416666666666667</v>
+        <v>3.033898305084746</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -4458,65 +4296,59 @@
         <v>4</v>
       </c>
       <c r="Q59">
-        <v>23.116575517</v>
+        <v>3.0731859965</v>
       </c>
       <c r="R59">
-        <v>0.1915409990679832</v>
-      </c>
-      <c r="S59">
-        <v>4.333333333333333</v>
-      </c>
-      <c r="T59">
-        <v>0.5416666666666666</v>
+        <v>0.865618536230936</v>
       </c>
       <c r="W59">
-        <v>0.6217891385615432</v>
+        <v>0.698916236193398</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>B3A24</t>
+          <t>B3A14</t>
         </is>
       </c>
       <c r="B60">
-        <v>1.938789752776512</v>
+        <v>1.825901354378047</v>
       </c>
       <c r="C60">
-        <v>0.8220375430277773</v>
+        <v>0.8914800363669158</v>
       </c>
       <c r="D60">
-        <v>961.8098517393934</v>
+        <v>991.9334492925896</v>
       </c>
       <c r="E60">
-        <v>2.79305649673674</v>
+        <v>3.032875255714756</v>
       </c>
       <c r="F60">
-        <v>0.8292818078677676</v>
+        <v>0.8468554720307088</v>
       </c>
       <c r="G60">
-        <v>0.7067589868329188</v>
+        <v>0.6748966455715509</v>
       </c>
       <c r="H60">
-        <v>134.8362436684375</v>
+        <v>160.5236328196875</v>
       </c>
       <c r="I60">
-        <v>0.408391413738524</v>
+        <v>0.37127779797685</v>
       </c>
       <c r="J60">
-        <v>568.57375</v>
+        <v>697.1215833333333</v>
       </c>
       <c r="K60">
-        <v>0.79717972385056</v>
+        <v>0.9772779050114151</v>
       </c>
       <c r="L60">
-        <v>25.97261220583333</v>
+        <v>19.50983015020833</v>
       </c>
       <c r="M60">
-        <v>0.9104348603269561</v>
+        <v>0.3455847505002158</v>
       </c>
       <c r="N60">
-        <v>11.28813559322034</v>
+        <v>33.78947368421053</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -4524,758 +4356,710 @@
         </is>
       </c>
       <c r="P60">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="Q60">
-        <v>28.59338011</v>
+        <v>4.3617551855</v>
       </c>
       <c r="R60">
+        <v>0.8045654922611513</v>
+      </c>
+      <c r="S60">
+        <v>5.666666666666667</v>
+      </c>
+      <c r="T60">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="U60">
+        <v>2.926640926640927</v>
+      </c>
+      <c r="V60">
         <v>0</v>
       </c>
-      <c r="S60">
-        <v>2.333333333333333</v>
-      </c>
-      <c r="T60">
-        <v>0.2916666666666667</v>
-      </c>
       <c r="W60">
-        <v>0.5957188752888963</v>
+        <v>0.6244746036724601</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>B4A02</t>
+          <t>B3A15</t>
         </is>
       </c>
       <c r="B61">
-        <v>0.7219950451524363</v>
+        <v>3.109399544191365</v>
       </c>
       <c r="C61">
-        <v>0.9337277226821048</v>
+        <v>0.7653052190679919</v>
       </c>
       <c r="D61">
-        <v>940.1657715297354</v>
+        <v>432.675640523626</v>
       </c>
       <c r="E61">
-        <v>3.062506222892643</v>
+        <v>1.12498455111615</v>
       </c>
       <c r="F61">
-        <v>0.8106200714201319</v>
+        <v>0.3366772845238523</v>
       </c>
       <c r="G61">
-        <v>0.7749409286170713</v>
-      </c>
-      <c r="H61">
-        <v>200.0871802265625</v>
-      </c>
-      <c r="I61">
-        <v>0.6060231595046155</v>
-      </c>
-      <c r="J61">
-        <v>313.8654273333333</v>
-      </c>
-      <c r="K61">
-        <v>0.440061038146458</v>
+        <v>0</v>
       </c>
       <c r="L61">
-        <v>20.31620173861111</v>
+        <v>17.99802764583333</v>
       </c>
       <c r="M61">
-        <v>0.7121570270129556</v>
-      </c>
-      <c r="N61">
-        <v>13</v>
+        <v>0.2683267220456703</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>B4</t>
-        </is>
-      </c>
-      <c r="P61">
-        <v>16</v>
-      </c>
-      <c r="Q61">
-        <v>3.8597674015</v>
-      </c>
-      <c r="R61">
-        <v>0.8650118528606515</v>
-      </c>
-      <c r="S61">
-        <v>5.333333333333333</v>
-      </c>
-      <c r="T61">
-        <v>0.6666666666666666</v>
+          <t>B3</t>
+        </is>
       </c>
       <c r="W61">
-        <v>0.7261510583638319</v>
+        <v>0.3425773064093786</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>B4A03</t>
+          <t>B3A16</t>
         </is>
       </c>
       <c r="B62">
-        <v>1.292398706065661</v>
+        <v>1.626887657587317</v>
       </c>
       <c r="C62">
-        <v>0.8813700924559824</v>
+        <v>0.911044159660464</v>
       </c>
       <c r="D62">
-        <v>666.26620934</v>
+        <v>941.7955308036528</v>
       </c>
       <c r="E62">
-        <v>2.543287669</v>
+        <v>2.753839423059208</v>
       </c>
       <c r="F62">
-        <v>0.5744612051992042</v>
+        <v>0.8011175815998943</v>
       </c>
       <c r="G62">
-        <v>0.6435571275651567</v>
+        <v>0.5761905996751149</v>
+      </c>
+      <c r="H62">
+        <v>102.683986036875</v>
+      </c>
+      <c r="I62">
+        <v>0.1569124455027409</v>
       </c>
       <c r="J62">
-        <v>4.230416666666667</v>
+        <v>548.5222083333333</v>
       </c>
       <c r="K62">
-        <v>0.005931336770482527</v>
+        <v>0.7676881557516025</v>
       </c>
       <c r="L62">
-        <v>18.13950867447222</v>
+        <v>18.17005770458333</v>
       </c>
       <c r="M62">
-        <v>0.6358559899775336</v>
+        <v>0.2771180179560043</v>
       </c>
       <c r="N62">
-        <v>0.8571428571428571</v>
+        <v>10.33898305084746</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>B4</t>
+          <t>B3</t>
         </is>
       </c>
       <c r="P62">
-        <v>1</v>
+        <v>16</v>
+      </c>
+      <c r="Q62">
+        <v>2.194161519</v>
+      </c>
+      <c r="R62">
+        <v>0.9072671496957458</v>
       </c>
       <c r="S62">
-        <v>0.3333333333333333</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="T62">
-        <v>0.04166666666666666</v>
+        <v>0.4583333333333333</v>
+      </c>
+      <c r="U62">
+        <v>3.789203084832905</v>
+      </c>
+      <c r="V62">
+        <v>0.07024932448854497</v>
       </c>
       <c r="W62">
-        <v>0.4638070697725044</v>
+        <v>0.5473245297403828</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>B4A04</t>
+          <t>B3A17</t>
         </is>
       </c>
       <c r="B63">
-        <v>4.543539835776487</v>
+        <v>3.404752088070881</v>
       </c>
       <c r="C63">
-        <v>0.5829462625496148</v>
+        <v>0.7362704657987329</v>
       </c>
       <c r="D63">
-        <v>931.0850222829723</v>
+        <v>803.6205597323058</v>
       </c>
       <c r="E63">
-        <v>3.951922152773463</v>
+        <v>2.029796058820261</v>
       </c>
       <c r="F63">
-        <v>0.8027905611083682</v>
+        <v>0.6750686374552197</v>
       </c>
       <c r="G63">
+        <v>0.3200677323665221</v>
+      </c>
+      <c r="H63">
+        <v>89.29260579419355</v>
+      </c>
+      <c r="I63">
+        <v>0.107281299645013</v>
+      </c>
+      <c r="J63">
+        <v>65.56358333333333</v>
+      </c>
+      <c r="K63">
+        <v>0.08650644070997579</v>
+      </c>
+      <c r="L63">
+        <v>18.41030944395833</v>
+      </c>
+      <c r="M63">
+        <v>0.2893956637881637</v>
+      </c>
+      <c r="N63">
         <v>1</v>
       </c>
-      <c r="H63">
-        <v>146.71501500875</v>
-      </c>
-      <c r="I63">
-        <v>0.4443697834198685</v>
-      </c>
-      <c r="J63">
-        <v>291.6330833333333</v>
-      </c>
-      <c r="K63">
-        <v>0.4088897541213501</v>
-      </c>
-      <c r="L63">
-        <v>15.80551888080556</v>
-      </c>
-      <c r="M63">
-        <v>0.5540411284240931</v>
-      </c>
-      <c r="N63">
-        <v>2.95</v>
-      </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>B4</t>
+          <t>B3</t>
         </is>
       </c>
       <c r="P63">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q63">
-        <v>23.557545837</v>
+        <v>1.707558192</v>
       </c>
       <c r="R63">
-        <v>0.1761188867362627</v>
+        <v>0.9303226554247241</v>
       </c>
       <c r="S63">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="T63">
-        <v>0.04166666666666666</v>
+        <v>0.125</v>
       </c>
       <c r="W63">
-        <v>0.5013528803782781</v>
+        <v>0.4087391118985439</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>B4A06</t>
+          <t>B3A18</t>
         </is>
       </c>
       <c r="B64">
-        <v>1.719547623997414</v>
+        <v>7.778655903268493</v>
       </c>
       <c r="C64">
-        <v>0.8421618849547311</v>
-      </c>
-      <c r="D64">
-        <v>935.1347230762776</v>
-      </c>
-      <c r="E64">
-        <v>2.488230333792243</v>
-      </c>
-      <c r="F64">
-        <v>0.8062822525161057</v>
-      </c>
-      <c r="G64">
-        <v>0.6296253411889707</v>
-      </c>
-      <c r="H64">
-        <v>190.33094006125</v>
-      </c>
-      <c r="I64">
-        <v>0.5764735027841117</v>
-      </c>
-      <c r="J64">
-        <v>153.0529166666667</v>
-      </c>
-      <c r="K64">
-        <v>0.2145907753266065</v>
+        <v>0.306292052782121</v>
       </c>
       <c r="L64">
-        <v>18.19182849305556</v>
+        <v>19.40861536033333</v>
       </c>
       <c r="M64">
-        <v>0.6376899905912089</v>
-      </c>
-      <c r="N64">
-        <v>7.689655172413793</v>
+        <v>0.3404123453126636</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>B4</t>
-        </is>
-      </c>
-      <c r="P64">
-        <v>8</v>
-      </c>
-      <c r="Q64">
-        <v>6.554619498</v>
-      </c>
-      <c r="R64">
-        <v>0.7707644401332026</v>
-      </c>
-      <c r="S64">
-        <v>2</v>
-      </c>
-      <c r="T64">
-        <v>0.25</v>
-      </c>
-      <c r="U64">
-        <v>3.131147540983607</v>
-      </c>
-      <c r="V64">
-        <v>0.2059257769284924</v>
+          <t>B3</t>
+        </is>
       </c>
       <c r="W64">
-        <v>0.54816821826927</v>
+        <v>0.3233521990473923</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>B4A07</t>
+          <t>B3A19</t>
         </is>
       </c>
       <c r="B65">
-        <v>6.244953306955439</v>
+        <v>1.702722532239643</v>
       </c>
       <c r="C65">
-        <v>0.4267726902357388</v>
+        <v>0.9035891811259514</v>
       </c>
       <c r="D65">
-        <v>899.7614602872376</v>
+        <v>838.7181694002497</v>
       </c>
       <c r="E65">
-        <v>2.162868994009377</v>
+        <v>2.367598667232508</v>
       </c>
       <c r="F65">
-        <v>0.775783081330838</v>
+        <v>0.7070861338682416</v>
       </c>
       <c r="G65">
-        <v>0.5472954452029056</v>
+        <v>0.4395619186599191</v>
       </c>
       <c r="H65">
-        <v>68.9591740921875</v>
+        <v>118.3972807875</v>
       </c>
       <c r="I65">
-        <v>0.2088632390783643</v>
+        <v>0.2151490730602286</v>
       </c>
       <c r="J65">
-        <v>184.1729583333333</v>
+        <v>144.3691666666667</v>
       </c>
       <c r="K65">
-        <v>0.2582232262127954</v>
+        <v>0.1976565882197254</v>
       </c>
       <c r="L65">
-        <v>17.647548625</v>
+        <v>19.740281801875</v>
       </c>
       <c r="M65">
-        <v>0.6186109945424156</v>
+        <v>0.3573615799540212</v>
       </c>
       <c r="N65">
-        <v>2.694915254237288</v>
+        <v>1.983050847457627</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>B4</t>
+          <t>B3</t>
         </is>
       </c>
       <c r="P65">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q65">
-        <v>3.2345367155</v>
+        <v>0.94745741625</v>
       </c>
       <c r="R65">
-        <v>0.8868781269281003</v>
+        <v>0.9663366052222869</v>
       </c>
       <c r="S65">
-        <v>3.333333333333333</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="T65">
-        <v>0.4166666666666667</v>
-      </c>
-      <c r="U65">
-        <v>6.712264150943396</v>
-      </c>
-      <c r="V65">
-        <v>0.4414446116448663</v>
+        <v>0.04166666666666666</v>
       </c>
       <c r="W65">
-        <v>0.508948675760299</v>
+        <v>0.4785509683471301</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>B4A08</t>
+          <t>B3A20</t>
         </is>
       </c>
       <c r="B66">
-        <v>1.565465264178534</v>
+        <v>3.520144908087444</v>
       </c>
       <c r="C66">
-        <v>0.8563051799098323</v>
+        <v>0.7249267271797364</v>
       </c>
       <c r="D66">
-        <v>825.6953914759764</v>
+        <v>917.4690102689739</v>
       </c>
       <c r="E66">
-        <v>2.814837724279613</v>
+        <v>2.654039794401924</v>
       </c>
       <c r="F66">
-        <v>0.7119225965017602</v>
+        <v>0.7789259197935986</v>
       </c>
       <c r="G66">
-        <v>0.7122705396168183</v>
+        <v>0.5408875110612112</v>
       </c>
       <c r="H66">
-        <v>154.55160473125</v>
+        <v>151.9766271153571</v>
       </c>
       <c r="I66">
-        <v>0.4681052114367623</v>
+        <v>0.3396008775197312</v>
       </c>
       <c r="J66">
-        <v>166.536875</v>
+        <v>485.0668333333334</v>
       </c>
       <c r="K66">
-        <v>0.2334962175503798</v>
+        <v>0.6781884782769337</v>
       </c>
       <c r="L66">
-        <v>15.04469039813889</v>
+        <v>19.92031495479167</v>
       </c>
       <c r="M66">
-        <v>0.527371313010077</v>
+        <v>0.3665618600240344</v>
       </c>
       <c r="N66">
-        <v>6.677966101694915</v>
+        <v>5.186440677966102</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>B4</t>
+          <t>B3</t>
         </is>
       </c>
       <c r="P66">
         <v>8</v>
       </c>
       <c r="Q66">
-        <v>14.8992245665</v>
+        <v>3.29197626225</v>
       </c>
       <c r="R66">
-        <v>0.4789274821940595</v>
+        <v>0.8552521454860493</v>
       </c>
       <c r="S66">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="T66">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="U66">
+        <v>9.417177914110429</v>
+      </c>
+      <c r="V66">
+        <v>0.528606355620075</v>
       </c>
       <c r="W66">
-        <v>0.4985498175274612</v>
+        <v>0.6458833194401522</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>B4A09</t>
+          <t>B3A21</t>
         </is>
       </c>
       <c r="B67">
-        <v>6.692488984265891</v>
+        <v>7.967395770673756</v>
       </c>
       <c r="C67">
-        <v>0.3856931721483144</v>
+        <v>0.2877379025107086</v>
       </c>
       <c r="D67">
-        <v>844.2071193141553</v>
+        <v>863.5299298005199</v>
       </c>
       <c r="E67">
-        <v>2.641342805042894</v>
+        <v>2.677901633048614</v>
       </c>
       <c r="F67">
-        <v>0.7278835882722631</v>
+        <v>0.7297204516218514</v>
       </c>
       <c r="G67">
-        <v>0.6683691385947966</v>
+        <v>0.5493283902064392</v>
       </c>
       <c r="H67">
-        <v>73.60762752531249</v>
+        <v>143.5188982909375</v>
       </c>
       <c r="I67">
-        <v>0.2229424541143435</v>
+        <v>0.3082548351176205</v>
       </c>
       <c r="J67">
-        <v>113.1500833333333</v>
+        <v>239.5789583333333</v>
       </c>
       <c r="K67">
-        <v>0.1586442430473347</v>
+        <v>0.3319438041820783</v>
       </c>
       <c r="L67">
-        <v>14.34343415708333</v>
+        <v>20.457332395</v>
       </c>
       <c r="M67">
-        <v>0.5027897221088958</v>
+        <v>0.3940051990555137</v>
       </c>
       <c r="N67">
-        <v>1</v>
+        <v>1.983050847457627</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>B4</t>
+          <t>B3</t>
         </is>
       </c>
       <c r="P67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q67">
-        <v>11.85427911</v>
+        <v>5.67190590325</v>
       </c>
       <c r="R67">
-        <v>0.5854187555162746</v>
+        <v>0.7424899048106153</v>
       </c>
       <c r="S67">
-        <v>4.333333333333333</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="T67">
-        <v>0.5416666666666666</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="W67">
-        <v>0.4741759675586112</v>
+        <v>0.4700183942714367</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>B4A10</t>
+          <t>B3A22</t>
         </is>
       </c>
       <c r="B68">
-        <v>0.9113912774758922</v>
+        <v>1.70503530389312</v>
       </c>
       <c r="C68">
-        <v>0.9163429501469215</v>
+        <v>0.9033618231575899</v>
       </c>
       <c r="D68">
-        <v>954.6694808040943</v>
+        <v>1111.033140487697</v>
       </c>
       <c r="E68">
-        <v>3.324423197436492</v>
+        <v>3.307029389479954</v>
       </c>
       <c r="F68">
-        <v>0.8231253106065234</v>
+        <v>0.9555031540725488</v>
       </c>
       <c r="G68">
-        <v>0.8412167722239693</v>
+        <v>0.7718758408691314</v>
       </c>
       <c r="H68">
-        <v>330.164247171875</v>
+        <v>183.8040500878125</v>
       </c>
       <c r="I68">
-        <v>1</v>
+        <v>0.4575597020169162</v>
       </c>
       <c r="J68">
-        <v>310.4554166666667</v>
+        <v>560.2451333333333</v>
       </c>
       <c r="K68">
-        <v>0.4352799673327231</v>
+        <v>0.7842225786678604</v>
       </c>
       <c r="L68">
-        <v>16.67464521666666</v>
+        <v>22.29942168833333</v>
       </c>
       <c r="M68">
-        <v>0.5845071788900709</v>
+        <v>0.488141957414037</v>
       </c>
       <c r="N68">
-        <v>6.610169491525424</v>
+        <v>12.3</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>B4</t>
+          <t>B3</t>
         </is>
       </c>
       <c r="P68">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Q68">
-        <v>8.946038475</v>
+        <v>6.7486626605</v>
       </c>
       <c r="R68">
-        <v>0.6871290333432356</v>
+        <v>0.6914726383678531</v>
       </c>
       <c r="S68">
-        <v>3</v>
+        <v>5.333333333333333</v>
       </c>
       <c r="T68">
-        <v>0.375</v>
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="U68">
+        <v>10.79144385026738</v>
+      </c>
+      <c r="V68">
+        <v>0.640530177881191</v>
       </c>
       <c r="W68">
-        <v>0.7078251515679305</v>
+        <v>0.7065927265681994</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>B4A11</t>
+          <t>B3A23</t>
         </is>
       </c>
       <c r="B69">
-        <v>4.410626045842244</v>
+        <v>1.189745895568634</v>
       </c>
       <c r="C69">
-        <v>0.5951464841509069</v>
+        <v>0.9540175603198443</v>
       </c>
       <c r="D69">
-        <v>817.2379250340023</v>
+        <v>1050.074936152694</v>
       </c>
       <c r="E69">
-        <v>2.393989412593131</v>
+        <v>3.156049903851567</v>
       </c>
       <c r="F69">
-        <v>0.7046304866857737</v>
+        <v>0.8998945497514735</v>
       </c>
       <c r="G69">
-        <v>0.6057784845060843</v>
+        <v>0.7184684060747184</v>
       </c>
       <c r="H69">
-        <v>76.5980043496875</v>
+        <v>117.7899405009375</v>
       </c>
       <c r="I69">
-        <v>0.2319996941092551</v>
+        <v>0.2128981479276881</v>
       </c>
       <c r="J69">
-        <v>410.664875</v>
+        <v>355.4359583333333</v>
       </c>
       <c r="K69">
-        <v>0.5757805590701729</v>
+        <v>0.4953525640102679</v>
       </c>
       <c r="L69">
-        <v>16.21837887297222</v>
+        <v>22.60026640083333</v>
       </c>
       <c r="M69">
-        <v>0.5685133781278956</v>
+        <v>0.5035161013855298</v>
       </c>
       <c r="N69">
-        <v>3.779661016949153</v>
+        <v>3.416666666666667</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>B4</t>
+          <t>B3</t>
         </is>
       </c>
       <c r="P69">
         <v>4</v>
       </c>
       <c r="Q69">
-        <v>3.395191248</v>
+        <v>12.077124826</v>
       </c>
       <c r="R69">
-        <v>0.8812595350763516</v>
+        <v>0.4390074718415056</v>
       </c>
       <c r="S69">
-        <v>3</v>
+        <v>4.333333333333333</v>
       </c>
       <c r="T69">
-        <v>0.375</v>
-      </c>
-      <c r="U69">
-        <v>9.261224489795918</v>
-      </c>
-      <c r="V69">
-        <v>0.6090817578565169</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="W69">
-        <v>0.5719100421758841</v>
+        <v>0.5956026834972118</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>B4A12</t>
+          <t>B3A24</t>
         </is>
       </c>
       <c r="B70">
-        <v>1.557799648651538</v>
+        <v>1.938789752776512</v>
       </c>
       <c r="C70">
-        <v>0.8570088104976437</v>
+        <v>0.8803824959448555</v>
       </c>
       <c r="D70">
-        <v>857.5264607957037</v>
+        <v>961.8098517393934</v>
       </c>
       <c r="E70">
-        <v>2.553084119794869</v>
+        <v>2.79305649673674</v>
       </c>
       <c r="F70">
-        <v>0.7393676540295967</v>
+        <v>0.8193754759360552</v>
       </c>
       <c r="G70">
-        <v>0.6460360354019402</v>
+        <v>0.5900632347324082</v>
       </c>
       <c r="H70">
-        <v>162.0354838759375</v>
+        <v>134.8362436684375</v>
       </c>
       <c r="I70">
-        <v>0.4907723512279208</v>
+        <v>0.2760751725143514</v>
       </c>
       <c r="J70">
-        <v>54.90058333333334</v>
+        <v>568.57375</v>
       </c>
       <c r="K70">
-        <v>0.07697441512363405</v>
+        <v>0.7959695505434</v>
       </c>
       <c r="L70">
-        <v>14.81665724805556</v>
+        <v>26.334488324375</v>
       </c>
       <c r="M70">
-        <v>0.5193779187569026</v>
+        <v>0.694346995493513</v>
       </c>
       <c r="N70">
-        <v>0.9833333333333333</v>
+        <v>11.28813559322034</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>B4</t>
+          <t>B3</t>
         </is>
       </c>
       <c r="P70">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="Q70">
-        <v>11.22132051</v>
+        <v>10.22743296833333</v>
       </c>
       <c r="R70">
-        <v>0.6075552989247481</v>
+        <v>0.5266467847171419</v>
+      </c>
+      <c r="S70">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="T70">
+        <v>0.2916666666666667</v>
       </c>
       <c r="W70">
-        <v>0.5624417834231981</v>
+        <v>0.609315797068549</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>B4A13</t>
+          <t>B4A01</t>
         </is>
       </c>
       <c r="B71">
-        <v>4.056336430908098</v>
+        <v>1.488076964966721</v>
       </c>
       <c r="C71">
-        <v>0.6276669006958829</v>
+        <v>0.9246900018747707</v>
       </c>
       <c r="D71">
-        <v>740.1297030877272</v>
+        <v>1055.421961573569</v>
       </c>
       <c r="E71">
-        <v>2.080240700410156</v>
+        <v>3.432112786752799</v>
       </c>
       <c r="F71">
-        <v>0.63814702783844</v>
+        <v>0.9047723282911775</v>
       </c>
       <c r="G71">
-        <v>0.5263870643176107</v>
+        <v>0.8161228016791309</v>
       </c>
       <c r="H71">
-        <v>88.9824012521875</v>
+        <v>171.7965678403226</v>
       </c>
       <c r="I71">
-        <v>0.2695095002393326</v>
+        <v>0.4130575601906514</v>
       </c>
       <c r="J71">
-        <v>122.4278333333333</v>
+        <v>691.7772916666667</v>
       </c>
       <c r="K71">
-        <v>0.1716522902583685</v>
+        <v>0.9697401293620359</v>
       </c>
       <c r="L71">
-        <v>14.4999541025</v>
+        <v>20.12140622708333</v>
       </c>
       <c r="M71">
-        <v>0.5082763175084837</v>
+        <v>0.3768382785322132</v>
       </c>
       <c r="N71">
-        <v>0.9833333333333333</v>
+        <v>34.94915254237288</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
@@ -5283,68 +5067,74 @@
         </is>
       </c>
       <c r="P71">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="Q71">
-        <v>1.424821897</v>
+        <v>11.52827427625</v>
       </c>
       <c r="R71">
-        <v>0.9501695185557409</v>
+        <v>0.4650122816978798</v>
       </c>
       <c r="S71">
-        <v>1.333333333333333</v>
+        <v>4.666666666666667</v>
       </c>
       <c r="T71">
-        <v>0.1666666666666667</v>
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="U71">
+        <v>4.727078891257996</v>
+      </c>
+      <c r="V71">
+        <v>0.1466323900216009</v>
       </c>
       <c r="W71">
-        <v>0.4823094107600657</v>
+        <v>0.6222443449980881</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>B4A14</t>
+          <t>B4A02</t>
         </is>
       </c>
       <c r="B72">
-        <v>1.035234654258313</v>
+        <v>0.7219950451524363</v>
       </c>
       <c r="C72">
-        <v>0.9049753061925556</v>
+        <v>1</v>
       </c>
       <c r="D72">
-        <v>899.4694821174611</v>
+        <v>940.1657715297354</v>
       </c>
       <c r="E72">
-        <v>2.765656411943148</v>
+        <v>3.062506222892643</v>
       </c>
       <c r="F72">
-        <v>0.7755313349133395</v>
+        <v>0.7996308475402127</v>
       </c>
       <c r="G72">
-        <v>0.6998256304219475</v>
+        <v>0.6853782943919974</v>
       </c>
       <c r="H72">
-        <v>102.4966450978125</v>
+        <v>200.0871802265625</v>
       </c>
       <c r="I72">
-        <v>0.3104413817540195</v>
+        <v>0.5179082540176206</v>
       </c>
       <c r="J72">
-        <v>96.73041666666667</v>
+        <v>313.8654273333333</v>
       </c>
       <c r="K72">
-        <v>0.1356227346870708</v>
+        <v>0.436720034977846</v>
       </c>
       <c r="L72">
-        <v>16.62617626361111</v>
+        <v>20.36415362979167</v>
       </c>
       <c r="M72">
-        <v>0.5828081651691708</v>
+        <v>0.3892434608833699</v>
       </c>
       <c r="N72">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
@@ -5352,68 +5142,62 @@
         </is>
       </c>
       <c r="P72">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="Q72">
-        <v>2.512306821</v>
+        <v>2.25621978075</v>
       </c>
       <c r="R72">
-        <v>0.9121367669252448</v>
+        <v>0.9043267986337655</v>
       </c>
       <c r="S72">
-        <v>1</v>
+        <v>5.333333333333333</v>
       </c>
       <c r="T72">
-        <v>0.125</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="W72">
-        <v>0.5557926650079186</v>
+        <v>0.6749842946389348</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>B4A15</t>
+          <t>B4A03</t>
         </is>
       </c>
       <c r="B73">
-        <v>1.647421926406839</v>
+        <v>1.292398706065661</v>
       </c>
       <c r="C73">
-        <v>0.848782337912909</v>
+        <v>0.9439262335751082</v>
       </c>
       <c r="D73">
-        <v>892.7724353911411</v>
+        <v>666.26620934</v>
       </c>
       <c r="E73">
-        <v>2.631552202183076</v>
+        <v>2.543287669</v>
       </c>
       <c r="F73">
-        <v>0.7697570760964498</v>
+        <v>0.5497682975572799</v>
       </c>
       <c r="G73">
-        <v>0.6658917105278124</v>
-      </c>
-      <c r="H73">
-        <v>60.3461720246875</v>
-      </c>
-      <c r="I73">
-        <v>0.1827762168120912</v>
+        <v>0.5017100897636932</v>
       </c>
       <c r="J73">
-        <v>80.89975</v>
+        <v>4.230416666666667</v>
       </c>
       <c r="K73">
-        <v>0.1134270450659731</v>
+        <v>0</v>
       </c>
       <c r="L73">
-        <v>17.35934430347222</v>
+        <v>18.23460002335417</v>
       </c>
       <c r="M73">
-        <v>0.608508381099597</v>
+        <v>0.2804163405118205</v>
       </c>
       <c r="N73">
-        <v>1.9</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
@@ -5421,68 +5205,62 @@
         </is>
       </c>
       <c r="P73">
-        <v>2</v>
-      </c>
-      <c r="Q73">
-        <v>1.71014179</v>
-      </c>
-      <c r="R73">
-        <v>0.9401909888435362</v>
+        <v>1</v>
       </c>
       <c r="S73">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="T73">
-        <v>0.375</v>
+        <v>0.04166666666666666</v>
       </c>
       <c r="W73">
-        <v>0.5630417195447961</v>
+        <v>0.3862479380124281</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>B4A16</t>
+          <t>B4A04</t>
         </is>
       </c>
       <c r="B74">
-        <v>2.668287177350798</v>
+        <v>4.543539835776487</v>
       </c>
       <c r="C74">
-        <v>0.755076618643774</v>
+        <v>0.6243214680133081</v>
       </c>
       <c r="D74">
-        <v>984.282715387383</v>
+        <v>931.0850222829723</v>
       </c>
       <c r="E74">
-        <v>2.832724909576293</v>
+        <v>3.951922152773463</v>
       </c>
       <c r="F74">
-        <v>0.8486581294559357</v>
+        <v>0.7913470111426208</v>
       </c>
       <c r="G74">
-        <v>0.7167967384145673</v>
+        <v>1</v>
       </c>
       <c r="H74">
-        <v>135.46246887375</v>
+        <v>146.71501500875</v>
       </c>
       <c r="I74">
-        <v>0.4102881218487347</v>
+        <v>0.3201002858572309</v>
       </c>
       <c r="J74">
-        <v>260.4987083333334</v>
+        <v>291.6330833333333</v>
       </c>
       <c r="K74">
-        <v>0.3652372069104391</v>
+        <v>0.4053627603969946</v>
       </c>
       <c r="L74">
-        <v>16.73865680055556</v>
+        <v>15.40011132185417</v>
       </c>
       <c r="M74">
-        <v>0.5867510185537649</v>
+        <v>0.1355647424222231</v>
       </c>
       <c r="N74">
-        <v>6.35593220338983</v>
+        <v>2.95</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
@@ -5490,137 +5268,107 @@
         </is>
       </c>
       <c r="P74">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q74">
-        <v>1.0787394635</v>
+        <v>11.843459849</v>
       </c>
       <c r="R74">
-        <v>0.9622731044965638</v>
+        <v>0.4500786337447721</v>
       </c>
       <c r="S74">
-        <v>1.333333333333333</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="T74">
-        <v>0.1666666666666667</v>
+        <v>0.04166666666666666</v>
       </c>
       <c r="W74">
-        <v>0.6014684506238057</v>
+        <v>0.4710551960304771</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>B4A17</t>
+          <t>B4A05</t>
         </is>
       </c>
       <c r="B75">
-        <v>3.095392060730346</v>
+        <v>10.89437505956174</v>
       </c>
       <c r="C75">
-        <v>0.7158724530955456</v>
+        <v>0</v>
       </c>
       <c r="D75">
-        <v>706.9460658690535</v>
+        <v>594.6992647</v>
       </c>
       <c r="E75">
-        <v>2.220446207460934</v>
+        <v>3.022235294</v>
       </c>
       <c r="F75">
-        <v>0.6095357731142722</v>
+        <v>0.4844819599695962</v>
       </c>
       <c r="G75">
-        <v>0.5618648651524227</v>
-      </c>
-      <c r="H75">
-        <v>104.8937559309375</v>
-      </c>
-      <c r="I75">
-        <v>0.3177017403593446</v>
-      </c>
-      <c r="J75">
-        <v>128.8154583333333</v>
-      </c>
-      <c r="K75">
-        <v>0.1806081823190923</v>
+        <v>0.6711328689291099</v>
       </c>
       <c r="L75">
-        <v>12.99774696763889</v>
+        <v>15.50266761604167</v>
       </c>
       <c r="M75">
-        <v>0.4556184742322397</v>
-      </c>
-      <c r="N75">
-        <v>2</v>
+        <v>0.1408057028463535</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
           <t>B4</t>
         </is>
       </c>
-      <c r="P75">
-        <v>2</v>
-      </c>
-      <c r="Q75">
-        <v>1.2469799705</v>
-      </c>
-      <c r="R75">
-        <v>0.9563892073723773</v>
-      </c>
-      <c r="S75">
-        <v>5</v>
-      </c>
-      <c r="T75">
-        <v>0.625</v>
-      </c>
       <c r="W75">
-        <v>0.5528238369556618</v>
+        <v>0.3241051329362649</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>B4A18</t>
+          <t>B4A06</t>
         </is>
       </c>
       <c r="B76">
-        <v>2.93340592717423</v>
+        <v>1.719547623997414</v>
       </c>
       <c r="C76">
-        <v>0.730741239296728</v>
+        <v>0.9019351835625555</v>
       </c>
       <c r="D76">
-        <v>976.9563461971909</v>
+        <v>935.1347230762776</v>
       </c>
       <c r="E76">
-        <v>3.142902868993676</v>
+        <v>2.488230333792243</v>
       </c>
       <c r="F76">
-        <v>0.8423412626904708</v>
+        <v>0.7950413163061399</v>
       </c>
       <c r="G76">
-        <v>0.795284610246683</v>
+        <v>0.4822341256760957</v>
       </c>
       <c r="H76">
-        <v>151.39790363125</v>
+        <v>190.33094006125</v>
       </c>
       <c r="I76">
-        <v>0.4585532956039184</v>
+        <v>0.4817496676812886</v>
       </c>
       <c r="J76">
-        <v>693.9295833333333</v>
+        <v>153.0529166666667</v>
       </c>
       <c r="K76">
-        <v>0.972937272628926</v>
+        <v>0.2099044525538446</v>
       </c>
       <c r="L76">
-        <v>17.45057982055556</v>
+        <v>18.29261047583333</v>
       </c>
       <c r="M76">
-        <v>0.6117065189917097</v>
+        <v>0.2833808634407921</v>
       </c>
       <c r="N76">
-        <v>10.48333333333333</v>
+        <v>7.689655172413793</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
@@ -5628,68 +5376,74 @@
         </is>
       </c>
       <c r="P76">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="Q76">
-        <v>4.6450910745</v>
+        <v>4.09512267625</v>
       </c>
       <c r="R76">
-        <v>0.8375466259452318</v>
+        <v>0.817198672108985</v>
       </c>
       <c r="S76">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T76">
-        <v>0.625</v>
+        <v>0.25</v>
+      </c>
+      <c r="U76">
+        <v>3.131147540983607</v>
+      </c>
+      <c r="V76">
+        <v>0.01665555505139046</v>
       </c>
       <c r="W76">
-        <v>0.7342638531754585</v>
+        <v>0.4708999818201213</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>B4A20</t>
+          <t>B4A07</t>
         </is>
       </c>
       <c r="B77">
-        <v>3.144980069906421</v>
+        <v>6.244953306955439</v>
       </c>
       <c r="C77">
-        <v>0.7113207455487642</v>
+        <v>0.4570633171411546</v>
       </c>
       <c r="D77">
-        <v>990.9597563929921</v>
+        <v>899.7614602872376</v>
       </c>
       <c r="E77">
-        <v>2.953631968905547</v>
+        <v>2.162868994009377</v>
       </c>
       <c r="F77">
-        <v>0.8544151391458708</v>
+        <v>0.7627723576739119</v>
       </c>
       <c r="G77">
-        <v>0.7473912326012507</v>
+        <v>0.3671409097550509</v>
       </c>
       <c r="H77">
-        <v>152.0578600525</v>
+        <v>68.9591740921875</v>
       </c>
       <c r="I77">
-        <v>0.4605521686705908</v>
+        <v>0.03192151623942003</v>
       </c>
       <c r="J77">
-        <v>585.0162666666666</v>
+        <v>184.1729583333333</v>
       </c>
       <c r="K77">
-        <v>0.8202332694912822</v>
+        <v>0.2537972463820258</v>
       </c>
       <c r="L77">
-        <v>14.72761090888889</v>
+        <v>17.70737708666667</v>
       </c>
       <c r="M77">
-        <v>0.5162565195414774</v>
+        <v>0.253473532488539</v>
       </c>
       <c r="N77">
-        <v>9.85</v>
+        <v>2.694915254237288</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
@@ -5697,74 +5451,74 @@
         </is>
       </c>
       <c r="P77">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="Q77">
-        <v>5.3957587795</v>
+        <v>2.72380961475</v>
       </c>
       <c r="R77">
-        <v>0.8112934267042834</v>
+        <v>0.8821721615846049</v>
       </c>
       <c r="S77">
-        <v>4</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="T77">
-        <v>0.5</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="U77">
-        <v>4.831024930747922</v>
+        <v>6.712264150943396</v>
       </c>
       <c r="V77">
-        <v>0.3177213942185137</v>
+        <v>0.308311084308207</v>
       </c>
       <c r="W77">
-        <v>0.6376870995468926</v>
+        <v>0.4148131991377312</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>B4A21</t>
+          <t>B4A08</t>
         </is>
       </c>
       <c r="B78">
-        <v>2.98039018954707</v>
+        <v>1.565465264178534</v>
       </c>
       <c r="C78">
-        <v>0.7264285309388857</v>
+        <v>0.9170823133002</v>
       </c>
       <c r="D78">
-        <v>748.9641781174147</v>
+        <v>825.6953914759764</v>
       </c>
       <c r="E78">
-        <v>2.339591991004429</v>
+        <v>2.814837724279613</v>
       </c>
       <c r="F78">
-        <v>0.6457641981251995</v>
+        <v>0.6952062152805429</v>
       </c>
       <c r="G78">
-        <v>0.5920136836102656</v>
+        <v>0.5977681191734737</v>
       </c>
       <c r="H78">
-        <v>61.79041457875</v>
+        <v>154.55160473125</v>
       </c>
       <c r="I78">
-        <v>0.1871505322215688</v>
+        <v>0.3491442619445448</v>
       </c>
       <c r="J78">
-        <v>538.9304166666667</v>
+        <v>166.536875</v>
       </c>
       <c r="K78">
-        <v>0.7556177201866963</v>
+        <v>0.2289226983985064</v>
       </c>
       <c r="L78">
-        <v>13.41004905030556</v>
+        <v>15.1030800713125</v>
       </c>
       <c r="M78">
-        <v>0.4700711671716443</v>
+        <v>0.1203854787685196</v>
       </c>
       <c r="N78">
-        <v>1.9</v>
+        <v>6.677966101694915</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
@@ -5772,91 +5526,952 @@
         </is>
       </c>
       <c r="P78">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Q78">
-        <v>6.434649477000001</v>
+        <v>7.85454117025</v>
       </c>
       <c r="R78">
-        <v>0.774960167274886</v>
+        <v>0.6390755689226308</v>
       </c>
       <c r="S78">
-        <v>1.666666666666667</v>
+        <v>0</v>
       </c>
       <c r="T78">
-        <v>0.2083333333333333</v>
+        <v>0</v>
       </c>
       <c r="W78">
-        <v>0.5450424166078099</v>
+        <v>0.4434480819735523</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
+          <t>B4A09</t>
+        </is>
+      </c>
+      <c r="B79">
+        <v>6.692488984265891</v>
+      </c>
+      <c r="C79">
+        <v>0.4130681383652425</v>
+      </c>
+      <c r="D79">
+        <v>844.2071193141553</v>
+      </c>
+      <c r="E79">
+        <v>2.641342805042894</v>
+      </c>
+      <c r="F79">
+        <v>0.7120933818216612</v>
+      </c>
+      <c r="G79">
+        <v>0.5363960821200183</v>
+      </c>
+      <c r="H79">
+        <v>73.60762752531249</v>
+      </c>
+      <c r="I79">
+        <v>0.04914961865838969</v>
+      </c>
+      <c r="J79">
+        <v>113.1500833333333</v>
+      </c>
+      <c r="K79">
+        <v>0.1536241025652297</v>
+      </c>
+      <c r="L79">
+        <v>14.49188114510417</v>
+      </c>
+      <c r="M79">
+        <v>0.08915122436310551</v>
+      </c>
+      <c r="N79">
+        <v>1</v>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="P79">
+        <v>1</v>
+      </c>
+      <c r="Q79">
+        <v>3.95142637</v>
+      </c>
+      <c r="R79">
+        <v>0.8240070740005321</v>
+      </c>
+      <c r="S79">
+        <v>4.333333333333333</v>
+      </c>
+      <c r="T79">
+        <v>0.5416666666666666</v>
+      </c>
+      <c r="W79">
+        <v>0.4148945360701057</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>B4A10</t>
+        </is>
+      </c>
+      <c r="B80">
+        <v>0.9113912774758922</v>
+      </c>
+      <c r="C80">
+        <v>0.9813813255054202</v>
+      </c>
+      <c r="D80">
+        <v>954.6694808040943</v>
+      </c>
+      <c r="E80">
+        <v>3.324423197436492</v>
+      </c>
+      <c r="F80">
+        <v>0.8128617331777446</v>
+      </c>
+      <c r="G80">
+        <v>0.7780287209137213</v>
+      </c>
+      <c r="H80">
+        <v>330.164247171875</v>
+      </c>
+      <c r="I80">
+        <v>1</v>
+      </c>
+      <c r="J80">
+        <v>310.4554166666667</v>
+      </c>
+      <c r="K80">
+        <v>0.4319104368176926</v>
+      </c>
+      <c r="L80">
+        <v>17.04876937625</v>
+      </c>
+      <c r="M80">
+        <v>0.2198165349081643</v>
+      </c>
+      <c r="N80">
+        <v>6.610169491525424</v>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="P80">
+        <v>8</v>
+      </c>
+      <c r="Q80">
+        <v>4.4750757815</v>
+      </c>
+      <c r="R80">
+        <v>0.7991963065089764</v>
+      </c>
+      <c r="S80">
+        <v>3</v>
+      </c>
+      <c r="T80">
+        <v>0.375</v>
+      </c>
+      <c r="W80">
+        <v>0.6747743822289649</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>B4A11</t>
+        </is>
+      </c>
+      <c r="B81">
+        <v>4.410626045842244</v>
+      </c>
+      <c r="C81">
+        <v>0.6373876127843419</v>
+      </c>
+      <c r="D81">
+        <v>817.2379250340023</v>
+      </c>
+      <c r="E81">
+        <v>2.393989412593131</v>
+      </c>
+      <c r="F81">
+        <v>0.687490963329454</v>
+      </c>
+      <c r="G81">
+        <v>0.4488973724545661</v>
+      </c>
+      <c r="H81">
+        <v>76.5980043496875</v>
+      </c>
+      <c r="I81">
+        <v>0.06023255601439794</v>
+      </c>
+      <c r="J81">
+        <v>410.664875</v>
+      </c>
+      <c r="K81">
+        <v>0.5732493572912475</v>
+      </c>
+      <c r="L81">
+        <v>16.3130408974375</v>
+      </c>
+      <c r="M81">
+        <v>0.1822184150569114</v>
+      </c>
+      <c r="N81">
+        <v>3.779661016949153</v>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="P81">
+        <v>4</v>
+      </c>
+      <c r="Q81">
+        <v>2.02887792975</v>
+      </c>
+      <c r="R81">
+        <v>0.9150983677072484</v>
+      </c>
+      <c r="S81">
+        <v>3</v>
+      </c>
+      <c r="T81">
+        <v>0.375</v>
+      </c>
+      <c r="U81">
+        <v>9.261224489795918</v>
+      </c>
+      <c r="V81">
+        <v>0.515905099709737</v>
+      </c>
+      <c r="W81">
+        <v>0.4883866382608782</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>B4A12</t>
+        </is>
+      </c>
+      <c r="B82">
+        <v>1.557799648651538</v>
+      </c>
+      <c r="C82">
+        <v>0.9178358847865323</v>
+      </c>
+      <c r="D82">
+        <v>857.5264607957037</v>
+      </c>
+      <c r="E82">
+        <v>2.553084119794869</v>
+      </c>
+      <c r="F82">
+        <v>0.724243837996424</v>
+      </c>
+      <c r="G82">
+        <v>0.5051754831240297</v>
+      </c>
+      <c r="H82">
+        <v>162.0354838759375</v>
+      </c>
+      <c r="I82">
+        <v>0.3768810217617106</v>
+      </c>
+      <c r="J82">
+        <v>54.90058333333334</v>
+      </c>
+      <c r="K82">
+        <v>0.07146697303820813</v>
+      </c>
+      <c r="L82">
+        <v>14.71463431541667</v>
+      </c>
+      <c r="M82">
+        <v>0.1005346363633773</v>
+      </c>
+      <c r="N82">
+        <v>0.9833333333333333</v>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="P82">
+        <v>1</v>
+      </c>
+      <c r="Q82">
+        <v>5.91437160775</v>
+      </c>
+      <c r="R82">
+        <v>0.731001760096018</v>
+      </c>
+      <c r="W82">
+        <v>0.4895913710237572</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>B4A13</t>
+        </is>
+      </c>
+      <c r="B83">
+        <v>4.056336430908098</v>
+      </c>
+      <c r="C83">
+        <v>0.672216199057396</v>
+      </c>
+      <c r="D83">
+        <v>740.1297030877272</v>
+      </c>
+      <c r="E83">
+        <v>2.080240700410156</v>
+      </c>
+      <c r="F83">
+        <v>0.617149642568963</v>
+      </c>
+      <c r="G83">
+        <v>0.3379120036940255</v>
+      </c>
+      <c r="H83">
+        <v>88.9824012521875</v>
+      </c>
+      <c r="I83">
+        <v>0.1061316192841371</v>
+      </c>
+      <c r="J83">
+        <v>122.4278333333333</v>
+      </c>
+      <c r="K83">
+        <v>0.1667097652485029</v>
+      </c>
+      <c r="L83">
+        <v>14.38611968541667</v>
+      </c>
+      <c r="M83">
+        <v>0.08374646955003613</v>
+      </c>
+      <c r="N83">
+        <v>0.9833333333333333</v>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="P83">
+        <v>1</v>
+      </c>
+      <c r="Q83">
+        <v>0.9924028764999999</v>
+      </c>
+      <c r="R83">
+        <v>0.9642070671390313</v>
+      </c>
+      <c r="S83">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="T83">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="W83">
+        <v>0.3893424291510948</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>B4A14</t>
+        </is>
+      </c>
+      <c r="B84">
+        <v>1.035234654258313</v>
+      </c>
+      <c r="C84">
+        <v>0.9692068514288525</v>
+      </c>
+      <c r="D84">
+        <v>899.4694821174611</v>
+      </c>
+      <c r="E84">
+        <v>2.765656411943148</v>
+      </c>
+      <c r="F84">
+        <v>0.7625060030676597</v>
+      </c>
+      <c r="G84">
+        <v>0.5803707375306559</v>
+      </c>
+      <c r="H84">
+        <v>102.4966450978125</v>
+      </c>
+      <c r="I84">
+        <v>0.1562181223408834</v>
+      </c>
+      <c r="J84">
+        <v>96.73041666666667</v>
+      </c>
+      <c r="K84">
+        <v>0.1304652311393144</v>
+      </c>
+      <c r="L84">
+        <v>16.32558588020833</v>
+      </c>
+      <c r="M84">
+        <v>0.1828595045068006</v>
+      </c>
+      <c r="N84">
+        <v>2</v>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="P84">
+        <v>2</v>
+      </c>
+      <c r="Q84">
+        <v>2.06345293625</v>
+      </c>
+      <c r="R84">
+        <v>0.9134601868395696</v>
+      </c>
+      <c r="S84">
+        <v>1</v>
+      </c>
+      <c r="T84">
+        <v>0.125</v>
+      </c>
+      <c r="W84">
+        <v>0.477510829606717</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>B4A15</t>
+        </is>
+      </c>
+      <c r="B85">
+        <v>1.647421926406839</v>
+      </c>
+      <c r="C85">
+        <v>0.9090255299208716</v>
+      </c>
+      <c r="D85">
+        <v>892.7724353911411</v>
+      </c>
+      <c r="E85">
+        <v>2.631552202183076</v>
+      </c>
+      <c r="F85">
+        <v>0.7563966790548159</v>
+      </c>
+      <c r="G85">
+        <v>0.53293275740635</v>
+      </c>
+      <c r="H85">
+        <v>60.3461720246875</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>80.89975</v>
+      </c>
+      <c r="K85">
+        <v>0.108137105887897</v>
+      </c>
+      <c r="L85">
+        <v>16.95464400197917</v>
+      </c>
+      <c r="M85">
+        <v>0.2150064219319874</v>
+      </c>
+      <c r="N85">
+        <v>1.9</v>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="P85">
+        <v>2</v>
+      </c>
+      <c r="Q85">
+        <v>1.467972922666667</v>
+      </c>
+      <c r="R85">
+        <v>0.9416743236998848</v>
+      </c>
+      <c r="S85">
+        <v>3</v>
+      </c>
+      <c r="T85">
+        <v>0.375</v>
+      </c>
+      <c r="W85">
+        <v>0.4797716022377259</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>B4A16</t>
+        </is>
+      </c>
+      <c r="B86">
+        <v>2.668287177350798</v>
+      </c>
+      <c r="C86">
+        <v>0.8086689516670225</v>
+      </c>
+      <c r="D86">
+        <v>984.282715387383</v>
+      </c>
+      <c r="E86">
+        <v>2.832724909576293</v>
+      </c>
+      <c r="F86">
+        <v>0.8398761549864866</v>
+      </c>
+      <c r="G86">
+        <v>0.6040955263600328</v>
+      </c>
+      <c r="H86">
+        <v>135.46246887375</v>
+      </c>
+      <c r="I86">
+        <v>0.2783960889502532</v>
+      </c>
+      <c r="J86">
+        <v>260.4987083333334</v>
+      </c>
+      <c r="K86">
+        <v>0.3614497503347991</v>
+      </c>
+      <c r="L86">
+        <v>16.83286806979167</v>
+      </c>
+      <c r="M86">
+        <v>0.2087832754516804</v>
+      </c>
+      <c r="N86">
+        <v>6.35593220338983</v>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="P86">
+        <v>8</v>
+      </c>
+      <c r="Q86">
+        <v>0.9632191780000001</v>
+      </c>
+      <c r="R86">
+        <v>0.9655898051735361</v>
+      </c>
+      <c r="S86">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="T86">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="W86">
+        <v>0.5291907774488097</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>B4A17</t>
+        </is>
+      </c>
+      <c r="B87">
+        <v>3.095392060730346</v>
+      </c>
+      <c r="C87">
+        <v>0.7666822304892303</v>
+      </c>
+      <c r="D87">
+        <v>706.9460658690535</v>
+      </c>
+      <c r="E87">
+        <v>2.220446207460934</v>
+      </c>
+      <c r="F87">
+        <v>0.5868781512716429</v>
+      </c>
+      <c r="G87">
+        <v>0.38750825476394</v>
+      </c>
+      <c r="H87">
+        <v>104.8937559309375</v>
+      </c>
+      <c r="I87">
+        <v>0.1651022967306731</v>
+      </c>
+      <c r="J87">
+        <v>128.8154583333333</v>
+      </c>
+      <c r="K87">
+        <v>0.1757190946761382</v>
+      </c>
+      <c r="L87">
+        <v>12.7473499040625</v>
+      </c>
+      <c r="M87">
+        <v>0</v>
+      </c>
+      <c r="N87">
+        <v>2</v>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="P87">
+        <v>2</v>
+      </c>
+      <c r="Q87">
+        <v>1.005487459666667</v>
+      </c>
+      <c r="R87">
+        <v>0.9635871131325097</v>
+      </c>
+      <c r="S87">
+        <v>5</v>
+      </c>
+      <c r="T87">
+        <v>0.625</v>
+      </c>
+      <c r="W87">
+        <v>0.4588096426330168</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>B4A18</t>
+        </is>
+      </c>
+      <c r="B88">
+        <v>2.93340592717423</v>
+      </c>
+      <c r="C88">
+        <v>0.7826063439539909</v>
+      </c>
+      <c r="D88">
+        <v>976.9563461971909</v>
+      </c>
+      <c r="E88">
+        <v>3.142902868993676</v>
+      </c>
+      <c r="F88">
+        <v>0.8331927368994226</v>
+      </c>
+      <c r="G88">
+        <v>0.7138177781831853</v>
+      </c>
+      <c r="H88">
+        <v>151.39790363125</v>
+      </c>
+      <c r="I88">
+        <v>0.337456012006954</v>
+      </c>
+      <c r="J88">
+        <v>693.9295833333333</v>
+      </c>
+      <c r="K88">
+        <v>0.9727757967109103</v>
+      </c>
+      <c r="L88">
+        <v>17.63547567520833</v>
+      </c>
+      <c r="M88">
+        <v>0.2497991363446681</v>
+      </c>
+      <c r="N88">
+        <v>10.48333333333333</v>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="P88">
+        <v>16</v>
+      </c>
+      <c r="Q88">
+        <v>3.14699305475</v>
+      </c>
+      <c r="R88">
+        <v>0.8621215213937934</v>
+      </c>
+      <c r="S88">
+        <v>5</v>
+      </c>
+      <c r="T88">
+        <v>0.625</v>
+      </c>
+      <c r="W88">
+        <v>0.6720961656866156</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>B4A19</t>
+        </is>
+      </c>
+      <c r="B89">
+        <v>1.25617934230505</v>
+      </c>
+      <c r="C89">
+        <v>0.9474867930222883</v>
+      </c>
+      <c r="L89">
+        <v>17.21286807625</v>
+      </c>
+      <c r="M89">
+        <v>0.2282025125720888</v>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="W89">
+        <v>0.5878446527971886</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>B4A20</t>
+        </is>
+      </c>
+      <c r="B90">
+        <v>3.144980069906421</v>
+      </c>
+      <c r="C90">
+        <v>0.7618074608575578</v>
+      </c>
+      <c r="D90">
+        <v>990.9597563929921</v>
+      </c>
+      <c r="E90">
+        <v>2.953631968905547</v>
+      </c>
+      <c r="F90">
+        <v>0.8459672289504764</v>
+      </c>
+      <c r="G90">
+        <v>0.6468651507261209</v>
+      </c>
+      <c r="H90">
+        <v>152.0578600525</v>
+      </c>
+      <c r="I90">
+        <v>0.3399019431066032</v>
+      </c>
+      <c r="J90">
+        <v>585.0162666666666</v>
+      </c>
+      <c r="K90">
+        <v>0.819160650407494</v>
+      </c>
+      <c r="L90">
+        <v>14.58769866375</v>
+      </c>
+      <c r="M90">
+        <v>0.09404781142428659</v>
+      </c>
+      <c r="N90">
+        <v>9.85</v>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="P90">
+        <v>16</v>
+      </c>
+      <c r="Q90">
+        <v>3.55116901125</v>
+      </c>
+      <c r="R90">
+        <v>0.8429714651497245</v>
+      </c>
+      <c r="S90">
+        <v>4</v>
+      </c>
+      <c r="T90">
+        <v>0.5</v>
+      </c>
+      <c r="U90">
+        <v>4.831024930747922</v>
+      </c>
+      <c r="V90">
+        <v>0.155098028107015</v>
+      </c>
+      <c r="W90">
+        <v>0.556202193192142</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>B4A21</t>
+        </is>
+      </c>
+      <c r="B91">
+        <v>2.98039018954707</v>
+      </c>
+      <c r="C91">
+        <v>0.77798753672242</v>
+      </c>
+      <c r="D91">
+        <v>748.9641781174147</v>
+      </c>
+      <c r="E91">
+        <v>2.339591991004429</v>
+      </c>
+      <c r="F91">
+        <v>0.6252088174030913</v>
+      </c>
+      <c r="G91">
+        <v>0.4296548459987961</v>
+      </c>
+      <c r="H91">
+        <v>61.79041457875</v>
+      </c>
+      <c r="I91">
+        <v>0.005352653091438228</v>
+      </c>
+      <c r="J91">
+        <v>538.9304166666667</v>
+      </c>
+      <c r="K91">
+        <v>0.7541595577317992</v>
+      </c>
+      <c r="L91">
+        <v>13.37128533022917</v>
+      </c>
+      <c r="M91">
+        <v>0.0318851310069178</v>
+      </c>
+      <c r="N91">
+        <v>1.9</v>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="P91">
+        <v>2</v>
+      </c>
+      <c r="Q91">
+        <v>3.534682079</v>
+      </c>
+      <c r="R91">
+        <v>0.8437526241345729</v>
+      </c>
+      <c r="S91">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="T91">
+        <v>0.2083333333333333</v>
+      </c>
+      <c r="W91">
+        <v>0.4595418124277961</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
           <t>B4A22</t>
         </is>
       </c>
-      <c r="B79">
+      <c r="B92">
         <v>0.9985906350334441</v>
       </c>
-      <c r="C79">
-        <v>0.9083388785888178</v>
-      </c>
-      <c r="D79">
+      <c r="C92">
+        <v>0.9728091568060565</v>
+      </c>
+      <c r="D92">
         <v>729.3911372457928</v>
       </c>
-      <c r="E79">
+      <c r="E92">
         <v>2.420880084084988</v>
       </c>
-      <c r="F79">
-        <v>0.6288881319358856</v>
-      </c>
-      <c r="G79">
-        <v>0.61258293825095</v>
-      </c>
-      <c r="H79">
+      <c r="F92">
+        <v>0.6073534770586047</v>
+      </c>
+      <c r="G92">
+        <v>0.4584096699584418</v>
+      </c>
+      <c r="H92">
         <v>114.1203750196875</v>
       </c>
-      <c r="I79">
-        <v>0.3456472831241457</v>
-      </c>
-      <c r="J79">
+      <c r="I92">
+        <v>0.1992980009425456</v>
+      </c>
+      <c r="J92">
         <v>414.1980833333333</v>
       </c>
-      <c r="K79">
-        <v>0.5807343615337464</v>
-      </c>
-      <c r="L79">
-        <v>15.65610951194444</v>
-      </c>
-      <c r="M79">
-        <v>0.5488037846870603</v>
-      </c>
-      <c r="N79">
+      <c r="K92">
+        <v>0.5782327177439144</v>
+      </c>
+      <c r="L92">
+        <v>15.9044354025</v>
+      </c>
+      <c r="M92">
+        <v>0.1613373443726056</v>
+      </c>
+      <c r="N92">
         <v>2.833333333333333</v>
       </c>
-      <c r="O79" t="inlineStr">
+      <c r="O92" t="inlineStr">
         <is>
           <t>B4</t>
         </is>
       </c>
-      <c r="P79">
+      <c r="P92">
         <v>4</v>
       </c>
-      <c r="Q79">
-        <v>2.6573583345</v>
-      </c>
-      <c r="R79">
-        <v>0.9070638614855248</v>
-      </c>
-      <c r="S79">
+      <c r="Q92">
+        <v>1.777189273</v>
+      </c>
+      <c r="R92">
+        <v>0.9270235004501621</v>
+      </c>
+      <c r="S92">
         <v>6</v>
       </c>
-      <c r="T79">
+      <c r="T92">
         <v>0.75</v>
       </c>
-      <c r="W79">
-        <v>0.6602574049507663</v>
+      <c r="W92">
+        <v>0.5818079834165413</v>
       </c>
     </row>
   </sheetData>

--- a/Data Analysis/1_Data/ecological_multifunctionality.xlsx
+++ b/Data Analysis/1_Data/ecological_multifunctionality.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W92"/>
+  <dimension ref="A1:Y92"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -362,7 +362,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>TNleaching_av</t>
+          <t>av_leaching</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -437,35 +437,45 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>meanHerb</t>
+          <t>mean_diversity</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>herbivory_standardized</t>
+          <t>mean_div_standardized</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>mean_diversity</t>
+          <t>mean_above_control</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>mean_div_standardized</t>
+          <t>above_pathogen_control_standardized</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>mean_flower_cover</t>
+          <t>mean_below_control</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>mean_flower_cover_standardized</t>
+          <t>below_pathogen_control_standardized</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>biomass_stability</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>biomass_stability_standardized</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>multifunctionality</t>
         </is>
@@ -478,40 +488,40 @@
         </is>
       </c>
       <c r="B2">
-        <v>2.095065631874623</v>
+        <v>2.813264729287163</v>
       </c>
       <c r="C2">
-        <v>0.8650197313925341</v>
+        <v>0.8185219025405732</v>
       </c>
       <c r="D2">
-        <v>828.3773512579434</v>
+        <v>870.7120698129983</v>
       </c>
       <c r="E2">
-        <v>2.866126361212376</v>
+        <v>2.501219340892978</v>
       </c>
       <c r="F2">
-        <v>0.6976528103196753</v>
+        <v>0.7409760260026874</v>
       </c>
       <c r="G2">
-        <v>0.6159109451427114</v>
+        <v>0.2031038447534122</v>
       </c>
       <c r="H2">
-        <v>152.379692735</v>
+        <v>115.2180067008</v>
       </c>
       <c r="I2">
-        <v>0.341094719692547</v>
+        <v>0.4502033243127747</v>
       </c>
       <c r="J2">
-        <v>435.4745416666667</v>
+        <v>382.2721153846154</v>
       </c>
       <c r="K2">
-        <v>0.6082417777902314</v>
+        <v>0.5448113711800024</v>
       </c>
       <c r="L2">
-        <v>16.549191498125</v>
+        <v>17.14971632958333</v>
       </c>
       <c r="M2">
-        <v>0.1942864793541164</v>
+        <v>0.2332183852201103</v>
       </c>
       <c r="N2">
         <v>11.83333333333333</v>
@@ -525,19 +535,31 @@
         <v>16</v>
       </c>
       <c r="Q2">
-        <v>4.569769934333333</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="R2">
-        <v>0.7947096508245413</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S2">
-        <v>2.666666666666667</v>
+        <v>-1.019097643441838</v>
       </c>
       <c r="T2">
-        <v>0.3333333333333333</v>
+        <v>0.6918869784244981</v>
+      </c>
+      <c r="U2">
+        <v>0.2314310867246534</v>
+      </c>
+      <c r="V2">
+        <v>0.2216812478742441</v>
       </c>
       <c r="W2">
-        <v>0.5562811809812113</v>
+        <v>2.259870857882385</v>
+      </c>
+      <c r="X2">
+        <v>0.3095837336681162</v>
+      </c>
+      <c r="Y2">
+        <v>0.4547320147309752</v>
       </c>
     </row>
     <row r="3">
@@ -547,40 +569,40 @@
         </is>
       </c>
       <c r="B3">
-        <v>2.614593071827771</v>
+        <v>5.003784345866223</v>
       </c>
       <c r="C3">
-        <v>0.8139473727884285</v>
+        <v>0.6373746883013849</v>
       </c>
       <c r="D3">
-        <v>655.9329685983965</v>
+        <v>673.5165133337398</v>
       </c>
       <c r="E3">
-        <v>2.472243181288298</v>
+        <v>2.210478914653579</v>
       </c>
       <c r="F3">
-        <v>0.5403418864281665</v>
+        <v>0.6224479165285582</v>
       </c>
       <c r="G3">
-        <v>0.4765788354798875</v>
+        <v>0.1601965597224594</v>
       </c>
       <c r="H3">
-        <v>275.3171712859375</v>
+        <v>173.367179246</v>
       </c>
       <c r="I3">
-        <v>0.7967257165554308</v>
+        <v>0.7413296543555572</v>
       </c>
       <c r="J3">
-        <v>329.558375</v>
+        <v>350.5780769230769</v>
       </c>
       <c r="K3">
-        <v>0.4588539165409685</v>
+        <v>0.4984473010720544</v>
       </c>
       <c r="L3">
-        <v>16.26800568854167</v>
+        <v>16.39226137708333</v>
       </c>
       <c r="M3">
-        <v>0.1799169693057225</v>
+        <v>0.1979468035573365</v>
       </c>
       <c r="N3">
         <v>5.728813559322034</v>
@@ -594,19 +616,31 @@
         <v>8</v>
       </c>
       <c r="Q3">
-        <v>3.58199777625</v>
+        <v>2.333333333333333</v>
       </c>
       <c r="R3">
-        <v>0.8415107830527547</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="S3">
-        <v>2.333333333333333</v>
+        <v>-0.9612707239316846</v>
       </c>
       <c r="T3">
-        <v>0.2916666666666667</v>
+        <v>0.7176499229651693</v>
+      </c>
+      <c r="U3">
+        <v>0.2451824460250201</v>
+      </c>
+      <c r="V3">
+        <v>0.2403557239196652</v>
       </c>
       <c r="W3">
-        <v>0.5499427683522532</v>
+        <v>3.037901513434422</v>
+      </c>
+      <c r="X3">
+        <v>0.4538193710537792</v>
+      </c>
+      <c r="Y3">
+        <v>0.4561234608142631</v>
       </c>
     </row>
     <row r="4">
@@ -616,40 +650,40 @@
         </is>
       </c>
       <c r="B4">
-        <v>7.874606776195011</v>
+        <v>10.62294565431209</v>
       </c>
       <c r="C4">
-        <v>0.2968595627659594</v>
+        <v>0.1726925144091227</v>
       </c>
       <c r="D4">
-        <v>776.4263094419364</v>
+        <v>792.8045437231686</v>
       </c>
       <c r="E4">
-        <v>2.584558235505043</v>
+        <v>2.286344724644616</v>
       </c>
       <c r="F4">
-        <v>0.6502609135285969</v>
+        <v>0.6941482376584547</v>
       </c>
       <c r="G4">
-        <v>0.5163091267147911</v>
+        <v>0.1713927871459866</v>
       </c>
       <c r="H4">
-        <v>111.1061707528571</v>
+        <v>46.4265112432</v>
       </c>
       <c r="I4">
-        <v>0.1881267542972417</v>
+        <v>0.1057957474868344</v>
       </c>
       <c r="J4">
-        <v>307.92475</v>
+        <v>171.8553846153846</v>
       </c>
       <c r="K4">
-        <v>0.4283410961517118</v>
+        <v>0.2370002959486542</v>
       </c>
       <c r="L4">
-        <v>14.43893112102083</v>
+        <v>14.56786224204167</v>
       </c>
       <c r="M4">
-        <v>0.08644530579539533</v>
+        <v>0.1129919915718463</v>
       </c>
       <c r="N4">
         <v>6.186440677966102</v>
@@ -663,19 +697,31 @@
         <v>8</v>
       </c>
       <c r="Q4">
-        <v>2.2009045385</v>
+        <v>2.333333333333333</v>
       </c>
       <c r="R4">
-        <v>0.9069476621047519</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="S4">
-        <v>2.333333333333333</v>
+        <v>-1.173673359843958</v>
       </c>
       <c r="T4">
-        <v>0.2916666666666667</v>
+        <v>0.6230206849622786</v>
+      </c>
+      <c r="U4">
+        <v>0.4639863703953452</v>
+      </c>
+      <c r="V4">
+        <v>0.5374935235398688</v>
       </c>
       <c r="W4">
-        <v>0.4206196360031393</v>
+        <v>1.541192873274919</v>
+      </c>
+      <c r="X4">
+        <v>0.1763512235540355</v>
+      </c>
+      <c r="Y4">
+        <v>0.3122553672943749</v>
       </c>
     </row>
     <row r="5">
@@ -685,40 +731,40 @@
         </is>
       </c>
       <c r="B5">
-        <v>6.762593017775271</v>
+        <v>10.03208662826186</v>
       </c>
       <c r="C5">
-        <v>0.4061765325256969</v>
+        <v>0.221554193513477</v>
       </c>
       <c r="D5">
-        <v>701.0418942996629</v>
+        <v>689.4003266994483</v>
       </c>
       <c r="E5">
-        <v>2.261728394637732</v>
+        <v>1.947248635589016</v>
       </c>
       <c r="F5">
-        <v>0.5814921208885685</v>
+        <v>0.6319951822128911</v>
       </c>
       <c r="G5">
-        <v>0.4021114024077352</v>
+        <v>0.1213492045104929</v>
       </c>
       <c r="H5">
-        <v>95.08300676656251</v>
+        <v>64.0126486612</v>
       </c>
       <c r="I5">
-        <v>0.1287416890915327</v>
+        <v>0.1938414998515946</v>
       </c>
       <c r="J5">
-        <v>425.0958333333334</v>
+        <v>281.1561538461539</v>
       </c>
       <c r="K5">
-        <v>0.5936032850157896</v>
+        <v>0.396892464112006</v>
       </c>
       <c r="L5">
-        <v>16.83161025833333</v>
+        <v>16.50655385</v>
       </c>
       <c r="M5">
-        <v>0.2087189971923463</v>
+        <v>0.2032689369444313</v>
       </c>
       <c r="N5">
         <v>3.35</v>
@@ -732,19 +778,31 @@
         <v>4</v>
       </c>
       <c r="Q5">
-        <v>2.788366455</v>
+        <v>4.333333333333333</v>
       </c>
       <c r="R5">
-        <v>0.8791134266404671</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="S5">
-        <v>4.333333333333333</v>
+        <v>-1.000705414297165</v>
       </c>
       <c r="T5">
-        <v>0.5416666666666666</v>
+        <v>0.700081051071759</v>
+      </c>
+      <c r="U5">
+        <v>0.4077682474107153</v>
+      </c>
+      <c r="V5">
+        <v>0.4611487805902014</v>
       </c>
       <c r="W5">
-        <v>0.4677030150536003</v>
+        <v>2.155129477973325</v>
+      </c>
+      <c r="X5">
+        <v>0.2901661958320036</v>
+      </c>
+      <c r="Y5">
+        <v>0.3761964175305524</v>
       </c>
     </row>
     <row r="6">
@@ -754,40 +812,40 @@
         </is>
       </c>
       <c r="B6">
-        <v>5.452538173207431</v>
+        <v>7.607418619499584</v>
       </c>
       <c r="C6">
-        <v>0.5349620126898404</v>
+        <v>0.4220645436230555</v>
       </c>
       <c r="D6">
-        <v>480.0111760454392</v>
+        <v>464.5123518702242</v>
       </c>
       <c r="E6">
-        <v>1.84865571757305</v>
+        <v>1.432234262794714</v>
       </c>
       <c r="F6">
-        <v>0.3798587248873637</v>
+        <v>0.496822022249841</v>
       </c>
       <c r="G6">
-        <v>0.2559912061846156</v>
+        <v>0.045343714753362</v>
       </c>
       <c r="H6">
-        <v>104.9201081617857</v>
+        <v>35.9593211412</v>
       </c>
       <c r="I6">
-        <v>0.1651999633930487</v>
+        <v>0.05339131064146539</v>
       </c>
       <c r="J6">
-        <v>409.3909166666667</v>
+        <v>170.7674358974359</v>
       </c>
       <c r="K6">
-        <v>0.5714525219569752</v>
+        <v>0.235408774858843</v>
       </c>
       <c r="L6">
-        <v>16.21302675770833</v>
+        <v>15.53355351541667</v>
       </c>
       <c r="M6">
-        <v>0.1771073669995812</v>
+        <v>0.1579602877027958</v>
       </c>
       <c r="N6">
         <v>1.864406779661017</v>
@@ -801,19 +859,31 @@
         <v>2</v>
       </c>
       <c r="Q6">
-        <v>7.410009961</v>
+        <v>4</v>
       </c>
       <c r="R6">
-        <v>0.6601376769537439</v>
+        <v>0.5</v>
       </c>
       <c r="S6">
-        <v>4</v>
+        <v>-0.6793816856907595</v>
       </c>
       <c r="T6">
-        <v>0.5</v>
+        <v>0.8432366171958556</v>
+      </c>
+      <c r="U6">
+        <v>0.2263218824286326</v>
+      </c>
+      <c r="V6">
+        <v>0.2147429000968968</v>
       </c>
       <c r="W6">
-        <v>0.4055886841331461</v>
+        <v>1.036141073848968</v>
+      </c>
+      <c r="X6">
+        <v>0.08272192028282797</v>
+      </c>
+      <c r="Y6">
+        <v>0.3051692091404943</v>
       </c>
     </row>
     <row r="7">
@@ -823,40 +893,40 @@
         </is>
       </c>
       <c r="B7">
-        <v>1.266329559472203</v>
+        <v>1.175780674075467</v>
       </c>
       <c r="C7">
-        <v>0.9464889717501007</v>
+        <v>0.9539352869803478</v>
       </c>
       <c r="D7">
-        <v>834.7057465626099</v>
+        <v>876.9293567024525</v>
       </c>
       <c r="E7">
-        <v>3.054211065243965</v>
+        <v>2.708056805399216</v>
       </c>
       <c r="F7">
-        <v>0.7034258352032589</v>
+        <v>0.7447130435816957</v>
       </c>
       <c r="G7">
-        <v>0.6824439679874053</v>
+        <v>0.2336287846781446</v>
       </c>
       <c r="H7">
-        <v>190.1838700915625</v>
+        <v>78.1513537172</v>
       </c>
       <c r="I7">
-        <v>0.4812045968234252</v>
+        <v>0.2646275340176196</v>
       </c>
       <c r="J7">
-        <v>285.4118083333333</v>
+        <v>242.4952179487179</v>
       </c>
       <c r="K7">
-        <v>0.3965880568201705</v>
+        <v>0.3403367700636496</v>
       </c>
       <c r="L7">
-        <v>15.98448257208333</v>
+        <v>16.4322984775</v>
       </c>
       <c r="M7">
-        <v>0.1654280152687566</v>
+        <v>0.1998111677049684</v>
       </c>
       <c r="N7">
         <v>12.89830508474576</v>
@@ -870,19 +940,31 @@
         <v>16</v>
       </c>
       <c r="Q7">
-        <v>4.619948390499999</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="R7">
-        <v>0.7923321708127331</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S7">
-        <v>2.666666666666667</v>
+        <v>-1.035940727081229</v>
       </c>
       <c r="T7">
-        <v>0.3333333333333333</v>
+        <v>0.6843830782795259</v>
+      </c>
+      <c r="U7">
+        <v>0.5279453887864048</v>
+      </c>
+      <c r="V7">
+        <v>0.6243504756959108</v>
       </c>
       <c r="W7">
-        <v>0.562655618499898</v>
+        <v>3.859743076186436</v>
+      </c>
+      <c r="X7">
+        <v>0.6061769173633896</v>
+      </c>
+      <c r="Y7">
+        <v>0.4985296391698585</v>
       </c>
     </row>
     <row r="8">
@@ -892,40 +974,40 @@
         </is>
       </c>
       <c r="B8">
-        <v>5.834182375549821</v>
+        <v>8.587698582789461</v>
       </c>
       <c r="C8">
-        <v>0.4974443224539482</v>
+        <v>0.3409993099769062</v>
       </c>
       <c r="D8">
-        <v>692.6924213740515</v>
+        <v>657.0426526658875</v>
       </c>
       <c r="E8">
-        <v>2.262530900179275</v>
+        <v>1.945600343904767</v>
       </c>
       <c r="F8">
-        <v>0.5738753851058309</v>
+        <v>0.6125459917815566</v>
       </c>
       <c r="G8">
-        <v>0.4023952804604635</v>
+        <v>0.1211059506843051</v>
       </c>
       <c r="H8">
-        <v>116.0377657446875</v>
+        <v>41.2355401532</v>
       </c>
       <c r="I8">
-        <v>0.2064042362233141</v>
+        <v>0.07980692775573352</v>
       </c>
       <c r="J8">
-        <v>195.5060666666667</v>
+        <v>117.4245256410256</v>
       </c>
       <c r="K8">
-        <v>0.269781858254839</v>
+        <v>0.1573753480397434</v>
       </c>
       <c r="L8">
-        <v>16.644063020625</v>
+        <v>16.02291770791667</v>
       </c>
       <c r="M8">
-        <v>0.1991347229333008</v>
+        <v>0.1807479782732143</v>
       </c>
       <c r="N8">
         <v>2</v>
@@ -939,19 +1021,31 @@
         <v>2</v>
       </c>
       <c r="Q8">
-        <v>0.63398203825</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="R8">
-        <v>0.9811892233043098</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="S8">
-        <v>1.333333333333333</v>
+        <v>-0.7957577952195469</v>
       </c>
       <c r="T8">
-        <v>0.1666666666666667</v>
+        <v>0.791388943464544</v>
+      </c>
+      <c r="U8">
+        <v>0.4524248929101558</v>
+      </c>
+      <c r="V8">
+        <v>0.5217929277201457</v>
       </c>
       <c r="W8">
-        <v>0.4121114619253342</v>
+        <v>1.389560270267715</v>
+      </c>
+      <c r="X8">
+        <v>0.1482407307513151</v>
+      </c>
+      <c r="Y8">
+        <v>0.312067077511413</v>
       </c>
     </row>
     <row r="9">
@@ -961,40 +1055,40 @@
         </is>
       </c>
       <c r="B9">
-        <v>9.555711420707254</v>
+        <v>11.79392739577335</v>
       </c>
       <c r="C9">
-        <v>0.1315978794498683</v>
+        <v>0.0758570061647692</v>
       </c>
       <c r="D9">
-        <v>604.6068150246119</v>
+        <v>576.1427017766376</v>
       </c>
       <c r="E9">
-        <v>2.077015005533984</v>
+        <v>1.785966977601064</v>
       </c>
       <c r="F9">
-        <v>0.4935200386302585</v>
+        <v>0.5639195500571393</v>
       </c>
       <c r="G9">
-        <v>0.3367709474237064</v>
+        <v>0.09754736119938923</v>
       </c>
       <c r="H9">
-        <v>98.8683452184375</v>
+        <v>40.0482818796</v>
       </c>
       <c r="I9">
-        <v>0.1427709139676277</v>
+        <v>0.07386286821236809</v>
       </c>
       <c r="J9">
-        <v>332.1990833333333</v>
+        <v>319.7814102564103</v>
       </c>
       <c r="K9">
-        <v>0.4625784638175073</v>
+        <v>0.4533959639205207</v>
       </c>
       <c r="L9">
-        <v>15.94020312770833</v>
+        <v>15.53623958875</v>
       </c>
       <c r="M9">
-        <v>0.1631651915443776</v>
+        <v>0.15808536716081</v>
       </c>
       <c r="N9">
         <v>1</v>
@@ -1008,19 +1102,31 @@
         <v>1</v>
       </c>
       <c r="Q9">
-        <v>2.164679347</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="R9">
-        <v>0.908664029551951</v>
+        <v>0.2083333333333333</v>
       </c>
       <c r="S9">
-        <v>1.666666666666667</v>
+        <v>-1.060244319340101</v>
       </c>
       <c r="T9">
-        <v>0.2083333333333333</v>
+        <v>0.6735553858344103</v>
+      </c>
+      <c r="U9">
+        <v>0.1648513815037616</v>
+      </c>
+      <c r="V9">
+        <v>0.1312653782063204</v>
       </c>
       <c r="W9">
-        <v>0.3559250997148288</v>
+        <v>2.567495039214939</v>
+      </c>
+      <c r="X9">
+        <v>0.3666128102901184</v>
+      </c>
+      <c r="Y9">
+        <v>0.2802435024379179</v>
       </c>
     </row>
     <row r="10">
@@ -1030,40 +1136,28 @@
         </is>
       </c>
       <c r="B10">
-        <v>4.444804068467144</v>
+        <v>4.650199394755413</v>
       </c>
       <c r="C10">
-        <v>0.6340277282168674</v>
+        <v>0.6666147500683968</v>
       </c>
       <c r="D10">
-        <v>676.5846424714285</v>
+        <v>1301.651</v>
       </c>
       <c r="E10">
-        <v>3.16392122</v>
+        <v>7.901</v>
       </c>
       <c r="F10">
-        <v>0.5591812005697393</v>
+        <v>1</v>
       </c>
       <c r="G10">
-        <v>0.7212528029230316</v>
-      </c>
-      <c r="H10">
-        <v>214.3728571428572</v>
-      </c>
-      <c r="I10">
-        <v>0.5708538430353383</v>
-      </c>
-      <c r="J10">
-        <v>95.10555555555555</v>
-      </c>
-      <c r="K10">
-        <v>0.1281734702697966</v>
+        <v>1</v>
       </c>
       <c r="L10">
-        <v>17.21739746645833</v>
+        <v>17.39287826625</v>
       </c>
       <c r="M10">
-        <v>0.228433979153593</v>
+        <v>0.2445414428859278</v>
       </c>
       <c r="N10">
         <v>0.9523809523809523</v>
@@ -1076,8 +1170,8 @@
       <c r="P10">
         <v>1</v>
       </c>
-      <c r="W10">
-        <v>0.4736538373613944</v>
+      <c r="Y10">
+        <v>0.7277890482385811</v>
       </c>
     </row>
     <row r="11">
@@ -1087,36 +1181,24 @@
         </is>
       </c>
       <c r="B11">
-        <v>7.113432774102546</v>
+        <v>9.175395448587471</v>
       </c>
       <c r="C11">
-        <v>0.3716870860215055</v>
-      </c>
-      <c r="D11">
-        <v>466.45181375</v>
-      </c>
-      <c r="E11">
-        <v>2.6041568625</v>
-      </c>
-      <c r="F11">
-        <v>0.3674893117630961</v>
-      </c>
-      <c r="G11">
-        <v>0.5232419387384689</v>
+        <v>0.292399128882582</v>
       </c>
       <c r="L11">
-        <v>15.60870769744681</v>
+        <v>14.60005486</v>
       </c>
       <c r="M11">
-        <v>0.1462246961360277</v>
+        <v>0.1144910702292742</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="W11">
-        <v>0.3521607581647745</v>
+      <c r="Y11">
+        <v>0.2034450995559281</v>
       </c>
     </row>
     <row r="12">
@@ -1126,40 +1208,40 @@
         </is>
       </c>
       <c r="B12">
-        <v>2.325544502250153</v>
+        <v>2.710670323817271</v>
       </c>
       <c r="C12">
-        <v>0.8423624112718686</v>
+        <v>0.8270060496838982</v>
       </c>
       <c r="D12">
-        <v>912.9959398422051</v>
+        <v>950.9130416145175</v>
       </c>
       <c r="E12">
-        <v>2.774944281334617</v>
+        <v>2.6233511580021</v>
       </c>
       <c r="F12">
-        <v>0.7748453992766966</v>
+        <v>0.7891823331596233</v>
       </c>
       <c r="G12">
-        <v>0.5836562254685655</v>
+        <v>0.2211279797381161</v>
       </c>
       <c r="H12">
-        <v>119.3581357134375</v>
+        <v>79.6784137132</v>
       </c>
       <c r="I12">
-        <v>0.2187101944766251</v>
+        <v>0.2722728254797649</v>
       </c>
       <c r="J12">
-        <v>297.311575</v>
+        <v>277.5409487179487</v>
       </c>
       <c r="K12">
-        <v>0.4133719034003929</v>
+        <v>0.3916039104232066</v>
       </c>
       <c r="L12">
-        <v>19.78529996729167</v>
+        <v>20.27226660125</v>
       </c>
       <c r="M12">
-        <v>0.3596621547279532</v>
+        <v>0.3786227905114034</v>
       </c>
       <c r="N12">
         <v>11.03333333333333</v>
@@ -1173,25 +1255,31 @@
         <v>16</v>
       </c>
       <c r="Q12">
-        <v>4.68073917325</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="R12">
-        <v>0.7894518735311615</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S12">
-        <v>2.666666666666667</v>
+        <v>-0.394387953689032</v>
       </c>
       <c r="T12">
-        <v>0.3333333333333333</v>
+        <v>0.9702065089728211</v>
       </c>
       <c r="U12">
-        <v>13.57215189873418</v>
+        <v>0.2819151319075614</v>
       </c>
       <c r="V12">
-        <v>0.8669983345808914</v>
+        <v>0.2902390589132616</v>
       </c>
       <c r="W12">
-        <v>0.5758213144519431</v>
+        <v>4.078294161783221</v>
+      </c>
+      <c r="X12">
+        <v>0.6466931295555873</v>
+      </c>
+      <c r="Y12">
+        <v>0.5120287919771016</v>
       </c>
     </row>
     <row r="13">
@@ -1201,40 +1289,40 @@
         </is>
       </c>
       <c r="B13">
-        <v>6.7695929031412</v>
+        <v>7.824389819187211</v>
       </c>
       <c r="C13">
-        <v>0.4054884059165834</v>
+        <v>0.4041218928948557</v>
       </c>
       <c r="D13">
-        <v>705.031891045062</v>
+        <v>659.8557433919196</v>
       </c>
       <c r="E13">
-        <v>2.407601046433697</v>
+        <v>2.233130154891505</v>
       </c>
       <c r="F13">
-        <v>0.58513196154132</v>
+        <v>0.6142368530336501</v>
       </c>
       <c r="G13">
-        <v>0.4537123474411335</v>
+        <v>0.1635394151821023</v>
       </c>
       <c r="H13">
-        <v>120.089965424375</v>
+        <v>61.1355557432</v>
       </c>
       <c r="I13">
-        <v>0.2214225024290789</v>
+        <v>0.1794372105771712</v>
       </c>
       <c r="J13">
-        <v>453.8560083333334</v>
+        <v>404.5358461538461</v>
       </c>
       <c r="K13">
-        <v>0.6341676404642451</v>
+        <v>0.5773801829930424</v>
       </c>
       <c r="L13">
-        <v>16.47564418041667</v>
+        <v>16.02128836083333</v>
       </c>
       <c r="M13">
-        <v>0.1905279720439203</v>
+        <v>0.1806721062381619</v>
       </c>
       <c r="N13">
         <v>5.3</v>
@@ -1248,25 +1336,31 @@
         <v>8</v>
       </c>
       <c r="Q13">
-        <v>3.779633855</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="R13">
-        <v>0.8321466881256491</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S13">
-        <v>3.666666666666667</v>
+        <v>-0.8032783680769304</v>
       </c>
       <c r="T13">
-        <v>0.4583333333333333</v>
+        <v>0.7880383914538178</v>
       </c>
       <c r="U13">
-        <v>15.20522388059701</v>
+        <v>0.3048129576926495</v>
       </c>
       <c r="V13">
-        <v>1</v>
+        <v>0.3213345229889077</v>
       </c>
       <c r="W13">
-        <v>0.531214539032807</v>
+        <v>2.417458139643524</v>
+      </c>
+      <c r="X13">
+        <v>0.3387981378390733</v>
+      </c>
+      <c r="Y13">
+        <v>0.4025892046534116</v>
       </c>
     </row>
     <row r="14">
@@ -1276,40 +1370,40 @@
         </is>
       </c>
       <c r="B14">
-        <v>6.202177180698082</v>
+        <v>6.603782064222194</v>
       </c>
       <c r="C14">
-        <v>0.4612684418215895</v>
+        <v>0.5050612740431377</v>
       </c>
       <c r="D14">
-        <v>633.0952679188338</v>
+        <v>583.109034912637</v>
       </c>
       <c r="E14">
-        <v>2.054620898268954</v>
+        <v>1.697644652531016</v>
       </c>
       <c r="F14">
-        <v>0.5195083878934385</v>
+        <v>0.5681067960139915</v>
       </c>
       <c r="G14">
-        <v>0.3288492631064082</v>
+        <v>0.08451280929549751</v>
       </c>
       <c r="H14">
-        <v>99.45453668906251</v>
+        <v>59.763006962</v>
       </c>
       <c r="I14">
-        <v>0.1449434573389538</v>
+        <v>0.1725654861486792</v>
       </c>
       <c r="J14">
-        <v>442.4480833333333</v>
+        <v>308.8033333333333</v>
       </c>
       <c r="K14">
-        <v>0.6180775045513266</v>
+        <v>0.4373365296288114</v>
       </c>
       <c r="L14">
-        <v>15.69750223</v>
+        <v>14.95458779333333</v>
       </c>
       <c r="M14">
-        <v>0.1507623857500812</v>
+        <v>0.1310002200723593</v>
       </c>
       <c r="N14">
         <v>3.2</v>
@@ -1323,25 +1417,31 @@
         <v>4</v>
       </c>
       <c r="Q14">
-        <v>1.93711442825</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="R14">
-        <v>0.919446167685493</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S14">
-        <v>3.666666666666667</v>
+        <v>-0.4680097095443029</v>
       </c>
       <c r="T14">
-        <v>0.4583333333333333</v>
+        <v>0.9374066775248885</v>
       </c>
       <c r="U14">
-        <v>7.139013452914798</v>
+        <v>0.2354820903689676</v>
       </c>
       <c r="V14">
-        <v>0.343066666737522</v>
+        <v>0.2271825491538669</v>
       </c>
       <c r="W14">
-        <v>0.4382506231353496</v>
+        <v>2.332909442000188</v>
+      </c>
+      <c r="X14">
+        <v>0.3231240314170564</v>
+      </c>
+      <c r="Y14">
+        <v>0.3844629706631622</v>
       </c>
     </row>
     <row r="15">
@@ -1351,40 +1451,40 @@
         </is>
       </c>
       <c r="B15">
-        <v>1.699209011408265</v>
+        <v>1.39202396258024</v>
       </c>
       <c r="C15">
-        <v>0.9039345792359711</v>
+        <v>0.9360528315966634</v>
       </c>
       <c r="D15">
-        <v>814.3056057503242</v>
+        <v>841.413155045985</v>
       </c>
       <c r="E15">
-        <v>2.903930960374873</v>
+        <v>2.680548594249792</v>
       </c>
       <c r="F15">
-        <v>0.6848159799606366</v>
+        <v>0.7233653605344572</v>
       </c>
       <c r="G15">
-        <v>0.6292839319183426</v>
+        <v>0.2295691405765428</v>
       </c>
       <c r="H15">
-        <v>192.928677510625</v>
+        <v>111.7443072136</v>
       </c>
       <c r="I15">
-        <v>0.4913774046220325</v>
+        <v>0.4328120986234676</v>
       </c>
       <c r="J15">
-        <v>226.6676666666667</v>
+        <v>173.5197435897436</v>
       </c>
       <c r="K15">
-        <v>0.3137332674080375</v>
+        <v>0.2394350268923179</v>
       </c>
       <c r="L15">
-        <v>15.27959484229167</v>
+        <v>16.25210635125</v>
       </c>
       <c r="M15">
-        <v>0.1294059580702085</v>
+        <v>0.1914203567728611</v>
       </c>
       <c r="N15">
         <v>6.559322033898305</v>
@@ -1398,19 +1498,31 @@
         <v>8</v>
       </c>
       <c r="Q15">
-        <v>5.21802827</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="R15">
-        <v>0.7639948510224823</v>
+        <v>0.2083333333333333</v>
       </c>
       <c r="S15">
-        <v>1.666666666666667</v>
+        <v>-0.5893170082206015</v>
       </c>
       <c r="T15">
-        <v>0.2083333333333333</v>
+        <v>0.8833620693277079</v>
+      </c>
+      <c r="U15">
+        <v>0.8045631405858695</v>
+      </c>
+      <c r="V15">
+        <v>1</v>
       </c>
       <c r="W15">
-        <v>0.5156099131963806</v>
+        <v>2.539175812312433</v>
+      </c>
+      <c r="X15">
+        <v>0.3613628349666473</v>
+      </c>
+      <c r="Y15">
+        <v>0.5205713052623998</v>
       </c>
     </row>
     <row r="16">
@@ -1420,40 +1532,40 @@
         </is>
       </c>
       <c r="B16">
-        <v>3.853968818605062</v>
+        <v>4.23496647898634</v>
       </c>
       <c r="C16">
-        <v>0.692110030394446</v>
+        <v>0.7009528520341082</v>
       </c>
       <c r="D16">
-        <v>662.3028872476706</v>
+        <v>601.8196013282181</v>
       </c>
       <c r="E16">
-        <v>2.123226916759468</v>
+        <v>1.799419929991905</v>
       </c>
       <c r="F16">
-        <v>0.5461527906303022</v>
+        <v>0.5793531349479127</v>
       </c>
       <c r="G16">
-        <v>0.3531179340704553</v>
+        <v>0.09953273925708785</v>
       </c>
       <c r="H16">
-        <v>67.78081792354838</v>
+        <v>25.2950142252</v>
       </c>
       <c r="I16">
-        <v>0.02755429151588618</v>
+        <v>0</v>
       </c>
       <c r="J16">
-        <v>77.20100000000001</v>
+        <v>9.844230769230769</v>
       </c>
       <c r="K16">
-        <v>0.1029202596859885</v>
+        <v>0</v>
       </c>
       <c r="L16">
-        <v>17.93460484791667</v>
+        <v>17.11920969583333</v>
       </c>
       <c r="M16">
-        <v>0.2650856106492196</v>
+        <v>0.2317978159571884</v>
       </c>
       <c r="N16">
         <v>0.95</v>
@@ -1467,19 +1579,31 @@
         <v>1</v>
       </c>
       <c r="Q16">
-        <v>1.54509958</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="R16">
-        <v>0.9380200246202453</v>
+        <v>0.2083333333333333</v>
       </c>
       <c r="S16">
-        <v>1.666666666666667</v>
+        <v>-1.661903214290655</v>
       </c>
       <c r="T16">
-        <v>0.2083333333333333</v>
+        <v>0.405505403675303</v>
+      </c>
+      <c r="U16">
+        <v>0.650748794702753</v>
+      </c>
+      <c r="V16">
+        <v>0.7911186628975807</v>
       </c>
       <c r="W16">
-        <v>0.3916617843624846</v>
+        <v>0.6035046795562488</v>
+      </c>
+      <c r="X16">
+        <v>0.002517386384649483</v>
+      </c>
+      <c r="Y16">
+        <v>0.3019111328487163</v>
       </c>
     </row>
     <row r="17">
@@ -1489,40 +1613,40 @@
         </is>
       </c>
       <c r="B17">
-        <v>1.136531189147966</v>
+        <v>1.071580227281821</v>
       </c>
       <c r="C17">
-        <v>0.9592488539153734</v>
+        <v>0.9625522473199343</v>
       </c>
       <c r="D17">
-        <v>745.9491221775057</v>
+        <v>682.3257811817598</v>
       </c>
       <c r="E17">
-        <v>2.427065160490093</v>
+        <v>2.064475816133158</v>
       </c>
       <c r="F17">
-        <v>0.622458358222127</v>
+        <v>0.6277428931625112</v>
       </c>
       <c r="G17">
-        <v>0.4605975769010921</v>
+        <v>0.138649516386767</v>
       </c>
       <c r="H17">
-        <v>126.9768313448387</v>
+        <v>74.47090715375001</v>
       </c>
       <c r="I17">
-        <v>0.2469466112817081</v>
+        <v>0.2462012202106107</v>
       </c>
       <c r="J17">
-        <v>155.476625</v>
+        <v>119.2246153846154</v>
       </c>
       <c r="K17">
-        <v>0.2133229354503053</v>
+        <v>0.1600086346489483</v>
       </c>
       <c r="L17">
-        <v>17.775413358125</v>
+        <v>17.18886838291667</v>
       </c>
       <c r="M17">
-        <v>0.2569504073984943</v>
+        <v>0.2350415363419744</v>
       </c>
       <c r="N17">
         <v>1.983050847457627</v>
@@ -1536,19 +1660,31 @@
         <v>2</v>
       </c>
       <c r="Q17">
-        <v>1.852894555</v>
+        <v>0</v>
       </c>
       <c r="R17">
-        <v>0.9234365468351391</v>
+        <v>0</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>-1.011894091914848</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>0.6950962916657664</v>
+      </c>
+      <c r="U17">
+        <v>0.3187591849925189</v>
+      </c>
+      <c r="V17">
+        <v>0.3402736316214968</v>
       </c>
       <c r="W17">
-        <v>0.4603701612505299</v>
+        <v>1.231438563271949</v>
+      </c>
+      <c r="X17">
+        <v>0.1189272518667831</v>
+      </c>
+      <c r="Y17">
+        <v>0.3524493223224792</v>
       </c>
     </row>
     <row r="18">
@@ -1558,40 +1694,40 @@
         </is>
       </c>
       <c r="B18">
-        <v>2.892220428878251</v>
+        <v>4.497018075011564</v>
       </c>
       <c r="C18">
-        <v>0.7866551012986476</v>
+        <v>0.6792822327675088</v>
       </c>
       <c r="D18">
-        <v>714.1590786180997</v>
+        <v>689.6108122507695</v>
       </c>
       <c r="E18">
-        <v>2.624414273372065</v>
+        <v>2.479256042832511</v>
       </c>
       <c r="F18">
-        <v>0.5934581609077576</v>
+        <v>0.6321216985244914</v>
       </c>
       <c r="G18">
-        <v>0.5304077887594206</v>
+        <v>0.1998625153576704</v>
       </c>
       <c r="H18">
-        <v>184.2882473682143</v>
+        <v>97.4972370524</v>
       </c>
       <c r="I18">
-        <v>0.4593542344259761</v>
+        <v>0.3614835299036266</v>
       </c>
       <c r="J18">
-        <v>185.8095416666667</v>
+        <v>134.5203846153846</v>
       </c>
       <c r="K18">
-        <v>0.2561055406832375</v>
+        <v>0.1823842658841719</v>
       </c>
       <c r="L18">
-        <v>18.00750354520833</v>
+        <v>17.10500709041667</v>
       </c>
       <c r="M18">
-        <v>0.2688109713450515</v>
+        <v>0.2311364586644217</v>
       </c>
       <c r="N18">
         <v>2</v>
@@ -1605,19 +1741,31 @@
         <v>2</v>
       </c>
       <c r="Q18">
-        <v>0.55887011425</v>
+        <v>2.333333333333333</v>
       </c>
       <c r="R18">
-        <v>0.9847480633245231</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="S18">
-        <v>2.333333333333333</v>
+        <v>-0.7624413743133345</v>
       </c>
       <c r="T18">
-        <v>0.2916666666666667</v>
+        <v>0.8062320150196476</v>
+      </c>
+      <c r="U18">
+        <v>0.1397202845406313</v>
+      </c>
+      <c r="V18">
+        <v>0.09713711073965478</v>
       </c>
       <c r="W18">
-        <v>0.5214008159264101</v>
+        <v>1.902551130038404</v>
+      </c>
+      <c r="X18">
+        <v>0.2433418210541713</v>
+      </c>
+      <c r="Y18">
+        <v>0.3724648314582031</v>
       </c>
     </row>
     <row r="19">
@@ -1627,40 +1775,40 @@
         </is>
       </c>
       <c r="B19">
-        <v>2.173775254829633</v>
+        <v>2.39641692676325</v>
       </c>
       <c r="C19">
-        <v>0.8572821495440859</v>
+        <v>0.8529935491843315</v>
       </c>
       <c r="D19">
-        <v>63.60968471467833</v>
+        <v>-362.0518748214354</v>
       </c>
       <c r="E19">
-        <v>2.011711592971416</v>
+        <v>1.584181062135045</v>
       </c>
       <c r="F19">
         <v>0</v>
       </c>
       <c r="G19">
-        <v>0.313670539220751</v>
+        <v>0.06776792563165331</v>
       </c>
       <c r="H19">
-        <v>85.71637923125</v>
+        <v>46.580965416</v>
       </c>
       <c r="I19">
-        <v>0.09402708544534275</v>
+        <v>0.1065690289372644</v>
       </c>
       <c r="J19">
-        <v>56.48408333333333</v>
+        <v>53.65576923076923</v>
       </c>
       <c r="K19">
-        <v>0.07370039675182005</v>
+        <v>0.06409032547975378</v>
       </c>
       <c r="L19">
-        <v>18.12868266854167</v>
+        <v>17.22569867041667</v>
       </c>
       <c r="M19">
-        <v>0.27500361895047</v>
+        <v>0.2367565723172916</v>
       </c>
       <c r="N19">
         <v>1</v>
@@ -1674,19 +1822,31 @@
         <v>1</v>
       </c>
       <c r="Q19">
-        <v>1.045497178</v>
+        <v>0</v>
       </c>
       <c r="R19">
-        <v>0.9616914329366177</v>
+        <v>0</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>-1.537712703617512</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>0.4608345352640616</v>
+      </c>
+      <c r="U19">
+        <v>0.1163233587135575</v>
+      </c>
+      <c r="V19">
+        <v>0.06536386408450168</v>
       </c>
       <c r="W19">
-        <v>0.3219219028561359</v>
+        <v>1.279663954042972</v>
+      </c>
+      <c r="X19">
+        <v>0.1278675422350279</v>
+      </c>
+      <c r="Y19">
+        <v>0.1982243343133886</v>
       </c>
     </row>
     <row r="20">
@@ -1696,40 +1856,40 @@
         </is>
       </c>
       <c r="B20">
-        <v>2.185989068317086</v>
+        <v>3.063092334736524</v>
       </c>
       <c r="C20">
-        <v>0.8560814655871208</v>
+        <v>0.7978621584211051</v>
       </c>
       <c r="D20">
-        <v>799.4162616745616</v>
+        <v>797.1924656038281</v>
       </c>
       <c r="E20">
-        <v>2.781380475817904</v>
+        <v>2.642121951611116</v>
       </c>
       <c r="F20">
-        <v>0.6712333022498698</v>
+        <v>0.6967856808864893</v>
       </c>
       <c r="G20">
-        <v>0.5859329628396042</v>
+        <v>0.2238981613810915</v>
       </c>
       <c r="H20">
-        <v>196.8196160846875</v>
+        <v>136.2243085884</v>
       </c>
       <c r="I20">
-        <v>0.5057980047687795</v>
+        <v>0.5553722770017252</v>
       </c>
       <c r="J20">
-        <v>238.2480416666667</v>
+        <v>183.2476923076923</v>
       </c>
       <c r="K20">
-        <v>0.3300666328248477</v>
+        <v>0.2536656935494822</v>
       </c>
       <c r="L20">
-        <v>18.22061450770833</v>
+        <v>17.46539568208333</v>
       </c>
       <c r="M20">
-        <v>0.2797016351434999</v>
+        <v>0.2479182825858949</v>
       </c>
       <c r="N20">
         <v>3.559322033898305</v>
@@ -1743,19 +1903,31 @@
         <v>4</v>
       </c>
       <c r="Q20">
-        <v>3.5945891465</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="R20">
-        <v>0.8409141977175818</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="S20">
-        <v>1.333333333333333</v>
+        <v>-1.458672806225103</v>
       </c>
       <c r="T20">
-        <v>0.1666666666666667</v>
+        <v>0.4960482473253356</v>
+      </c>
+      <c r="U20">
+        <v>0.3480496476955625</v>
+      </c>
+      <c r="V20">
+        <v>0.3800503571189321</v>
       </c>
       <c r="W20">
-        <v>0.5295493584747463</v>
+        <v>2.560460464897154</v>
+      </c>
+      <c r="X20">
+        <v>0.3653087018938461</v>
+      </c>
+      <c r="Y20">
+        <v>0.4183576226830569</v>
       </c>
     </row>
     <row r="21">
@@ -1765,40 +1937,40 @@
         </is>
       </c>
       <c r="B21">
-        <v>3.356827381619648</v>
+        <v>2.598609080226484</v>
       </c>
       <c r="C21">
-        <v>0.7409817237721223</v>
+        <v>0.8362730664898705</v>
       </c>
       <c r="D21">
-        <v>917.5395358708413</v>
+        <v>927.2100813371653</v>
       </c>
       <c r="E21">
-        <v>2.73056528632354</v>
+        <v>2.482292313178938</v>
       </c>
       <c r="F21">
-        <v>0.7789902561750838</v>
+        <v>0.7749352217095716</v>
       </c>
       <c r="G21">
-        <v>0.5679576140152887</v>
+        <v>0.2003106061817443</v>
       </c>
       <c r="H21">
-        <v>123.234310468125</v>
+        <v>93.86231739920001</v>
       </c>
       <c r="I21">
-        <v>0.233076076942331</v>
+        <v>0.3432851485283125</v>
       </c>
       <c r="J21">
-        <v>581.4750416666667</v>
+        <v>501.1975641025641</v>
       </c>
       <c r="K21">
-        <v>0.8141659829681285</v>
+        <v>0.718783137153259</v>
       </c>
       <c r="L21">
-        <v>19.373500355</v>
+        <v>19.18825071</v>
       </c>
       <c r="M21">
-        <v>0.3386178542509189</v>
+        <v>0.3281446004807311</v>
       </c>
       <c r="N21">
         <v>12.15254237288136</v>
@@ -1812,25 +1984,31 @@
         <v>16</v>
       </c>
       <c r="Q21">
-        <v>3.626466306</v>
+        <v>7.333333333333333</v>
       </c>
       <c r="R21">
-        <v>0.839403842171912</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="S21">
-        <v>7.333333333333333</v>
+        <v>-0.755348809499524</v>
       </c>
       <c r="T21">
-        <v>0.9166666666666666</v>
+        <v>0.8093918816612942</v>
       </c>
       <c r="U21">
-        <v>9.609856262833675</v>
+        <v>0.3543622701498473</v>
       </c>
       <c r="V21">
-        <v>0.5442985856962799</v>
+        <v>0.3886229581419586</v>
       </c>
       <c r="W21">
-        <v>0.6415731780731924</v>
+        <v>3.906252654340075</v>
+      </c>
+      <c r="X21">
+        <v>0.6147991208738268</v>
+      </c>
+      <c r="Y21">
+        <v>0.5931212407887235</v>
       </c>
     </row>
     <row r="22">
@@ -1840,40 +2018,40 @@
         </is>
       </c>
       <c r="B22">
-        <v>0.9990682892502492</v>
+        <v>0.8470214289750483</v>
       </c>
       <c r="C22">
-        <v>0.9727622008118715</v>
+        <v>0.9811223621174903</v>
       </c>
       <c r="D22">
-        <v>813.5264000739855</v>
+        <v>810.2287041847036</v>
       </c>
       <c r="E22">
-        <v>2.500077708360005</v>
+        <v>2.221810285043644</v>
       </c>
       <c r="F22">
-        <v>0.6841051561984712</v>
+        <v>0.7046213580246169</v>
       </c>
       <c r="G22">
-        <v>0.4864250121536806</v>
+        <v>0.1618688360735901</v>
       </c>
       <c r="H22">
-        <v>140.165478528125</v>
+        <v>94.331812516</v>
       </c>
       <c r="I22">
-        <v>0.2958263876869464</v>
+        <v>0.345635695996907</v>
       </c>
       <c r="J22">
-        <v>128.7385</v>
+        <v>101.4121794871795</v>
       </c>
       <c r="K22">
-        <v>0.1756105499545552</v>
+        <v>0.1339514621701476</v>
       </c>
       <c r="L22">
-        <v>17.93935104833333</v>
+        <v>17.20161876333333</v>
       </c>
       <c r="M22">
-        <v>0.2653281569380242</v>
+        <v>0.2356352694512683</v>
       </c>
       <c r="N22">
         <v>3.694915254237288</v>
@@ -1887,19 +2065,31 @@
         <v>4</v>
       </c>
       <c r="Q22">
-        <v>0.6450701425000001</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="R22">
-        <v>0.9806638634539456</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S22">
-        <v>2.666666666666667</v>
+        <v>-0.787107857840073</v>
       </c>
       <c r="T22">
-        <v>0.3333333333333333</v>
+        <v>0.7952426479135342</v>
+      </c>
+      <c r="U22">
+        <v>0.2179829708833508</v>
+      </c>
+      <c r="V22">
+        <v>0.2034185793155251</v>
       </c>
       <c r="W22">
-        <v>0.5242568325663535</v>
+        <v>1.577221861175118</v>
+      </c>
+      <c r="X22">
+        <v>0.1830304771246527</v>
+      </c>
+      <c r="Y22">
+        <v>0.4077860021521065</v>
       </c>
     </row>
     <row r="23">
@@ -1909,40 +2099,40 @@
         </is>
       </c>
       <c r="B23">
-        <v>1.370103848357541</v>
+        <v>0.9806401652694139</v>
       </c>
       <c r="C23">
-        <v>0.9362873976112719</v>
+        <v>0.9700726268552763</v>
       </c>
       <c r="D23">
-        <v>961.0739699344375</v>
+        <v>982.779108216858</v>
       </c>
       <c r="E23">
-        <v>3.028067005123522</v>
+        <v>2.839018103463625</v>
       </c>
       <c r="F23">
-        <v>0.8187041740077048</v>
+        <v>0.8083360336698544</v>
       </c>
       <c r="G23">
-        <v>0.6731957765504538</v>
+        <v>0.2529559687810056</v>
       </c>
       <c r="H23">
-        <v>151.3133351287097</v>
+        <v>105.8838912079167</v>
       </c>
       <c r="I23">
-        <v>0.3371425841445167</v>
+        <v>0.4034716741671714</v>
       </c>
       <c r="J23">
-        <v>659.353575</v>
+        <v>580.2130641025641</v>
       </c>
       <c r="K23">
-        <v>0.9240085867748759</v>
+        <v>0.8343720730996927</v>
       </c>
       <c r="L23">
-        <v>20.34326158791667</v>
+        <v>21.2025648425</v>
       </c>
       <c r="M23">
-        <v>0.3881758095459888</v>
+        <v>0.4219429777762483</v>
       </c>
       <c r="N23">
         <v>33.2280701754386</v>
@@ -1956,25 +2146,25 @@
         <v>60</v>
       </c>
       <c r="Q23">
-        <v>7.306620341</v>
+        <v>6.333333333333333</v>
       </c>
       <c r="R23">
-        <v>0.6650363281629801</v>
-      </c>
-      <c r="S23">
-        <v>6.333333333333333</v>
-      </c>
-      <c r="T23">
         <v>0.7916666666666666</v>
       </c>
       <c r="U23">
-        <v>3.057603686635945</v>
+        <v>0.5947681296885415</v>
       </c>
       <c r="V23">
-        <v>0.01066595066272064</v>
+        <v>0.7150963901185717</v>
       </c>
       <c r="W23">
-        <v>0.6160981415696866</v>
+        <v>4.98284602843752</v>
+      </c>
+      <c r="X23">
+        <v>0.8143839706609451</v>
+      </c>
+      <c r="Y23">
+        <v>0.6680331535328258</v>
       </c>
     </row>
     <row r="24">
@@ -1984,40 +2174,40 @@
         </is>
       </c>
       <c r="B24">
-        <v>1.87831184917383</v>
+        <v>2.359231208098899</v>
       </c>
       <c r="C24">
-        <v>0.886327801125847</v>
+        <v>0.8560686594433526</v>
       </c>
       <c r="D24">
-        <v>790.0249197554833</v>
+        <v>827.5179842743217</v>
       </c>
       <c r="E24">
-        <v>2.375324300110834</v>
+        <v>2.222399237288418</v>
       </c>
       <c r="F24">
-        <v>0.6626661303241366</v>
+        <v>0.7150134059986122</v>
       </c>
       <c r="G24">
-        <v>0.4422947815550168</v>
+        <v>0.1619557532669196</v>
       </c>
       <c r="H24">
-        <v>112.8774740863333</v>
+        <v>77.94017594125</v>
       </c>
       <c r="I24">
-        <v>0.1946915603522473</v>
+        <v>0.2635702634115568</v>
       </c>
       <c r="J24">
-        <v>442.4108333333334</v>
+        <v>379.4884615384615</v>
       </c>
       <c r="K24">
-        <v>0.6180249658501381</v>
+        <v>0.5407392639843241</v>
       </c>
       <c r="L24">
-        <v>17.9985813475</v>
+        <v>18.22820436166667</v>
       </c>
       <c r="M24">
-        <v>0.2683550180029762</v>
+        <v>0.2834391654399762</v>
       </c>
       <c r="N24">
         <v>3.6</v>
@@ -2031,19 +2221,31 @@
         <v>4</v>
       </c>
       <c r="Q24">
-        <v>2.5428031785</v>
+        <v>4.666666666666667</v>
       </c>
       <c r="R24">
-        <v>0.8907483358448023</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="S24">
-        <v>4.666666666666667</v>
+        <v>-1.33318693909328</v>
       </c>
       <c r="T24">
-        <v>0.5833333333333334</v>
+        <v>0.5519544837795801</v>
+      </c>
+      <c r="U24">
+        <v>0.2280327668409885</v>
+      </c>
+      <c r="V24">
+        <v>0.2170662973172846</v>
       </c>
       <c r="W24">
-        <v>0.5683052407985623</v>
+        <v>5.028966557127412</v>
+      </c>
+      <c r="X24">
+        <v>0.8229340500243738</v>
+      </c>
+      <c r="Y24">
+        <v>0.4996074675999314</v>
       </c>
     </row>
     <row r="25">
@@ -2053,40 +2255,40 @@
         </is>
       </c>
       <c r="B25">
-        <v>0.7408975943918668</v>
+        <v>0.6724456699305441</v>
       </c>
       <c r="C25">
-        <v>0.9981417771246597</v>
+        <v>0.9955590794083361</v>
       </c>
       <c r="D25">
-        <v>873.7027658075027</v>
+        <v>914.8376385850046</v>
       </c>
       <c r="E25">
-        <v>3.219755117538084</v>
+        <v>3.040924993516866</v>
       </c>
       <c r="F25">
-        <v>0.7390005348937705</v>
+        <v>0.7674985315773335</v>
       </c>
       <c r="G25">
-        <v>0.7410034679201478</v>
+        <v>0.2827532577004839</v>
       </c>
       <c r="H25">
-        <v>195.54534427125</v>
+        <v>133.2872406672</v>
       </c>
       <c r="I25">
-        <v>0.5010752973936624</v>
+        <v>0.5406677202976605</v>
       </c>
       <c r="J25">
-        <v>192.1180833333333</v>
+        <v>111.9438461538462</v>
       </c>
       <c r="K25">
-        <v>0.2650033282150609</v>
+        <v>0.149357858937143</v>
       </c>
       <c r="L25">
-        <v>16.56638317395833</v>
+        <v>16.49151634791667</v>
       </c>
       <c r="M25">
-        <v>0.1951650299431444</v>
+        <v>0.2025687019258525</v>
       </c>
       <c r="N25">
         <v>1.983050847457627</v>
@@ -2099,14 +2301,26 @@
       <c r="P25">
         <v>2</v>
       </c>
-      <c r="Q25">
-        <v>6.1132243405</v>
-      </c>
-      <c r="R25">
-        <v>0.7215800195020812</v>
+      <c r="S25">
+        <v>-0.511202244335448</v>
+      </c>
+      <c r="T25">
+        <v>0.9181636175828851</v>
+      </c>
+      <c r="U25">
+        <v>0.08608989262336765</v>
+      </c>
+      <c r="V25">
+        <v>0.02430653106461261</v>
       </c>
       <c r="W25">
-        <v>0.5944242078560753</v>
+        <v>1.436201281210562</v>
+      </c>
+      <c r="X25">
+        <v>0.1568873000010577</v>
+      </c>
+      <c r="Y25">
+        <v>0.4486402887217072</v>
       </c>
     </row>
     <row r="26">
@@ -2116,40 +2330,40 @@
         </is>
       </c>
       <c r="B26">
-        <v>1.389876030177799</v>
+        <v>1.637969963880097</v>
       </c>
       <c r="C26">
-        <v>0.9343436851474973</v>
+        <v>0.9157140806210777</v>
       </c>
       <c r="D26">
-        <v>1016.709276471273</v>
+        <v>1145.358663001164</v>
       </c>
       <c r="E26">
-        <v>3.368916242312652</v>
+        <v>3.544633181031509</v>
       </c>
       <c r="F26">
-        <v>0.8694570100080276</v>
+        <v>0.9060575422666076</v>
       </c>
       <c r="G26">
-        <v>0.7937676763296724</v>
+        <v>0.3570901879088728</v>
       </c>
       <c r="H26">
-        <v>221.300390919375</v>
+        <v>142.5673003768</v>
       </c>
       <c r="I26">
-        <v>0.5965286751337395</v>
+        <v>0.5871287378423848</v>
       </c>
       <c r="J26">
-        <v>713.231575</v>
+        <v>616.7175512820513</v>
       </c>
       <c r="K26">
-        <v>1</v>
+        <v>0.8877731757991271</v>
       </c>
       <c r="L26">
-        <v>19.00962763604167</v>
+        <v>18.89425527208333</v>
       </c>
       <c r="M26">
-        <v>0.3200227740114285</v>
+        <v>0.3144544344018968</v>
       </c>
       <c r="N26">
         <v>33.47457627118644</v>
@@ -2163,25 +2377,25 @@
         <v>60</v>
       </c>
       <c r="Q26">
-        <v>4.071412934</v>
+        <v>4.666666666666667</v>
       </c>
       <c r="R26">
-        <v>0.8183220513954514</v>
-      </c>
-      <c r="S26">
-        <v>4.666666666666667</v>
-      </c>
-      <c r="T26">
         <v>0.5833333333333334</v>
       </c>
       <c r="U26">
-        <v>3.079295154185022</v>
+        <v>0.2032358553309727</v>
       </c>
       <c r="V26">
-        <v>0.01243256067223224</v>
+        <v>0.1833918568580152</v>
       </c>
       <c r="W26">
-        <v>0.6586897517812647</v>
+        <v>4.993074059988925</v>
+      </c>
+      <c r="X26">
+        <v>0.8162800998680531</v>
+      </c>
+      <c r="Y26">
+        <v>0.6168026054332632</v>
       </c>
     </row>
     <row r="27">
@@ -2191,40 +2405,40 @@
         </is>
       </c>
       <c r="B27">
-        <v>5.03432563844431</v>
+        <v>6.174000995376301</v>
       </c>
       <c r="C27">
-        <v>0.576074567880535</v>
+        <v>0.5406024501024322</v>
       </c>
       <c r="D27">
-        <v>548.7226506533721</v>
+        <v>518.2429384907324</v>
       </c>
       <c r="E27">
-        <v>1.92094178688546</v>
+        <v>1.587541858605282</v>
       </c>
       <c r="F27">
-        <v>0.4425401841835008</v>
+        <v>0.5291178050086915</v>
       </c>
       <c r="G27">
-        <v>0.2815616571454121</v>
+        <v>0.06826390981226653</v>
       </c>
       <c r="H27">
-        <v>119.3736232370968</v>
+        <v>44.40259668125</v>
       </c>
       <c r="I27">
-        <v>0.2187675943511546</v>
+        <v>0.09566293229874817</v>
       </c>
       <c r="J27">
-        <v>142.4275</v>
+        <v>118.075</v>
       </c>
       <c r="K27">
-        <v>0.1949179937282425</v>
+        <v>0.1583269036081355</v>
       </c>
       <c r="L27">
-        <v>16.046611876875</v>
+        <v>15.39947375375</v>
       </c>
       <c r="M27">
-        <v>0.168603024956573</v>
+        <v>0.1517167411429083</v>
       </c>
       <c r="N27">
         <v>1</v>
@@ -2238,19 +2452,31 @@
         <v>1</v>
       </c>
       <c r="Q27">
-        <v>21.34269891</v>
+        <v>2</v>
       </c>
       <c r="R27">
+        <v>0.25</v>
+      </c>
+      <c r="S27">
+        <v>-2.57209142287238</v>
+      </c>
+      <c r="T27">
         <v>0</v>
       </c>
-      <c r="S27">
-        <v>2</v>
-      </c>
-      <c r="T27">
-        <v>0.25</v>
+      <c r="U27">
+        <v>0.2169251495462083</v>
+      </c>
+      <c r="V27">
+        <v>0.2019820479305677</v>
       </c>
       <c r="W27">
-        <v>0.2665581277806773</v>
+        <v>1.062002979425445</v>
+      </c>
+      <c r="X27">
+        <v>0.08751634375215032</v>
+      </c>
+      <c r="Y27">
+        <v>0.20831891336559</v>
       </c>
     </row>
     <row r="28">
@@ -2260,40 +2486,40 @@
         </is>
       </c>
       <c r="B28">
-        <v>1.903937605799871</v>
+        <v>2.075840817204807</v>
       </c>
       <c r="C28">
-        <v>0.8838086505839147</v>
+        <v>0.8795039117296526</v>
       </c>
       <c r="D28">
-        <v>648.7983906320918</v>
+        <v>638.6032790314146</v>
       </c>
       <c r="E28">
-        <v>2.035724943587848</v>
+        <v>1.962920347908493</v>
       </c>
       <c r="F28">
-        <v>0.533833428256634</v>
+        <v>0.6014626583849895</v>
       </c>
       <c r="G28">
-        <v>0.322165014161533</v>
+        <v>0.1236620257308251</v>
       </c>
       <c r="H28">
-        <v>80.2080049490625</v>
+        <v>52.3862463348</v>
       </c>
       <c r="I28">
-        <v>0.07361194357916995</v>
+        <v>0.1356334172128486</v>
       </c>
       <c r="J28">
-        <v>153.53375</v>
+        <v>62.20987179487179</v>
       </c>
       <c r="K28">
-        <v>0.2105826366832804</v>
+        <v>0.07660381477440198</v>
       </c>
       <c r="L28">
-        <v>18.54128809604167</v>
+        <v>17.81299285875</v>
       </c>
       <c r="M28">
-        <v>0.2960890992073462</v>
+        <v>0.2641044625852236</v>
       </c>
       <c r="N28">
         <v>0.9833333333333333</v>
@@ -2306,14 +2532,26 @@
       <c r="P28">
         <v>1</v>
       </c>
-      <c r="Q28">
-        <v>13.7963962</v>
-      </c>
-      <c r="R28">
-        <v>0.3575475458329737</v>
+      <c r="S28">
+        <v>-1.102399389618816</v>
+      </c>
+      <c r="T28">
+        <v>0.6547745352046623</v>
+      </c>
+      <c r="U28">
+        <v>0.3374767695716056</v>
+      </c>
+      <c r="V28">
+        <v>0.3656922885859016</v>
       </c>
       <c r="W28">
-        <v>0.382519759757836</v>
+        <v>0.8559792271251629</v>
+      </c>
+      <c r="X28">
+        <v>0.04932251807502108</v>
+      </c>
+      <c r="Y28">
+        <v>0.3500844035870585</v>
       </c>
     </row>
     <row r="29">
@@ -2323,40 +2561,40 @@
         </is>
       </c>
       <c r="B29">
-        <v>2.494660573312057</v>
+        <v>2.268599779202153</v>
       </c>
       <c r="C29">
-        <v>0.8257373863689109</v>
+        <v>0.8635635162539946</v>
       </c>
       <c r="D29">
-        <v>953.7906142421343</v>
+        <v>956.6004474053108</v>
       </c>
       <c r="E29">
-        <v>2.598086318190543</v>
+        <v>2.251747536584524</v>
       </c>
       <c r="F29">
-        <v>0.8120599946188712</v>
+        <v>0.7926008557076495</v>
       </c>
       <c r="G29">
-        <v>0.5210945463425779</v>
+        <v>0.166286956393226</v>
       </c>
       <c r="H29">
-        <v>123.441344703125</v>
+        <v>63.83012122</v>
       </c>
       <c r="I29">
-        <v>0.2338433874158308</v>
+        <v>0.1929276683770822</v>
       </c>
       <c r="J29">
-        <v>321.4800416666667</v>
+        <v>229.5128205128205</v>
       </c>
       <c r="K29">
-        <v>0.4474599530214684</v>
+        <v>0.3213452873083789</v>
       </c>
       <c r="L29">
-        <v>20.663866608125</v>
+        <v>20.76231654958333</v>
       </c>
       <c r="M29">
-        <v>0.4045597695554779</v>
+        <v>0.4014424139285164</v>
       </c>
       <c r="N29">
         <v>3.677966101694915</v>
@@ -2370,25 +2608,31 @@
         <v>4</v>
       </c>
       <c r="Q29">
-        <v>2.91523699475</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="R29">
-        <v>0.8731022378677181</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="S29">
-        <v>1.333333333333333</v>
+        <v>-1.090517443382615</v>
       </c>
       <c r="T29">
-        <v>0.1666666666666667</v>
+        <v>0.6600681583910872</v>
       </c>
       <c r="U29">
-        <v>3.663265306122449</v>
+        <v>0.2869006174457089</v>
       </c>
       <c r="V29">
-        <v>0.05999262148114465</v>
+        <v>0.2970093954467886</v>
       </c>
       <c r="W29">
-        <v>0.4827240625931852</v>
+        <v>2.25085548316566</v>
+      </c>
+      <c r="X29">
+        <v>0.3079124135096388</v>
+      </c>
+      <c r="Y29">
+        <v>0.4169823331983029</v>
       </c>
     </row>
     <row r="30">
@@ -2398,36 +2642,24 @@
         </is>
       </c>
       <c r="B30">
-        <v>5.358723557574902</v>
+        <v>2.038356981546432</v>
       </c>
       <c r="C30">
-        <v>0.5441844970543293</v>
-      </c>
-      <c r="D30">
-        <v>765.69556865</v>
-      </c>
-      <c r="E30">
-        <v>3.559882353</v>
-      </c>
-      <c r="F30">
-        <v>0.6404718863536584</v>
-      </c>
-      <c r="G30">
-        <v>0.8613199670400836</v>
+        <v>0.8826036750721595</v>
       </c>
       <c r="L30">
-        <v>19.07895547791667</v>
+        <v>18.2814526225</v>
       </c>
       <c r="M30">
-        <v>0.3235656523733645</v>
+        <v>0.2859187193384419</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="W30">
-        <v>0.5923855007053589</v>
+      <c r="Y30">
+        <v>0.5842611972053007</v>
       </c>
     </row>
     <row r="31">
@@ -2437,40 +2669,40 @@
         </is>
       </c>
       <c r="B31">
-        <v>2.013311318365398</v>
+        <v>0.7360342021259476</v>
       </c>
       <c r="C31">
-        <v>0.8730566227978314</v>
+        <v>0.9903005620330179</v>
       </c>
       <c r="D31">
-        <v>857.7172489851876</v>
+        <v>858.5921718212161</v>
       </c>
       <c r="E31">
-        <v>2.350635469275505</v>
+        <v>2.174151864269008</v>
       </c>
       <c r="F31">
-        <v>0.7244178829023376</v>
+        <v>0.7336911326631342</v>
       </c>
       <c r="G31">
-        <v>0.4335613624583748</v>
+        <v>0.1548354370009114</v>
       </c>
       <c r="H31">
-        <v>177.1940864143333</v>
+        <v>76.80272141</v>
       </c>
       <c r="I31">
-        <v>0.4330618485285115</v>
+        <v>0.2578755484434986</v>
       </c>
       <c r="J31">
-        <v>150.5134916666667</v>
+        <v>130.1305</v>
       </c>
       <c r="K31">
-        <v>0.206322758828591</v>
+        <v>0.1759624614075828</v>
       </c>
       <c r="L31">
-        <v>21.30009535354167</v>
+        <v>20.85060737375</v>
       </c>
       <c r="M31">
-        <v>0.4370731291872781</v>
+        <v>0.4055537567937125</v>
       </c>
       <c r="N31">
         <v>1.627118644067797</v>
@@ -2484,19 +2716,31 @@
         <v>2</v>
       </c>
       <c r="Q31">
-        <v>0.236966825</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="R31">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S31">
-        <v>2.666666666666667</v>
+        <v>-1.598882708023645</v>
       </c>
       <c r="T31">
-        <v>0.3333333333333333</v>
+        <v>0.4335821855899429</v>
+      </c>
+      <c r="U31">
+        <v>0.0827885435279237</v>
+      </c>
+      <c r="V31">
+        <v>0.01982326775559581</v>
       </c>
       <c r="W31">
-        <v>0.5551033672545322</v>
+        <v>1.090745637070177</v>
+      </c>
+      <c r="X31">
+        <v>0.09284481701469087</v>
+      </c>
+      <c r="Y31">
+        <v>0.359780250203542</v>
       </c>
     </row>
     <row r="32">
@@ -2506,40 +2750,40 @@
         </is>
       </c>
       <c r="B32">
-        <v>0.9993273242222674</v>
+        <v>0.6936343066418474</v>
       </c>
       <c r="C32">
-        <v>0.9727367362724371</v>
+        <v>0.9938068638679096</v>
       </c>
       <c r="D32">
-        <v>1010.778519775807</v>
+        <v>1029.288345796775</v>
       </c>
       <c r="E32">
-        <v>2.521925385274342</v>
+        <v>2.439337530630742</v>
       </c>
       <c r="F32">
-        <v>0.8640467275694197</v>
+        <v>0.8362912883513184</v>
       </c>
       <c r="G32">
-        <v>0.4941534023740833</v>
+        <v>0.1939713670120237</v>
       </c>
       <c r="H32">
-        <v>168.7766671846875</v>
+        <v>67.7049339964</v>
       </c>
       <c r="I32">
-        <v>0.4018652015838838</v>
+        <v>0.2123270849778836</v>
       </c>
       <c r="J32">
-        <v>184.4895</v>
+        <v>146.1408974358974</v>
       </c>
       <c r="K32">
-        <v>0.2542437078058841</v>
+        <v>0.1993834965677083</v>
       </c>
       <c r="L32">
-        <v>21.769751060625</v>
+        <v>21.68616878791667</v>
       </c>
       <c r="M32">
-        <v>0.461074064413063</v>
+        <v>0.4444624371802761</v>
       </c>
       <c r="N32">
         <v>3.933333333333333</v>
@@ -2553,19 +2797,31 @@
         <v>4</v>
       </c>
       <c r="Q32">
-        <v>6.5395552285</v>
+        <v>0</v>
       </c>
       <c r="R32">
-        <v>0.7013802516720424</v>
+        <v>0</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>-1.518151748796495</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>0.4695492964598048</v>
+      </c>
+      <c r="U32">
+        <v>0.472248451133825</v>
+      </c>
+      <c r="V32">
+        <v>0.5487135073586293</v>
       </c>
       <c r="W32">
-        <v>0.5186875114613516</v>
+        <v>1.557222072208001</v>
+      </c>
+      <c r="X32">
+        <v>0.1793228053399155</v>
+      </c>
+      <c r="Y32">
+        <v>0.4077828147115469</v>
       </c>
     </row>
     <row r="33">
@@ -2575,40 +2831,40 @@
         </is>
       </c>
       <c r="B33">
-        <v>1.08660229088038</v>
+        <v>0.7101404810624976</v>
       </c>
       <c r="C33">
-        <v>0.9641571347893538</v>
+        <v>0.9924418692376782</v>
       </c>
       <c r="D33">
-        <v>1107.679249668098</v>
+        <v>1228.302213247796</v>
       </c>
       <c r="E33">
-        <v>3.62140707432442</v>
+        <v>3.558252237712686</v>
       </c>
       <c r="F33">
-        <v>0.9524435956495637</v>
+        <v>0.9559123279389198</v>
       </c>
       <c r="G33">
-        <v>0.8830837022171001</v>
+        <v>0.3591000795308614</v>
       </c>
       <c r="H33">
-        <v>232.0746173662963</v>
+        <v>192.7909867556</v>
       </c>
       <c r="I33">
-        <v>0.6364601231697685</v>
+        <v>0.8385757809677933</v>
       </c>
       <c r="J33">
-        <v>344.1929166666667</v>
+        <v>337.4911538461538</v>
       </c>
       <c r="K33">
-        <v>0.4794949853102615</v>
+        <v>0.4793029115121026</v>
       </c>
       <c r="L33">
-        <v>23.14746620666667</v>
+        <v>23.61659908</v>
       </c>
       <c r="M33">
-        <v>0.531479792441109</v>
+        <v>0.5343546868339075</v>
       </c>
       <c r="N33">
         <v>12.86440677966102</v>
@@ -2622,19 +2878,31 @@
         <v>16</v>
       </c>
       <c r="Q33">
-        <v>9.12461412</v>
+        <v>3</v>
       </c>
       <c r="R33">
-        <v>0.5788988858947699</v>
+        <v>0.375</v>
       </c>
       <c r="S33">
-        <v>3</v>
+        <v>-1.122665910493637</v>
       </c>
       <c r="T33">
-        <v>0.375</v>
+        <v>0.6457454314973707</v>
+      </c>
+      <c r="U33">
+        <v>0.1755318038826786</v>
+      </c>
+      <c r="V33">
+        <v>0.1457694928551716</v>
       </c>
       <c r="W33">
-        <v>0.6751272774339908</v>
+        <v>2.963281691573024</v>
+      </c>
+      <c r="X33">
+        <v>0.4399859346834002</v>
+      </c>
+      <c r="Y33">
+        <v>0.5766188515057206</v>
       </c>
     </row>
     <row r="34">
@@ -2644,24 +2912,24 @@
         </is>
       </c>
       <c r="B34">
-        <v>1.577238168341571</v>
+        <v>0.9146349656140685</v>
       </c>
       <c r="C34">
-        <v>0.9159249731156649</v>
+        <v>0.9755309929673042</v>
       </c>
       <c r="L34">
-        <v>21.70601268541667</v>
+        <v>21.99240037083333</v>
       </c>
       <c r="M34">
-        <v>0.4578168259898949</v>
+        <v>0.4587223905265653</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="W34">
-        <v>0.6868708995527799</v>
+      <c r="Y34">
+        <v>0.7171266917469348</v>
       </c>
     </row>
     <row r="35">
@@ -2671,40 +2939,40 @@
         </is>
       </c>
       <c r="B35">
-        <v>0.9556834864386684</v>
+        <v>0.9077257805083475</v>
       </c>
       <c r="C35">
-        <v>0.9770271616912454</v>
+        <v>0.9761023549515071</v>
       </c>
       <c r="D35">
-        <v>845.6928104684499</v>
+        <v>857.0664466363648</v>
       </c>
       <c r="E35">
-        <v>2.759213488094072</v>
+        <v>2.462653275859922</v>
       </c>
       <c r="F35">
-        <v>0.7134486909624694</v>
+        <v>0.7327740667567505</v>
       </c>
       <c r="G35">
-        <v>0.5780916197159226</v>
+        <v>0.1974122896907081</v>
       </c>
       <c r="H35">
-        <v>164.713646173125</v>
+        <v>101.5226671016</v>
       </c>
       <c r="I35">
-        <v>0.3868068293479019</v>
+        <v>0.3816370183502008</v>
       </c>
       <c r="J35">
-        <v>340.3929333333333</v>
+        <v>334.3515</v>
       </c>
       <c r="K35">
-        <v>0.4741353560788141</v>
+        <v>0.474710024707399</v>
       </c>
       <c r="L35">
-        <v>18.16133644729167</v>
+        <v>18.40017289458333</v>
       </c>
       <c r="M35">
-        <v>0.2766723333232239</v>
+        <v>0.2914470372377352</v>
       </c>
       <c r="N35">
         <v>6.135593220338983</v>
@@ -2718,25 +2986,31 @@
         <v>8</v>
       </c>
       <c r="Q35">
-        <v>2.07165073475</v>
+        <v>3</v>
       </c>
       <c r="R35">
-        <v>0.9130717711017509</v>
+        <v>0.375</v>
       </c>
       <c r="S35">
-        <v>3</v>
+        <v>-1.468379965955051</v>
       </c>
       <c r="T35">
-        <v>0.375</v>
+        <v>0.4917235310878367</v>
       </c>
       <c r="U35">
-        <v>7.326145552560646</v>
+        <v>0.1496236035425811</v>
       </c>
       <c r="V35">
-        <v>0.3583071957421785</v>
+        <v>0.1105859116496234</v>
       </c>
       <c r="W35">
-        <v>0.5613956619959451</v>
+        <v>2.951371914817594</v>
+      </c>
+      <c r="X35">
+        <v>0.4377780342244889</v>
+      </c>
+      <c r="Y35">
+        <v>0.446917026865625</v>
       </c>
     </row>
     <row r="36">
@@ -2746,40 +3020,40 @@
         </is>
       </c>
       <c r="B36">
-        <v>5.517142053953108</v>
+        <v>7.358028853615001</v>
       </c>
       <c r="C36">
-        <v>0.5286111016292858</v>
+        <v>0.44268808016107</v>
       </c>
       <c r="D36">
-        <v>797.0526848735647</v>
+        <v>855.92110160506</v>
       </c>
       <c r="E36">
-        <v>2.48792606317468</v>
+        <v>2.592476867396955</v>
       </c>
       <c r="F36">
-        <v>0.6690771493818031</v>
+        <v>0.7320856355178325</v>
       </c>
       <c r="G36">
-        <v>0.4821264930854841</v>
+        <v>0.2165715717963027</v>
       </c>
       <c r="H36">
-        <v>93.236065658125</v>
+        <v>65.1453640424</v>
       </c>
       <c r="I36">
-        <v>0.1218965542449143</v>
+        <v>0.1995124880613656</v>
       </c>
       <c r="J36">
-        <v>95.69158333333333</v>
+        <v>84.00628205128206</v>
       </c>
       <c r="K36">
-        <v>0.1290000243182489</v>
+        <v>0.1084890001999248</v>
       </c>
       <c r="L36">
-        <v>15.50459700958333</v>
+        <v>14.82336068583333</v>
       </c>
       <c r="M36">
-        <v>0.140904301135952</v>
+        <v>0.124889509959132</v>
       </c>
       <c r="N36">
         <v>1</v>
@@ -2793,19 +3067,31 @@
         <v>1</v>
       </c>
       <c r="Q36">
-        <v>3.345633474666667</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="R36">
-        <v>0.8527098402866575</v>
+        <v>0.2083333333333333</v>
       </c>
       <c r="S36">
-        <v>1.666666666666667</v>
+        <v>-2.47887339261411</v>
       </c>
       <c r="T36">
-        <v>0.2083333333333333</v>
+        <v>0.04153032815992834</v>
+      </c>
+      <c r="U36">
+        <v>0.2687833024585698</v>
+      </c>
+      <c r="V36">
+        <v>0.2724059102680065</v>
       </c>
       <c r="W36">
-        <v>0.3915823496769599</v>
+        <v>1.728354121261013</v>
+      </c>
+      <c r="X36">
+        <v>0.2110482135820394</v>
+      </c>
+      <c r="Y36">
+        <v>0.2557554071038935</v>
       </c>
     </row>
     <row r="37">
@@ -2815,40 +3101,40 @@
         </is>
       </c>
       <c r="B37">
-        <v>1.365713000697533</v>
+        <v>1.844119286466969</v>
       </c>
       <c r="C37">
-        <v>0.9367190416959195</v>
+        <v>0.8986663558614945</v>
       </c>
       <c r="D37">
-        <v>1004.951093615742</v>
+        <v>1177.519511472431</v>
       </c>
       <c r="E37">
-        <v>3.163390120458246</v>
+        <v>3.403669917036881</v>
       </c>
       <c r="F37">
-        <v>0.8587307075343737</v>
+        <v>0.9253884269804534</v>
       </c>
       <c r="G37">
-        <v>0.7210649319415701</v>
+        <v>0.3362869201096756</v>
       </c>
       <c r="H37">
-        <v>144.923307941875</v>
+        <v>61.1306341656</v>
       </c>
       <c r="I37">
-        <v>0.313459859466606</v>
+        <v>0.1794125704875191</v>
       </c>
       <c r="J37">
-        <v>330.4918833333333</v>
+        <v>266.2105897435898</v>
       </c>
       <c r="K37">
-        <v>0.4601705693029016</v>
+        <v>0.3750291353760667</v>
       </c>
       <c r="L37">
-        <v>18.41559329854167</v>
+        <v>18.78181159708333</v>
       </c>
       <c r="M37">
-        <v>0.2896656859547942</v>
+        <v>0.3092183919783377</v>
       </c>
       <c r="N37">
         <v>6</v>
@@ -2862,19 +3148,31 @@
         <v>8</v>
       </c>
       <c r="Q37">
-        <v>1.730854418</v>
+        <v>5.666666666666667</v>
       </c>
       <c r="R37">
-        <v>0.9292188687422164</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="S37">
-        <v>5.666666666666667</v>
+        <v>-1.785782758889025</v>
       </c>
       <c r="T37">
-        <v>0.7083333333333334</v>
+        <v>0.350314813129475</v>
+      </c>
+      <c r="U37">
+        <v>0.1870355989054326</v>
+      </c>
+      <c r="V37">
+        <v>0.1613917553451152</v>
       </c>
       <c r="W37">
-        <v>0.6521703747464643</v>
+        <v>2.4032244352052</v>
+      </c>
+      <c r="X37">
+        <v>0.3361594147792935</v>
+      </c>
+      <c r="Y37">
+        <v>0.4580201117380764</v>
       </c>
     </row>
     <row r="38">
@@ -2884,40 +3182,40 @@
         </is>
       </c>
       <c r="B38">
-        <v>4.138422420662683</v>
+        <v>4.45829362716574</v>
       </c>
       <c r="C38">
-        <v>0.6641467020824199</v>
+        <v>0.6824845897777494</v>
       </c>
       <c r="D38">
-        <v>736.0154404505465</v>
+        <v>717.6041019280676</v>
       </c>
       <c r="E38">
-        <v>2.332496835604216</v>
+        <v>2.210539761878858</v>
       </c>
       <c r="F38">
-        <v>0.6133964414115498</v>
+        <v>0.6489475934008841</v>
       </c>
       <c r="G38">
-        <v>0.4271450080044754</v>
+        <v>0.1602055395168147</v>
       </c>
       <c r="H38">
-        <v>67.318532718125</v>
+        <v>30.4613218792</v>
       </c>
       <c r="I38">
-        <v>0.02584096965940489</v>
+        <v>0.02586534117939243</v>
       </c>
       <c r="J38">
-        <v>449.8763333333333</v>
+        <v>204.8405128205128</v>
       </c>
       <c r="K38">
-        <v>0.6285545678292791</v>
+        <v>0.2852530548540268</v>
       </c>
       <c r="L38">
-        <v>18.939353515625</v>
+        <v>17.61658203125</v>
       </c>
       <c r="M38">
-        <v>0.3164315377361496</v>
+        <v>0.2549584130165277</v>
       </c>
       <c r="N38">
         <v>0.7333333333333333</v>
@@ -2931,19 +3229,31 @@
         <v>1</v>
       </c>
       <c r="Q38">
-        <v>5.754061869666667</v>
+        <v>4.333333333333333</v>
       </c>
       <c r="R38">
-        <v>0.7385973145850881</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="S38">
-        <v>4.333333333333333</v>
+        <v>-2.447393696741595</v>
       </c>
       <c r="T38">
-        <v>0.5416666666666666</v>
+        <v>0.05555510530162636</v>
+      </c>
+      <c r="U38">
+        <v>0.3451972616050876</v>
+      </c>
+      <c r="V38">
+        <v>0.3761767898187565</v>
       </c>
       <c r="W38">
-        <v>0.4944724009968792</v>
+        <v>0.7129800354265221</v>
+      </c>
+      <c r="X38">
+        <v>0.02281253493604877</v>
+      </c>
+      <c r="Y38">
+        <v>0.3053925628468493</v>
       </c>
     </row>
     <row r="39">
@@ -2953,40 +3263,40 @@
         </is>
       </c>
       <c r="B39">
-        <v>1.406406261621896</v>
+        <v>1.331719516371994</v>
       </c>
       <c r="C39">
-        <v>0.9327186739484778</v>
+        <v>0.9410397681911508</v>
       </c>
       <c r="D39">
-        <v>877.0060330270752</v>
+        <v>861.6532718160278</v>
       </c>
       <c r="E39">
-        <v>2.576887445112982</v>
+        <v>2.15263714219207</v>
       </c>
       <c r="F39">
-        <v>0.7420139123674653</v>
+        <v>0.7355310645651214</v>
       </c>
       <c r="G39">
-        <v>0.5135956637831848</v>
+        <v>0.1516603081601881</v>
       </c>
       <c r="H39">
-        <v>173.841501374375</v>
+        <v>110.2395217592</v>
       </c>
       <c r="I39">
-        <v>0.4206364947484525</v>
+        <v>0.4252783256106065</v>
       </c>
       <c r="J39">
-        <v>478.5481916666667</v>
+        <v>509.6371538461539</v>
       </c>
       <c r="K39">
-        <v>0.6689943583660577</v>
+        <v>0.7311291097571909</v>
       </c>
       <c r="L39">
-        <v>21.43688112</v>
+        <v>21.42001224</v>
       </c>
       <c r="M39">
-        <v>0.4440633270515046</v>
+        <v>0.432068614440138</v>
       </c>
       <c r="N39">
         <v>3.610169491525424</v>
@@ -3000,25 +3310,31 @@
         <v>4</v>
       </c>
       <c r="Q39">
-        <v>4.4228744065</v>
+        <v>5.666666666666667</v>
       </c>
       <c r="R39">
-        <v>0.8016696334132396</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="S39">
-        <v>5.666666666666667</v>
+        <v>-2.044371416713645</v>
       </c>
       <c r="T39">
-        <v>0.7083333333333334</v>
+        <v>0.2351088622191451</v>
       </c>
       <c r="U39">
-        <v>10.38050314465409</v>
+        <v>0.1479047577539238</v>
       </c>
       <c r="V39">
-        <v>0.6070620890020189</v>
+        <v>0.1082517028048877</v>
       </c>
       <c r="W39">
-        <v>0.6487874984459705</v>
+        <v>2.965130262270036</v>
+      </c>
+      <c r="X39">
+        <v>0.4403286329702006</v>
+      </c>
+      <c r="Y39">
+        <v>0.4908729722051963</v>
       </c>
     </row>
     <row r="40">
@@ -3028,40 +3344,40 @@
         </is>
       </c>
       <c r="B40">
-        <v>2.906916865566272</v>
+        <v>2.991736858382932</v>
       </c>
       <c r="C40">
-        <v>0.7852103620471447</v>
+        <v>0.8037629710248058</v>
       </c>
       <c r="D40">
-        <v>985.8426334202379</v>
+        <v>1007.797378137004</v>
       </c>
       <c r="E40">
-        <v>2.923565604627012</v>
+        <v>2.529344489221601</v>
       </c>
       <c r="F40">
-        <v>0.8412991769670165</v>
+        <v>0.823373736795078</v>
       </c>
       <c r="G40">
-        <v>0.6362294846750176</v>
+        <v>0.2072545360469593</v>
       </c>
       <c r="H40">
-        <v>124.1271808390625</v>
+        <v>89.070791474</v>
       </c>
       <c r="I40">
-        <v>0.2363852339380231</v>
+        <v>0.3192961681722459</v>
       </c>
       <c r="J40">
-        <v>330.23375</v>
+        <v>259.0865384615385</v>
       </c>
       <c r="K40">
-        <v>0.4598064890326519</v>
+        <v>0.3646076167206114</v>
       </c>
       <c r="L40">
-        <v>19.872664053125</v>
+        <v>19.59678643958333</v>
       </c>
       <c r="M40">
-        <v>0.3641267438589305</v>
+        <v>0.3471684398530923</v>
       </c>
       <c r="N40">
         <v>6.220338983050848</v>
@@ -3075,19 +3391,31 @@
         <v>8</v>
       </c>
       <c r="Q40">
-        <v>3.12606545625</v>
+        <v>2</v>
       </c>
       <c r="R40">
-        <v>0.863113081336643</v>
+        <v>0.25</v>
       </c>
       <c r="S40">
-        <v>2</v>
+        <v>-0.846345379850909</v>
       </c>
       <c r="T40">
-        <v>0.25</v>
+        <v>0.7688512542992849</v>
+      </c>
+      <c r="U40">
+        <v>0.486419836610353</v>
+      </c>
+      <c r="V40">
+        <v>0.5679583829255702</v>
       </c>
       <c r="W40">
-        <v>0.5545213214819285</v>
+        <v>1.689488470807592</v>
+      </c>
+      <c r="X40">
+        <v>0.2038430837769933</v>
+      </c>
+      <c r="Y40">
+        <v>0.4656116189614641</v>
       </c>
     </row>
     <row r="41">
@@ -3097,40 +3425,40 @@
         </is>
       </c>
       <c r="B41">
-        <v>1.13456411529597</v>
+        <v>0.9167533653688136</v>
       </c>
       <c r="C41">
-        <v>0.9594422279192161</v>
+        <v>0.9753558097772917</v>
       </c>
       <c r="D41">
-        <v>1091.19812954318</v>
+        <v>1199.117536403405</v>
       </c>
       <c r="E41">
-        <v>3.047672135596225</v>
+        <v>2.938898922213582</v>
       </c>
       <c r="F41">
-        <v>0.9374088337533967</v>
+        <v>0.9383703273292716</v>
       </c>
       <c r="G41">
-        <v>0.6801308891122624</v>
+        <v>0.2676963157450034</v>
       </c>
       <c r="H41">
-        <v>175.416226305</v>
+        <v>110.9779696704</v>
       </c>
       <c r="I41">
-        <v>0.4264727417447518</v>
+        <v>0.4289753967967581</v>
       </c>
       <c r="J41">
-        <v>370.9917916666666</v>
+        <v>324.4254487179487</v>
       </c>
       <c r="K41">
-        <v>0.5172930547280841</v>
+        <v>0.4601895609269757</v>
       </c>
       <c r="L41">
-        <v>21.186137615625</v>
+        <v>21.24144189791667</v>
       </c>
       <c r="M41">
-        <v>0.4312495178801773</v>
+        <v>0.4237533233689614</v>
       </c>
       <c r="N41">
         <v>11.2</v>
@@ -3144,19 +3472,31 @@
         <v>16</v>
       </c>
       <c r="Q41">
-        <v>3.69489422</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="R41">
-        <v>0.8361616938434666</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="S41">
-        <v>1.333333333333333</v>
+        <v>-1.54801040680585</v>
       </c>
       <c r="T41">
-        <v>0.1666666666666667</v>
+        <v>0.4562467211735867</v>
+      </c>
+      <c r="U41">
+        <v>0.2793487897798765</v>
+      </c>
+      <c r="V41">
+        <v>0.2867539420211062</v>
       </c>
       <c r="W41">
-        <v>0.6193532032060027</v>
+        <v>2.343764760437876</v>
+      </c>
+      <c r="X41">
+        <v>0.3251364505456744</v>
+      </c>
+      <c r="Y41">
+        <v>0.4729144514351296</v>
       </c>
     </row>
     <row r="42">
@@ -3166,40 +3506,40 @@
         </is>
       </c>
       <c r="B42">
-        <v>0.7742258026830298</v>
+        <v>0.6187439129779645</v>
       </c>
       <c r="C42">
-        <v>0.9948654339046902</v>
+        <v>1</v>
       </c>
       <c r="D42">
-        <v>971.6103559477901</v>
+        <v>1007.335780123657</v>
       </c>
       <c r="E42">
-        <v>2.805361940402622</v>
+        <v>2.652072847749746</v>
       </c>
       <c r="F42">
-        <v>0.8283159026861067</v>
+        <v>0.823096284600739</v>
       </c>
       <c r="G42">
-        <v>0.5944161584257603</v>
+        <v>0.2253667082304452</v>
       </c>
       <c r="H42">
-        <v>161.3252078546875</v>
+        <v>100.557466054</v>
       </c>
       <c r="I42">
-        <v>0.3742485961139383</v>
+        <v>0.3768046978468813</v>
       </c>
       <c r="J42">
-        <v>169.8209166666667</v>
+        <v>142.2470512820513</v>
       </c>
       <c r="K42">
-        <v>0.233554625480807</v>
+        <v>0.1936873289339885</v>
       </c>
       <c r="L42">
-        <v>21.99163470125</v>
+        <v>21.60993606916667</v>
       </c>
       <c r="M42">
-        <v>0.4724130406162352</v>
+        <v>0.4409125910067298</v>
       </c>
       <c r="N42">
         <v>2</v>
@@ -3213,19 +3553,31 @@
         <v>2</v>
       </c>
       <c r="Q42">
-        <v>1.35963345075</v>
+        <v>2</v>
       </c>
       <c r="R42">
-        <v>0.9468075013352468</v>
+        <v>0.25</v>
       </c>
       <c r="S42">
-        <v>2</v>
+        <v>-1.820442695176075</v>
       </c>
       <c r="T42">
-        <v>0.25</v>
+        <v>0.3348731810330309</v>
+      </c>
+      <c r="U42">
+        <v>0.2218767116537631</v>
+      </c>
+      <c r="V42">
+        <v>0.208706316124366</v>
       </c>
       <c r="W42">
-        <v>0.586827657320348</v>
+        <v>1.792634842757805</v>
+      </c>
+      <c r="X42">
+        <v>0.2229649301928028</v>
+      </c>
+      <c r="Y42">
+        <v>0.4076412037968983</v>
       </c>
     </row>
     <row r="43">
@@ -3235,40 +3587,40 @@
         </is>
       </c>
       <c r="B43">
-        <v>2.404323882427713</v>
+        <v>1.395749491872198</v>
       </c>
       <c r="C43">
-        <v>0.834617971910975</v>
+        <v>0.9357447452194874</v>
       </c>
       <c r="D43">
-        <v>962.3463114578503</v>
+        <v>1001.743157216678</v>
       </c>
       <c r="E43">
-        <v>2.61686311036833</v>
+        <v>2.641252258387419</v>
       </c>
       <c r="F43">
-        <v>0.8198648567592489</v>
+        <v>0.8197347330931846</v>
       </c>
       <c r="G43">
-        <v>0.5277366427817703</v>
+        <v>0.2237698126147321</v>
       </c>
       <c r="H43">
-        <v>125.714529449375</v>
+        <v>90.6913976952</v>
       </c>
       <c r="I43">
-        <v>0.2422682668276714</v>
+        <v>0.3274098028289681</v>
       </c>
       <c r="J43">
-        <v>155.9118333333333</v>
+        <v>126.2232051282051</v>
       </c>
       <c r="K43">
-        <v>0.2139367684860035</v>
+        <v>0.1702466201275843</v>
       </c>
       <c r="L43">
-        <v>21.91894548875</v>
+        <v>21.30893264416667</v>
       </c>
       <c r="M43">
-        <v>0.4686983852750701</v>
+        <v>0.4268960916088172</v>
       </c>
       <c r="N43">
         <v>1.88135593220339</v>
@@ -3282,19 +3634,31 @@
         <v>2</v>
       </c>
       <c r="Q43">
-        <v>6.598724384</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="R43">
-        <v>0.6985767878897056</v>
+        <v>0.04166666666666666</v>
       </c>
       <c r="S43">
-        <v>0.3333333333333333</v>
+        <v>-1.485043139252253</v>
       </c>
       <c r="T43">
-        <v>0.04166666666666666</v>
+        <v>0.4842997842729641</v>
+      </c>
+      <c r="U43">
+        <v>0.2685142008552549</v>
+      </c>
+      <c r="V43">
+        <v>0.2720404677444623</v>
       </c>
       <c r="W43">
-        <v>0.4809207933246389</v>
+        <v>1.507974293939214</v>
+      </c>
+      <c r="X43">
+        <v>0.1701929791078292</v>
+      </c>
+      <c r="Y43">
+        <v>0.3872001703284696</v>
       </c>
     </row>
     <row r="44">
@@ -3304,40 +3668,40 @@
         </is>
       </c>
       <c r="B44">
-        <v>1.57617971818797</v>
+        <v>1.143627946389912</v>
       </c>
       <c r="C44">
-        <v>0.9160290244932286</v>
+        <v>0.956594189008135</v>
       </c>
       <c r="D44">
-        <v>1151.611594239395</v>
+        <v>1210.126021964464</v>
       </c>
       <c r="E44">
-        <v>3.091423669845631</v>
+        <v>2.844564490838305</v>
       </c>
       <c r="F44">
-        <v>0.9925205039642586</v>
+        <v>0.9449871852596519</v>
       </c>
       <c r="G44">
-        <v>0.6956075427970684</v>
+        <v>0.2537745010610041</v>
       </c>
       <c r="H44">
-        <v>151.1668673634375</v>
+        <v>87.2339902252</v>
       </c>
       <c r="I44">
-        <v>0.3365997451772152</v>
+        <v>0.3101001438235678</v>
       </c>
       <c r="J44">
-        <v>557.3905416666666</v>
+        <v>372.6879487179487</v>
       </c>
       <c r="K44">
-        <v>0.780196362866779</v>
+        <v>0.530791038119612</v>
       </c>
       <c r="L44">
-        <v>21.42118804020833</v>
+        <v>20.76279274708333</v>
       </c>
       <c r="M44">
-        <v>0.4432613595977034</v>
+        <v>0.4014645885000253</v>
       </c>
       <c r="N44">
         <v>6.915254237288136</v>
@@ -3351,25 +3715,31 @@
         <v>8</v>
       </c>
       <c r="Q44">
-        <v>3.78289459325</v>
+        <v>4.666666666666667</v>
       </c>
       <c r="R44">
-        <v>0.831992192738478</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="S44">
-        <v>4.666666666666667</v>
+        <v>-1.057303568606605</v>
       </c>
       <c r="T44">
-        <v>0.5833333333333334</v>
+        <v>0.6748655437798236</v>
       </c>
       <c r="U44">
-        <v>5.419354838709677</v>
+        <v>0.3533872806922469</v>
       </c>
       <c r="V44">
-        <v>0.2030131588813034</v>
+        <v>0.3872989132331756</v>
       </c>
       <c r="W44">
-        <v>0.6425059137610408</v>
+        <v>3.401077723047435</v>
+      </c>
+      <c r="X44">
+        <v>0.5211469907343621</v>
+      </c>
+      <c r="Y44">
+        <v>0.556435642685269</v>
       </c>
     </row>
     <row r="45">
@@ -3379,40 +3749,40 @@
         </is>
       </c>
       <c r="B45">
-        <v>3.67911496942543</v>
+        <v>5.855716016589727</v>
       </c>
       <c r="C45">
-        <v>0.7092991099345289</v>
+        <v>0.5669233452932314</v>
       </c>
       <c r="D45">
-        <v>1159.810624825328</v>
+        <v>1234.640977423058</v>
       </c>
       <c r="E45">
-        <v>3.445955299958285</v>
+        <v>3.409601048929084</v>
       </c>
       <c r="F45">
-        <v>1</v>
+        <v>0.9597223617323291</v>
       </c>
       <c r="G45">
-        <v>0.8210194478581516</v>
+        <v>0.3371622327380108</v>
       </c>
       <c r="H45">
-        <v>181.2209807528125</v>
+        <v>112.3924553636</v>
       </c>
       <c r="I45">
-        <v>0.4479863280552536</v>
+        <v>0.4360570801765042</v>
       </c>
       <c r="J45">
-        <v>562.0825416666667</v>
+        <v>386.626282051282</v>
       </c>
       <c r="K45">
-        <v>0.7868141235641375</v>
+        <v>0.5511809251527474</v>
       </c>
       <c r="L45">
-        <v>22.94683949083333</v>
+        <v>23.040762315</v>
       </c>
       <c r="M45">
-        <v>0.5212271142799483</v>
+        <v>0.507540321947799</v>
       </c>
       <c r="N45">
         <v>11.22033898305085</v>
@@ -3426,19 +3796,31 @@
         <v>16</v>
       </c>
       <c r="Q45">
-        <v>13.236153298</v>
+        <v>4.333333333333333</v>
       </c>
       <c r="R45">
-        <v>0.3840921309600713</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="S45">
-        <v>4.333333333333333</v>
+        <v>-0.731112442471976</v>
       </c>
       <c r="T45">
-        <v>0.5416666666666666</v>
+        <v>0.8201896240429966</v>
+      </c>
+      <c r="U45">
+        <v>0.1799247235403907</v>
+      </c>
+      <c r="V45">
+        <v>0.151735119316202</v>
       </c>
       <c r="W45">
-        <v>0.6515131151648448</v>
+        <v>2.189137107426769</v>
+      </c>
+      <c r="X45">
+        <v>0.2964707187646027</v>
+      </c>
+      <c r="Y45">
+        <v>0.516864839583109</v>
       </c>
     </row>
     <row r="46">
@@ -3448,24 +3830,24 @@
         </is>
       </c>
       <c r="B46">
-        <v>5.981748578534632</v>
+        <v>3.68650514208163</v>
       </c>
       <c r="C46">
-        <v>0.4829377661931928</v>
+        <v>0.74630841175895</v>
       </c>
       <c r="L46">
-        <v>16.410262208</v>
+        <v>15.90949442666667</v>
       </c>
       <c r="M46">
-        <v>0.1871867404539718</v>
+        <v>0.175466319589929</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="W46">
-        <v>0.3350622533235823</v>
+      <c r="Y46">
+        <v>0.4608873656744395</v>
       </c>
     </row>
     <row r="47">
@@ -3475,40 +3857,40 @@
         </is>
       </c>
       <c r="B47">
-        <v>1.333235766632308</v>
+        <v>1.809020597434316</v>
       </c>
       <c r="C47">
-        <v>0.9399117295447043</v>
+        <v>0.9015688771142564</v>
       </c>
       <c r="D47">
-        <v>769.90286227345</v>
+        <v>738.9485760541409</v>
       </c>
       <c r="E47">
-        <v>2.366237997369227</v>
+        <v>1.990728391365028</v>
       </c>
       <c r="F47">
-        <v>0.6443099542383888</v>
+        <v>0.6617770922549774</v>
       </c>
       <c r="G47">
-        <v>0.4390805957391429</v>
+        <v>0.1277659188913868</v>
       </c>
       <c r="H47">
-        <v>133.0338306171875</v>
+        <v>55.39370319</v>
       </c>
       <c r="I47">
-        <v>0.2693950675945206</v>
+        <v>0.150690379138417</v>
       </c>
       <c r="J47">
-        <v>234.8489166666667</v>
+        <v>221.565641025641</v>
       </c>
       <c r="K47">
-        <v>0.3252723881892107</v>
+        <v>0.3097196439763946</v>
       </c>
       <c r="L47">
-        <v>18.75657013854167</v>
+        <v>17.89147361041667</v>
       </c>
       <c r="M47">
-        <v>0.3070907122600335</v>
+        <v>0.2677589904647106</v>
       </c>
       <c r="N47">
         <v>1</v>
@@ -3522,19 +3904,31 @@
         <v>1</v>
       </c>
       <c r="Q47">
-        <v>2.06449731075</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="R47">
-        <v>0.9134107038604532</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="S47">
-        <v>0.6666666666666666</v>
+        <v>-1.536001281277885</v>
       </c>
       <c r="T47">
-        <v>0.08333333333333333</v>
+        <v>0.4615970050479438</v>
+      </c>
+      <c r="U47">
+        <v>0.4548407613285498</v>
+      </c>
+      <c r="V47">
+        <v>0.5250736998913001</v>
       </c>
       <c r="W47">
-        <v>0.4902255605949734</v>
+        <v>2.748694971202441</v>
+      </c>
+      <c r="X47">
+        <v>0.4002046585006649</v>
+      </c>
+      <c r="Y47">
+        <v>0.3889489598613385</v>
       </c>
     </row>
     <row r="48">
@@ -3544,40 +3938,40 @@
         </is>
       </c>
       <c r="B48">
-        <v>2.775396414933245</v>
+        <v>3.786722414738152</v>
       </c>
       <c r="C48">
-        <v>0.7981395340252586</v>
+        <v>0.738020843995129</v>
       </c>
       <c r="D48">
-        <v>696.5614238650267</v>
+        <v>677.2660150068546</v>
       </c>
       <c r="E48">
-        <v>1.964231324205769</v>
+        <v>1.797527951189686</v>
       </c>
       <c r="F48">
-        <v>0.5774048497773214</v>
+        <v>0.6247016252465389</v>
       </c>
       <c r="G48">
-        <v>0.2968748841847817</v>
+        <v>0.09925352224282744</v>
       </c>
       <c r="H48">
-        <v>108.986184225625</v>
+        <v>37.8631158088</v>
       </c>
       <c r="I48">
-        <v>0.1802696582666082</v>
+        <v>0.06292274041894994</v>
       </c>
       <c r="J48">
-        <v>144.7225</v>
+        <v>117.894358974359</v>
       </c>
       <c r="K48">
-        <v>0.1981549418954287</v>
+        <v>0.1580626503421039</v>
       </c>
       <c r="L48">
-        <v>17.8247310559375</v>
+        <v>16.435712111875</v>
       </c>
       <c r="M48">
-        <v>0.259470702271591</v>
+        <v>0.1999701267073845</v>
       </c>
       <c r="N48">
         <v>1.932203389830508</v>
@@ -3591,19 +3985,31 @@
         <v>2</v>
       </c>
       <c r="Q48">
-        <v>9.63668605</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="R48">
-        <v>0.5546366651891479</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="S48">
-        <v>0.6666666666666666</v>
+        <v>-1.186029765726801</v>
       </c>
       <c r="T48">
-        <v>0.08333333333333333</v>
+        <v>0.61751568137263</v>
+      </c>
+      <c r="U48">
+        <v>0.1200298150105244</v>
+      </c>
+      <c r="V48">
+        <v>0.07039726680631563</v>
       </c>
       <c r="W48">
-        <v>0.3685355711179338</v>
+        <v>0.8820082649149967</v>
+      </c>
+      <c r="X48">
+        <v>0.05414792544086373</v>
+      </c>
+      <c r="Y48">
+        <v>0.2708325715906076</v>
       </c>
     </row>
     <row r="49">
@@ -3613,40 +4019,40 @@
         </is>
       </c>
       <c r="B49">
-        <v>1.815511680039976</v>
+        <v>2.420979241851507</v>
       </c>
       <c r="C49">
-        <v>0.8925013975747504</v>
+        <v>0.8509623439306431</v>
       </c>
       <c r="D49">
-        <v>890.8958090422312</v>
+        <v>924.1148284617932</v>
       </c>
       <c r="E49">
-        <v>2.573170232495415</v>
+        <v>2.257242245942205</v>
       </c>
       <c r="F49">
-        <v>0.7546847426020699</v>
+        <v>0.7730747615744021</v>
       </c>
       <c r="G49">
-        <v>0.5122807381847606</v>
+        <v>0.1670978620647274</v>
       </c>
       <c r="H49">
-        <v>119.8886665934375</v>
+        <v>62.0938932396</v>
       </c>
       <c r="I49">
-        <v>0.2206764485154273</v>
+        <v>0.1842351684165962</v>
       </c>
       <c r="J49">
-        <v>280.7613333333333</v>
+        <v>181.2729487179487</v>
       </c>
       <c r="K49">
-        <v>0.3900288644333315</v>
+        <v>0.2507769121039999</v>
       </c>
       <c r="L49">
-        <v>16.74420179975</v>
+        <v>16.26757026616667</v>
       </c>
       <c r="M49">
-        <v>0.2042521404694234</v>
+        <v>0.192140448094476</v>
       </c>
       <c r="N49">
         <v>3.491525423728814</v>
@@ -3660,19 +4066,31 @@
         <v>4</v>
       </c>
       <c r="Q49">
-        <v>2.79178667325</v>
+        <v>2.333333333333333</v>
       </c>
       <c r="R49">
-        <v>0.8789513750122068</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="S49">
-        <v>2.333333333333333</v>
+        <v>-0.9956581805243985</v>
       </c>
       <c r="T49">
-        <v>0.2916666666666667</v>
+        <v>0.7023296855290859</v>
+      </c>
+      <c r="U49">
+        <v>0.3940111154255836</v>
+      </c>
+      <c r="V49">
+        <v>0.4424664651842483</v>
       </c>
       <c r="W49">
-        <v>0.5181302966823296</v>
+        <v>0.9754249577126826</v>
+      </c>
+      <c r="X49">
+        <v>0.07146602998081229</v>
+      </c>
+      <c r="Y49">
+        <v>0.3926216343545658</v>
       </c>
     </row>
     <row r="50">
@@ -3682,40 +4100,40 @@
         </is>
       </c>
       <c r="B50">
-        <v>0.983265948598725</v>
+        <v>0.8786257682716357</v>
       </c>
       <c r="C50">
-        <v>0.9743156564072326</v>
+        <v>0.9785088096169253</v>
       </c>
       <c r="D50">
-        <v>772.0165795662651</v>
+        <v>735.5685782084339</v>
       </c>
       <c r="E50">
-        <v>2.672861675954276</v>
+        <v>2.165236473379724</v>
       </c>
       <c r="F50">
-        <v>0.6462381748916222</v>
+        <v>0.6597454807834461</v>
       </c>
       <c r="G50">
-        <v>0.5475455574012923</v>
+        <v>0.1535197093499728</v>
       </c>
       <c r="H50">
-        <v>155.2948253259375</v>
+        <v>109.3305764172</v>
       </c>
       <c r="I50">
-        <v>0.3518987868009025</v>
+        <v>0.4207276517137379</v>
       </c>
       <c r="J50">
-        <v>363.53175</v>
+        <v>309.4958974358975</v>
       </c>
       <c r="K50">
-        <v>0.5067711513729426</v>
+        <v>0.4383496567708289</v>
       </c>
       <c r="L50">
-        <v>17.139229081875</v>
+        <v>16.67179149708333</v>
       </c>
       <c r="M50">
-        <v>0.2244393202858452</v>
+        <v>0.2109633788959009</v>
       </c>
       <c r="N50">
         <v>6.35593220338983</v>
@@ -3728,14 +4146,26 @@
       <c r="P50">
         <v>8</v>
       </c>
-      <c r="Q50">
-        <v>5.7939364345</v>
-      </c>
-      <c r="R50">
-        <v>0.7367080380287125</v>
+      <c r="S50">
+        <v>-1.719018652508012</v>
+      </c>
+      <c r="T50">
+        <v>0.3800594369927521</v>
+      </c>
+      <c r="U50">
+        <v>0.2767194558216268</v>
+      </c>
+      <c r="V50">
+        <v>0.2831832816270143</v>
       </c>
       <c r="W50">
-        <v>0.5697023835983642</v>
+        <v>2.348475068568395</v>
+      </c>
+      <c r="X50">
+        <v>0.3260096735872604</v>
+      </c>
+      <c r="Y50">
+        <v>0.4278963421486487</v>
       </c>
     </row>
     <row r="51">
@@ -3745,40 +4175,40 @@
         </is>
       </c>
       <c r="B51">
-        <v>1.469352354643475</v>
+        <v>1.002883629259998</v>
       </c>
       <c r="C51">
-        <v>0.9265307323917905</v>
+        <v>0.9682331813162236</v>
       </c>
       <c r="D51">
-        <v>972.281952784939</v>
+        <v>936.2348494130874</v>
       </c>
       <c r="E51">
-        <v>2.964106549473492</v>
+        <v>2.555012885459033</v>
       </c>
       <c r="F51">
-        <v>0.8289285611984056</v>
+        <v>0.7803597288210897</v>
       </c>
       <c r="G51">
-        <v>0.6505704254947626</v>
+        <v>0.2110426614476562</v>
       </c>
       <c r="H51">
-        <v>112.6675989174194</v>
+        <v>85.54742265759999</v>
       </c>
       <c r="I51">
-        <v>0.1939137208068444</v>
+        <v>0.3016562708528405</v>
       </c>
       <c r="J51">
-        <v>559.8954583333333</v>
+        <v>400.8861538461538</v>
       </c>
       <c r="K51">
-        <v>0.7837293848332805</v>
+        <v>0.5720411792484855</v>
       </c>
       <c r="L51">
-        <v>20.12160857166667</v>
+        <v>20.05613381</v>
       </c>
       <c r="M51">
-        <v>0.3768486189989947</v>
+        <v>0.3685583696882025</v>
       </c>
       <c r="N51">
         <v>5.491525423728813</v>
@@ -3792,19 +4222,31 @@
         <v>8</v>
       </c>
       <c r="Q51">
-        <v>7.691581521</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="R51">
-        <v>0.6467966775102746</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S51">
-        <v>3.666666666666667</v>
+        <v>-0.6055895411415485</v>
       </c>
       <c r="T51">
-        <v>0.4583333333333333</v>
+        <v>0.876112359906389</v>
+      </c>
+      <c r="U51">
+        <v>0.1704249607823244</v>
+      </c>
+      <c r="V51">
+        <v>0.1388343516038813</v>
       </c>
       <c r="W51">
-        <v>0.6082064318209608</v>
+        <v>2.998279994948021</v>
+      </c>
+      <c r="X51">
+        <v>0.4464741142412194</v>
+      </c>
+      <c r="Y51">
+        <v>0.5121645550459322</v>
       </c>
     </row>
     <row r="52">
@@ -3814,40 +4256,40 @@
         </is>
       </c>
       <c r="B52">
-        <v>0.7231897938302607</v>
+        <v>0.675106066584323</v>
       </c>
       <c r="C52">
-        <v>0.9998825497399692</v>
+        <v>0.9953390752417649</v>
       </c>
       <c r="D52">
-        <v>884.1512260972701</v>
+        <v>943.991013777351</v>
       </c>
       <c r="E52">
-        <v>2.829127670606511</v>
+        <v>2.955095779901564</v>
       </c>
       <c r="F52">
-        <v>0.7485320540773909</v>
+        <v>0.7850217177384895</v>
       </c>
       <c r="G52">
-        <v>0.6028230402012745</v>
+        <v>0.2700866375809209</v>
       </c>
       <c r="H52">
-        <v>202.9518392865625</v>
+        <v>91.29715428679999</v>
       </c>
       <c r="I52">
-        <v>0.5285252560788698</v>
+        <v>0.3304425492240205</v>
       </c>
       <c r="J52">
-        <v>260.8305</v>
+        <v>153.6873076923077</v>
       </c>
       <c r="K52">
-        <v>0.3619177208913587</v>
+        <v>0.2104228689915203</v>
       </c>
       <c r="L52">
-        <v>20.597621738125</v>
+        <v>20.12857680958333</v>
       </c>
       <c r="M52">
-        <v>0.4011744410905382</v>
+        <v>0.3719317441275226</v>
       </c>
       <c r="N52">
         <v>1</v>
@@ -3860,14 +4302,26 @@
       <c r="P52">
         <v>1</v>
       </c>
-      <c r="Q52">
-        <v>2.337091009</v>
-      </c>
-      <c r="R52">
-        <v>0.9004950799364797</v>
+      <c r="S52">
+        <v>-0.390713495517238</v>
+      </c>
+      <c r="T52">
+        <v>0.9718435469284799</v>
+      </c>
+      <c r="U52">
+        <v>0.4640198872263714</v>
+      </c>
+      <c r="V52">
+        <v>0.537539039713539</v>
       </c>
       <c r="W52">
-        <v>0.649050020287983</v>
+        <v>2.173968670705522</v>
+      </c>
+      <c r="X52">
+        <v>0.2936587098507883</v>
+      </c>
+      <c r="Y52">
+        <v>0.5295873210441162</v>
       </c>
     </row>
     <row r="53">
@@ -3877,40 +4331,40 @@
         </is>
       </c>
       <c r="B53">
-        <v>1.235925826614334</v>
+        <v>1.042897672376869</v>
       </c>
       <c r="C53">
-        <v>0.9494778232101132</v>
+        <v>0.9649241799330779</v>
       </c>
       <c r="D53">
-        <v>963.5470426919795</v>
+        <v>972.8863491148774</v>
       </c>
       <c r="E53">
-        <v>2.690502686665903</v>
+        <v>2.268363497938214</v>
       </c>
       <c r="F53">
-        <v>0.8209602136324221</v>
+        <v>0.8023898041767772</v>
       </c>
       <c r="G53">
-        <v>0.5537858828691359</v>
+        <v>0.1687391292784614</v>
       </c>
       <c r="H53">
-        <v>107.9302736590323</v>
+        <v>78.21535347625</v>
       </c>
       <c r="I53">
-        <v>0.1763562415467805</v>
+        <v>0.2649479515603004</v>
       </c>
       <c r="J53">
-        <v>574.8780416666667</v>
+        <v>417.6919230769231</v>
       </c>
       <c r="K53">
-        <v>0.8048613437267657</v>
+        <v>0.5966257352298554</v>
       </c>
       <c r="L53">
-        <v>19.94108721166667</v>
+        <v>20.18134109</v>
       </c>
       <c r="M53">
-        <v>0.36762338995805</v>
+        <v>0.3743887610358567</v>
       </c>
       <c r="N53">
         <v>6.203389830508475</v>
@@ -3924,19 +4378,31 @@
         <v>8</v>
       </c>
       <c r="Q53">
-        <v>1.34282915525</v>
+        <v>6</v>
       </c>
       <c r="R53">
-        <v>0.9476036971474709</v>
+        <v>0.75</v>
       </c>
       <c r="S53">
-        <v>6</v>
+        <v>-0.4288801960791515</v>
       </c>
       <c r="T53">
-        <v>0.75</v>
+        <v>0.9548395875578904</v>
+      </c>
+      <c r="U53">
+        <v>0.199481621832267</v>
+      </c>
+      <c r="V53">
+        <v>0.1782935722441714</v>
       </c>
       <c r="W53">
-        <v>0.6713335740113423</v>
+        <v>2.19923090756511</v>
+      </c>
+      <c r="X53">
+        <v>0.2983419634079955</v>
+      </c>
+      <c r="Y53">
+        <v>0.5353490684424387</v>
       </c>
     </row>
     <row r="54">
@@ -3946,40 +4412,40 @@
         </is>
       </c>
       <c r="B54">
-        <v>1.079519997394771</v>
+        <v>0.9046072052730504</v>
       </c>
       <c r="C54">
-        <v>0.964853362562557</v>
+        <v>0.9763602486548978</v>
       </c>
       <c r="D54">
-        <v>800.328067796833</v>
+        <v>788.4386873146162</v>
       </c>
       <c r="E54">
-        <v>2.308053410886439</v>
+        <v>1.951811858806947</v>
       </c>
       <c r="F54">
-        <v>0.6720650896429542</v>
+        <v>0.6915240572987129</v>
       </c>
       <c r="G54">
-        <v>0.4184983987891018</v>
+        <v>0.1220226420568437</v>
       </c>
       <c r="H54">
-        <v>115.11182788125</v>
+        <v>46.913539688</v>
       </c>
       <c r="I54">
-        <v>0.2029725244562933</v>
+        <v>0.1082340763151742</v>
       </c>
       <c r="J54">
-        <v>240.8029166666667</v>
+        <v>182.8228205128205</v>
       </c>
       <c r="K54">
-        <v>0.3336701177697888</v>
+        <v>0.2530441638662822</v>
       </c>
       <c r="L54">
-        <v>19.97367921229167</v>
+        <v>19.20569175791667</v>
       </c>
       <c r="M54">
-        <v>0.3692889472675465</v>
+        <v>0.3289567588062484</v>
       </c>
       <c r="N54">
         <v>1.864406779661017</v>
@@ -3992,14 +4458,26 @@
       <c r="P54">
         <v>2</v>
       </c>
-      <c r="Q54">
-        <v>2.3487922305</v>
-      </c>
-      <c r="R54">
-        <v>0.8999406702882915</v>
+      <c r="S54">
+        <v>-0.951522905393257</v>
+      </c>
+      <c r="T54">
+        <v>0.7219927534414485</v>
+      </c>
+      <c r="U54">
+        <v>0.09279550814808123</v>
+      </c>
+      <c r="V54">
+        <v>0.03341282039578649</v>
       </c>
       <c r="W54">
-        <v>0.5516127301109333</v>
+        <v>1.161661085411861</v>
+      </c>
+      <c r="X54">
+        <v>0.1059915160799036</v>
+      </c>
+      <c r="Y54">
+        <v>0.3712821152128108</v>
       </c>
     </row>
     <row r="55">
@@ -4009,40 +4487,40 @@
         </is>
       </c>
       <c r="B55">
-        <v>0.8097760221559134</v>
+        <v>0.8637637605319486</v>
       </c>
       <c r="C55">
-        <v>0.9913706549618542</v>
+        <v>0.9797378382362855</v>
       </c>
       <c r="D55">
-        <v>922.4330881276862</v>
+        <v>942.626970427123</v>
       </c>
       <c r="E55">
-        <v>3.070241885028659</v>
+        <v>2.82574750977417</v>
       </c>
       <c r="F55">
-        <v>0.7834543576712484</v>
+        <v>0.7842018337490636</v>
       </c>
       <c r="G55">
-        <v>0.6881147050334921</v>
+        <v>0.250997503103121</v>
       </c>
       <c r="H55">
-        <v>254.4268867953125</v>
+        <v>160.814415098</v>
       </c>
       <c r="I55">
-        <v>0.7193021248289343</v>
+        <v>0.6784837014667312</v>
       </c>
       <c r="J55">
-        <v>433.2290416666667</v>
+        <v>395.8517948717949</v>
       </c>
       <c r="K55">
-        <v>0.6050746461521413</v>
+        <v>0.5646765963879261</v>
       </c>
       <c r="L55">
-        <v>22.50614931416667</v>
+        <v>22.36750696166667</v>
       </c>
       <c r="M55">
-        <v>0.4987064119328997</v>
+        <v>0.4761895715214939</v>
       </c>
       <c r="N55">
         <v>11.5</v>
@@ -4055,14 +4533,26 @@
       <c r="P55">
         <v>16</v>
       </c>
-      <c r="Q55">
-        <v>6.217877152250001</v>
-      </c>
-      <c r="R55">
-        <v>0.7166215176444565</v>
+      <c r="S55">
+        <v>-0.6142770080829645</v>
+      </c>
+      <c r="T55">
+        <v>0.8722419353548734</v>
+      </c>
+      <c r="U55">
+        <v>0.2823229594857957</v>
+      </c>
+      <c r="V55">
+        <v>0.290792892623373</v>
       </c>
       <c r="W55">
-        <v>0.714663488317861</v>
+        <v>4.180372373878496</v>
+      </c>
+      <c r="X55">
+        <v>0.6656169545741584</v>
+      </c>
+      <c r="Y55">
+        <v>0.6181043141130029</v>
       </c>
     </row>
     <row r="56">
@@ -4072,36 +4562,36 @@
         </is>
       </c>
       <c r="B56">
-        <v>6.435055089500657</v>
+        <v>4.267376878276081</v>
       </c>
       <c r="C56">
-        <v>0.4383752832419159</v>
+        <v>0.6982726415948677</v>
       </c>
       <c r="D56">
-        <v>750.8267404082933</v>
+        <v>1162.64967222488</v>
       </c>
       <c r="E56">
-        <v>2.78332076369537</v>
+        <v>1.57525640908611</v>
       </c>
       <c r="F56">
-        <v>0.6269079240383133</v>
+        <v>0.9164506295692739</v>
       </c>
       <c r="G56">
-        <v>0.586619319650709</v>
+        <v>0.06645083107715304</v>
       </c>
       <c r="L56">
-        <v>19.45792183833333</v>
+        <v>18.21921867666667</v>
       </c>
       <c r="M56">
-        <v>0.3429320668168241</v>
+        <v>0.2830207388111353</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="W56">
-        <v>0.4987086484369406</v>
+      <c r="Y56">
+        <v>0.4910487102631075</v>
       </c>
     </row>
     <row r="57">
@@ -4111,40 +4601,40 @@
         </is>
       </c>
       <c r="B57">
-        <v>1.167208942651994</v>
+        <v>1.268561254316011</v>
       </c>
       <c r="C57">
-        <v>0.9562330647430684</v>
+        <v>0.9462627039462286</v>
       </c>
       <c r="D57">
-        <v>874.7313058615135</v>
+        <v>833.5776464733858</v>
       </c>
       <c r="E57">
-        <v>2.721435365830919</v>
+        <v>2.435110757541504</v>
       </c>
       <c r="F57">
-        <v>0.7399388118249205</v>
+        <v>0.7186556802837452</v>
       </c>
       <c r="G57">
-        <v>0.5647279988701689</v>
+        <v>0.1933475825591806</v>
       </c>
       <c r="H57">
-        <v>231.912202086875</v>
+        <v>202.9204186712</v>
       </c>
       <c r="I57">
-        <v>0.635858179510758</v>
+        <v>0.889289216945143</v>
       </c>
       <c r="J57">
-        <v>315.6002083333333</v>
+        <v>308.5635897435898</v>
       </c>
       <c r="K57">
-        <v>0.4391668306982903</v>
+        <v>0.4369858173452918</v>
       </c>
       <c r="L57">
-        <v>21.96201894354166</v>
+        <v>21.80528788708333</v>
       </c>
       <c r="M57">
-        <v>0.4708995790065924</v>
+        <v>0.4500093268269618</v>
       </c>
       <c r="N57">
         <v>3.254237288135593</v>
@@ -4158,19 +4648,31 @@
         <v>4</v>
       </c>
       <c r="Q57">
-        <v>2.509934303333333</v>
+        <v>0</v>
       </c>
       <c r="R57">
-        <v>0.8923056793680828</v>
+        <v>0</v>
       </c>
       <c r="S57">
-        <v>0</v>
+        <v>-1.384072060386383</v>
       </c>
       <c r="T57">
-        <v>0</v>
+        <v>0.5292842366191833</v>
+      </c>
+      <c r="U57">
+        <v>0.2174399877180209</v>
+      </c>
+      <c r="V57">
+        <v>0.202681203039294</v>
       </c>
       <c r="W57">
-        <v>0.5873912680027351</v>
+        <v>4.312780101525268</v>
+      </c>
+      <c r="X57">
+        <v>0.690163433373723</v>
+      </c>
+      <c r="Y57">
+        <v>0.5056679200938752</v>
       </c>
     </row>
     <row r="58">
@@ -4180,40 +4682,40 @@
         </is>
       </c>
       <c r="B58">
-        <v>8.03801840660449</v>
+        <v>12.71122695655753</v>
       </c>
       <c r="C58">
-        <v>0.2807953152468926</v>
+        <v>0</v>
       </c>
       <c r="D58">
-        <v>771.2549657006074</v>
+        <v>713.8205147827568</v>
       </c>
       <c r="E58">
-        <v>2.128997105629884</v>
+        <v>1.846643069246183</v>
       </c>
       <c r="F58">
-        <v>0.645543399109382</v>
+        <v>0.6466733969667903</v>
       </c>
       <c r="G58">
-        <v>0.3551590788297286</v>
+        <v>0.1065018997630688</v>
       </c>
       <c r="H58">
-        <v>115.4052684690625</v>
+        <v>37.5051436404</v>
       </c>
       <c r="I58">
-        <v>0.2040600742346113</v>
+        <v>0.06113053738179166</v>
       </c>
       <c r="J58">
-        <v>137.2265833333333</v>
+        <v>72.74282051282051</v>
       </c>
       <c r="K58">
-        <v>0.1875824391871292</v>
+        <v>0.09201208700815416</v>
       </c>
       <c r="L58">
-        <v>24.04860521375</v>
+        <v>23.6872104275</v>
       </c>
       <c r="M58">
-        <v>0.5775309286505486</v>
+        <v>0.5376427687210804</v>
       </c>
       <c r="N58">
         <v>1</v>
@@ -4227,19 +4729,31 @@
         <v>1</v>
       </c>
       <c r="Q58">
-        <v>5.195490260333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="R58">
-        <v>0.765062713041004</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="S58">
-        <v>0.6666666666666666</v>
+        <v>-1.67486576535385</v>
       </c>
       <c r="T58">
-        <v>0.08333333333333333</v>
+        <v>0.3997303513817413</v>
+      </c>
+      <c r="U58">
+        <v>0.389249727780955</v>
+      </c>
+      <c r="V58">
+        <v>0.4360004557105367</v>
       </c>
       <c r="W58">
-        <v>0.3873834102040787</v>
+        <v>1.420991482783528</v>
+      </c>
+      <c r="X58">
+        <v>0.1540676232248591</v>
+      </c>
+      <c r="Y58">
+        <v>0.2517092453491356</v>
       </c>
     </row>
     <row r="59">
@@ -4249,40 +4763,40 @@
         </is>
       </c>
       <c r="B59">
-        <v>1.145410111775375</v>
+        <v>0.6924872803624826</v>
       </c>
       <c r="C59">
-        <v>0.9583760077756468</v>
+        <v>0.9939017183552165</v>
       </c>
       <c r="D59">
-        <v>870.8383767477686</v>
+        <v>841.6262690872577</v>
       </c>
       <c r="E59">
-        <v>2.965250120862364</v>
+        <v>2.621399623865686</v>
       </c>
       <c r="F59">
-        <v>0.7363875202949643</v>
+        <v>0.7234934567495312</v>
       </c>
       <c r="G59">
-        <v>0.6509749520708715</v>
+        <v>0.2208399735859556</v>
       </c>
       <c r="H59">
-        <v>268.7253422890625</v>
+        <v>225.03363813</v>
       </c>
       <c r="I59">
-        <v>0.7722950738222517</v>
+        <v>1</v>
       </c>
       <c r="J59">
-        <v>359.9379166666667</v>
+        <v>323.8462820512821</v>
       </c>
       <c r="K59">
-        <v>0.5017022833025696</v>
+        <v>0.4593423188195963</v>
       </c>
       <c r="L59">
-        <v>20.71277758875</v>
+        <v>20.99222184416667</v>
       </c>
       <c r="M59">
-        <v>0.4070592798565461</v>
+        <v>0.4121481639481523</v>
       </c>
       <c r="N59">
         <v>3.033898305084746</v>
@@ -4295,14 +4809,26 @@
       <c r="P59">
         <v>4</v>
       </c>
-      <c r="Q59">
-        <v>3.0731859965</v>
-      </c>
-      <c r="R59">
-        <v>0.865618536230936</v>
+      <c r="S59">
+        <v>-1.086829674307075</v>
+      </c>
+      <c r="T59">
+        <v>0.6617111265964968</v>
+      </c>
+      <c r="U59">
+        <v>0.1895459894682848</v>
+      </c>
+      <c r="V59">
+        <v>0.1648008894828135</v>
       </c>
       <c r="W59">
-        <v>0.698916236193398</v>
+        <v>4.060652057421678</v>
+      </c>
+      <c r="X59">
+        <v>0.6434225384172394</v>
+      </c>
+      <c r="Y59">
+        <v>0.5866289095505557</v>
       </c>
     </row>
     <row r="60">
@@ -4312,40 +4838,40 @@
         </is>
       </c>
       <c r="B60">
-        <v>1.825901354378047</v>
+        <v>0.8316001654117181</v>
       </c>
       <c r="C60">
-        <v>0.8914800363669158</v>
+        <v>0.9823976389574705</v>
       </c>
       <c r="D60">
-        <v>991.9334492925896</v>
+        <v>979.6777570703656</v>
       </c>
       <c r="E60">
-        <v>3.032875255714756</v>
+        <v>2.616260508286441</v>
       </c>
       <c r="F60">
-        <v>0.8468554720307088</v>
+        <v>0.8064719080537793</v>
       </c>
       <c r="G60">
-        <v>0.6748966455715509</v>
+        <v>0.2200815462154731</v>
       </c>
       <c r="H60">
-        <v>160.5236328196875</v>
+        <v>111.4478500092</v>
       </c>
       <c r="I60">
-        <v>0.37127779797685</v>
+        <v>0.4313278728958421</v>
       </c>
       <c r="J60">
-        <v>697.1215833333333</v>
+        <v>650.37</v>
       </c>
       <c r="K60">
-        <v>0.9772779050114151</v>
+        <v>0.9370021339060759</v>
       </c>
       <c r="L60">
-        <v>19.50983015020833</v>
+        <v>19.76049363375</v>
       </c>
       <c r="M60">
-        <v>0.3455847505002158</v>
+        <v>0.3547916148667022</v>
       </c>
       <c r="N60">
         <v>33.78947368421053</v>
@@ -4359,25 +4885,25 @@
         <v>60</v>
       </c>
       <c r="Q60">
-        <v>4.3617551855</v>
+        <v>5.666666666666667</v>
       </c>
       <c r="R60">
-        <v>0.8045654922611513</v>
-      </c>
-      <c r="S60">
-        <v>5.666666666666667</v>
-      </c>
-      <c r="T60">
         <v>0.7083333333333334</v>
       </c>
       <c r="U60">
-        <v>2.926640926640927</v>
+        <v>0.2920738235139098</v>
       </c>
       <c r="V60">
-        <v>0</v>
+        <v>0.3040346582363419</v>
       </c>
       <c r="W60">
-        <v>0.6244746036724601</v>
+        <v>3.264209423554901</v>
+      </c>
+      <c r="X60">
+        <v>0.495773586390557</v>
+      </c>
+      <c r="Y60">
+        <v>0.5822460325395084</v>
       </c>
     </row>
     <row r="61">
@@ -4387,10 +4913,10 @@
         </is>
       </c>
       <c r="B61">
-        <v>3.109399544191365</v>
+        <v>1.340887017403234</v>
       </c>
       <c r="C61">
-        <v>0.7653052190679919</v>
+        <v>0.9402816525090198</v>
       </c>
       <c r="D61">
         <v>432.675640523626</v>
@@ -4399,24 +4925,24 @@
         <v>1.12498455111615</v>
       </c>
       <c r="F61">
-        <v>0.3366772845238523</v>
+        <v>0.4776859662698841</v>
       </c>
       <c r="G61">
         <v>0</v>
       </c>
       <c r="L61">
-        <v>17.99802764583333</v>
+        <v>18.44930529166667</v>
       </c>
       <c r="M61">
-        <v>0.2683267220456703</v>
+        <v>0.2937349321815769</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="W61">
-        <v>0.3425773064093786</v>
+      <c r="Y61">
+        <v>0.4279256377401202</v>
       </c>
     </row>
     <row r="62">
@@ -4426,40 +4952,40 @@
         </is>
       </c>
       <c r="B62">
-        <v>1.626887657587317</v>
+        <v>1.781220700091808</v>
       </c>
       <c r="C62">
-        <v>0.911044159660464</v>
+        <v>0.9038678174759935</v>
       </c>
       <c r="D62">
-        <v>941.7955308036528</v>
+        <v>958.4918656362097</v>
       </c>
       <c r="E62">
-        <v>2.753839423059208</v>
+        <v>2.669950560400654</v>
       </c>
       <c r="F62">
-        <v>0.8011175815998943</v>
+        <v>0.7937377283184526</v>
       </c>
       <c r="G62">
-        <v>0.5761905996751149</v>
+        <v>0.2280050895602654</v>
       </c>
       <c r="H62">
-        <v>102.683986036875</v>
+        <v>76.23030212720001</v>
       </c>
       <c r="I62">
-        <v>0.1569124455027409</v>
+        <v>0.2550097067168988</v>
       </c>
       <c r="J62">
-        <v>548.5222083333333</v>
+        <v>455.2126923076923</v>
       </c>
       <c r="K62">
-        <v>0.7676881557516025</v>
+        <v>0.6515135204273964</v>
       </c>
       <c r="L62">
-        <v>18.17005770458333</v>
+        <v>18.54124040916667</v>
       </c>
       <c r="M62">
-        <v>0.2771180179560043</v>
+        <v>0.2980159748942495</v>
       </c>
       <c r="N62">
         <v>10.33898305084746</v>
@@ -4473,25 +4999,31 @@
         <v>16</v>
       </c>
       <c r="Q62">
-        <v>2.194161519</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="R62">
-        <v>0.9072671496957458</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S62">
-        <v>3.666666666666667</v>
+        <v>-0.9276073003238816</v>
       </c>
       <c r="T62">
-        <v>0.4583333333333333</v>
+        <v>0.7326475905359738</v>
       </c>
       <c r="U62">
-        <v>3.789203084832905</v>
+        <v>0.1669130100930245</v>
       </c>
       <c r="V62">
-        <v>0.07024932448854497</v>
+        <v>0.1340650893376933</v>
       </c>
       <c r="W62">
-        <v>0.5473245297403828</v>
+        <v>2.173784861817515</v>
+      </c>
+      <c r="X62">
+        <v>0.2936246343398432</v>
+      </c>
+      <c r="Y62">
+        <v>0.47488204849401</v>
       </c>
     </row>
     <row r="63">
@@ -4501,40 +5033,40 @@
         </is>
       </c>
       <c r="B63">
-        <v>3.404752088070881</v>
+        <v>2.244100031449752</v>
       </c>
       <c r="C63">
-        <v>0.7362704657987329</v>
+        <v>0.8655895474391622</v>
       </c>
       <c r="D63">
-        <v>803.6205597323058</v>
+        <v>744.7720380074095</v>
       </c>
       <c r="E63">
-        <v>2.029796058820261</v>
+        <v>1.734933104705882</v>
       </c>
       <c r="F63">
-        <v>0.6750686374552197</v>
+        <v>0.6652773939262682</v>
       </c>
       <c r="G63">
-        <v>0.3200677323665221</v>
+        <v>0.09001581507465463</v>
       </c>
       <c r="H63">
-        <v>89.29260579419355</v>
+        <v>54.8284311848</v>
       </c>
       <c r="I63">
-        <v>0.107281299645013</v>
+        <v>0.1478603205641204</v>
       </c>
       <c r="J63">
-        <v>65.56358333333333</v>
+        <v>29.9974358974359</v>
       </c>
       <c r="K63">
-        <v>0.08650644070997579</v>
+        <v>0.02948139968334619</v>
       </c>
       <c r="L63">
-        <v>18.41030944395833</v>
+        <v>17.01574388791667</v>
       </c>
       <c r="M63">
-        <v>0.2893956637881637</v>
+        <v>0.2269798361140405</v>
       </c>
       <c r="N63">
         <v>1</v>
@@ -4548,19 +5080,31 @@
         <v>1</v>
       </c>
       <c r="Q63">
-        <v>1.707558192</v>
+        <v>1</v>
       </c>
       <c r="R63">
-        <v>0.9303226554247241</v>
+        <v>0.125</v>
       </c>
       <c r="S63">
-        <v>1</v>
+        <v>-0.5462452308386635</v>
       </c>
       <c r="T63">
-        <v>0.125</v>
+        <v>0.9025513296472754</v>
+      </c>
+      <c r="U63">
+        <v>0.0762124666863655</v>
+      </c>
+      <c r="V63">
+        <v>0.01089289318184347</v>
       </c>
       <c r="W63">
-        <v>0.4087391118985439</v>
+        <v>1.114954172112448</v>
+      </c>
+      <c r="X63">
+        <v>0.09733272948584863</v>
+      </c>
+      <c r="Y63">
+        <v>0.316098126511656</v>
       </c>
     </row>
     <row r="64">
@@ -4570,24 +5114,24 @@
         </is>
       </c>
       <c r="B64">
-        <v>7.778655903268493</v>
+        <v>1.007476481744424</v>
       </c>
       <c r="C64">
-        <v>0.306292052782121</v>
+        <v>0.9678533707787289</v>
       </c>
       <c r="L64">
-        <v>19.40861536033333</v>
+        <v>18.98826920041667</v>
       </c>
       <c r="M64">
-        <v>0.3404123453126636</v>
+        <v>0.3188322788396454</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="W64">
-        <v>0.3233521990473923</v>
+      <c r="Y64">
+        <v>0.6433428248091871</v>
       </c>
     </row>
     <row r="65">
@@ -4597,40 +5141,40 @@
         </is>
       </c>
       <c r="B65">
-        <v>1.702722532239643</v>
+        <v>2.35487853771158</v>
       </c>
       <c r="C65">
-        <v>0.9035891811259514</v>
+        <v>0.8564286078817033</v>
       </c>
       <c r="D65">
-        <v>838.7181694002497</v>
+        <v>794.3731951185905</v>
       </c>
       <c r="E65">
-        <v>2.367598667232508</v>
+        <v>1.829367209925923</v>
       </c>
       <c r="F65">
-        <v>0.7070861338682416</v>
+        <v>0.6950911051735392</v>
       </c>
       <c r="G65">
-        <v>0.4395619186599191</v>
+        <v>0.1039523395605303</v>
       </c>
       <c r="H65">
-        <v>118.3972807875</v>
+        <v>44.897319408</v>
       </c>
       <c r="I65">
-        <v>0.2151490730602286</v>
+        <v>0.09813978288016498</v>
       </c>
       <c r="J65">
-        <v>144.3691666666667</v>
+        <v>93.61538461538461</v>
       </c>
       <c r="K65">
-        <v>0.1976565882197254</v>
+        <v>0.1225458110887347</v>
       </c>
       <c r="L65">
-        <v>19.740281801875</v>
+        <v>19.24348027041666</v>
       </c>
       <c r="M65">
-        <v>0.3573615799540212</v>
+        <v>0.3307164154038575</v>
       </c>
       <c r="N65">
         <v>1.983050847457627</v>
@@ -4644,19 +5188,31 @@
         <v>2</v>
       </c>
       <c r="Q65">
-        <v>0.94745741625</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="R65">
-        <v>0.9663366052222869</v>
+        <v>0.04166666666666666</v>
       </c>
       <c r="S65">
-        <v>0.3333333333333333</v>
+        <v>-1.385944877613435</v>
       </c>
       <c r="T65">
-        <v>0.04166666666666666</v>
+        <v>0.5284498624771043</v>
+      </c>
+      <c r="U65">
+        <v>0.06819124629979556</v>
+      </c>
+      <c r="V65">
+        <v>0</v>
       </c>
       <c r="W65">
-        <v>0.4785509683471301</v>
+        <v>2.119867323365915</v>
+      </c>
+      <c r="X65">
+        <v>0.2836291020695697</v>
+      </c>
+      <c r="Y65">
+        <v>0.3060619693201871</v>
       </c>
     </row>
     <row r="66">
@@ -4666,40 +5222,40 @@
         </is>
       </c>
       <c r="B66">
-        <v>3.520144908087444</v>
+        <v>5.768294627152565</v>
       </c>
       <c r="C66">
-        <v>0.7249267271797364</v>
+        <v>0.5741527446748231</v>
       </c>
       <c r="D66">
-        <v>917.4690102689739</v>
+        <v>908.1890415674118</v>
       </c>
       <c r="E66">
-        <v>2.654039794401924</v>
+        <v>2.426963928839512</v>
       </c>
       <c r="F66">
-        <v>0.7789259197935986</v>
+        <v>0.7635022669087962</v>
       </c>
       <c r="G66">
-        <v>0.5408875110612112</v>
+        <v>0.1921452788213204</v>
       </c>
       <c r="H66">
-        <v>151.9766271153571</v>
+        <v>77.49222236919999</v>
       </c>
       <c r="I66">
-        <v>0.3396008775197312</v>
+        <v>0.261327564612032</v>
       </c>
       <c r="J66">
-        <v>485.0668333333334</v>
+        <v>391.1703846153846</v>
       </c>
       <c r="K66">
-        <v>0.6781884782769337</v>
+        <v>0.5578283295255106</v>
       </c>
       <c r="L66">
-        <v>19.92031495479167</v>
+        <v>19.45771324291667</v>
       </c>
       <c r="M66">
-        <v>0.3665618600240344</v>
+        <v>0.3406923694318202</v>
       </c>
       <c r="N66">
         <v>5.186440677966102</v>
@@ -4713,25 +5269,31 @@
         <v>8</v>
       </c>
       <c r="Q66">
-        <v>3.29197626225</v>
+        <v>8</v>
       </c>
       <c r="R66">
-        <v>0.8552521454860493</v>
+        <v>1</v>
       </c>
       <c r="S66">
-        <v>8</v>
+        <v>-0.716170377852074</v>
       </c>
       <c r="T66">
-        <v>1</v>
+        <v>0.8268465856343549</v>
       </c>
       <c r="U66">
-        <v>9.417177914110429</v>
+        <v>0.3532388874340821</v>
       </c>
       <c r="V66">
-        <v>0.528606355620075</v>
+        <v>0.3870973937844891</v>
       </c>
       <c r="W66">
-        <v>0.6458833194401522</v>
+        <v>2.834340600322842</v>
+      </c>
+      <c r="X66">
+        <v>0.4160821201627792</v>
+      </c>
+      <c r="Y66">
+        <v>0.5319674653555926</v>
       </c>
     </row>
     <row r="67">
@@ -4741,40 +5303,40 @@
         </is>
       </c>
       <c r="B67">
-        <v>7.967395770673756</v>
+        <v>4.634270652459132</v>
       </c>
       <c r="C67">
-        <v>0.2877379025107086</v>
+        <v>0.6679319933706098</v>
       </c>
       <c r="D67">
-        <v>863.5299298005199</v>
+        <v>818.8409120553962</v>
       </c>
       <c r="E67">
-        <v>2.677901633048614</v>
+        <v>2.515178081988641</v>
       </c>
       <c r="F67">
-        <v>0.7297204516218514</v>
+        <v>0.7097978880415029</v>
       </c>
       <c r="G67">
-        <v>0.5493283902064392</v>
+        <v>0.2051638667827247</v>
       </c>
       <c r="H67">
-        <v>143.5188982909375</v>
+        <v>47.6341898124</v>
       </c>
       <c r="I67">
-        <v>0.3082548351176205</v>
+        <v>0.111842042117239</v>
       </c>
       <c r="J67">
-        <v>239.5789583333333</v>
+        <v>186.5998717948718</v>
       </c>
       <c r="K67">
-        <v>0.3319438041820783</v>
+        <v>0.2585694764784586</v>
       </c>
       <c r="L67">
-        <v>20.457332395</v>
+        <v>19.51674812333333</v>
       </c>
       <c r="M67">
-        <v>0.3940051990555137</v>
+        <v>0.3434413825562257</v>
       </c>
       <c r="N67">
         <v>1.983050847457627</v>
@@ -4788,19 +5350,31 @@
         <v>2</v>
       </c>
       <c r="Q67">
-        <v>5.67190590325</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="R67">
-        <v>0.7424899048106153</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="S67">
-        <v>3.333333333333333</v>
+        <v>-0.6166659216415455</v>
       </c>
       <c r="T67">
-        <v>0.4166666666666667</v>
+        <v>0.8711776309090629</v>
+      </c>
+      <c r="U67">
+        <v>0.3341450838158363</v>
+      </c>
+      <c r="V67">
+        <v>0.3611678278051172</v>
       </c>
       <c r="W67">
-        <v>0.4700183942714367</v>
+        <v>0.9162660823837382</v>
+      </c>
+      <c r="X67">
+        <v>0.06049882961512109</v>
+      </c>
+      <c r="Y67">
+        <v>0.4006257604342729</v>
       </c>
     </row>
     <row r="68">
@@ -4810,40 +5384,40 @@
         </is>
       </c>
       <c r="B68">
-        <v>1.70503530389312</v>
+        <v>0.8158122852628428</v>
       </c>
       <c r="C68">
-        <v>0.9033618231575899</v>
+        <v>0.9837032335232828</v>
       </c>
       <c r="D68">
-        <v>1111.033140487697</v>
+        <v>1155.612559516232</v>
       </c>
       <c r="E68">
-        <v>3.307029389479954</v>
+        <v>3.122841494967197</v>
       </c>
       <c r="F68">
-        <v>0.9555031540725488</v>
+        <v>0.9122208402149681</v>
       </c>
       <c r="G68">
-        <v>0.7718758408691314</v>
+        <v>0.2948424422763286</v>
       </c>
       <c r="H68">
-        <v>183.8040500878125</v>
+        <v>141.0223841124</v>
       </c>
       <c r="I68">
-        <v>0.4575597020169162</v>
+        <v>0.5793940482055104</v>
       </c>
       <c r="J68">
-        <v>560.2451333333333</v>
+        <v>364.2266794871795</v>
       </c>
       <c r="K68">
-        <v>0.7842225786678604</v>
+        <v>0.518413351372823</v>
       </c>
       <c r="L68">
-        <v>22.29942168833333</v>
+        <v>22.72051004333333</v>
       </c>
       <c r="M68">
-        <v>0.488141957414037</v>
+        <v>0.4926274824244748</v>
       </c>
       <c r="N68">
         <v>12.3</v>
@@ -4857,25 +5431,31 @@
         <v>16</v>
       </c>
       <c r="Q68">
-        <v>6.7486626605</v>
+        <v>5.333333333333333</v>
       </c>
       <c r="R68">
-        <v>0.6914726383678531</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="S68">
-        <v>5.333333333333333</v>
+        <v>-0.8743934316383419</v>
       </c>
       <c r="T68">
-        <v>0.6666666666666666</v>
+        <v>0.7563553370207129</v>
       </c>
       <c r="U68">
-        <v>10.79144385026738</v>
+        <v>0.3971980876573364</v>
       </c>
       <c r="V68">
-        <v>0.640530177881191</v>
+        <v>0.4467944036301372</v>
       </c>
       <c r="W68">
-        <v>0.7065927265681994</v>
+        <v>3.629766775435469</v>
+      </c>
+      <c r="X68">
+        <v>0.5635426354289883</v>
+      </c>
+      <c r="Y68">
+        <v>0.6214560440763893</v>
       </c>
     </row>
     <row r="69">
@@ -4885,40 +5465,40 @@
         </is>
       </c>
       <c r="B69">
-        <v>1.189745895568634</v>
+        <v>1.222969348145958</v>
       </c>
       <c r="C69">
-        <v>0.9540175603198443</v>
+        <v>0.9500329723026733</v>
       </c>
       <c r="D69">
-        <v>1050.074936152694</v>
+        <v>1059.194416158953</v>
       </c>
       <c r="E69">
-        <v>3.156049903851567</v>
+        <v>2.733724799848018</v>
       </c>
       <c r="F69">
-        <v>0.8998945497514735</v>
+        <v>0.8542668961444996</v>
       </c>
       <c r="G69">
-        <v>0.7184684060747184</v>
+        <v>0.237416850783134</v>
       </c>
       <c r="H69">
-        <v>117.7899405009375</v>
+        <v>48.8067238412</v>
       </c>
       <c r="I69">
-        <v>0.2128981479276881</v>
+        <v>0.1177123840965592</v>
       </c>
       <c r="J69">
-        <v>355.4359583333333</v>
+        <v>301.3658974358974</v>
       </c>
       <c r="K69">
-        <v>0.4953525640102679</v>
+        <v>0.4264565718793265</v>
       </c>
       <c r="L69">
-        <v>22.60026640083333</v>
+        <v>22.542616135</v>
       </c>
       <c r="M69">
-        <v>0.5035161013855298</v>
+        <v>0.4843436901086682</v>
       </c>
       <c r="N69">
         <v>3.416666666666667</v>
@@ -4932,19 +5512,31 @@
         <v>4</v>
       </c>
       <c r="Q69">
-        <v>12.077124826</v>
+        <v>4.333333333333333</v>
       </c>
       <c r="R69">
-        <v>0.4390074718415056</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="S69">
-        <v>4.333333333333333</v>
+        <v>-0.5644465323086085</v>
       </c>
       <c r="T69">
-        <v>0.5416666666666666</v>
+        <v>0.8944423187521697</v>
+      </c>
+      <c r="U69">
+        <v>0.1863967799717657</v>
+      </c>
+      <c r="V69">
+        <v>0.1605242331886833</v>
       </c>
       <c r="W69">
-        <v>0.5956026834972118</v>
+        <v>1.45201807705575</v>
+      </c>
+      <c r="X69">
+        <v>0.1598195053246524</v>
+      </c>
+      <c r="Y69">
+        <v>0.4826682089247033</v>
       </c>
     </row>
     <row r="70">
@@ -4954,40 +5546,40 @@
         </is>
       </c>
       <c r="B70">
-        <v>1.938789752776512</v>
+        <v>0.8783340032070126</v>
       </c>
       <c r="C70">
-        <v>0.8803824959448555</v>
+        <v>0.9785329374212457</v>
       </c>
       <c r="D70">
-        <v>961.8098517393934</v>
+        <v>967.5596028930293</v>
       </c>
       <c r="E70">
-        <v>2.79305649673674</v>
+        <v>2.483676006578784</v>
       </c>
       <c r="F70">
-        <v>0.8193754759360552</v>
+        <v>0.7991880628667972</v>
       </c>
       <c r="G70">
-        <v>0.5900632347324082</v>
+        <v>0.2005148107633725</v>
       </c>
       <c r="H70">
-        <v>134.8362436684375</v>
+        <v>94.0571918956</v>
       </c>
       <c r="I70">
-        <v>0.2760751725143514</v>
+        <v>0.3442607960650296</v>
       </c>
       <c r="J70">
-        <v>568.57375</v>
+        <v>512.3392307692308</v>
       </c>
       <c r="K70">
-        <v>0.7959695505434</v>
+        <v>0.7350818810031347</v>
       </c>
       <c r="L70">
-        <v>26.334488324375</v>
+        <v>26.55105998208333</v>
       </c>
       <c r="M70">
-        <v>0.694346995493513</v>
+        <v>0.6710005388445577</v>
       </c>
       <c r="N70">
         <v>11.28813559322034</v>
@@ -5001,19 +5593,31 @@
         <v>16</v>
       </c>
       <c r="Q70">
-        <v>10.22743296833333</v>
+        <v>2.333333333333333</v>
       </c>
       <c r="R70">
-        <v>0.5266467847171419</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="S70">
-        <v>2.333333333333333</v>
+        <v>-1.093688034025946</v>
       </c>
       <c r="T70">
-        <v>0.2916666666666667</v>
+        <v>0.6586556025849467</v>
+      </c>
+      <c r="U70">
+        <v>0.7683568704970393</v>
+      </c>
+      <c r="V70">
+        <v>0.9508315426352157</v>
       </c>
       <c r="W70">
-        <v>0.609315797068549</v>
+        <v>3.727290492743089</v>
+      </c>
+      <c r="X70">
+        <v>0.5816221229475144</v>
+      </c>
+      <c r="Y70">
+        <v>0.6211354961798481</v>
       </c>
     </row>
     <row r="71">
@@ -5023,40 +5627,40 @@
         </is>
       </c>
       <c r="B71">
-        <v>1.488076964966721</v>
+        <v>1.533643868174295</v>
       </c>
       <c r="C71">
-        <v>0.9246900018747707</v>
+        <v>0.9243414316233347</v>
       </c>
       <c r="D71">
-        <v>1055.421961573569</v>
+        <v>1110.854887684022</v>
       </c>
       <c r="E71">
-        <v>3.432112786752799</v>
+        <v>3.591608040777307</v>
       </c>
       <c r="F71">
-        <v>0.9047723282911775</v>
+        <v>0.8853183971708553</v>
       </c>
       <c r="G71">
-        <v>0.8161228016791309</v>
+        <v>0.3640227074847447</v>
       </c>
       <c r="H71">
-        <v>171.7965678403226</v>
+        <v>167.2972334604167</v>
       </c>
       <c r="I71">
-        <v>0.4130575601906514</v>
+        <v>0.7109402100562092</v>
       </c>
       <c r="J71">
-        <v>691.7772916666667</v>
+        <v>615.7452564102564</v>
       </c>
       <c r="K71">
-        <v>0.9697401293620359</v>
+        <v>0.8863508405654458</v>
       </c>
       <c r="L71">
-        <v>20.12140622708333</v>
+        <v>20.60656245416667</v>
       </c>
       <c r="M71">
-        <v>0.3768382785322132</v>
+        <v>0.3941895822219333</v>
       </c>
       <c r="N71">
         <v>34.94915254237288</v>
@@ -5070,25 +5674,25 @@
         <v>60</v>
       </c>
       <c r="Q71">
-        <v>11.52827427625</v>
+        <v>4.666666666666667</v>
       </c>
       <c r="R71">
-        <v>0.4650122816978798</v>
-      </c>
-      <c r="S71">
-        <v>4.666666666666667</v>
-      </c>
-      <c r="T71">
         <v>0.5833333333333334</v>
       </c>
       <c r="U71">
-        <v>4.727078891257996</v>
+        <v>0.4555387523322594</v>
       </c>
       <c r="V71">
-        <v>0.1466323900216009</v>
+        <v>0.526021578278737</v>
       </c>
       <c r="W71">
-        <v>0.6222443449980881</v>
+        <v>3.231067725698165</v>
+      </c>
+      <c r="X71">
+        <v>0.4896295946592574</v>
+      </c>
+      <c r="Y71">
+        <v>0.640460852821539</v>
       </c>
     </row>
     <row r="72">
@@ -5098,40 +5702,40 @@
         </is>
       </c>
       <c r="B72">
-        <v>0.7219950451524363</v>
+        <v>0.6617605719075088</v>
       </c>
       <c r="C72">
-        <v>1</v>
+        <v>0.99644269429409</v>
       </c>
       <c r="D72">
-        <v>940.1657715297354</v>
+        <v>964.0300716470809</v>
       </c>
       <c r="E72">
-        <v>3.062506222892643</v>
+        <v>2.763925064330018</v>
       </c>
       <c r="F72">
-        <v>0.7996308475402127</v>
+        <v>0.7970665715239834</v>
       </c>
       <c r="G72">
-        <v>0.6853782943919974</v>
+        <v>0.2418737863833878</v>
       </c>
       <c r="H72">
-        <v>200.0871802265625</v>
+        <v>111.95119069</v>
       </c>
       <c r="I72">
-        <v>0.5179082540176206</v>
+        <v>0.4338478696343794</v>
       </c>
       <c r="J72">
-        <v>313.8654273333333</v>
+        <v>306.6930933333333</v>
       </c>
       <c r="K72">
-        <v>0.436720034977846</v>
+        <v>0.434249535353111</v>
       </c>
       <c r="L72">
-        <v>20.36415362979167</v>
+        <v>20.96768225958333</v>
       </c>
       <c r="M72">
-        <v>0.3892434608833699</v>
+        <v>0.4110054557795083</v>
       </c>
       <c r="N72">
         <v>13</v>
@@ -5145,19 +5749,31 @@
         <v>16</v>
       </c>
       <c r="Q72">
-        <v>2.25621978075</v>
+        <v>5.333333333333333</v>
       </c>
       <c r="R72">
-        <v>0.9043267986337655</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="S72">
-        <v>5.333333333333333</v>
+        <v>-1.954007242935438</v>
       </c>
       <c r="T72">
-        <v>0.6666666666666666</v>
+        <v>0.275367745404212</v>
+      </c>
+      <c r="U72">
+        <v>0.3618746321584899</v>
+      </c>
+      <c r="V72">
+        <v>0.3988248168317528</v>
       </c>
       <c r="W72">
-        <v>0.6749842946389348</v>
+        <v>4.334073732835398</v>
+      </c>
+      <c r="X72">
+        <v>0.6941109648268283</v>
+      </c>
+      <c r="Y72">
+        <v>0.534945610669792</v>
       </c>
     </row>
     <row r="73">
@@ -5167,34 +5783,16 @@
         </is>
       </c>
       <c r="B73">
-        <v>1.292398706065661</v>
+        <v>1.013534756809366</v>
       </c>
       <c r="C73">
-        <v>0.9439262335751082</v>
-      </c>
-      <c r="D73">
-        <v>666.26620934</v>
-      </c>
-      <c r="E73">
-        <v>2.543287669</v>
-      </c>
-      <c r="F73">
-        <v>0.5497682975572799</v>
-      </c>
-      <c r="G73">
-        <v>0.5017100897636932</v>
-      </c>
-      <c r="J73">
-        <v>4.230416666666667</v>
-      </c>
-      <c r="K73">
-        <v>0</v>
+        <v>0.9673523756528223</v>
       </c>
       <c r="L73">
-        <v>18.23460002335417</v>
+        <v>18.322116713375</v>
       </c>
       <c r="M73">
-        <v>0.2804163405118205</v>
+        <v>0.2878122798694097</v>
       </c>
       <c r="N73">
         <v>0.8571428571428571</v>
@@ -5207,14 +5805,14 @@
       <c r="P73">
         <v>1</v>
       </c>
-      <c r="S73">
+      <c r="Q73">
         <v>0.3333333333333333</v>
       </c>
-      <c r="T73">
+      <c r="R73">
         <v>0.04166666666666666</v>
       </c>
-      <c r="W73">
-        <v>0.3862479380124281</v>
+      <c r="Y73">
+        <v>0.4322771073962995</v>
       </c>
     </row>
     <row r="74">
@@ -5224,40 +5822,40 @@
         </is>
       </c>
       <c r="B74">
-        <v>4.543539835776487</v>
+        <v>5.37547026623286</v>
       </c>
       <c r="C74">
-        <v>0.6243214680133081</v>
+        <v>0.6066377487475203</v>
       </c>
       <c r="D74">
-        <v>931.0850222829723</v>
+        <v>970.6620158721365</v>
       </c>
       <c r="E74">
-        <v>3.951922152773463</v>
+        <v>4.452826108356576</v>
       </c>
       <c r="F74">
-        <v>0.7913470111426208</v>
+        <v>0.8010528267173979</v>
       </c>
       <c r="G74">
-        <v>1</v>
+        <v>0.4911207157576051</v>
       </c>
       <c r="H74">
-        <v>146.71501500875</v>
+        <v>85.6636192112</v>
       </c>
       <c r="I74">
-        <v>0.3201002858572309</v>
+        <v>0.3022380138894571</v>
       </c>
       <c r="J74">
-        <v>291.6330833333333</v>
+        <v>284.9810256410257</v>
       </c>
       <c r="K74">
-        <v>0.4053627603969946</v>
+        <v>0.4024877316342105</v>
       </c>
       <c r="L74">
-        <v>15.40011132185417</v>
+        <v>14.38105597704167</v>
       </c>
       <c r="M74">
-        <v>0.1355647424222231</v>
+        <v>0.1042931872280127</v>
       </c>
       <c r="N74">
         <v>2.95</v>
@@ -5271,19 +5869,31 @@
         <v>4</v>
       </c>
       <c r="Q74">
-        <v>11.843459849</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="R74">
-        <v>0.4500786337447721</v>
+        <v>0.04166666666666666</v>
       </c>
       <c r="S74">
-        <v>0.3333333333333333</v>
+        <v>-1.132070635144987</v>
       </c>
       <c r="T74">
-        <v>0.04166666666666666</v>
+        <v>0.641555455588824</v>
+      </c>
+      <c r="U74">
+        <v>0.1604913406406163</v>
+      </c>
+      <c r="V74">
+        <v>0.1253444014594112</v>
       </c>
       <c r="W74">
-        <v>0.4710551960304771</v>
+        <v>3.316011292720438</v>
+      </c>
+      <c r="X74">
+        <v>0.5053769041564342</v>
+      </c>
+      <c r="Y74">
+        <v>0.402177365184554</v>
       </c>
     </row>
     <row r="75">
@@ -5293,36 +5903,24 @@
         </is>
       </c>
       <c r="B75">
-        <v>10.89437505956174</v>
+        <v>8.397804491748785</v>
       </c>
       <c r="C75">
-        <v>0</v>
-      </c>
-      <c r="D75">
-        <v>594.6992647</v>
-      </c>
-      <c r="E75">
-        <v>3.022235294</v>
-      </c>
-      <c r="F75">
-        <v>0.4844819599695962</v>
-      </c>
-      <c r="G75">
-        <v>0.6711328689291099</v>
+        <v>0.3567027920786652</v>
       </c>
       <c r="L75">
-        <v>15.50266761604167</v>
+        <v>14.20987689875</v>
       </c>
       <c r="M75">
-        <v>0.1408057028463535</v>
+        <v>0.09632207710589247</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
           <t>B4</t>
         </is>
       </c>
-      <c r="W75">
-        <v>0.3241051329362649</v>
+      <c r="Y75">
+        <v>0.2265124345922788</v>
       </c>
     </row>
     <row r="76">
@@ -5332,40 +5930,40 @@
         </is>
       </c>
       <c r="B76">
-        <v>1.719547623997414</v>
+        <v>1.782545232434082</v>
       </c>
       <c r="C76">
-        <v>0.9019351835625555</v>
+        <v>0.9037582839469821</v>
       </c>
       <c r="D76">
-        <v>935.1347230762776</v>
+        <v>1005.270956197545</v>
       </c>
       <c r="E76">
-        <v>2.488230333792243</v>
+        <v>2.353039606296398</v>
       </c>
       <c r="F76">
-        <v>0.7950413163061399</v>
+        <v>0.8218551832253911</v>
       </c>
       <c r="G76">
-        <v>0.4822341256760957</v>
+        <v>0.1812355748661308</v>
       </c>
       <c r="H76">
-        <v>190.33094006125</v>
+        <v>169.6096032784</v>
       </c>
       <c r="I76">
-        <v>0.4817496676812886</v>
+        <v>0.7225171888737136</v>
       </c>
       <c r="J76">
-        <v>153.0529166666667</v>
+        <v>148.8394871794872</v>
       </c>
       <c r="K76">
-        <v>0.2099044525538446</v>
+        <v>0.2033311665440737</v>
       </c>
       <c r="L76">
-        <v>18.29261047583333</v>
+        <v>18.65772095166666</v>
       </c>
       <c r="M76">
-        <v>0.2833808634407921</v>
+        <v>0.3034399977399024</v>
       </c>
       <c r="N76">
         <v>7.689655172413793</v>
@@ -5379,25 +5977,31 @@
         <v>8</v>
       </c>
       <c r="Q76">
-        <v>4.09512267625</v>
+        <v>2</v>
       </c>
       <c r="R76">
-        <v>0.817198672108985</v>
+        <v>0.25</v>
       </c>
       <c r="S76">
-        <v>2</v>
+        <v>-1.376599108941444</v>
       </c>
       <c r="T76">
-        <v>0.25</v>
+        <v>0.5326135724244097</v>
       </c>
       <c r="U76">
-        <v>3.131147540983607</v>
+        <v>0.1819735616857008</v>
       </c>
       <c r="V76">
-        <v>0.01665555505139046</v>
+        <v>0.1545174609036637</v>
       </c>
       <c r="W76">
-        <v>0.4708999818201213</v>
+        <v>2.656304490841908</v>
+      </c>
+      <c r="X76">
+        <v>0.3830767989130323</v>
+      </c>
+      <c r="Y76">
+        <v>0.4456345227437299</v>
       </c>
     </row>
     <row r="77">
@@ -5407,40 +6011,40 @@
         </is>
       </c>
       <c r="B77">
-        <v>6.244953306955439</v>
+        <v>6.470060526093794</v>
       </c>
       <c r="C77">
-        <v>0.4570633171411546</v>
+        <v>0.5161195106060081</v>
       </c>
       <c r="D77">
-        <v>899.7614602872376</v>
+        <v>864.1034109893671</v>
       </c>
       <c r="E77">
-        <v>2.162868994009377</v>
+        <v>1.806250733014492</v>
       </c>
       <c r="F77">
-        <v>0.7627723576739119</v>
+        <v>0.7370037669390967</v>
       </c>
       <c r="G77">
-        <v>0.3671409097550509</v>
+        <v>0.1005408247719626</v>
       </c>
       <c r="H77">
-        <v>68.9591740921875</v>
+        <v>47.108142838</v>
       </c>
       <c r="I77">
-        <v>0.03192151623942003</v>
+        <v>0.1092083653444846</v>
       </c>
       <c r="J77">
-        <v>184.1729583333333</v>
+        <v>70.61499999999999</v>
       </c>
       <c r="K77">
-        <v>0.2537972463820258</v>
+        <v>0.08889937483191129</v>
       </c>
       <c r="L77">
-        <v>17.70737708666667</v>
+        <v>17.61308750666667</v>
       </c>
       <c r="M77">
-        <v>0.253473532488539</v>
+        <v>0.2547956872876816</v>
       </c>
       <c r="N77">
         <v>2.694915254237288</v>
@@ -5454,25 +6058,31 @@
         <v>4</v>
       </c>
       <c r="Q77">
-        <v>2.72380961475</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="R77">
-        <v>0.8821721615846049</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="S77">
-        <v>3.333333333333333</v>
+        <v>-0.9066587597174209</v>
       </c>
       <c r="T77">
-        <v>0.4166666666666667</v>
+        <v>0.7419805464399709</v>
       </c>
       <c r="U77">
-        <v>6.712264150943396</v>
+        <v>0.2902623101548458</v>
       </c>
       <c r="V77">
-        <v>0.308311084308207</v>
+        <v>0.3015746059541723</v>
       </c>
       <c r="W77">
-        <v>0.4148131991377312</v>
+        <v>1.242859854944097</v>
+      </c>
+      <c r="X77">
+        <v>0.1210445942521303</v>
+      </c>
+      <c r="Y77">
+        <v>0.3387833943094085</v>
       </c>
     </row>
     <row r="78">
@@ -5482,40 +6092,40 @@
         </is>
       </c>
       <c r="B78">
-        <v>1.565465264178534</v>
+        <v>1.667006999653265</v>
       </c>
       <c r="C78">
-        <v>0.9170823133002</v>
+        <v>0.9133128338574046</v>
       </c>
       <c r="D78">
-        <v>825.6953914759764</v>
+        <v>844.2846047425069</v>
       </c>
       <c r="E78">
-        <v>2.814837724279613</v>
+        <v>2.670002544093911</v>
       </c>
       <c r="F78">
-        <v>0.6952062152805429</v>
+        <v>0.7250912995467522</v>
       </c>
       <c r="G78">
-        <v>0.5977681191734737</v>
+        <v>0.228012761280268</v>
       </c>
       <c r="H78">
-        <v>154.55160473125</v>
+        <v>102.957254056</v>
       </c>
       <c r="I78">
-        <v>0.3491442619445448</v>
+        <v>0.3888193395575589</v>
       </c>
       <c r="J78">
-        <v>166.536875</v>
+        <v>156.2683333333333</v>
       </c>
       <c r="K78">
-        <v>0.2289226983985064</v>
+        <v>0.2141985586662881</v>
       </c>
       <c r="L78">
-        <v>15.1030800713125</v>
+        <v>15.10699347595833</v>
       </c>
       <c r="M78">
-        <v>0.1203854787685196</v>
+        <v>0.1380971298791223</v>
       </c>
       <c r="N78">
         <v>6.677966101694915</v>
@@ -5529,19 +6139,31 @@
         <v>8</v>
       </c>
       <c r="Q78">
-        <v>7.85454117025</v>
+        <v>0</v>
       </c>
       <c r="R78">
-        <v>0.6390755689226308</v>
+        <v>0</v>
       </c>
       <c r="S78">
-        <v>0</v>
+        <v>-1.126452331932567</v>
       </c>
       <c r="T78">
-        <v>0</v>
+        <v>0.6440585118695387</v>
+      </c>
+      <c r="U78">
+        <v>0.17317336636282</v>
+      </c>
+      <c r="V78">
+        <v>0.1425667123876401</v>
       </c>
       <c r="W78">
-        <v>0.4434480819735523</v>
+        <v>2.773600791048716</v>
+      </c>
+      <c r="X78">
+        <v>0.4048218374954839</v>
+      </c>
+      <c r="Y78">
+        <v>0.3798978984540057</v>
       </c>
     </row>
     <row r="79">
@@ -5551,40 +6173,40 @@
         </is>
       </c>
       <c r="B79">
-        <v>6.692488984265891</v>
+        <v>7.426832498544667</v>
       </c>
       <c r="C79">
-        <v>0.4130681383652425</v>
+        <v>0.4369982938134929</v>
       </c>
       <c r="D79">
-        <v>844.2071193141553</v>
+        <v>824.1377555140724</v>
       </c>
       <c r="E79">
-        <v>2.641342805042894</v>
+        <v>2.493586792433825</v>
       </c>
       <c r="F79">
-        <v>0.7120933818216612</v>
+        <v>0.7129816557315387</v>
       </c>
       <c r="G79">
-        <v>0.5363960821200183</v>
+        <v>0.2019774381628826</v>
       </c>
       <c r="H79">
-        <v>73.60762752531249</v>
+        <v>44.3637632324</v>
       </c>
       <c r="I79">
-        <v>0.04914961865838969</v>
+        <v>0.09546851096905824</v>
       </c>
       <c r="J79">
-        <v>113.1500833333333</v>
+        <v>41.35012820512821</v>
       </c>
       <c r="K79">
-        <v>0.1536241025652297</v>
+        <v>0.04608884536138932</v>
       </c>
       <c r="L79">
-        <v>14.49188114510417</v>
+        <v>14.04834562354167</v>
       </c>
       <c r="M79">
-        <v>0.08915122436310551</v>
+        <v>0.08880022574589005</v>
       </c>
       <c r="N79">
         <v>1</v>
@@ -5598,19 +6220,31 @@
         <v>1</v>
       </c>
       <c r="Q79">
-        <v>3.95142637</v>
+        <v>4.333333333333333</v>
       </c>
       <c r="R79">
-        <v>0.8240070740005321</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="S79">
-        <v>4.333333333333333</v>
+        <v>-0.389471081015986</v>
       </c>
       <c r="T79">
-        <v>0.5416666666666666</v>
+        <v>0.9723970651888925</v>
+      </c>
+      <c r="U79">
+        <v>0.3781242293694638</v>
+      </c>
+      <c r="V79">
+        <v>0.4208919235981351</v>
       </c>
       <c r="W79">
-        <v>0.4148945360701057</v>
+        <v>0.8606043970441799</v>
+      </c>
+      <c r="X79">
+        <v>0.05017995772283684</v>
+      </c>
+      <c r="Y79">
+        <v>0.3567450582960783</v>
       </c>
     </row>
     <row r="80">
@@ -5620,40 +6254,40 @@
         </is>
       </c>
       <c r="B80">
-        <v>0.9113912774758922</v>
+        <v>0.7836703974105198</v>
       </c>
       <c r="C80">
-        <v>0.9813813255054202</v>
+        <v>0.986361239140201</v>
       </c>
       <c r="D80">
-        <v>954.6694808040943</v>
+        <v>1004.19269737696</v>
       </c>
       <c r="E80">
-        <v>3.324423197436492</v>
+        <v>3.305629035542037</v>
       </c>
       <c r="F80">
-        <v>0.8128617331777446</v>
+        <v>0.8212070754190615</v>
       </c>
       <c r="G80">
-        <v>0.7780287209137213</v>
+        <v>0.3218181099019017</v>
       </c>
       <c r="H80">
-        <v>330.164247171875</v>
+        <v>198.04823638</v>
       </c>
       <c r="I80">
-        <v>1</v>
+        <v>0.8648964270282454</v>
       </c>
       <c r="J80">
-        <v>310.4554166666667</v>
+        <v>350.2982051282052</v>
       </c>
       <c r="K80">
-        <v>0.4319104368176926</v>
+        <v>0.4980378866790473</v>
       </c>
       <c r="L80">
-        <v>17.04876937625</v>
+        <v>17.28420541916667</v>
       </c>
       <c r="M80">
-        <v>0.2198165349081643</v>
+        <v>0.2394809925082852</v>
       </c>
       <c r="N80">
         <v>6.610169491525424</v>
@@ -5667,19 +6301,31 @@
         <v>8</v>
       </c>
       <c r="Q80">
-        <v>4.4750757815</v>
+        <v>3</v>
       </c>
       <c r="R80">
-        <v>0.7991963065089764</v>
+        <v>0.375</v>
       </c>
       <c r="S80">
-        <v>3</v>
+        <v>-1.20366931536268</v>
       </c>
       <c r="T80">
-        <v>0.375</v>
+        <v>0.6096569411381311</v>
+      </c>
+      <c r="U80">
+        <v>0.3303346114367731</v>
+      </c>
+      <c r="V80">
+        <v>0.355993170259615</v>
       </c>
       <c r="W80">
-        <v>0.6747743822289649</v>
+        <v>3.198257316627551</v>
+      </c>
+      <c r="X80">
+        <v>0.4835470190802443</v>
+      </c>
+      <c r="Y80">
+        <v>0.5555998861154733</v>
       </c>
     </row>
     <row r="81">
@@ -5689,40 +6335,40 @@
         </is>
       </c>
       <c r="B81">
-        <v>4.410626045842244</v>
+        <v>4.916436510502518</v>
       </c>
       <c r="C81">
-        <v>0.6373876127843419</v>
+        <v>0.6445980050551827</v>
       </c>
       <c r="D81">
-        <v>817.2379250340023</v>
+        <v>825.7249027478038</v>
       </c>
       <c r="E81">
-        <v>2.393989412593131</v>
+        <v>2.127817125808322</v>
       </c>
       <c r="F81">
-        <v>0.687490963329454</v>
+        <v>0.7139356405191779</v>
       </c>
       <c r="G81">
-        <v>0.4488973724545661</v>
+        <v>0.1479973861124179</v>
       </c>
       <c r="H81">
-        <v>76.5980043496875</v>
+        <v>40.7742455676</v>
       </c>
       <c r="I81">
-        <v>0.06023255601439794</v>
+        <v>0.07749743659883106</v>
       </c>
       <c r="J81">
-        <v>410.664875</v>
+        <v>350.0344871794872</v>
       </c>
       <c r="K81">
-        <v>0.5732493572912475</v>
+        <v>0.4976521031671758</v>
       </c>
       <c r="L81">
-        <v>16.3130408974375</v>
+        <v>16.06899846154167</v>
       </c>
       <c r="M81">
-        <v>0.1822184150569114</v>
+        <v>0.1828937706522884</v>
       </c>
       <c r="N81">
         <v>3.779661016949153</v>
@@ -5736,25 +6382,31 @@
         <v>4</v>
       </c>
       <c r="Q81">
-        <v>2.02887792975</v>
+        <v>3</v>
       </c>
       <c r="R81">
-        <v>0.9150983677072484</v>
+        <v>0.375</v>
       </c>
       <c r="S81">
-        <v>3</v>
+        <v>-0.3275141611830821</v>
       </c>
       <c r="T81">
-        <v>0.375</v>
+        <v>1</v>
       </c>
       <c r="U81">
-        <v>9.261224489795918</v>
+        <v>0.2572213614690207</v>
       </c>
       <c r="V81">
-        <v>0.515905099709737</v>
+        <v>0.2567046850049774</v>
       </c>
       <c r="W81">
-        <v>0.4883866382608782</v>
+        <v>2.096077665636558</v>
+      </c>
+      <c r="X81">
+        <v>0.2792188433975049</v>
+      </c>
+      <c r="Y81">
+        <v>0.4175497870507556</v>
       </c>
     </row>
     <row r="82">
@@ -5764,40 +6416,40 @@
         </is>
       </c>
       <c r="B82">
-        <v>1.557799648651538</v>
+        <v>1.409321096780074</v>
       </c>
       <c r="C82">
-        <v>0.9178358847865323</v>
+        <v>0.9346224277550786</v>
       </c>
       <c r="D82">
-        <v>857.5264607957037</v>
+        <v>860.5820955838788</v>
       </c>
       <c r="E82">
-        <v>2.553084119794869</v>
+        <v>2.295484009664331</v>
       </c>
       <c r="F82">
-        <v>0.724243837996424</v>
+        <v>0.7348872138821897</v>
       </c>
       <c r="G82">
-        <v>0.5051754831240297</v>
+        <v>0.1727415569486321</v>
       </c>
       <c r="H82">
-        <v>162.0354838759375</v>
+        <v>51.1210193612</v>
       </c>
       <c r="I82">
-        <v>0.3768810217617106</v>
+        <v>0.1292990040239251</v>
       </c>
       <c r="J82">
-        <v>54.90058333333334</v>
+        <v>19.21935897435898</v>
       </c>
       <c r="K82">
-        <v>0.07146697303820813</v>
+        <v>0.01371453820569594</v>
       </c>
       <c r="L82">
-        <v>14.71463431541667</v>
+        <v>13.9896852975</v>
       </c>
       <c r="M82">
-        <v>0.1005346363633773</v>
+        <v>0.08606865408804465</v>
       </c>
       <c r="N82">
         <v>0.9833333333333333</v>
@@ -5810,14 +6462,26 @@
       <c r="P82">
         <v>1</v>
       </c>
-      <c r="Q82">
-        <v>5.91437160775</v>
-      </c>
-      <c r="R82">
-        <v>0.731001760096018</v>
+      <c r="S82">
+        <v>-1.816154692047206</v>
+      </c>
+      <c r="T82">
+        <v>0.3367835644277383</v>
+      </c>
+      <c r="U82">
+        <v>0.1378526305046144</v>
+      </c>
+      <c r="V82">
+        <v>0.0946008188869794</v>
       </c>
       <c r="W82">
-        <v>0.4895913710237572</v>
+        <v>0.5899254850199525</v>
+      </c>
+      <c r="X82">
+        <v>0</v>
+      </c>
+      <c r="Y82">
+        <v>0.2780797531353649</v>
       </c>
     </row>
     <row r="83">
@@ -5827,40 +6491,40 @@
         </is>
       </c>
       <c r="B83">
-        <v>4.056336430908098</v>
+        <v>4.033602709547567</v>
       </c>
       <c r="C83">
-        <v>0.672216199057396</v>
+        <v>0.7176048306817597</v>
       </c>
       <c r="D83">
-        <v>740.1297030877272</v>
+        <v>706.1781152890081</v>
       </c>
       <c r="E83">
-        <v>2.080240700410156</v>
+        <v>1.8736807230348</v>
       </c>
       <c r="F83">
-        <v>0.617149642568963</v>
+        <v>0.6420797885710791</v>
       </c>
       <c r="G83">
-        <v>0.3379120036940255</v>
+        <v>0.1104920993121371</v>
       </c>
       <c r="H83">
-        <v>88.9824012521875</v>
+        <v>29.6650736028</v>
       </c>
       <c r="I83">
-        <v>0.1061316192841371</v>
+        <v>0.02187888998215423</v>
       </c>
       <c r="J83">
-        <v>122.4278333333333</v>
+        <v>98.38858974358973</v>
       </c>
       <c r="K83">
-        <v>0.1667097652485029</v>
+        <v>0.1295283613709362</v>
       </c>
       <c r="L83">
-        <v>14.38611968541667</v>
+        <v>13.60098937083333</v>
       </c>
       <c r="M83">
-        <v>0.08374646955003613</v>
+        <v>0.06796867325860938</v>
       </c>
       <c r="N83">
         <v>0.9833333333333333</v>
@@ -5874,19 +6538,31 @@
         <v>1</v>
       </c>
       <c r="Q83">
-        <v>0.9924028764999999</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="R83">
-        <v>0.9642070671390313</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="S83">
-        <v>1.333333333333333</v>
+        <v>-0.714038504471876</v>
       </c>
       <c r="T83">
-        <v>0.1666666666666667</v>
+        <v>0.8277963740050138</v>
+      </c>
+      <c r="U83">
+        <v>0.1538282593601269</v>
+      </c>
+      <c r="V83">
+        <v>0.1162958740343532</v>
       </c>
       <c r="W83">
-        <v>0.3893424291510948</v>
+        <v>0.7802323477516002</v>
+      </c>
+      <c r="X83">
+        <v>0.03528014153309827</v>
+      </c>
+      <c r="Y83">
+        <v>0.2835591699415808</v>
       </c>
     </row>
     <row r="84">
@@ -5896,40 +6572,40 @@
         </is>
       </c>
       <c r="B84">
-        <v>1.035234654258313</v>
+        <v>1.052414688086237</v>
       </c>
       <c r="C84">
-        <v>0.9692068514288525</v>
+        <v>0.964137160784482</v>
       </c>
       <c r="D84">
-        <v>899.4694821174611</v>
+        <v>955.1556805013</v>
       </c>
       <c r="E84">
-        <v>2.765656411943148</v>
+        <v>2.696138821543334</v>
       </c>
       <c r="F84">
-        <v>0.7625060030676597</v>
+        <v>0.7917324513033079</v>
       </c>
       <c r="G84">
-        <v>0.5803707375306559</v>
+        <v>0.231869936289178</v>
       </c>
       <c r="H84">
-        <v>102.4966450978125</v>
+        <v>59.2065057252</v>
       </c>
       <c r="I84">
-        <v>0.1562181223408834</v>
+        <v>0.16977933880311</v>
       </c>
       <c r="J84">
-        <v>96.73041666666667</v>
+        <v>67.23102564102564</v>
       </c>
       <c r="K84">
-        <v>0.1304652311393144</v>
+        <v>0.08394908032736648</v>
       </c>
       <c r="L84">
-        <v>16.32558588020833</v>
+        <v>15.56825509375</v>
       </c>
       <c r="M84">
-        <v>0.1828595045068006</v>
+        <v>0.1595761983915721</v>
       </c>
       <c r="N84">
         <v>2</v>
@@ -5943,19 +6619,31 @@
         <v>2</v>
       </c>
       <c r="Q84">
-        <v>2.06345293625</v>
+        <v>1</v>
       </c>
       <c r="R84">
-        <v>0.9134601868395696</v>
+        <v>0.125</v>
       </c>
       <c r="S84">
-        <v>1</v>
+        <v>-1.60020019793378</v>
       </c>
       <c r="T84">
-        <v>0.125</v>
+        <v>0.4329952198692158</v>
+      </c>
+      <c r="U84">
+        <v>0.3573260414299296</v>
+      </c>
+      <c r="V84">
+        <v>0.3926477875835491</v>
       </c>
       <c r="W84">
-        <v>0.477510829606717</v>
+        <v>1.160429300600832</v>
+      </c>
+      <c r="X84">
+        <v>0.1057631609809458</v>
+      </c>
+      <c r="Y84">
+        <v>0.3457450334332727</v>
       </c>
     </row>
     <row r="85">
@@ -5965,40 +6653,40 @@
         </is>
       </c>
       <c r="B85">
-        <v>1.647421926406839</v>
+        <v>1.321750156016363</v>
       </c>
       <c r="C85">
-        <v>0.9090255299208716</v>
+        <v>0.9418641944334456</v>
       </c>
       <c r="D85">
-        <v>892.7724353911411</v>
+        <v>934.3217531772182</v>
       </c>
       <c r="E85">
-        <v>2.631552202183076</v>
+        <v>2.36225955882839</v>
       </c>
       <c r="F85">
-        <v>0.7563966790548159</v>
+        <v>0.7792098262364263</v>
       </c>
       <c r="G85">
-        <v>0.53293275740635</v>
+        <v>0.1825962495283338</v>
       </c>
       <c r="H85">
-        <v>60.3461720246875</v>
+        <v>29.7639001916</v>
       </c>
       <c r="I85">
-        <v>0</v>
+        <v>0.02237366954390341</v>
       </c>
       <c r="J85">
-        <v>80.89975</v>
+        <v>51.7598717948718</v>
       </c>
       <c r="K85">
-        <v>0.108137105887897</v>
+        <v>0.06131688523981407</v>
       </c>
       <c r="L85">
-        <v>16.95464400197917</v>
+        <v>15.96887133729167</v>
       </c>
       <c r="M85">
-        <v>0.2150064219319874</v>
+        <v>0.1782312596633691</v>
       </c>
       <c r="N85">
         <v>1.9</v>
@@ -6012,19 +6700,31 @@
         <v>2</v>
       </c>
       <c r="Q85">
-        <v>1.467972922666667</v>
+        <v>3</v>
       </c>
       <c r="R85">
-        <v>0.9416743236998848</v>
+        <v>0.375</v>
       </c>
       <c r="S85">
-        <v>3</v>
+        <v>-1.851713085829956</v>
       </c>
       <c r="T85">
-        <v>0.375</v>
+        <v>0.3209416531735951</v>
+      </c>
+      <c r="U85">
+        <v>0.07530113020270239</v>
+      </c>
+      <c r="V85">
+        <v>0.009655289613952461</v>
       </c>
       <c r="W85">
-        <v>0.4797716022377259</v>
+        <v>0.7652975136819987</v>
+      </c>
+      <c r="X85">
+        <v>0.03251143917425656</v>
+      </c>
+      <c r="Y85">
+        <v>0.2903700466607096</v>
       </c>
     </row>
     <row r="86">
@@ -6034,40 +6734,40 @@
         </is>
       </c>
       <c r="B86">
-        <v>2.668287177350798</v>
+        <v>2.539400797029873</v>
       </c>
       <c r="C86">
-        <v>0.8086689516670225</v>
+        <v>0.8411693547859329</v>
       </c>
       <c r="D86">
-        <v>984.282715387383</v>
+        <v>969.3120819520811</v>
       </c>
       <c r="E86">
-        <v>2.832724909576293</v>
+        <v>2.886406721124843</v>
       </c>
       <c r="F86">
-        <v>0.8398761549864866</v>
+        <v>0.8002414234671629</v>
       </c>
       <c r="G86">
-        <v>0.6040955263600328</v>
+        <v>0.2599495504838077</v>
       </c>
       <c r="H86">
-        <v>135.46246887375</v>
+        <v>88.0071601584</v>
       </c>
       <c r="I86">
-        <v>0.2783960889502532</v>
+        <v>0.3139710523042856</v>
       </c>
       <c r="J86">
-        <v>260.4987083333334</v>
+        <v>268.6414102564103</v>
       </c>
       <c r="K86">
-        <v>0.3614497503347991</v>
+        <v>0.3785850953656091</v>
       </c>
       <c r="L86">
-        <v>16.83286806979167</v>
+        <v>17.14615280625</v>
       </c>
       <c r="M86">
-        <v>0.2087832754516804</v>
+        <v>0.2330524465014525</v>
       </c>
       <c r="N86">
         <v>6.35593220338983</v>
@@ -6081,19 +6781,31 @@
         <v>8</v>
       </c>
       <c r="Q86">
-        <v>0.9632191780000001</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="R86">
-        <v>0.9655898051735361</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="S86">
-        <v>1.333333333333333</v>
+        <v>-1.413333462589079</v>
       </c>
       <c r="T86">
-        <v>0.1666666666666667</v>
+        <v>0.5162477496591965</v>
+      </c>
+      <c r="U86">
+        <v>0.1823399902473845</v>
+      </c>
+      <c r="V86">
+        <v>0.1550150743575815</v>
       </c>
       <c r="W86">
-        <v>0.5291907774488097</v>
+        <v>2.643810951523113</v>
+      </c>
+      <c r="X86">
+        <v>0.3807606773129513</v>
+      </c>
+      <c r="Y86">
+        <v>0.4045659090904647</v>
       </c>
     </row>
     <row r="87">
@@ -6106,34 +6818,34 @@
         <v>3.095392060730346</v>
       </c>
       <c r="C87">
-        <v>0.7666822304892303</v>
+        <v>0.7951911002209473</v>
       </c>
       <c r="D87">
-        <v>706.9460658690535</v>
+        <v>687.6515140523901</v>
       </c>
       <c r="E87">
-        <v>2.220446207460934</v>
+        <v>1.877251447170667</v>
       </c>
       <c r="F87">
-        <v>0.5868781512716429</v>
+        <v>0.630944025378624</v>
       </c>
       <c r="G87">
-        <v>0.38750825476394</v>
+        <v>0.1110190644825686</v>
       </c>
       <c r="H87">
-        <v>104.8937559309375</v>
+        <v>73.4244075916</v>
       </c>
       <c r="I87">
-        <v>0.1651022967306731</v>
+        <v>0.2409618752021621</v>
       </c>
       <c r="J87">
-        <v>128.8154583333333</v>
+        <v>101.8382051282051</v>
       </c>
       <c r="K87">
-        <v>0.1757190946761382</v>
+        <v>0.1345746797734286</v>
       </c>
       <c r="L87">
-        <v>12.7473499040625</v>
+        <v>12.14136647479167</v>
       </c>
       <c r="M87">
         <v>0</v>
@@ -6150,19 +6862,31 @@
         <v>2</v>
       </c>
       <c r="Q87">
-        <v>1.005487459666667</v>
+        <v>5</v>
       </c>
       <c r="R87">
-        <v>0.9635871131325097</v>
+        <v>0.625</v>
       </c>
       <c r="S87">
-        <v>5</v>
+        <v>-0.6974744579940655</v>
       </c>
       <c r="T87">
-        <v>0.625</v>
+        <v>0.8351759580186843</v>
+      </c>
+      <c r="U87">
+        <v>0.2605866789926531</v>
+      </c>
+      <c r="V87">
+        <v>0.2612748180447441</v>
       </c>
       <c r="W87">
-        <v>0.4588096426330168</v>
+        <v>1.412863028854081</v>
+      </c>
+      <c r="X87">
+        <v>0.1525607253602217</v>
+      </c>
+      <c r="Y87">
+        <v>0.378670224648138</v>
       </c>
     </row>
     <row r="88">
@@ -6172,40 +6896,40 @@
         </is>
       </c>
       <c r="B88">
-        <v>2.93340592717423</v>
+        <v>3.183276175047217</v>
       </c>
       <c r="C88">
-        <v>0.7826063439539909</v>
+        <v>0.7879234353418527</v>
       </c>
       <c r="D88">
-        <v>976.9563461971909</v>
+        <v>1089.560605949949</v>
       </c>
       <c r="E88">
-        <v>3.142902868993676</v>
+        <v>3.065558163535105</v>
       </c>
       <c r="F88">
-        <v>0.8331927368994226</v>
+        <v>0.8725190674008934</v>
       </c>
       <c r="G88">
-        <v>0.7138177781831853</v>
+        <v>0.2863886050818564</v>
       </c>
       <c r="H88">
-        <v>151.39790363125</v>
+        <v>116.396116648</v>
       </c>
       <c r="I88">
-        <v>0.337456012006954</v>
+        <v>0.4561015823670683</v>
       </c>
       <c r="J88">
-        <v>693.9295833333333</v>
+        <v>693.4347435897436</v>
       </c>
       <c r="K88">
-        <v>0.9727757967109103</v>
+        <v>1</v>
       </c>
       <c r="L88">
-        <v>17.63547567520833</v>
+        <v>18.21720135041667</v>
       </c>
       <c r="M88">
-        <v>0.2497991363446681</v>
+        <v>0.2829268001718372</v>
       </c>
       <c r="N88">
         <v>10.48333333333333</v>
@@ -6219,19 +6943,31 @@
         <v>16</v>
       </c>
       <c r="Q88">
-        <v>3.14699305475</v>
+        <v>5</v>
       </c>
       <c r="R88">
-        <v>0.8621215213937934</v>
+        <v>0.625</v>
       </c>
       <c r="S88">
-        <v>5</v>
+        <v>-0.6333708939956759</v>
       </c>
       <c r="T88">
-        <v>0.625</v>
+        <v>0.8637352618539839</v>
+      </c>
+      <c r="U88">
+        <v>0.168616944640567</v>
+      </c>
+      <c r="V88">
+        <v>0.1363790485759047</v>
       </c>
       <c r="W88">
-        <v>0.6720961656866156</v>
+        <v>1.630447529738109</v>
+      </c>
+      <c r="X88">
+        <v>0.1928977467183089</v>
+      </c>
+      <c r="Y88">
+        <v>0.5503871547511705</v>
       </c>
     </row>
     <row r="89">
@@ -6244,21 +6980,21 @@
         <v>1.25617934230505</v>
       </c>
       <c r="C89">
-        <v>0.9474867930222883</v>
+        <v>0.9472866385646472</v>
       </c>
       <c r="L89">
-        <v>17.21286807625</v>
+        <v>17.90040281916667</v>
       </c>
       <c r="M89">
-        <v>0.2282025125720888</v>
+        <v>0.2681747872253893</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
           <t>B4</t>
         </is>
       </c>
-      <c r="W89">
-        <v>0.5878446527971886</v>
+      <c r="Y89">
+        <v>0.6077307128950182</v>
       </c>
     </row>
     <row r="90">
@@ -6268,40 +7004,40 @@
         </is>
       </c>
       <c r="B90">
-        <v>3.144980069906421</v>
+        <v>3.28270051142621</v>
       </c>
       <c r="C90">
-        <v>0.7618074608575578</v>
+        <v>0.7797014402378958</v>
       </c>
       <c r="D90">
-        <v>990.9597563929921</v>
+        <v>1065.292555952169</v>
       </c>
       <c r="E90">
-        <v>2.953631968905547</v>
+        <v>2.826573011754531</v>
       </c>
       <c r="F90">
-        <v>0.8459672289504764</v>
+        <v>0.8579322981135081</v>
       </c>
       <c r="G90">
-        <v>0.6468651507261209</v>
+        <v>0.2511193301542233</v>
       </c>
       <c r="H90">
-        <v>152.0578600525</v>
+        <v>147.5316608672</v>
       </c>
       <c r="I90">
-        <v>0.3399019431066032</v>
+        <v>0.6119830218729293</v>
       </c>
       <c r="J90">
-        <v>585.0162666666666</v>
+        <v>567.9525256410257</v>
       </c>
       <c r="K90">
-        <v>0.819160650407494</v>
+        <v>0.8164365719018322</v>
       </c>
       <c r="L90">
-        <v>14.58769866375</v>
+        <v>14.59623066083333</v>
       </c>
       <c r="M90">
-        <v>0.09404781142428659</v>
+        <v>0.1143129929023565</v>
       </c>
       <c r="N90">
         <v>9.85</v>
@@ -6315,25 +7051,31 @@
         <v>16</v>
       </c>
       <c r="Q90">
-        <v>3.55116901125</v>
+        <v>4</v>
       </c>
       <c r="R90">
-        <v>0.8429714651497245</v>
+        <v>0.5</v>
       </c>
       <c r="S90">
-        <v>4</v>
+        <v>-1.035834938222531</v>
       </c>
       <c r="T90">
-        <v>0.5</v>
+        <v>0.6844302091404252</v>
       </c>
       <c r="U90">
-        <v>4.831024930747922</v>
+        <v>0.3646367785288091</v>
       </c>
       <c r="V90">
-        <v>0.155098028107015</v>
+        <v>0.4025758377381077</v>
       </c>
       <c r="W90">
-        <v>0.556202193192142</v>
+        <v>4.216377240397463</v>
+      </c>
+      <c r="X90">
+        <v>0.672291736389361</v>
+      </c>
+      <c r="Y90">
+        <v>0.5690783438450639</v>
       </c>
     </row>
     <row r="91">
@@ -6343,40 +7085,40 @@
         </is>
       </c>
       <c r="B91">
-        <v>2.98039018954707</v>
+        <v>3.038668028517401</v>
       </c>
       <c r="C91">
-        <v>0.77798753672242</v>
+        <v>0.7998819508930979</v>
       </c>
       <c r="D91">
-        <v>748.9641781174147</v>
+        <v>734.2236921921332</v>
       </c>
       <c r="E91">
-        <v>2.339591991004429</v>
+        <v>2.216358130007247</v>
       </c>
       <c r="F91">
-        <v>0.6252088174030913</v>
+        <v>0.6589371116709957</v>
       </c>
       <c r="G91">
-        <v>0.4296548459987961</v>
+        <v>0.1610642105414428</v>
       </c>
       <c r="H91">
-        <v>61.79041457875</v>
+        <v>34.4429306608</v>
       </c>
       <c r="I91">
-        <v>0.005352653091438228</v>
+        <v>0.04579943656746183</v>
       </c>
       <c r="J91">
-        <v>538.9304166666667</v>
+        <v>518.9996153846154</v>
       </c>
       <c r="K91">
-        <v>0.7541595577317992</v>
+        <v>0.7448251183513297</v>
       </c>
       <c r="L91">
-        <v>13.37128533022917</v>
+        <v>13.29757066045833</v>
       </c>
       <c r="M91">
-        <v>0.0318851310069178</v>
+        <v>0.05383970389127882</v>
       </c>
       <c r="N91">
         <v>1.9</v>
@@ -6390,19 +7132,31 @@
         <v>2</v>
       </c>
       <c r="Q91">
-        <v>3.534682079</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="R91">
-        <v>0.8437526241345729</v>
+        <v>0.2083333333333333</v>
       </c>
       <c r="S91">
-        <v>1.666666666666667</v>
+        <v>-1.10875161355244</v>
       </c>
       <c r="T91">
-        <v>0.2083333333333333</v>
+        <v>0.6519445038922881</v>
+      </c>
+      <c r="U91">
+        <v>0.1084997787626584</v>
+      </c>
+      <c r="V91">
+        <v>0.05473936848437524</v>
       </c>
       <c r="W91">
-        <v>0.4595418124277961</v>
+        <v>3.868551683434767</v>
+      </c>
+      <c r="X91">
+        <v>0.6078099058219762</v>
+      </c>
+      <c r="Y91">
+        <v>0.398717464344758</v>
       </c>
     </row>
     <row r="92">
@@ -6412,40 +7166,40 @@
         </is>
       </c>
       <c r="B92">
-        <v>0.9985906350334441</v>
+        <v>0.7955205331765982</v>
       </c>
       <c r="C92">
-        <v>0.9728091568060565</v>
+        <v>0.9853812802911068</v>
       </c>
       <c r="D92">
-        <v>729.3911372457928</v>
+        <v>783.7945610874324</v>
       </c>
       <c r="E92">
-        <v>2.420880084084988</v>
+        <v>2.27967384047498</v>
       </c>
       <c r="F92">
-        <v>0.6073534770586047</v>
+        <v>0.6887326176146994</v>
       </c>
       <c r="G92">
-        <v>0.4584096699584418</v>
+        <v>0.1704083023525325</v>
       </c>
       <c r="H92">
-        <v>114.1203750196875</v>
+        <v>81.8560800252</v>
       </c>
       <c r="I92">
-        <v>0.1992980009425456</v>
+        <v>0.2831754054086119</v>
       </c>
       <c r="J92">
-        <v>414.1980833333333</v>
+        <v>382.5914102564103</v>
       </c>
       <c r="K92">
-        <v>0.5782327177439144</v>
+        <v>0.5452784561757807</v>
       </c>
       <c r="L92">
-        <v>15.9044354025</v>
+        <v>16.25553747166667</v>
       </c>
       <c r="M92">
-        <v>0.1613373443726056</v>
+        <v>0.191580130028778</v>
       </c>
       <c r="N92">
         <v>2.833333333333333</v>
@@ -6459,19 +7213,31 @@
         <v>4</v>
       </c>
       <c r="Q92">
-        <v>1.777189273</v>
+        <v>6</v>
       </c>
       <c r="R92">
-        <v>0.9270235004501621</v>
+        <v>0.75</v>
       </c>
       <c r="S92">
-        <v>6</v>
+        <v>-1.26993673157125</v>
       </c>
       <c r="T92">
-        <v>0.75</v>
+        <v>0.5801336017817053</v>
+      </c>
+      <c r="U92">
+        <v>0.3612722184373502</v>
+      </c>
+      <c r="V92">
+        <v>0.3980067332983994</v>
       </c>
       <c r="W92">
-        <v>0.5818079834165413</v>
+        <v>5.984089296781033</v>
+      </c>
+      <c r="X92">
+        <v>1</v>
+      </c>
+      <c r="Y92">
+        <v>0.5592696526951614</v>
       </c>
     </row>
   </sheetData>

--- a/Data Analysis/1_Data/ecological_multifunctionality.xlsx
+++ b/Data Analysis/1_Data/ecological_multifunctionality.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y92"/>
+  <dimension ref="A1:Z92"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -477,6 +477,11 @@
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
+          <t>aggregates_standardized</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
           <t>multifunctionality</t>
         </is>
       </c>
@@ -559,7 +564,10 @@
         <v>0.3095837336681162</v>
       </c>
       <c r="Y2">
-        <v>0.4547320147309752</v>
+        <v>0.5329067273494283</v>
+      </c>
+      <c r="Z2">
+        <v>0.4618388067871982</v>
       </c>
     </row>
     <row r="3">
@@ -640,7 +648,10 @@
         <v>0.4538193710537792</v>
       </c>
       <c r="Y3">
-        <v>0.4561234608142631</v>
+        <v>0.5349234617545326</v>
+      </c>
+      <c r="Z3">
+        <v>0.4632870972633785</v>
       </c>
     </row>
     <row r="4">
@@ -721,7 +732,10 @@
         <v>0.1763512235540355</v>
       </c>
       <c r="Y4">
-        <v>0.3122553672943749</v>
+        <v>0.3687207077501685</v>
+      </c>
+      <c r="Z4">
+        <v>0.3173885800630833</v>
       </c>
     </row>
     <row r="5">
@@ -802,7 +816,10 @@
         <v>0.2901661958320036</v>
       </c>
       <c r="Y5">
-        <v>0.3761964175305524</v>
+        <v>0.9078847592894224</v>
+      </c>
+      <c r="Z5">
+        <v>0.4245317213268133</v>
       </c>
     </row>
     <row r="6">
@@ -883,7 +900,10 @@
         <v>0.08272192028282797</v>
       </c>
       <c r="Y6">
-        <v>0.3051692091404943</v>
+        <v>0.8102154638078963</v>
+      </c>
+      <c r="Z6">
+        <v>0.351082505019349</v>
       </c>
     </row>
     <row r="7">
@@ -964,7 +984,10 @@
         <v>0.6061769173633896</v>
       </c>
       <c r="Y7">
-        <v>0.4985296391698585</v>
+        <v>0.6360493681792212</v>
+      </c>
+      <c r="Z7">
+        <v>0.5110314327161642</v>
       </c>
     </row>
     <row r="8">
@@ -1045,7 +1068,10 @@
         <v>0.1482407307513151</v>
       </c>
       <c r="Y8">
-        <v>0.312067077511413</v>
+        <v>0.577888345759738</v>
+      </c>
+      <c r="Z8">
+        <v>0.3362326473521699</v>
       </c>
     </row>
     <row r="9">
@@ -1126,7 +1152,10 @@
         <v>0.3666128102901184</v>
       </c>
       <c r="Y9">
-        <v>0.2802435024379179</v>
+        <v>0.5269623043811215</v>
+      </c>
+      <c r="Z9">
+        <v>0.3026724844327546</v>
       </c>
     </row>
     <row r="10">
@@ -1170,7 +1199,7 @@
       <c r="P10">
         <v>1</v>
       </c>
-      <c r="Y10">
+      <c r="Z10">
         <v>0.7277890482385811</v>
       </c>
     </row>
@@ -1197,7 +1226,7 @@
           <t>B1</t>
         </is>
       </c>
-      <c r="Y11">
+      <c r="Z11">
         <v>0.2034450995559281</v>
       </c>
     </row>
@@ -1279,7 +1308,10 @@
         <v>0.6466931295555873</v>
       </c>
       <c r="Y12">
-        <v>0.5120287919771016</v>
+        <v>0.6286899729640903</v>
+      </c>
+      <c r="Z12">
+        <v>0.5226343538850097</v>
       </c>
     </row>
     <row r="13">
@@ -1360,7 +1392,10 @@
         <v>0.3387981378390733</v>
       </c>
       <c r="Y13">
-        <v>0.4025892046534116</v>
+        <v>0.5786033147410633</v>
+      </c>
+      <c r="Z13">
+        <v>0.4185904873886526</v>
       </c>
     </row>
     <row r="14">
@@ -1441,7 +1476,10 @@
         <v>0.3231240314170564</v>
       </c>
       <c r="Y14">
-        <v>0.3844629706631622</v>
+        <v>0.5881104701166693</v>
+      </c>
+      <c r="Z14">
+        <v>0.4029763797043901</v>
       </c>
     </row>
     <row r="15">
@@ -1522,7 +1560,10 @@
         <v>0.3613628349666473</v>
       </c>
       <c r="Y15">
-        <v>0.5205713052623998</v>
+        <v>0.3967074045852518</v>
+      </c>
+      <c r="Z15">
+        <v>0.5093109506553865</v>
       </c>
     </row>
     <row r="16">
@@ -1603,7 +1644,10 @@
         <v>0.002517386384649483</v>
       </c>
       <c r="Y16">
-        <v>0.3019111328487163</v>
+        <v>1</v>
+      </c>
+      <c r="Z16">
+        <v>0.3653737571351967</v>
       </c>
     </row>
     <row r="17">
@@ -1684,7 +1728,10 @@
         <v>0.1189272518667831</v>
       </c>
       <c r="Y17">
-        <v>0.3524493223224792</v>
+        <v>0.5991571254558291</v>
+      </c>
+      <c r="Z17">
+        <v>0.374877304425511</v>
       </c>
     </row>
     <row r="18">
@@ -1765,7 +1812,10 @@
         <v>0.2433418210541713</v>
       </c>
       <c r="Y18">
-        <v>0.3724648314582031</v>
+        <v>0.615833348345295</v>
+      </c>
+      <c r="Z18">
+        <v>0.3945892420843024</v>
       </c>
     </row>
     <row r="19">
@@ -1846,7 +1896,10 @@
         <v>0.1278675422350279</v>
       </c>
       <c r="Y19">
-        <v>0.1982243343133886</v>
+        <v>0.682795362548585</v>
+      </c>
+      <c r="Z19">
+        <v>0.2422762459711337</v>
       </c>
     </row>
     <row r="20">
@@ -1927,7 +1980,10 @@
         <v>0.3653087018938461</v>
       </c>
       <c r="Y20">
-        <v>0.4183576226830569</v>
+        <v>0.5691113227775285</v>
+      </c>
+      <c r="Z20">
+        <v>0.432062504509827</v>
       </c>
     </row>
     <row r="21">
@@ -2008,7 +2064,10 @@
         <v>0.6147991208738268</v>
       </c>
       <c r="Y21">
-        <v>0.5931212407887235</v>
+        <v>0.4762697184401813</v>
+      </c>
+      <c r="Z21">
+        <v>0.5824983751206743</v>
       </c>
     </row>
     <row r="22">
@@ -2089,7 +2148,10 @@
         <v>0.1830304771246527</v>
       </c>
       <c r="Y22">
-        <v>0.4077860021521065</v>
+        <v>0.6169762430128304</v>
+      </c>
+      <c r="Z22">
+        <v>0.4268032967758087</v>
       </c>
     </row>
     <row r="23">
@@ -2164,7 +2226,10 @@
         <v>0.8143839706609451</v>
       </c>
       <c r="Y23">
-        <v>0.6680331535328258</v>
+        <v>0.5893605834780353</v>
+      </c>
+      <c r="Z23">
+        <v>0.6601658965273468</v>
       </c>
     </row>
     <row r="24">
@@ -2245,7 +2310,10 @@
         <v>0.8229340500243738</v>
       </c>
       <c r="Y24">
-        <v>0.4996074675999314</v>
+        <v>0.6145812357572692</v>
+      </c>
+      <c r="Z24">
+        <v>0.5100596283415075</v>
       </c>
     </row>
     <row r="25">
@@ -2320,7 +2388,10 @@
         <v>0.1568873000010577</v>
       </c>
       <c r="Y25">
-        <v>0.4486402887217072</v>
+        <v>0.5996922527986955</v>
+      </c>
+      <c r="Z25">
+        <v>0.4637454851294061</v>
       </c>
     </row>
     <row r="26">
@@ -2395,7 +2466,10 @@
         <v>0.8162800998680531</v>
       </c>
       <c r="Y26">
-        <v>0.6168026054332632</v>
+        <v>0.5801183710685277</v>
+      </c>
+      <c r="Z26">
+        <v>0.6131341819967896</v>
       </c>
     </row>
     <row r="27">
@@ -2476,7 +2550,10 @@
         <v>0.08751634375215032</v>
       </c>
       <c r="Y27">
-        <v>0.20831891336559</v>
+        <v>0.6829831089609784</v>
+      </c>
+      <c r="Z27">
+        <v>0.2514702038742617</v>
       </c>
     </row>
     <row r="28">
@@ -2551,7 +2628,10 @@
         <v>0.04932251807502108</v>
       </c>
       <c r="Y28">
-        <v>0.3500844035870585</v>
+        <v>0.6188409714365701</v>
+      </c>
+      <c r="Z28">
+        <v>0.3769600603720096</v>
       </c>
     </row>
     <row r="29">
@@ -2632,7 +2712,10 @@
         <v>0.3079124135096388</v>
       </c>
       <c r="Y29">
-        <v>0.4169823331983029</v>
+        <v>0.594763872245282</v>
+      </c>
+      <c r="Z29">
+        <v>0.4331442912934828</v>
       </c>
     </row>
     <row r="30">
@@ -2658,7 +2741,7 @@
           <t>B2</t>
         </is>
       </c>
-      <c r="Y30">
+      <c r="Z30">
         <v>0.5842611972053007</v>
       </c>
     </row>
@@ -2740,7 +2823,10 @@
         <v>0.09284481701469087</v>
       </c>
       <c r="Y31">
-        <v>0.359780250203542</v>
+        <v>0.6533281703868384</v>
+      </c>
+      <c r="Z31">
+        <v>0.3864664247656599</v>
       </c>
     </row>
     <row r="32">
@@ -2821,7 +2907,10 @@
         <v>0.1793228053399155</v>
       </c>
       <c r="Y32">
-        <v>0.4077828147115469</v>
+        <v>0.5774938934128605</v>
+      </c>
+      <c r="Z32">
+        <v>0.4232110945934845</v>
       </c>
     </row>
     <row r="33">
@@ -2902,7 +2991,10 @@
         <v>0.4399859346834002</v>
       </c>
       <c r="Y33">
-        <v>0.5766188515057206</v>
+        <v>0.5989790510914346</v>
+      </c>
+      <c r="Z33">
+        <v>0.5786515969226036</v>
       </c>
     </row>
     <row r="34">
@@ -2928,7 +3020,7 @@
           <t>B2</t>
         </is>
       </c>
-      <c r="Y34">
+      <c r="Z34">
         <v>0.7171266917469348</v>
       </c>
     </row>
@@ -3010,7 +3102,10 @@
         <v>0.4377780342244889</v>
       </c>
       <c r="Y35">
-        <v>0.446917026865625</v>
+        <v>0.6415004625970644</v>
+      </c>
+      <c r="Z35">
+        <v>0.4646064301139377</v>
       </c>
     </row>
     <row r="36">
@@ -3091,7 +3186,10 @@
         <v>0.2110482135820394</v>
       </c>
       <c r="Y36">
-        <v>0.2557554071038935</v>
+        <v>0.5975978979229554</v>
+      </c>
+      <c r="Z36">
+        <v>0.2868319971783537</v>
       </c>
     </row>
     <row r="37">
@@ -3172,7 +3270,10 @@
         <v>0.3361594147792935</v>
       </c>
       <c r="Y37">
-        <v>0.4580201117380764</v>
+        <v>0.6409674193251149</v>
+      </c>
+      <c r="Z37">
+        <v>0.4746516851550799</v>
       </c>
     </row>
     <row r="38">
@@ -3253,7 +3354,10 @@
         <v>0.02281253493604877</v>
       </c>
       <c r="Y38">
-        <v>0.3053925628468493</v>
+        <v>0.3878842490321296</v>
+      </c>
+      <c r="Z38">
+        <v>0.3128918070455112</v>
       </c>
     </row>
     <row r="39">
@@ -3334,7 +3438,10 @@
         <v>0.4403286329702006</v>
       </c>
       <c r="Y39">
-        <v>0.4908729722051963</v>
+        <v>0.6126968147045188</v>
+      </c>
+      <c r="Z39">
+        <v>0.501947866977862</v>
       </c>
     </row>
     <row r="40">
@@ -3415,7 +3522,10 @@
         <v>0.2038430837769933</v>
       </c>
       <c r="Y40">
-        <v>0.4656116189614641</v>
+        <v>0.6403530622123499</v>
+      </c>
+      <c r="Z40">
+        <v>0.4814972047115446</v>
       </c>
     </row>
     <row r="41">
@@ -3496,7 +3606,10 @@
         <v>0.3251364505456744</v>
       </c>
       <c r="Y41">
-        <v>0.4729144514351296</v>
+        <v>0.478776788243877</v>
+      </c>
+      <c r="Z41">
+        <v>0.4734473911450157</v>
       </c>
     </row>
     <row r="42">
@@ -3577,7 +3690,10 @@
         <v>0.2229649301928028</v>
       </c>
       <c r="Y42">
-        <v>0.4076412037968983</v>
+        <v>0.661139318763453</v>
+      </c>
+      <c r="Z42">
+        <v>0.430686486975676</v>
       </c>
     </row>
     <row r="43">
@@ -3658,7 +3774,10 @@
         <v>0.1701929791078292</v>
       </c>
       <c r="Y43">
-        <v>0.3872001703284696</v>
+        <v>0.6305161911917418</v>
+      </c>
+      <c r="Z43">
+        <v>0.4093198085887671</v>
       </c>
     </row>
     <row r="44">
@@ -3739,7 +3858,10 @@
         <v>0.5211469907343621</v>
       </c>
       <c r="Y44">
-        <v>0.556435642685269</v>
+        <v>0.596078955458171</v>
+      </c>
+      <c r="Z44">
+        <v>0.5600395802100784</v>
       </c>
     </row>
     <row r="45">
@@ -3820,7 +3942,10 @@
         <v>0.2964707187646027</v>
       </c>
       <c r="Y45">
-        <v>0.516864839583109</v>
+        <v>0.5826263751744765</v>
+      </c>
+      <c r="Z45">
+        <v>0.522843161000506</v>
       </c>
     </row>
     <row r="46">
@@ -3846,7 +3971,7 @@
           <t>B2</t>
         </is>
       </c>
-      <c r="Y46">
+      <c r="Z46">
         <v>0.4608873656744395</v>
       </c>
     </row>
@@ -3928,7 +4053,10 @@
         <v>0.4002046585006649</v>
       </c>
       <c r="Y47">
-        <v>0.3889489598613385</v>
+        <v>0.566614599603148</v>
+      </c>
+      <c r="Z47">
+        <v>0.4051003816560484</v>
       </c>
     </row>
     <row r="48">
@@ -4009,7 +4137,10 @@
         <v>0.05414792544086373</v>
       </c>
       <c r="Y48">
-        <v>0.2708325715906076</v>
+        <v>0.6222562924529285</v>
+      </c>
+      <c r="Z48">
+        <v>0.3027801825780914</v>
       </c>
     </row>
     <row r="49">
@@ -4090,7 +4221,10 @@
         <v>0.07146602998081229</v>
       </c>
       <c r="Y49">
-        <v>0.3926216343545658</v>
+        <v>0.6336020089526978</v>
+      </c>
+      <c r="Z49">
+        <v>0.4145289411362141</v>
       </c>
     </row>
     <row r="50">
@@ -4165,7 +4299,10 @@
         <v>0.3260096735872604</v>
       </c>
       <c r="Y50">
-        <v>0.4278963421486487</v>
+        <v>0.6118374938834623</v>
+      </c>
+      <c r="Z50">
+        <v>0.4462904573221301</v>
       </c>
     </row>
     <row r="51">
@@ -4246,7 +4383,10 @@
         <v>0.4464741142412194</v>
       </c>
       <c r="Y51">
-        <v>0.5121645550459322</v>
+        <v>0.6743730996497096</v>
+      </c>
+      <c r="Z51">
+        <v>0.5269107863735483</v>
       </c>
     </row>
     <row r="52">
@@ -4321,7 +4461,10 @@
         <v>0.2936587098507883</v>
       </c>
       <c r="Y52">
-        <v>0.5295873210441162</v>
+        <v>0.6555409651319281</v>
+      </c>
+      <c r="Z52">
+        <v>0.5421826854528974</v>
       </c>
     </row>
     <row r="53">
@@ -4402,7 +4545,10 @@
         <v>0.2983419634079955</v>
       </c>
       <c r="Y53">
-        <v>0.5353490684424387</v>
+        <v>0.6109316377023839</v>
+      </c>
+      <c r="Z53">
+        <v>0.5422202111024337</v>
       </c>
     </row>
     <row r="54">
@@ -4477,7 +4623,10 @@
         <v>0.1059915160799036</v>
       </c>
       <c r="Y54">
-        <v>0.3712821152128108</v>
+        <v>0.6792937300270564</v>
+      </c>
+      <c r="Z54">
+        <v>0.4020832766942354</v>
       </c>
     </row>
     <row r="55">
@@ -4552,7 +4701,10 @@
         <v>0.6656169545741584</v>
       </c>
       <c r="Y55">
-        <v>0.6181043141130029</v>
+        <v>0.6287366970060058</v>
+      </c>
+      <c r="Z55">
+        <v>0.6191675524023031</v>
       </c>
     </row>
     <row r="56">
@@ -4590,7 +4742,7 @@
           <t>B3</t>
         </is>
       </c>
-      <c r="Y56">
+      <c r="Z56">
         <v>0.4910487102631075</v>
       </c>
     </row>
@@ -4672,7 +4824,10 @@
         <v>0.690163433373723</v>
       </c>
       <c r="Y57">
-        <v>0.5056679200938752</v>
+        <v>0.5714534258359116</v>
+      </c>
+      <c r="Z57">
+        <v>0.5116484206158785</v>
       </c>
     </row>
     <row r="58">
@@ -4753,7 +4908,10 @@
         <v>0.1540676232248591</v>
       </c>
       <c r="Y58">
-        <v>0.2517092453491356</v>
+        <v>0.5255938339302993</v>
+      </c>
+      <c r="Z58">
+        <v>0.2766078443110596</v>
       </c>
     </row>
     <row r="59">
@@ -4828,7 +4986,10 @@
         <v>0.6434225384172394</v>
       </c>
       <c r="Y59">
-        <v>0.5866289095505557</v>
+        <v>0.3947380546202585</v>
+      </c>
+      <c r="Z59">
+        <v>0.567439824057526</v>
       </c>
     </row>
     <row r="60">
@@ -4903,7 +5064,10 @@
         <v>0.495773586390557</v>
       </c>
       <c r="Y60">
-        <v>0.5822460325395084</v>
+        <v>0.598697904392959</v>
+      </c>
+      <c r="Z60">
+        <v>0.5838912197248535</v>
       </c>
     </row>
     <row r="61">
@@ -4941,7 +5105,7 @@
           <t>B3</t>
         </is>
       </c>
-      <c r="Y61">
+      <c r="Z61">
         <v>0.4279256377401202</v>
       </c>
     </row>
@@ -5023,7 +5187,10 @@
         <v>0.2936246343398432</v>
       </c>
       <c r="Y62">
-        <v>0.47488204849401</v>
+        <v>0.545484559726672</v>
+      </c>
+      <c r="Z62">
+        <v>0.4813004586060702</v>
       </c>
     </row>
     <row r="63">
@@ -5104,7 +5271,10 @@
         <v>0.09733272948584863</v>
       </c>
       <c r="Y63">
-        <v>0.316098126511656</v>
+        <v>0.5998123870918999</v>
+      </c>
+      <c r="Z63">
+        <v>0.3418903320189509</v>
       </c>
     </row>
     <row r="64">
@@ -5130,7 +5300,7 @@
           <t>B3</t>
         </is>
       </c>
-      <c r="Y64">
+      <c r="Z64">
         <v>0.6433428248091871</v>
       </c>
     </row>
@@ -5212,7 +5382,10 @@
         <v>0.2836291020695697</v>
       </c>
       <c r="Y65">
-        <v>0.3060619693201871</v>
+        <v>0.6128921960031078</v>
+      </c>
+      <c r="Z65">
+        <v>0.3339556262913617</v>
       </c>
     </row>
     <row r="66">
@@ -5293,7 +5466,10 @@
         <v>0.4160821201627792</v>
       </c>
       <c r="Y66">
-        <v>0.5319674653555926</v>
+        <v>0.6645498719476663</v>
+      </c>
+      <c r="Z66">
+        <v>0.5440204114094175</v>
       </c>
     </row>
     <row r="67">
@@ -5374,7 +5550,10 @@
         <v>0.06049882961512109</v>
       </c>
       <c r="Y67">
-        <v>0.4006257604342729</v>
+        <v>0.625978082019108</v>
+      </c>
+      <c r="Z67">
+        <v>0.4211123351238033</v>
       </c>
     </row>
     <row r="68">
@@ -5455,7 +5634,10 @@
         <v>0.5635426354289883</v>
       </c>
       <c r="Y68">
-        <v>0.6214560440763893</v>
+        <v>0.5562774968814153</v>
+      </c>
+      <c r="Z68">
+        <v>0.6155307216041189</v>
       </c>
     </row>
     <row r="69">
@@ -5536,7 +5718,10 @@
         <v>0.1598195053246524</v>
       </c>
       <c r="Y69">
-        <v>0.4826682089247033</v>
+        <v>0.5618809113988922</v>
+      </c>
+      <c r="Z69">
+        <v>0.4898693636950841</v>
       </c>
     </row>
     <row r="70">
@@ -5617,7 +5802,10 @@
         <v>0.5816221229475144</v>
       </c>
       <c r="Y70">
-        <v>0.6211354961798481</v>
+        <v>0.5497647114252703</v>
+      </c>
+      <c r="Z70">
+        <v>0.614647243020341</v>
       </c>
     </row>
     <row r="71">
@@ -5692,7 +5880,10 @@
         <v>0.4896295946592574</v>
       </c>
       <c r="Y71">
-        <v>0.640460852821539</v>
+        <v>0.4656345146707593</v>
+      </c>
+      <c r="Z71">
+        <v>0.622978219006461</v>
       </c>
     </row>
     <row r="72">
@@ -5773,7 +5964,10 @@
         <v>0.6941109648268283</v>
       </c>
       <c r="Y72">
-        <v>0.534945610669792</v>
+        <v>0.5021810721168496</v>
+      </c>
+      <c r="Z72">
+        <v>0.5319670162558882</v>
       </c>
     </row>
     <row r="73">
@@ -5811,7 +6005,7 @@
       <c r="R73">
         <v>0.04166666666666666</v>
       </c>
-      <c r="Y73">
+      <c r="Z73">
         <v>0.4322771073962995</v>
       </c>
     </row>
@@ -5893,7 +6087,10 @@
         <v>0.5053769041564342</v>
       </c>
       <c r="Y74">
-        <v>0.402177365184554</v>
+        <v>0.5352477992027502</v>
+      </c>
+      <c r="Z74">
+        <v>0.4142746773680264</v>
       </c>
     </row>
     <row r="75">
@@ -5919,7 +6116,7 @@
           <t>B4</t>
         </is>
       </c>
-      <c r="Y75">
+      <c r="Z75">
         <v>0.2265124345922788</v>
       </c>
     </row>
@@ -6001,7 +6198,10 @@
         <v>0.3830767989130323</v>
       </c>
       <c r="Y76">
-        <v>0.4456345227437299</v>
+        <v>0.583878886681464</v>
+      </c>
+      <c r="Z76">
+        <v>0.4582021921926148</v>
       </c>
     </row>
     <row r="77">
@@ -6082,7 +6282,10 @@
         <v>0.1210445942521303</v>
       </c>
       <c r="Y77">
-        <v>0.3387833943094085</v>
+        <v>0.5620731682909529</v>
+      </c>
+      <c r="Z77">
+        <v>0.3590824646713671</v>
       </c>
     </row>
     <row r="78">
@@ -6163,7 +6366,10 @@
         <v>0.4048218374954839</v>
       </c>
       <c r="Y78">
-        <v>0.3798978984540057</v>
+        <v>0.5000679002635895</v>
+      </c>
+      <c r="Z78">
+        <v>0.3908224440730588</v>
       </c>
     </row>
     <row r="79">
@@ -6244,7 +6450,10 @@
         <v>0.05017995772283684</v>
       </c>
       <c r="Y79">
-        <v>0.3567450582960783</v>
+        <v>0.6452137412134239</v>
+      </c>
+      <c r="Z79">
+        <v>0.382969484015837</v>
       </c>
     </row>
     <row r="80">
@@ -6325,7 +6534,10 @@
         <v>0.4835470190802443</v>
       </c>
       <c r="Y80">
-        <v>0.5555998861154733</v>
+        <v>0.6808911868735297</v>
+      </c>
+      <c r="Z80">
+        <v>0.5669900043662056</v>
       </c>
     </row>
     <row r="81">
@@ -6406,7 +6618,10 @@
         <v>0.2792188433975049</v>
       </c>
       <c r="Y81">
-        <v>0.4175497870507556</v>
+        <v>0.5868142752565406</v>
+      </c>
+      <c r="Z81">
+        <v>0.4329374677967361</v>
       </c>
     </row>
     <row r="82">
@@ -6481,7 +6696,10 @@
         <v>0</v>
       </c>
       <c r="Y82">
-        <v>0.2780797531353649</v>
+        <v>0</v>
+      </c>
+      <c r="Z82">
+        <v>0.2502717778218284</v>
       </c>
     </row>
     <row r="83">
@@ -6562,7 +6780,10 @@
         <v>0.03528014153309827</v>
       </c>
       <c r="Y83">
-        <v>0.2835591699415808</v>
+        <v>0.6119871397440688</v>
+      </c>
+      <c r="Z83">
+        <v>0.3134162581054433</v>
       </c>
     </row>
     <row r="84">
@@ -6643,7 +6864,10 @@
         <v>0.1057631609809458</v>
       </c>
       <c r="Y84">
-        <v>0.3457450334332727</v>
+        <v>0.5759859014309127</v>
+      </c>
+      <c r="Z84">
+        <v>0.3666760214330582</v>
       </c>
     </row>
     <row r="85">
@@ -6724,7 +6948,10 @@
         <v>0.03251143917425656</v>
       </c>
       <c r="Y85">
-        <v>0.2903700466607096</v>
+        <v>0.6060350084993592</v>
+      </c>
+      <c r="Z85">
+        <v>0.3190668613733141</v>
       </c>
     </row>
     <row r="86">
@@ -6805,7 +7032,10 @@
         <v>0.3807606773129513</v>
       </c>
       <c r="Y86">
-        <v>0.4045659090904647</v>
+        <v>0.5628408309384075</v>
+      </c>
+      <c r="Z86">
+        <v>0.4189545383493686</v>
       </c>
     </row>
     <row r="87">
@@ -6886,7 +7116,10 @@
         <v>0.1525607253602217</v>
       </c>
       <c r="Y87">
-        <v>0.378670224648138</v>
+        <v>0.6431040127003597</v>
+      </c>
+      <c r="Z87">
+        <v>0.4027096599256128</v>
       </c>
     </row>
     <row r="88">
@@ -6967,7 +7200,10 @@
         <v>0.1928977467183089</v>
       </c>
       <c r="Y88">
-        <v>0.5503871547511705</v>
+        <v>0.797701059445899</v>
+      </c>
+      <c r="Z88">
+        <v>0.5728702369961458</v>
       </c>
     </row>
     <row r="89">
@@ -6993,7 +7229,7 @@
           <t>B4</t>
         </is>
       </c>
-      <c r="Y89">
+      <c r="Z89">
         <v>0.6077307128950182</v>
       </c>
     </row>
@@ -7075,7 +7311,10 @@
         <v>0.672291736389361</v>
       </c>
       <c r="Y90">
-        <v>0.5690783438450639</v>
+        <v>0.5671346776639313</v>
+      </c>
+      <c r="Z90">
+        <v>0.5689016469195064</v>
       </c>
     </row>
     <row r="91">
@@ -7156,7 +7395,10 @@
         <v>0.6078099058219762</v>
       </c>
       <c r="Y91">
-        <v>0.398717464344758</v>
+        <v>0.5816529148067182</v>
+      </c>
+      <c r="Z91">
+        <v>0.4153479598412998</v>
       </c>
     </row>
     <row r="92">
@@ -7237,7 +7479,10 @@
         <v>1</v>
       </c>
       <c r="Y92">
-        <v>0.5592696526951614</v>
+        <v>0.6414502173738073</v>
+      </c>
+      <c r="Z92">
+        <v>0.5667406131204928</v>
       </c>
     </row>
   </sheetData>

--- a/Data Analysis/1_Data/ecological_multifunctionality.xlsx
+++ b/Data Analysis/1_Data/ecological_multifunctionality.xlsx
@@ -529,7 +529,7 @@
         <v>0.2332183852201103</v>
       </c>
       <c r="N2">
-        <v>11.83333333333333</v>
+        <v>11.55555555555556</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -564,10 +564,10 @@
         <v>0.3095837336681162</v>
       </c>
       <c r="Y2">
-        <v>0.5329067273494283</v>
+        <v>0.257956957205875</v>
       </c>
       <c r="Z2">
-        <v>0.4618388067871982</v>
+        <v>0.4368433731377843</v>
       </c>
     </row>
     <row r="3">
@@ -613,7 +613,7 @@
         <v>0.1979468035573365</v>
       </c>
       <c r="N3">
-        <v>5.728813559322034</v>
+        <v>5.685185185185185</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -648,10 +648,10 @@
         <v>0.4538193710537792</v>
       </c>
       <c r="Y3">
-        <v>0.5349234617545326</v>
+        <v>0.2532498541851478</v>
       </c>
       <c r="Z3">
-        <v>0.4632870972633785</v>
+        <v>0.4376804056661617</v>
       </c>
     </row>
     <row r="4">
@@ -697,7 +697,7 @@
         <v>0.1129919915718463</v>
       </c>
       <c r="N4">
-        <v>6.186440677966102</v>
+        <v>6.092592592592593</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -732,10 +732,10 @@
         <v>0.1763512235540355</v>
       </c>
       <c r="Y4">
-        <v>0.3687207077501685</v>
+        <v>0.1702297501409914</v>
       </c>
       <c r="Z4">
-        <v>0.3173885800630833</v>
+        <v>0.2993439475531582</v>
       </c>
     </row>
     <row r="5">
@@ -781,7 +781,7 @@
         <v>0.2032689369444313</v>
       </c>
       <c r="N5">
-        <v>3.35</v>
+        <v>3.296296296296296</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -816,10 +816,10 @@
         <v>0.2901661958320036</v>
       </c>
       <c r="Y5">
-        <v>0.9078847592894224</v>
+        <v>0.160709535150152</v>
       </c>
       <c r="Z5">
-        <v>0.4245317213268133</v>
+        <v>0.3566067009505159</v>
       </c>
     </row>
     <row r="6">
@@ -865,7 +865,7 @@
         <v>0.1579602877027958</v>
       </c>
       <c r="N6">
-        <v>1.864406779661017</v>
+        <v>1.851851851851852</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -900,10 +900,10 @@
         <v>0.08272192028282797</v>
       </c>
       <c r="Y6">
-        <v>0.8102154638078963</v>
+        <v>0.1353865041854264</v>
       </c>
       <c r="Z6">
-        <v>0.351082505019349</v>
+        <v>0.2897344177809427</v>
       </c>
     </row>
     <row r="7">
@@ -949,7 +949,7 @@
         <v>0.1998111677049684</v>
       </c>
       <c r="N7">
-        <v>12.89830508474576</v>
+        <v>12.85185185185185</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -984,10 +984,10 @@
         <v>0.6061769173633896</v>
       </c>
       <c r="Y7">
-        <v>0.6360493681792212</v>
+        <v>0.2621910960408731</v>
       </c>
       <c r="Z7">
-        <v>0.5110314327161642</v>
+        <v>0.4770443170672235</v>
       </c>
     </row>
     <row r="8">
@@ -1068,10 +1068,10 @@
         <v>0.1482407307513151</v>
       </c>
       <c r="Y8">
-        <v>0.577888345759738</v>
+        <v>0.1548245950020741</v>
       </c>
       <c r="Z8">
-        <v>0.3362326473521699</v>
+        <v>0.2977723063742004</v>
       </c>
     </row>
     <row r="9">
@@ -1152,10 +1152,10 @@
         <v>0.3666128102901184</v>
       </c>
       <c r="Y9">
-        <v>0.5269623043811215</v>
+        <v>0.1746890842429457</v>
       </c>
       <c r="Z9">
-        <v>0.3026724844327546</v>
+        <v>0.270647646238375</v>
       </c>
     </row>
     <row r="10">
@@ -1189,7 +1189,7 @@
         <v>0.2445414428859278</v>
       </c>
       <c r="N10">
-        <v>0.9523809523809523</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>0.3786227905114034</v>
       </c>
       <c r="N12">
-        <v>11.03333333333333</v>
+        <v>10.7962962962963</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1308,10 +1308,10 @@
         <v>0.6466931295555873</v>
       </c>
       <c r="Y12">
-        <v>0.6286899729640903</v>
+        <v>0.2518041922392355</v>
       </c>
       <c r="Z12">
-        <v>0.5226343538850097</v>
+        <v>0.4883720101827501</v>
       </c>
     </row>
     <row r="13">
@@ -1357,7 +1357,7 @@
         <v>0.1806721062381619</v>
       </c>
       <c r="N13">
-        <v>5.3</v>
+        <v>5.166666666666667</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -1392,10 +1392,10 @@
         <v>0.3387981378390733</v>
       </c>
       <c r="Y13">
-        <v>0.5786033147410633</v>
+        <v>0.1605393662912078</v>
       </c>
       <c r="Z13">
-        <v>0.4185904873886526</v>
+        <v>0.3805846738932112</v>
       </c>
     </row>
     <row r="14">
@@ -1441,7 +1441,7 @@
         <v>0.1310002200723593</v>
       </c>
       <c r="N14">
-        <v>3.2</v>
+        <v>3.111111111111111</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -1476,10 +1476,10 @@
         <v>0.3231240314170564</v>
       </c>
       <c r="Y14">
-        <v>0.5881104701166693</v>
+        <v>0.1334079099935809</v>
       </c>
       <c r="Z14">
-        <v>0.4029763797043901</v>
+        <v>0.3616397833295639</v>
       </c>
     </row>
     <row r="15">
@@ -1525,7 +1525,7 @@
         <v>0.1914203567728611</v>
       </c>
       <c r="N15">
-        <v>6.559322033898305</v>
+        <v>6.555555555555555</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -1560,10 +1560,10 @@
         <v>0.3613628349666473</v>
       </c>
       <c r="Y15">
-        <v>0.3967074045852518</v>
+        <v>0.2016718471293336</v>
       </c>
       <c r="Z15">
-        <v>0.5093109506553865</v>
+        <v>0.4915804454321211</v>
       </c>
     </row>
     <row r="16">
@@ -1609,7 +1609,7 @@
         <v>0.2317978159571884</v>
       </c>
       <c r="N16">
-        <v>0.95</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -1644,10 +1644,10 @@
         <v>0.002517386384649483</v>
       </c>
       <c r="Y16">
-        <v>1</v>
+        <v>0.1161380623010923</v>
       </c>
       <c r="Z16">
-        <v>0.3653737571351967</v>
+        <v>0.2850226718898414</v>
       </c>
     </row>
     <row r="17">
@@ -1693,7 +1693,7 @@
         <v>0.2350415363419744</v>
       </c>
       <c r="N17">
-        <v>1.983050847457627</v>
+        <v>1.981481481481481</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -1728,10 +1728,10 @@
         <v>0.1189272518667831</v>
       </c>
       <c r="Y17">
-        <v>0.5991571254558291</v>
+        <v>0.1900188806640827</v>
       </c>
       <c r="Z17">
-        <v>0.374877304425511</v>
+        <v>0.3376829185353523</v>
       </c>
     </row>
     <row r="18">
@@ -1812,10 +1812,10 @@
         <v>0.2433418210541713</v>
       </c>
       <c r="Y18">
-        <v>0.615833348345295</v>
+        <v>0.1642039281024077</v>
       </c>
       <c r="Z18">
-        <v>0.3945892420843024</v>
+        <v>0.3535320220622217</v>
       </c>
     </row>
     <row r="19">
@@ -1896,10 +1896,10 @@
         <v>0.1278675422350279</v>
       </c>
       <c r="Y19">
-        <v>0.682795362548585</v>
+        <v>0.1678917168888577</v>
       </c>
       <c r="Z19">
-        <v>0.2422762459711337</v>
+        <v>0.1954668236384312</v>
       </c>
     </row>
     <row r="20">
@@ -1945,7 +1945,7 @@
         <v>0.2479182825858949</v>
       </c>
       <c r="N20">
-        <v>3.559322033898305</v>
+        <v>3.648148148148148</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -1980,10 +1980,10 @@
         <v>0.3653087018938461</v>
       </c>
       <c r="Y20">
-        <v>0.5691113227775285</v>
+        <v>0.1821903962478089</v>
       </c>
       <c r="Z20">
-        <v>0.432062504509827</v>
+        <v>0.3968878748253071</v>
       </c>
     </row>
     <row r="21">
@@ -2029,7 +2029,7 @@
         <v>0.3281446004807311</v>
       </c>
       <c r="N21">
-        <v>12.15254237288136</v>
+        <v>11.92592592592593</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -2064,10 +2064,10 @@
         <v>0.6147991208738268</v>
       </c>
       <c r="Y21">
-        <v>0.4762697184401813</v>
+        <v>0.2392937685081673</v>
       </c>
       <c r="Z21">
-        <v>0.5824983751206743</v>
+        <v>0.5609551069450366</v>
       </c>
     </row>
     <row r="22">
@@ -2113,7 +2113,7 @@
         <v>0.2356352694512683</v>
       </c>
       <c r="N22">
-        <v>3.694915254237288</v>
+        <v>3.759259259259259</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -2148,10 +2148,10 @@
         <v>0.1830304771246527</v>
       </c>
       <c r="Y22">
-        <v>0.6169762430128304</v>
+        <v>0.1735674814922469</v>
       </c>
       <c r="Z22">
-        <v>0.4268032967758087</v>
+        <v>0.3864934093648466</v>
       </c>
     </row>
     <row r="23">
@@ -2197,7 +2197,7 @@
         <v>0.4219429777762483</v>
       </c>
       <c r="N23">
-        <v>33.2280701754386</v>
+        <v>32.85185185185185</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         <v>0.8143839706609451</v>
       </c>
       <c r="Y23">
-        <v>0.5893605834780353</v>
+        <v>0.2777982644896537</v>
       </c>
       <c r="Z23">
-        <v>0.6601658965273468</v>
+        <v>0.6290096646285086</v>
       </c>
     </row>
     <row r="24">
@@ -2275,7 +2275,7 @@
         <v>0.2834391654399762</v>
       </c>
       <c r="N24">
-        <v>3.6</v>
+        <v>3.555555555555555</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -2310,10 +2310,10 @@
         <v>0.8229340500243738</v>
       </c>
       <c r="Y24">
-        <v>0.6145812357572692</v>
+        <v>0.2544337843007431</v>
       </c>
       <c r="Z24">
-        <v>0.5100596283415075</v>
+        <v>0.4773189509363688</v>
       </c>
     </row>
     <row r="25">
@@ -2359,7 +2359,7 @@
         <v>0.2025687019258525</v>
       </c>
       <c r="N25">
-        <v>1.983050847457627</v>
+        <v>1.981481481481481</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -2388,10 +2388,10 @@
         <v>0.1568873000010577</v>
       </c>
       <c r="Y25">
-        <v>0.5996922527986955</v>
+        <v>0.2269023679670693</v>
       </c>
       <c r="Z25">
-        <v>0.4637454851294061</v>
+        <v>0.4264664966462434</v>
       </c>
     </row>
     <row r="26">
@@ -2437,7 +2437,7 @@
         <v>0.3144544344018968</v>
       </c>
       <c r="N26">
-        <v>33.47457627118644</v>
+        <v>34.27777777777778</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -2466,10 +2466,10 @@
         <v>0.8162800998680531</v>
       </c>
       <c r="Y26">
-        <v>0.5801183710685277</v>
+        <v>0.2625608208348425</v>
       </c>
       <c r="Z26">
-        <v>0.6131341819967896</v>
+        <v>0.5813784269734211</v>
       </c>
     </row>
     <row r="27">
@@ -2550,10 +2550,10 @@
         <v>0.08751634375215032</v>
       </c>
       <c r="Y27">
-        <v>0.6829831089609784</v>
+        <v>0.06739172595307573</v>
       </c>
       <c r="Z27">
-        <v>0.2514702038742617</v>
+        <v>0.1955073508735433</v>
       </c>
     </row>
     <row r="28">
@@ -2599,7 +2599,7 @@
         <v>0.2641044625852236</v>
       </c>
       <c r="N28">
-        <v>0.9833333333333333</v>
+        <v>0.9814814814814815</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -2628,10 +2628,10 @@
         <v>0.04932251807502108</v>
       </c>
       <c r="Y28">
-        <v>0.6188409714365701</v>
+        <v>0.156364379748628</v>
       </c>
       <c r="Z28">
-        <v>0.3769600603720096</v>
+        <v>0.3307124012032154</v>
       </c>
     </row>
     <row r="29">
@@ -2677,7 +2677,7 @@
         <v>0.4014424139285164</v>
       </c>
       <c r="N29">
-        <v>3.677966101694915</v>
+        <v>3.685185185185185</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -2712,10 +2712,10 @@
         <v>0.3079124135096388</v>
       </c>
       <c r="Y29">
-        <v>0.594763872245282</v>
+        <v>0.2291827418108969</v>
       </c>
       <c r="Z29">
-        <v>0.4331442912934828</v>
+        <v>0.3999096430721751</v>
       </c>
     </row>
     <row r="30">
@@ -2788,7 +2788,7 @@
         <v>0.4055537567937125</v>
       </c>
       <c r="N31">
-        <v>1.627118644067797</v>
+        <v>1.62962962962963</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
@@ -2823,10 +2823,10 @@
         <v>0.09284481701469087</v>
       </c>
       <c r="Y31">
-        <v>0.6533281703868384</v>
+        <v>0.1853852287088332</v>
       </c>
       <c r="Z31">
-        <v>0.3864664247656599</v>
+        <v>0.3439261573403867</v>
       </c>
     </row>
     <row r="32">
@@ -2872,7 +2872,7 @@
         <v>0.4444624371802761</v>
       </c>
       <c r="N32">
-        <v>3.933333333333333</v>
+        <v>3.925925925925926</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -2907,10 +2907,10 @@
         <v>0.1793228053399155</v>
       </c>
       <c r="Y32">
-        <v>0.5774938934128605</v>
+        <v>0.2516616844716736</v>
       </c>
       <c r="Z32">
-        <v>0.4232110945934845</v>
+        <v>0.3935899846897403</v>
       </c>
     </row>
     <row r="33">
@@ -2956,7 +2956,7 @@
         <v>0.5343546868339075</v>
       </c>
       <c r="N33">
-        <v>12.86440677966102</v>
+        <v>12.72222222222222</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -2991,10 +2991,10 @@
         <v>0.4399859346834002</v>
       </c>
       <c r="Y33">
-        <v>0.5989790510914346</v>
+        <v>0.2752522366203629</v>
       </c>
       <c r="Z33">
-        <v>0.5786515969226036</v>
+        <v>0.5492218865161426</v>
       </c>
     </row>
     <row r="34">
@@ -3067,7 +3067,7 @@
         <v>0.2914470372377352</v>
       </c>
       <c r="N35">
-        <v>6.135593220338983</v>
+        <v>6.074074074074074</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -3102,10 +3102,10 @@
         <v>0.4377780342244889</v>
       </c>
       <c r="Y35">
-        <v>0.6415004625970644</v>
+        <v>0.2632556384061693</v>
       </c>
       <c r="Z35">
-        <v>0.4646064301139377</v>
+        <v>0.4302205370056745</v>
       </c>
     </row>
     <row r="36">
@@ -3186,10 +3186,10 @@
         <v>0.2110482135820394</v>
       </c>
       <c r="Y36">
-        <v>0.5975978979229554</v>
+        <v>0.2320791337767583</v>
       </c>
       <c r="Z36">
-        <v>0.2868319971783537</v>
+        <v>0.2536030186196085</v>
       </c>
     </row>
     <row r="37">
@@ -3235,7 +3235,7 @@
         <v>0.3092183919783377</v>
       </c>
       <c r="N37">
-        <v>6</v>
+        <v>6.037037037037037</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -3270,10 +3270,10 @@
         <v>0.3361594147792935</v>
       </c>
       <c r="Y37">
-        <v>0.6409674193251149</v>
+        <v>0.2348699485863942</v>
       </c>
       <c r="Z37">
-        <v>0.4746516851550799</v>
+        <v>0.4377337332697417</v>
       </c>
     </row>
     <row r="38">
@@ -3319,7 +3319,7 @@
         <v>0.2549584130165277</v>
       </c>
       <c r="N38">
-        <v>0.7333333333333333</v>
+        <v>0.7037037037037037</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -3354,10 +3354,10 @@
         <v>0.02281253493604877</v>
       </c>
       <c r="Y38">
-        <v>0.3878842490321296</v>
+        <v>0.9745408842539789</v>
       </c>
       <c r="Z38">
-        <v>0.3128918070455112</v>
+        <v>0.3662242284293157</v>
       </c>
     </row>
     <row r="39">
@@ -3403,7 +3403,7 @@
         <v>0.432068614440138</v>
       </c>
       <c r="N39">
-        <v>3.610169491525424</v>
+        <v>3.611111111111111</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -3438,10 +3438,10 @@
         <v>0.4403286329702006</v>
       </c>
       <c r="Y39">
-        <v>0.6126968147045188</v>
+        <v>0.2447513819859251</v>
       </c>
       <c r="Z39">
-        <v>0.501947866977862</v>
+        <v>0.4684982821852625</v>
       </c>
     </row>
     <row r="40">
@@ -3487,7 +3487,7 @@
         <v>0.3471684398530923</v>
       </c>
       <c r="N40">
-        <v>6.220338983050848</v>
+        <v>6.25925925925926</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
@@ -3522,10 +3522,10 @@
         <v>0.2038430837769933</v>
       </c>
       <c r="Y40">
-        <v>0.6403530622123499</v>
+        <v>0.2232025060676819</v>
       </c>
       <c r="Z40">
-        <v>0.4814972047115446</v>
+        <v>0.4435744268802112</v>
       </c>
     </row>
     <row r="41">
@@ -3571,7 +3571,7 @@
         <v>0.4237533233689614</v>
       </c>
       <c r="N41">
-        <v>11.2</v>
+        <v>11.22222222222222</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
@@ -3606,10 +3606,10 @@
         <v>0.3251364505456744</v>
       </c>
       <c r="Y41">
-        <v>0.478776788243877</v>
+        <v>0.2245429766960785</v>
       </c>
       <c r="Z41">
-        <v>0.4734473911450157</v>
+        <v>0.4503352264588522</v>
       </c>
     </row>
     <row r="42">
@@ -3690,10 +3690,10 @@
         <v>0.2229649301928028</v>
       </c>
       <c r="Y42">
-        <v>0.661139318763453</v>
+        <v>0.1930623898842926</v>
       </c>
       <c r="Z42">
-        <v>0.430686486975676</v>
+        <v>0.3881340388957524</v>
       </c>
     </row>
     <row r="43">
@@ -3739,7 +3739,7 @@
         <v>0.4268960916088172</v>
       </c>
       <c r="N43">
-        <v>1.88135593220339</v>
+        <v>1.87037037037037</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -3774,10 +3774,10 @@
         <v>0.1701929791078292</v>
       </c>
       <c r="Y43">
-        <v>0.6305161911917418</v>
+        <v>0.230276263816248</v>
       </c>
       <c r="Z43">
-        <v>0.4093198085887671</v>
+        <v>0.3729343606455404</v>
       </c>
     </row>
     <row r="44">
@@ -3823,7 +3823,7 @@
         <v>0.4014645885000253</v>
       </c>
       <c r="N44">
-        <v>6.915254237288136</v>
+        <v>6.87037037037037</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -3858,10 +3858,10 @@
         <v>0.5211469907343621</v>
       </c>
       <c r="Y44">
-        <v>0.596078955458171</v>
+        <v>0.2749147008311783</v>
       </c>
       <c r="Z44">
-        <v>0.5600395802100784</v>
+        <v>0.5308428297894426</v>
       </c>
     </row>
     <row r="45">
@@ -3907,7 +3907,7 @@
         <v>0.507540321947799</v>
       </c>
       <c r="N45">
-        <v>11.22033898305085</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -3942,10 +3942,10 @@
         <v>0.2964707187646027</v>
       </c>
       <c r="Y45">
-        <v>0.5826263751744765</v>
+        <v>0.2671520248835246</v>
       </c>
       <c r="Z45">
-        <v>0.522843161000506</v>
+        <v>0.4941636746104195</v>
       </c>
     </row>
     <row r="46">
@@ -4053,10 +4053,10 @@
         <v>0.4002046585006649</v>
       </c>
       <c r="Y47">
-        <v>0.566614599603148</v>
+        <v>0.1459900740925717</v>
       </c>
       <c r="Z47">
-        <v>0.4051003816560484</v>
+        <v>0.3668617884278143</v>
       </c>
     </row>
     <row r="48">
@@ -4102,7 +4102,7 @@
         <v>0.1999701267073845</v>
       </c>
       <c r="N48">
-        <v>1.932203389830508</v>
+        <v>1.925925925925926</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -4137,10 +4137,10 @@
         <v>0.05414792544086373</v>
       </c>
       <c r="Y48">
-        <v>0.6222562924529285</v>
+        <v>0.1492307420428639</v>
       </c>
       <c r="Z48">
-        <v>0.3027801825780914</v>
+        <v>0.25977785981354</v>
       </c>
     </row>
     <row r="49">
@@ -4186,7 +4186,7 @@
         <v>0.192140448094476</v>
       </c>
       <c r="N49">
-        <v>3.491525423728814</v>
+        <v>3.444444444444445</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -4221,10 +4221,10 @@
         <v>0.07146602998081229</v>
       </c>
       <c r="Y49">
-        <v>0.6336020089526978</v>
+        <v>0.1486362155202371</v>
       </c>
       <c r="Z49">
-        <v>0.4145289411362141</v>
+        <v>0.3704411417332632</v>
       </c>
     </row>
     <row r="50">
@@ -4270,7 +4270,7 @@
         <v>0.2109633788959009</v>
       </c>
       <c r="N50">
-        <v>6.35593220338983</v>
+        <v>6.333333333333333</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -4299,10 +4299,10 @@
         <v>0.3260096735872604</v>
       </c>
       <c r="Y50">
-        <v>0.6118374938834623</v>
+        <v>0.2100108886364534</v>
       </c>
       <c r="Z50">
-        <v>0.4462904573221301</v>
+        <v>0.4061077967974292</v>
       </c>
     </row>
     <row r="51">
@@ -4348,7 +4348,7 @@
         <v>0.3685583696882025</v>
       </c>
       <c r="N51">
-        <v>5.491525423728813</v>
+        <v>5.333333333333333</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -4383,10 +4383,10 @@
         <v>0.4464741142412194</v>
       </c>
       <c r="Y51">
-        <v>0.6743730996497096</v>
+        <v>0.2478859201476175</v>
       </c>
       <c r="Z51">
-        <v>0.5269107863735483</v>
+        <v>0.4881392246006308</v>
       </c>
     </row>
     <row r="52">
@@ -4461,10 +4461,10 @@
         <v>0.2936587098507883</v>
       </c>
       <c r="Y52">
-        <v>0.6555409651319281</v>
+        <v>0.1859714351434707</v>
       </c>
       <c r="Z52">
-        <v>0.5421826854528974</v>
+        <v>0.4952257324540517</v>
       </c>
     </row>
     <row r="53">
@@ -4510,7 +4510,7 @@
         <v>0.3743887610358567</v>
       </c>
       <c r="N53">
-        <v>6.203389830508475</v>
+        <v>6.074074074074074</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -4545,10 +4545,10 @@
         <v>0.2983419634079955</v>
       </c>
       <c r="Y53">
-        <v>0.6109316377023839</v>
+        <v>0.2463241435986678</v>
       </c>
       <c r="Z53">
-        <v>0.5422202111024337</v>
+        <v>0.5090740752748231</v>
       </c>
     </row>
     <row r="54">
@@ -4594,7 +4594,7 @@
         <v>0.3289567588062484</v>
       </c>
       <c r="N54">
-        <v>1.864406779661017</v>
+        <v>1.851851851851852</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -4623,10 +4623,10 @@
         <v>0.1059915160799036</v>
       </c>
       <c r="Y54">
-        <v>0.6792937300270564</v>
+        <v>0.08767184358108708</v>
       </c>
       <c r="Z54">
-        <v>0.4020832766942354</v>
+        <v>0.3429210880496385</v>
       </c>
     </row>
     <row r="55">
@@ -4672,7 +4672,7 @@
         <v>0.4761895715214939</v>
       </c>
       <c r="N55">
-        <v>11.5</v>
+        <v>11.37037037037037</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -4701,10 +4701,10 @@
         <v>0.6656169545741584</v>
       </c>
       <c r="Y55">
-        <v>0.6287366970060058</v>
+        <v>0.2783918632235105</v>
       </c>
       <c r="Z55">
-        <v>0.6191675524023031</v>
+        <v>0.5841330690240537</v>
       </c>
     </row>
     <row r="56">
@@ -4789,7 +4789,7 @@
         <v>0.4500093268269618</v>
       </c>
       <c r="N57">
-        <v>3.254237288135593</v>
+        <v>3.185185185185185</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -4824,10 +4824,10 @@
         <v>0.690163433373723</v>
       </c>
       <c r="Y57">
-        <v>0.5714534258359116</v>
+        <v>0.2972274781089727</v>
       </c>
       <c r="Z57">
-        <v>0.5116484206158785</v>
+        <v>0.4867187890043385</v>
       </c>
     </row>
     <row r="58">
@@ -4908,10 +4908,10 @@
         <v>0.1540676232248591</v>
       </c>
       <c r="Y58">
-        <v>0.5255938339302993</v>
+        <v>0.2179525028826017</v>
       </c>
       <c r="Z58">
-        <v>0.2766078443110596</v>
+        <v>0.2486404505794507</v>
       </c>
     </row>
     <row r="59">
@@ -4957,7 +4957,7 @@
         <v>0.4121481639481523</v>
       </c>
       <c r="N59">
-        <v>3.033898305084746</v>
+        <v>3.018518518518519</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -4986,10 +4986,10 @@
         <v>0.6434225384172394</v>
       </c>
       <c r="Y59">
-        <v>0.3947380546202585</v>
+        <v>1</v>
       </c>
       <c r="Z59">
-        <v>0.567439824057526</v>
+        <v>0.6279660185955002</v>
       </c>
     </row>
     <row r="60">
@@ -5035,7 +5035,7 @@
         <v>0.3547916148667022</v>
       </c>
       <c r="N60">
-        <v>33.78947368421053</v>
+        <v>33.22222222222222</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -5064,10 +5064,10 @@
         <v>0.495773586390557</v>
       </c>
       <c r="Y60">
-        <v>0.598697904392959</v>
+        <v>0.2572970892523003</v>
       </c>
       <c r="Z60">
-        <v>0.5838912197248535</v>
+        <v>0.5497511382107876</v>
       </c>
     </row>
     <row r="61">
@@ -5152,7 +5152,7 @@
         <v>0.2980159748942495</v>
       </c>
       <c r="N62">
-        <v>10.33898305084746</v>
+        <v>10.38888888888889</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -5187,10 +5187,10 @@
         <v>0.2936246343398432</v>
       </c>
       <c r="Y62">
-        <v>0.545484559726672</v>
+        <v>0.1889170238053269</v>
       </c>
       <c r="Z62">
-        <v>0.4813004586060702</v>
+        <v>0.4488852280677661</v>
       </c>
     </row>
     <row r="63">
@@ -5271,10 +5271,10 @@
         <v>0.09733272948584863</v>
       </c>
       <c r="Y63">
-        <v>0.5998123870918999</v>
+        <v>0.08300196495180187</v>
       </c>
       <c r="Z63">
-        <v>0.3418903320189509</v>
+        <v>0.294907566369851</v>
       </c>
     </row>
     <row r="64">
@@ -5347,7 +5347,7 @@
         <v>0.3307164154038575</v>
       </c>
       <c r="N65">
-        <v>1.983050847457627</v>
+        <v>1.981481481481481</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
@@ -5382,10 +5382,10 @@
         <v>0.2836291020695697</v>
       </c>
       <c r="Y65">
-        <v>0.6128921960031078</v>
+        <v>0.1979732350129783</v>
       </c>
       <c r="Z65">
-        <v>0.3339556262913617</v>
+        <v>0.2962357207468044</v>
       </c>
     </row>
     <row r="66">
@@ -5431,7 +5431,7 @@
         <v>0.3406923694318202</v>
       </c>
       <c r="N66">
-        <v>5.186440677966102</v>
+        <v>5.166666666666667</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
@@ -5466,10 +5466,10 @@
         <v>0.4160821201627792</v>
       </c>
       <c r="Y66">
-        <v>0.6645498719476663</v>
+        <v>0.2232137599698851</v>
       </c>
       <c r="Z66">
-        <v>0.5440204114094175</v>
+        <v>0.5038989466841646</v>
       </c>
     </row>
     <row r="67">
@@ -5515,7 +5515,7 @@
         <v>0.3434413825562257</v>
       </c>
       <c r="N67">
-        <v>1.983050847457627</v>
+        <v>1.981481481481481</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
@@ -5550,10 +5550,10 @@
         <v>0.06049882961512109</v>
       </c>
       <c r="Y67">
-        <v>0.625978082019108</v>
+        <v>0.1626101452000377</v>
       </c>
       <c r="Z67">
-        <v>0.4211123351238033</v>
+        <v>0.3789879772311606</v>
       </c>
     </row>
     <row r="68">
@@ -5599,7 +5599,7 @@
         <v>0.4926274824244748</v>
       </c>
       <c r="N68">
-        <v>12.3</v>
+        <v>12.18518518518519</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
@@ -5634,10 +5634,10 @@
         <v>0.5635426354289883</v>
       </c>
       <c r="Y68">
-        <v>0.5562774968814153</v>
+        <v>0.2786914248453622</v>
       </c>
       <c r="Z68">
-        <v>0.6155307216041189</v>
+        <v>0.5902956241462959</v>
       </c>
     </row>
     <row r="69">
@@ -5683,7 +5683,7 @@
         <v>0.4843436901086682</v>
       </c>
       <c r="N69">
-        <v>3.416666666666667</v>
+        <v>3.425925925925926</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
@@ -5718,10 +5718,10 @@
         <v>0.1598195053246524</v>
       </c>
       <c r="Y69">
-        <v>0.5618809113988922</v>
+        <v>0.2751526068373289</v>
       </c>
       <c r="Z69">
-        <v>0.4898693636950841</v>
+        <v>0.4638031541894874</v>
       </c>
     </row>
     <row r="70">
@@ -5767,7 +5767,7 @@
         <v>0.6710005388445577</v>
       </c>
       <c r="N70">
-        <v>11.28813559322034</v>
+        <v>11.14814814814815</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
@@ -5802,10 +5802,10 @@
         <v>0.5816221229475144</v>
       </c>
       <c r="Y70">
-        <v>0.5497647114252703</v>
+        <v>0.2881704189419155</v>
       </c>
       <c r="Z70">
-        <v>0.614647243020341</v>
+        <v>0.5908659437036724</v>
       </c>
     </row>
     <row r="71">
@@ -5851,7 +5851,7 @@
         <v>0.3941895822219333</v>
       </c>
       <c r="N71">
-        <v>34.94915254237288</v>
+        <v>34.55555555555556</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
@@ -5880,10 +5880,10 @@
         <v>0.4896295946592574</v>
       </c>
       <c r="Y71">
-        <v>0.4656345146707593</v>
+        <v>0.3537062882326431</v>
       </c>
       <c r="Z71">
-        <v>0.622978219006461</v>
+        <v>0.6117853963626494</v>
       </c>
     </row>
     <row r="72">
@@ -5929,7 +5929,7 @@
         <v>0.4110054557795083</v>
       </c>
       <c r="N72">
-        <v>13</v>
+        <v>13.09259259259259</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
@@ -5964,10 +5964,10 @@
         <v>0.6941109648268283</v>
       </c>
       <c r="Y72">
-        <v>0.5021810721168496</v>
+        <v>0.2926364621243586</v>
       </c>
       <c r="Z72">
-        <v>0.5319670162558882</v>
+        <v>0.5129175062565707</v>
       </c>
     </row>
     <row r="73">
@@ -5989,7 +5989,7 @@
         <v>0.2878122798694097</v>
       </c>
       <c r="N73">
-        <v>0.8571428571428571</v>
+        <v>0.8</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
@@ -6052,7 +6052,7 @@
         <v>0.1042931872280127</v>
       </c>
       <c r="N74">
-        <v>2.95</v>
+        <v>2.851851851851852</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
@@ -6087,10 +6087,10 @@
         <v>0.5053769041564342</v>
       </c>
       <c r="Y74">
-        <v>0.5352477992027502</v>
+        <v>0.2500738063642959</v>
       </c>
       <c r="Z74">
-        <v>0.4142746773680264</v>
+        <v>0.3883497689281669</v>
       </c>
     </row>
     <row r="75">
@@ -6163,7 +6163,7 @@
         <v>0.3034399977399024</v>
       </c>
       <c r="N76">
-        <v>7.689655172413793</v>
+        <v>7.69811320754717</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
@@ -6198,10 +6198,10 @@
         <v>0.3830767989130323</v>
       </c>
       <c r="Y76">
-        <v>0.583878886681464</v>
+        <v>0.2433711358906481</v>
       </c>
       <c r="Z76">
-        <v>0.4582021921926148</v>
+        <v>0.4272469421207225</v>
       </c>
     </row>
     <row r="77">
@@ -6247,7 +6247,7 @@
         <v>0.2547956872876816</v>
       </c>
       <c r="N77">
-        <v>2.694915254237288</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
@@ -6282,10 +6282,10 @@
         <v>0.1210445942521303</v>
       </c>
       <c r="Y77">
-        <v>0.5620731682909529</v>
+        <v>0.1483421034153823</v>
       </c>
       <c r="Z77">
-        <v>0.3590824646713671</v>
+        <v>0.3214705496826789</v>
       </c>
     </row>
     <row r="78">
@@ -6331,7 +6331,7 @@
         <v>0.1380971298791223</v>
       </c>
       <c r="N78">
-        <v>6.677966101694915</v>
+        <v>6.685185185185185</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
@@ -6366,10 +6366,10 @@
         <v>0.4048218374954839</v>
       </c>
       <c r="Y78">
-        <v>0.5000679002635895</v>
+        <v>0.2312243203600459</v>
       </c>
       <c r="Z78">
-        <v>0.3908224440730588</v>
+        <v>0.366382118627282</v>
       </c>
     </row>
     <row r="79">
@@ -6450,10 +6450,10 @@
         <v>0.05017995772283684</v>
       </c>
       <c r="Y79">
-        <v>0.6452137412134239</v>
+        <v>0</v>
       </c>
       <c r="Z79">
-        <v>0.382969484015837</v>
+        <v>0.3243136893600712</v>
       </c>
     </row>
     <row r="80">
@@ -6499,7 +6499,7 @@
         <v>0.2394809925082852</v>
       </c>
       <c r="N80">
-        <v>6.610169491525424</v>
+        <v>6.592592592592593</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
@@ -6534,10 +6534,10 @@
         <v>0.4835470190802443</v>
       </c>
       <c r="Y80">
-        <v>0.6808911868735297</v>
+        <v>0.2645072720608249</v>
       </c>
       <c r="Z80">
-        <v>0.5669900043662056</v>
+        <v>0.5291369212014143</v>
       </c>
     </row>
     <row r="81">
@@ -6583,7 +6583,7 @@
         <v>0.1828937706522884</v>
       </c>
       <c r="N81">
-        <v>3.779661016949153</v>
+        <v>3.759259259259259</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
@@ -6618,10 +6618,10 @@
         <v>0.2792188433975049</v>
       </c>
       <c r="Y81">
-        <v>0.5868142752565406</v>
+        <v>0.1815784376029904</v>
       </c>
       <c r="Z81">
-        <v>0.4329374677967361</v>
+        <v>0.3960978461918679</v>
       </c>
     </row>
     <row r="82">
@@ -6667,7 +6667,7 @@
         <v>0.08606865408804465</v>
       </c>
       <c r="N82">
-        <v>0.9833333333333333</v>
+        <v>0.9814814814814815</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
@@ -6696,10 +6696,10 @@
         <v>0</v>
       </c>
       <c r="Y82">
-        <v>0</v>
+        <v>0.131644287510149</v>
       </c>
       <c r="Z82">
-        <v>0.2502717778218284</v>
+        <v>0.2634362065728433</v>
       </c>
     </row>
     <row r="83">
@@ -6745,7 +6745,7 @@
         <v>0.06796867325860938</v>
       </c>
       <c r="N83">
-        <v>0.9833333333333333</v>
+        <v>0.9814814814814815</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
@@ -6780,10 +6780,10 @@
         <v>0.03528014153309827</v>
       </c>
       <c r="Y83">
-        <v>0.6119871397440688</v>
+        <v>0.04338224772508872</v>
       </c>
       <c r="Z83">
-        <v>0.3134162581054433</v>
+        <v>0.261724904285536</v>
       </c>
     </row>
     <row r="84">
@@ -6864,10 +6864,10 @@
         <v>0.1057631609809458</v>
       </c>
       <c r="Y84">
-        <v>0.5759859014309127</v>
+        <v>0.1833784408786485</v>
       </c>
       <c r="Z84">
-        <v>0.3666760214330582</v>
+        <v>0.3309844341101251</v>
       </c>
     </row>
     <row r="85">
@@ -6913,7 +6913,7 @@
         <v>0.1782312596633691</v>
       </c>
       <c r="N85">
-        <v>1.9</v>
+        <v>1.907407407407407</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
@@ -6948,10 +6948,10 @@
         <v>0.03251143917425656</v>
       </c>
       <c r="Y85">
-        <v>0.6060350084993592</v>
+        <v>0.1632758599237923</v>
       </c>
       <c r="Z85">
-        <v>0.3190668613733141</v>
+        <v>0.2788160296846263</v>
       </c>
     </row>
     <row r="86">
@@ -6997,7 +6997,7 @@
         <v>0.2330524465014525</v>
       </c>
       <c r="N86">
-        <v>6.35593220338983</v>
+        <v>6.537037037037037</v>
       </c>
       <c r="O86" t="inlineStr">
         <is>
@@ -7032,10 +7032,10 @@
         <v>0.3807606773129513</v>
       </c>
       <c r="Y86">
-        <v>0.5628408309384075</v>
+        <v>0.1565376364396137</v>
       </c>
       <c r="Z86">
-        <v>0.4189545383493686</v>
+        <v>0.3820178843040237</v>
       </c>
     </row>
     <row r="87">
@@ -7116,10 +7116,10 @@
         <v>0.1525607253602217</v>
       </c>
       <c r="Y87">
-        <v>0.6431040127003597</v>
+        <v>0.1064792360950618</v>
       </c>
       <c r="Z87">
-        <v>0.4027096599256128</v>
+        <v>0.3539255893251311</v>
       </c>
     </row>
     <row r="88">
@@ -7165,7 +7165,7 @@
         <v>0.2829268001718372</v>
       </c>
       <c r="N88">
-        <v>10.48333333333333</v>
+        <v>10.33333333333333</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
@@ -7200,10 +7200,10 @@
         <v>0.1928977467183089</v>
       </c>
       <c r="Y88">
-        <v>0.797701059445899</v>
+        <v>0.1891495494652774</v>
       </c>
       <c r="Z88">
-        <v>0.5728702369961458</v>
+        <v>0.517547372452453</v>
       </c>
     </row>
     <row r="89">
@@ -7276,7 +7276,7 @@
         <v>0.1143129929023565</v>
       </c>
       <c r="N90">
-        <v>9.85</v>
+        <v>9.62962962962963</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
@@ -7311,10 +7311,10 @@
         <v>0.672291736389361</v>
       </c>
       <c r="Y90">
-        <v>0.5671346776639313</v>
+        <v>0.1312630330506945</v>
       </c>
       <c r="Z90">
-        <v>0.5689016469195064</v>
+        <v>0.5292769519546667</v>
       </c>
     </row>
     <row r="91">
@@ -7360,7 +7360,7 @@
         <v>0.05383970389127882</v>
       </c>
       <c r="N91">
-        <v>1.9</v>
+        <v>1.888888888888889</v>
       </c>
       <c r="O91" t="inlineStr">
         <is>
@@ -7395,10 +7395,10 @@
         <v>0.6078099058219762</v>
       </c>
       <c r="Y91">
-        <v>0.5816529148067182</v>
+        <v>0.09273992238029152</v>
       </c>
       <c r="Z91">
-        <v>0.4153479598412998</v>
+        <v>0.3709013241661701</v>
       </c>
     </row>
     <row r="92">
@@ -7444,7 +7444,7 @@
         <v>0.191580130028778</v>
       </c>
       <c r="N92">
-        <v>2.833333333333333</v>
+        <v>2.777777777777778</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
@@ -7479,10 +7479,10 @@
         <v>1</v>
       </c>
       <c r="Y92">
-        <v>0.6414502173738073</v>
+        <v>0.1659300950003614</v>
       </c>
       <c r="Z92">
-        <v>0.5667406131204928</v>
+        <v>0.5235115110865433</v>
       </c>
     </row>
   </sheetData>
